--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BCGcalc/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{AF49C751-8791-4BCD-BD60-C78962984F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FE13902-9C77-4613-8EA7-FDB502FFD733}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614C22D4-6558-4998-802C-2764CB46DF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="180">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -701,12 +701,21 @@
   <si>
     <t>non-parasitic lampreys, present</t>
   </si>
+  <si>
+    <t>Add "BCG_MariNW_v2_Bugs500ct" and "BCG_ORWA_v1_Bugs500ct"</t>
+  </si>
+  <si>
+    <t>BCG_MariNW_v2_Bugs500ct</t>
+  </si>
+  <si>
+    <t>BCG_ORWA_v1_Bugs500ct</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -803,6 +812,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -885,7 +901,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
@@ -931,6 +947,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
@@ -939,7 +957,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -947,6 +965,50 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1010,17 +1072,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A15:C18" totalsRowShown="0">
   <autoFilter ref="A15:C18" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Worksheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descriptions"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="6">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="11">
       <calculatedColumnFormula>HYPERLINK(FileName&amp;A16&amp;"!A1",A16)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1318,7 +1376,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1344,7 +1402,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
-        <v>45393</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1353,7 +1411,7 @@
       </c>
       <c r="B7" s="6" t="str">
         <f ca="1">LEFT(CELL("filename",B7),FIND("]",CELL("filename",B7)))</f>
-        <v>https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BCGcalc/inst/extdata/[MetricFlags.xlsx]</v>
+        <v>C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\[MetricFlags.xlsx]</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1576,6 +1634,14 @@
       </c>
       <c r="B42" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="15">
+        <v>45695</v>
+      </c>
+      <c r="B43" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1690,7 +1756,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J161"/>
+  <dimension ref="A1:J333"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -6786,34 +6852,5601 @@
         <v>162</v>
       </c>
     </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B162" t="s">
+        <v>54</v>
+      </c>
+      <c r="C162" t="s">
+        <v>150</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E162">
+        <v>5</v>
+      </c>
+      <c r="F162" t="s">
+        <v>55</v>
+      </c>
+      <c r="G162" t="b">
+        <v>0</v>
+      </c>
+      <c r="I162" s="19" t="str">
+        <f t="shared" ref="I162:I225" si="9">B162</f>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J162" s="19" t="str">
+        <f t="shared" ref="J162:J225" si="10">B162</f>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B163" t="s">
+        <v>54</v>
+      </c>
+      <c r="C163" t="s">
+        <v>150</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E163">
+        <v>1.2</v>
+      </c>
+      <c r="F163" t="s">
+        <v>116</v>
+      </c>
+      <c r="G163" t="b">
+        <v>0</v>
+      </c>
+      <c r="H163" t="s">
+        <v>115</v>
+      </c>
+      <c r="I163" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J163" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B164" t="s">
+        <v>54</v>
+      </c>
+      <c r="C164" t="s">
+        <v>138</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164">
+        <v>5</v>
+      </c>
+      <c r="F164" t="s">
+        <v>139</v>
+      </c>
+      <c r="G164" t="b">
+        <v>0</v>
+      </c>
+      <c r="I164" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J164" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B165" t="s">
+        <v>54</v>
+      </c>
+      <c r="C165" t="s">
+        <v>138</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E165">
+        <v>260</v>
+      </c>
+      <c r="F165" t="s">
+        <v>140</v>
+      </c>
+      <c r="G165" t="b">
+        <v>0</v>
+      </c>
+      <c r="I165" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J165" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B166" t="s">
+        <v>54</v>
+      </c>
+      <c r="C166" t="s">
+        <v>56</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E166">
+        <v>6</v>
+      </c>
+      <c r="F166" t="s">
+        <v>57</v>
+      </c>
+      <c r="G166" t="b">
+        <v>0</v>
+      </c>
+      <c r="I166" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J166" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B167" t="s">
+        <v>54</v>
+      </c>
+      <c r="C167" t="s">
+        <v>56</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E167">
+        <v>10</v>
+      </c>
+      <c r="F167" t="s">
+        <v>58</v>
+      </c>
+      <c r="G167" t="b">
+        <v>0</v>
+      </c>
+      <c r="I167" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J167" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B168" t="s">
+        <v>54</v>
+      </c>
+      <c r="C168" t="s">
+        <v>59</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E168">
+        <v>8</v>
+      </c>
+      <c r="F168" t="s">
+        <v>60</v>
+      </c>
+      <c r="G168" t="b">
+        <v>0</v>
+      </c>
+      <c r="I168" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J168" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B169" t="s">
+        <v>54</v>
+      </c>
+      <c r="C169" t="s">
+        <v>14</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E169">
+        <v>600</v>
+      </c>
+      <c r="F169" t="s">
+        <v>61</v>
+      </c>
+      <c r="G169" t="b">
+        <v>1</v>
+      </c>
+      <c r="I169" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J169" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B170" t="s">
+        <v>54</v>
+      </c>
+      <c r="C170" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E170">
+        <v>450</v>
+      </c>
+      <c r="F170" t="s">
+        <v>38</v>
+      </c>
+      <c r="G170" t="b">
+        <v>1</v>
+      </c>
+      <c r="I170" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J170" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" t="s">
+        <v>54</v>
+      </c>
+      <c r="C171" t="s">
+        <v>62</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E171">
+        <v>75</v>
+      </c>
+      <c r="F171" t="s">
+        <v>63</v>
+      </c>
+      <c r="G171" t="b">
+        <v>0</v>
+      </c>
+      <c r="I171" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J171" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B172" t="s">
+        <v>54</v>
+      </c>
+      <c r="C172" t="s">
+        <v>48</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E172">
+        <v>1000</v>
+      </c>
+      <c r="F172" t="s">
+        <v>64</v>
+      </c>
+      <c r="G172" t="b">
+        <v>0</v>
+      </c>
+      <c r="I172" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J172" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B173" t="s">
+        <v>54</v>
+      </c>
+      <c r="C173" t="s">
+        <v>51</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E173">
+        <v>50</v>
+      </c>
+      <c r="F173" t="s">
+        <v>65</v>
+      </c>
+      <c r="G173" t="b">
+        <v>1</v>
+      </c>
+      <c r="I173" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J173" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B174" t="s">
+        <v>54</v>
+      </c>
+      <c r="C174" t="s">
+        <v>66</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E174" s="17">
+        <v>35</v>
+      </c>
+      <c r="F174" t="s">
+        <v>67</v>
+      </c>
+      <c r="G174" t="b">
+        <v>1</v>
+      </c>
+      <c r="H174" t="s">
+        <v>110</v>
+      </c>
+      <c r="I174" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J174" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B175" t="s">
+        <v>54</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E175">
+        <v>10</v>
+      </c>
+      <c r="F175" t="s">
+        <v>69</v>
+      </c>
+      <c r="G175" t="b">
+        <v>1</v>
+      </c>
+      <c r="I175" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J175" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B176" t="s">
+        <v>54</v>
+      </c>
+      <c r="C176" t="s">
+        <v>70</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E176">
+        <v>25</v>
+      </c>
+      <c r="F176" t="s">
+        <v>71</v>
+      </c>
+      <c r="G176" t="b">
+        <v>1</v>
+      </c>
+      <c r="I176" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J176" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B177" t="s">
+        <v>54</v>
+      </c>
+      <c r="C177" t="s">
+        <v>72</v>
+      </c>
+      <c r="D177" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+      <c r="F177" t="s">
+        <v>73</v>
+      </c>
+      <c r="G177" t="b">
+        <v>1</v>
+      </c>
+      <c r="I177" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J177" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" t="s">
+        <v>54</v>
+      </c>
+      <c r="C178" t="s">
+        <v>74</v>
+      </c>
+      <c r="D178" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="F178" t="s">
+        <v>75</v>
+      </c>
+      <c r="G178" t="b">
+        <v>1</v>
+      </c>
+      <c r="I178" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J178" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>54</v>
+      </c>
+      <c r="C179" t="s">
+        <v>76</v>
+      </c>
+      <c r="D179" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="F179" t="s">
+        <v>77</v>
+      </c>
+      <c r="G179" t="b">
+        <v>1</v>
+      </c>
+      <c r="I179" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J179" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B180" t="s">
+        <v>54</v>
+      </c>
+      <c r="C180" t="s">
+        <v>78</v>
+      </c>
+      <c r="D180" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="F180" t="s">
+        <v>79</v>
+      </c>
+      <c r="G180" t="b">
+        <v>1</v>
+      </c>
+      <c r="I180" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J180" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B181" t="s">
+        <v>54</v>
+      </c>
+      <c r="C181" t="s">
+        <v>80</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E181">
+        <v>50</v>
+      </c>
+      <c r="F181" t="s">
+        <v>81</v>
+      </c>
+      <c r="G181" t="b">
+        <v>1</v>
+      </c>
+      <c r="I181" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J181" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B182" t="s">
+        <v>54</v>
+      </c>
+      <c r="C182" t="s">
+        <v>91</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E182" s="17">
+        <v>50</v>
+      </c>
+      <c r="F182" t="s">
+        <v>82</v>
+      </c>
+      <c r="G182" t="b">
+        <v>1</v>
+      </c>
+      <c r="H182" t="s">
+        <v>110</v>
+      </c>
+      <c r="I182" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J182" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B183" t="s">
+        <v>54</v>
+      </c>
+      <c r="C183" t="s">
+        <v>83</v>
+      </c>
+      <c r="D183" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E183">
+        <v>30</v>
+      </c>
+      <c r="F183" t="s">
+        <v>84</v>
+      </c>
+      <c r="G183" t="b">
+        <v>1</v>
+      </c>
+      <c r="I183" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J183" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B184" t="s">
+        <v>54</v>
+      </c>
+      <c r="C184" t="s">
+        <v>85</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E184">
+        <v>10</v>
+      </c>
+      <c r="F184" t="s">
+        <v>86</v>
+      </c>
+      <c r="G184" t="b">
+        <v>1</v>
+      </c>
+      <c r="I184" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J184" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B185" t="s">
+        <v>54</v>
+      </c>
+      <c r="C185" t="s">
+        <v>87</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E185">
+        <v>10</v>
+      </c>
+      <c r="F185" t="s">
+        <v>88</v>
+      </c>
+      <c r="G185" t="b">
+        <v>1</v>
+      </c>
+      <c r="I185" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J185" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B186" t="s">
+        <v>54</v>
+      </c>
+      <c r="C186" t="s">
+        <v>89</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+      <c r="F186" t="s">
+        <v>49</v>
+      </c>
+      <c r="G186" t="b">
+        <v>1</v>
+      </c>
+      <c r="I186" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J186" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B187" t="s">
+        <v>54</v>
+      </c>
+      <c r="C187" t="s">
+        <v>101</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
+      <c r="F187" t="s">
+        <v>102</v>
+      </c>
+      <c r="G187" t="b">
+        <v>1</v>
+      </c>
+      <c r="H187" t="s">
+        <v>109</v>
+      </c>
+      <c r="I187" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J187" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B188" t="s">
+        <v>54</v>
+      </c>
+      <c r="C188" t="s">
+        <v>104</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E188">
+        <v>1000</v>
+      </c>
+      <c r="F188" t="s">
+        <v>105</v>
+      </c>
+      <c r="G188" t="b">
+        <v>0</v>
+      </c>
+      <c r="H188" t="s">
+        <v>117</v>
+      </c>
+      <c r="I188" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J188" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B189" t="s">
+        <v>54</v>
+      </c>
+      <c r="C189" t="s">
+        <v>106</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E189" s="8">
+        <v>10</v>
+      </c>
+      <c r="F189" t="s">
+        <v>107</v>
+      </c>
+      <c r="G189" t="b">
+        <v>1</v>
+      </c>
+      <c r="H189" t="s">
+        <v>117</v>
+      </c>
+      <c r="I189" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J189" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B190" t="s">
+        <v>54</v>
+      </c>
+      <c r="C190" t="s">
+        <v>113</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E190" s="8">
+        <v>10</v>
+      </c>
+      <c r="F190" t="s">
+        <v>108</v>
+      </c>
+      <c r="G190" t="b">
+        <v>1</v>
+      </c>
+      <c r="H190" t="s">
+        <v>117</v>
+      </c>
+      <c r="I190" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J190" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B191" t="s">
+        <v>103</v>
+      </c>
+      <c r="C191" t="s">
+        <v>150</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" s="21">
+        <v>8</v>
+      </c>
+      <c r="F191" t="s">
+        <v>111</v>
+      </c>
+      <c r="G191" t="b">
+        <v>0</v>
+      </c>
+      <c r="I191" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J191" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B192" t="s">
+        <v>103</v>
+      </c>
+      <c r="C192" t="s">
+        <v>150</v>
+      </c>
+      <c r="D192" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E192">
+        <v>3</v>
+      </c>
+      <c r="F192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G192" t="b">
+        <v>0</v>
+      </c>
+      <c r="I192" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J192" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B193" t="s">
+        <v>103</v>
+      </c>
+      <c r="C193" t="s">
+        <v>138</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E193">
+        <v>5</v>
+      </c>
+      <c r="F193" t="s">
+        <v>139</v>
+      </c>
+      <c r="G193" t="b">
+        <v>0</v>
+      </c>
+      <c r="I193" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J193" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B194" t="s">
+        <v>103</v>
+      </c>
+      <c r="C194" t="s">
+        <v>138</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E194">
+        <v>260</v>
+      </c>
+      <c r="F194" t="s">
+        <v>140</v>
+      </c>
+      <c r="G194" t="b">
+        <v>0</v>
+      </c>
+      <c r="I194" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J194" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B195" t="s">
+        <v>103</v>
+      </c>
+      <c r="C195" t="s">
+        <v>104</v>
+      </c>
+      <c r="D195" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E195">
+        <v>1000</v>
+      </c>
+      <c r="F195" t="s">
+        <v>105</v>
+      </c>
+      <c r="G195" t="b">
+        <v>0</v>
+      </c>
+      <c r="I195" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J195" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B196" t="s">
+        <v>103</v>
+      </c>
+      <c r="C196" t="s">
+        <v>56</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E196">
+        <v>6</v>
+      </c>
+      <c r="F196" t="s">
+        <v>57</v>
+      </c>
+      <c r="G196" t="b">
+        <v>0</v>
+      </c>
+      <c r="I196" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J196" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B197" t="s">
+        <v>103</v>
+      </c>
+      <c r="C197" t="s">
+        <v>56</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E197">
+        <v>10</v>
+      </c>
+      <c r="F197" t="s">
+        <v>58</v>
+      </c>
+      <c r="G197" t="b">
+        <v>0</v>
+      </c>
+      <c r="I197" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J197" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B198" t="s">
+        <v>103</v>
+      </c>
+      <c r="C198" t="s">
+        <v>59</v>
+      </c>
+      <c r="D198" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E198">
+        <v>8</v>
+      </c>
+      <c r="F198" t="s">
+        <v>60</v>
+      </c>
+      <c r="G198" t="b">
+        <v>0</v>
+      </c>
+      <c r="I198" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J198" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B199" t="s">
+        <v>103</v>
+      </c>
+      <c r="C199" t="s">
+        <v>14</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E199">
+        <v>600</v>
+      </c>
+      <c r="F199" t="s">
+        <v>61</v>
+      </c>
+      <c r="G199" t="b">
+        <v>1</v>
+      </c>
+      <c r="I199" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J199" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B200" t="s">
+        <v>103</v>
+      </c>
+      <c r="C200" t="s">
+        <v>14</v>
+      </c>
+      <c r="D200" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E200">
+        <v>450</v>
+      </c>
+      <c r="F200" t="s">
+        <v>38</v>
+      </c>
+      <c r="G200" t="b">
+        <v>1</v>
+      </c>
+      <c r="I200" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J200" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B201" t="s">
+        <v>103</v>
+      </c>
+      <c r="C201" t="s">
+        <v>62</v>
+      </c>
+      <c r="D201" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E201">
+        <v>75</v>
+      </c>
+      <c r="F201" t="s">
+        <v>63</v>
+      </c>
+      <c r="G201" t="b">
+        <v>0</v>
+      </c>
+      <c r="I201" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J201" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B202" t="s">
+        <v>103</v>
+      </c>
+      <c r="C202" t="s">
+        <v>48</v>
+      </c>
+      <c r="D202" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E202">
+        <v>1000</v>
+      </c>
+      <c r="F202" t="s">
+        <v>64</v>
+      </c>
+      <c r="G202" t="b">
+        <v>0</v>
+      </c>
+      <c r="I202" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J202" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B203" t="s">
+        <v>103</v>
+      </c>
+      <c r="C203" t="s">
+        <v>51</v>
+      </c>
+      <c r="D203" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E203">
+        <v>50</v>
+      </c>
+      <c r="F203" t="s">
+        <v>65</v>
+      </c>
+      <c r="G203" t="b">
+        <v>1</v>
+      </c>
+      <c r="I203" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J203" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B204" t="s">
+        <v>103</v>
+      </c>
+      <c r="C204" t="s">
+        <v>66</v>
+      </c>
+      <c r="D204" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E204">
+        <v>35</v>
+      </c>
+      <c r="F204" t="s">
+        <v>67</v>
+      </c>
+      <c r="G204" t="b">
+        <v>1</v>
+      </c>
+      <c r="I204" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J204" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B205" t="s">
+        <v>103</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E205">
+        <v>10</v>
+      </c>
+      <c r="F205" t="s">
+        <v>69</v>
+      </c>
+      <c r="G205" t="b">
+        <v>1</v>
+      </c>
+      <c r="I205" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J205" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B206" t="s">
+        <v>103</v>
+      </c>
+      <c r="C206" t="s">
+        <v>70</v>
+      </c>
+      <c r="D206" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E206">
+        <v>25</v>
+      </c>
+      <c r="F206" t="s">
+        <v>71</v>
+      </c>
+      <c r="G206" t="b">
+        <v>1</v>
+      </c>
+      <c r="I206" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J206" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B207" t="s">
+        <v>103</v>
+      </c>
+      <c r="C207" t="s">
+        <v>72</v>
+      </c>
+      <c r="D207" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207" t="s">
+        <v>73</v>
+      </c>
+      <c r="G207" t="b">
+        <v>1</v>
+      </c>
+      <c r="I207" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J207" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B208" t="s">
+        <v>103</v>
+      </c>
+      <c r="C208" t="s">
+        <v>74</v>
+      </c>
+      <c r="D208" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208" t="s">
+        <v>75</v>
+      </c>
+      <c r="G208" t="b">
+        <v>1</v>
+      </c>
+      <c r="I208" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J208" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B209" t="s">
+        <v>103</v>
+      </c>
+      <c r="C209" t="s">
+        <v>76</v>
+      </c>
+      <c r="D209" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209" t="s">
+        <v>77</v>
+      </c>
+      <c r="G209" t="b">
+        <v>1</v>
+      </c>
+      <c r="I209" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J209" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B210" t="s">
+        <v>103</v>
+      </c>
+      <c r="C210" t="s">
+        <v>78</v>
+      </c>
+      <c r="D210" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210" t="s">
+        <v>79</v>
+      </c>
+      <c r="G210" t="b">
+        <v>1</v>
+      </c>
+      <c r="I210" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J210" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B211" t="s">
+        <v>103</v>
+      </c>
+      <c r="C211" t="s">
+        <v>80</v>
+      </c>
+      <c r="D211" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211">
+        <v>50</v>
+      </c>
+      <c r="F211" t="s">
+        <v>81</v>
+      </c>
+      <c r="G211" t="b">
+        <v>1</v>
+      </c>
+      <c r="I211" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J211" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B212" t="s">
+        <v>103</v>
+      </c>
+      <c r="C212" t="s">
+        <v>91</v>
+      </c>
+      <c r="D212" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E212">
+        <v>50</v>
+      </c>
+      <c r="F212" t="s">
+        <v>82</v>
+      </c>
+      <c r="G212" t="b">
+        <v>1</v>
+      </c>
+      <c r="I212" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J212" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B213" t="s">
+        <v>103</v>
+      </c>
+      <c r="C213" t="s">
+        <v>83</v>
+      </c>
+      <c r="D213" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E213">
+        <v>30</v>
+      </c>
+      <c r="F213" t="s">
+        <v>84</v>
+      </c>
+      <c r="G213" t="b">
+        <v>1</v>
+      </c>
+      <c r="I213" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J213" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B214" t="s">
+        <v>103</v>
+      </c>
+      <c r="C214" t="s">
+        <v>85</v>
+      </c>
+      <c r="D214" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E214">
+        <v>10</v>
+      </c>
+      <c r="F214" t="s">
+        <v>86</v>
+      </c>
+      <c r="G214" t="b">
+        <v>1</v>
+      </c>
+      <c r="I214" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J214" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B215" t="s">
+        <v>103</v>
+      </c>
+      <c r="C215" t="s">
+        <v>87</v>
+      </c>
+      <c r="D215" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E215">
+        <v>10</v>
+      </c>
+      <c r="F215" t="s">
+        <v>88</v>
+      </c>
+      <c r="G215" t="b">
+        <v>1</v>
+      </c>
+      <c r="I215" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J215" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B216" t="s">
+        <v>103</v>
+      </c>
+      <c r="C216" t="s">
+        <v>89</v>
+      </c>
+      <c r="D216" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="F216" t="s">
+        <v>49</v>
+      </c>
+      <c r="G216" t="b">
+        <v>1</v>
+      </c>
+      <c r="I216" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J216" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B217" t="s">
+        <v>103</v>
+      </c>
+      <c r="C217" t="s">
+        <v>101</v>
+      </c>
+      <c r="D217" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217" t="s">
+        <v>102</v>
+      </c>
+      <c r="G217" t="b">
+        <v>1</v>
+      </c>
+      <c r="I217" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J217" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B218" t="s">
+        <v>103</v>
+      </c>
+      <c r="C218" t="s">
+        <v>106</v>
+      </c>
+      <c r="D218" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E218">
+        <v>10</v>
+      </c>
+      <c r="F218" t="s">
+        <v>107</v>
+      </c>
+      <c r="G218" t="b">
+        <v>1</v>
+      </c>
+      <c r="I218" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J218" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B219" t="s">
+        <v>103</v>
+      </c>
+      <c r="C219" t="s">
+        <v>113</v>
+      </c>
+      <c r="D219" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E219">
+        <v>10</v>
+      </c>
+      <c r="F219" t="s">
+        <v>108</v>
+      </c>
+      <c r="G219" t="b">
+        <v>1</v>
+      </c>
+      <c r="I219" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J219" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B220" t="s">
+        <v>119</v>
+      </c>
+      <c r="C220" t="s">
+        <v>150</v>
+      </c>
+      <c r="D220" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E220">
+        <v>0.7</v>
+      </c>
+      <c r="F220" t="s">
+        <v>112</v>
+      </c>
+      <c r="G220" t="b">
+        <v>0</v>
+      </c>
+      <c r="H220" t="s">
+        <v>120</v>
+      </c>
+      <c r="I220" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J220" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B221" t="s">
+        <v>119</v>
+      </c>
+      <c r="C221" t="s">
+        <v>138</v>
+      </c>
+      <c r="D221" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E221">
+        <v>5</v>
+      </c>
+      <c r="F221" t="s">
+        <v>139</v>
+      </c>
+      <c r="G221" t="b">
+        <v>0</v>
+      </c>
+      <c r="H221" t="s">
+        <v>118</v>
+      </c>
+      <c r="I221" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J221" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B222" t="s">
+        <v>119</v>
+      </c>
+      <c r="C222" t="s">
+        <v>138</v>
+      </c>
+      <c r="D222" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E222">
+        <v>260</v>
+      </c>
+      <c r="F222" t="s">
+        <v>140</v>
+      </c>
+      <c r="G222" t="b">
+        <v>0</v>
+      </c>
+      <c r="H222" t="s">
+        <v>118</v>
+      </c>
+      <c r="I222" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J222" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B223" t="s">
+        <v>119</v>
+      </c>
+      <c r="C223" t="s">
+        <v>104</v>
+      </c>
+      <c r="D223" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E223">
+        <v>1000</v>
+      </c>
+      <c r="F223" t="s">
+        <v>105</v>
+      </c>
+      <c r="G223" t="b">
+        <v>0</v>
+      </c>
+      <c r="H223" t="s">
+        <v>118</v>
+      </c>
+      <c r="I223" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J223" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B224" t="s">
+        <v>119</v>
+      </c>
+      <c r="C224" t="s">
+        <v>56</v>
+      </c>
+      <c r="D224" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E224">
+        <v>6</v>
+      </c>
+      <c r="F224" t="s">
+        <v>57</v>
+      </c>
+      <c r="G224" t="b">
+        <v>0</v>
+      </c>
+      <c r="H224" t="s">
+        <v>118</v>
+      </c>
+      <c r="I224" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J224" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A225" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B225" t="s">
+        <v>119</v>
+      </c>
+      <c r="C225" t="s">
+        <v>56</v>
+      </c>
+      <c r="D225" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E225">
+        <v>10</v>
+      </c>
+      <c r="F225" t="s">
+        <v>58</v>
+      </c>
+      <c r="G225" t="b">
+        <v>0</v>
+      </c>
+      <c r="H225" t="s">
+        <v>118</v>
+      </c>
+      <c r="I225" s="19" t="str">
+        <f t="shared" si="9"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J225" s="19" t="str">
+        <f t="shared" si="10"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A226" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B226" t="s">
+        <v>119</v>
+      </c>
+      <c r="C226" t="s">
+        <v>59</v>
+      </c>
+      <c r="D226" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E226">
+        <v>8</v>
+      </c>
+      <c r="F226" t="s">
+        <v>60</v>
+      </c>
+      <c r="G226" t="b">
+        <v>0</v>
+      </c>
+      <c r="H226" t="s">
+        <v>118</v>
+      </c>
+      <c r="I226" s="19" t="str">
+        <f t="shared" ref="I226:I289" si="11">B226</f>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J226" s="19" t="str">
+        <f t="shared" ref="J226:J289" si="12">B226</f>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A227" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B227" t="s">
+        <v>119</v>
+      </c>
+      <c r="C227" t="s">
+        <v>14</v>
+      </c>
+      <c r="D227" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E227">
+        <v>600</v>
+      </c>
+      <c r="F227" t="s">
+        <v>61</v>
+      </c>
+      <c r="G227" t="b">
+        <v>1</v>
+      </c>
+      <c r="H227" t="s">
+        <v>118</v>
+      </c>
+      <c r="I227" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J227" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A228" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B228" t="s">
+        <v>119</v>
+      </c>
+      <c r="C228" t="s">
+        <v>14</v>
+      </c>
+      <c r="D228" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E228">
+        <v>450</v>
+      </c>
+      <c r="F228" t="s">
+        <v>38</v>
+      </c>
+      <c r="G228" t="b">
+        <v>1</v>
+      </c>
+      <c r="H228" t="s">
+        <v>118</v>
+      </c>
+      <c r="I228" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J228" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A229" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B229" t="s">
+        <v>119</v>
+      </c>
+      <c r="C229" t="s">
+        <v>62</v>
+      </c>
+      <c r="D229" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E229">
+        <v>75</v>
+      </c>
+      <c r="F229" t="s">
+        <v>63</v>
+      </c>
+      <c r="G229" t="b">
+        <v>0</v>
+      </c>
+      <c r="H229" t="s">
+        <v>118</v>
+      </c>
+      <c r="I229" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J229" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A230" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B230" t="s">
+        <v>119</v>
+      </c>
+      <c r="C230" t="s">
+        <v>48</v>
+      </c>
+      <c r="D230" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E230">
+        <v>1000</v>
+      </c>
+      <c r="F230" t="s">
+        <v>64</v>
+      </c>
+      <c r="G230" t="b">
+        <v>0</v>
+      </c>
+      <c r="H230" t="s">
+        <v>118</v>
+      </c>
+      <c r="I230" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J230" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A231" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B231" t="s">
+        <v>119</v>
+      </c>
+      <c r="C231" t="s">
+        <v>51</v>
+      </c>
+      <c r="D231" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E231">
+        <v>50</v>
+      </c>
+      <c r="F231" t="s">
+        <v>65</v>
+      </c>
+      <c r="G231" t="b">
+        <v>1</v>
+      </c>
+      <c r="H231" t="s">
+        <v>118</v>
+      </c>
+      <c r="I231" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J231" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A232" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B232" t="s">
+        <v>119</v>
+      </c>
+      <c r="C232" t="s">
+        <v>66</v>
+      </c>
+      <c r="D232" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E232">
+        <v>35</v>
+      </c>
+      <c r="F232" t="s">
+        <v>67</v>
+      </c>
+      <c r="G232" t="b">
+        <v>1</v>
+      </c>
+      <c r="H232" t="s">
+        <v>118</v>
+      </c>
+      <c r="I232" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J232" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A233" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B233" t="s">
+        <v>119</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E233">
+        <v>10</v>
+      </c>
+      <c r="F233" t="s">
+        <v>69</v>
+      </c>
+      <c r="G233" t="b">
+        <v>1</v>
+      </c>
+      <c r="H233" t="s">
+        <v>118</v>
+      </c>
+      <c r="I233" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J233" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A234" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B234" t="s">
+        <v>119</v>
+      </c>
+      <c r="C234" t="s">
+        <v>70</v>
+      </c>
+      <c r="D234" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E234">
+        <v>25</v>
+      </c>
+      <c r="F234" t="s">
+        <v>71</v>
+      </c>
+      <c r="G234" t="b">
+        <v>1</v>
+      </c>
+      <c r="H234" t="s">
+        <v>118</v>
+      </c>
+      <c r="I234" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J234" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A235" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B235" t="s">
+        <v>119</v>
+      </c>
+      <c r="C235" t="s">
+        <v>72</v>
+      </c>
+      <c r="D235" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235" t="s">
+        <v>73</v>
+      </c>
+      <c r="G235" t="b">
+        <v>1</v>
+      </c>
+      <c r="H235" t="s">
+        <v>118</v>
+      </c>
+      <c r="I235" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J235" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A236" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B236" t="s">
+        <v>119</v>
+      </c>
+      <c r="C236" t="s">
+        <v>74</v>
+      </c>
+      <c r="D236" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+      <c r="F236" t="s">
+        <v>75</v>
+      </c>
+      <c r="G236" t="b">
+        <v>1</v>
+      </c>
+      <c r="H236" t="s">
+        <v>118</v>
+      </c>
+      <c r="I236" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J236" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A237" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B237" t="s">
+        <v>119</v>
+      </c>
+      <c r="C237" t="s">
+        <v>76</v>
+      </c>
+      <c r="D237" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+      <c r="F237" t="s">
+        <v>77</v>
+      </c>
+      <c r="G237" t="b">
+        <v>1</v>
+      </c>
+      <c r="H237" t="s">
+        <v>118</v>
+      </c>
+      <c r="I237" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J237" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A238" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B238" t="s">
+        <v>119</v>
+      </c>
+      <c r="C238" t="s">
+        <v>78</v>
+      </c>
+      <c r="D238" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
+      <c r="F238" t="s">
+        <v>79</v>
+      </c>
+      <c r="G238" t="b">
+        <v>1</v>
+      </c>
+      <c r="H238" t="s">
+        <v>118</v>
+      </c>
+      <c r="I238" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J238" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A239" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B239" t="s">
+        <v>119</v>
+      </c>
+      <c r="C239" t="s">
+        <v>80</v>
+      </c>
+      <c r="D239" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E239">
+        <v>50</v>
+      </c>
+      <c r="F239" t="s">
+        <v>81</v>
+      </c>
+      <c r="G239" t="b">
+        <v>1</v>
+      </c>
+      <c r="H239" t="s">
+        <v>118</v>
+      </c>
+      <c r="I239" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J239" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A240" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B240" t="s">
+        <v>119</v>
+      </c>
+      <c r="C240" t="s">
+        <v>91</v>
+      </c>
+      <c r="D240" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E240">
+        <v>50</v>
+      </c>
+      <c r="F240" t="s">
+        <v>82</v>
+      </c>
+      <c r="G240" t="b">
+        <v>1</v>
+      </c>
+      <c r="H240" t="s">
+        <v>118</v>
+      </c>
+      <c r="I240" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J240" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A241" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B241" t="s">
+        <v>119</v>
+      </c>
+      <c r="C241" t="s">
+        <v>83</v>
+      </c>
+      <c r="D241" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E241">
+        <v>30</v>
+      </c>
+      <c r="F241" t="s">
+        <v>84</v>
+      </c>
+      <c r="G241" t="b">
+        <v>1</v>
+      </c>
+      <c r="H241" t="s">
+        <v>118</v>
+      </c>
+      <c r="I241" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J241" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A242" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B242" t="s">
+        <v>119</v>
+      </c>
+      <c r="C242" t="s">
+        <v>85</v>
+      </c>
+      <c r="D242" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E242">
+        <v>10</v>
+      </c>
+      <c r="F242" t="s">
+        <v>86</v>
+      </c>
+      <c r="G242" t="b">
+        <v>1</v>
+      </c>
+      <c r="H242" t="s">
+        <v>118</v>
+      </c>
+      <c r="I242" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J242" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A243" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B243" t="s">
+        <v>119</v>
+      </c>
+      <c r="C243" t="s">
+        <v>87</v>
+      </c>
+      <c r="D243" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E243">
+        <v>10</v>
+      </c>
+      <c r="F243" t="s">
+        <v>88</v>
+      </c>
+      <c r="G243" t="b">
+        <v>1</v>
+      </c>
+      <c r="H243" t="s">
+        <v>118</v>
+      </c>
+      <c r="I243" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J243" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A244" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B244" t="s">
+        <v>119</v>
+      </c>
+      <c r="C244" t="s">
+        <v>89</v>
+      </c>
+      <c r="D244" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+      <c r="F244" t="s">
+        <v>49</v>
+      </c>
+      <c r="G244" t="b">
+        <v>1</v>
+      </c>
+      <c r="H244" t="s">
+        <v>118</v>
+      </c>
+      <c r="I244" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J244" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A245" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B245" t="s">
+        <v>119</v>
+      </c>
+      <c r="C245" t="s">
+        <v>101</v>
+      </c>
+      <c r="D245" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+      <c r="F245" t="s">
+        <v>102</v>
+      </c>
+      <c r="G245" t="b">
+        <v>1</v>
+      </c>
+      <c r="H245" t="s">
+        <v>118</v>
+      </c>
+      <c r="I245" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J245" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A246" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B246" t="s">
+        <v>119</v>
+      </c>
+      <c r="C246" t="s">
+        <v>106</v>
+      </c>
+      <c r="D246" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E246">
+        <v>10</v>
+      </c>
+      <c r="F246" t="s">
+        <v>107</v>
+      </c>
+      <c r="G246" t="b">
+        <v>1</v>
+      </c>
+      <c r="H246" t="s">
+        <v>118</v>
+      </c>
+      <c r="I246" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J246" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A247" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B247" t="s">
+        <v>119</v>
+      </c>
+      <c r="C247" t="s">
+        <v>113</v>
+      </c>
+      <c r="D247" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E247">
+        <v>10</v>
+      </c>
+      <c r="F247" t="s">
+        <v>108</v>
+      </c>
+      <c r="G247" t="b">
+        <v>1</v>
+      </c>
+      <c r="H247" t="s">
+        <v>118</v>
+      </c>
+      <c r="I247" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J247" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A248" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B248" t="s">
+        <v>54</v>
+      </c>
+      <c r="C248" t="s">
+        <v>150</v>
+      </c>
+      <c r="D248" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E248">
+        <v>5</v>
+      </c>
+      <c r="F248" t="s">
+        <v>55</v>
+      </c>
+      <c r="G248" t="b">
+        <v>0</v>
+      </c>
+      <c r="I248" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J248" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A249" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B249" t="s">
+        <v>54</v>
+      </c>
+      <c r="C249" t="s">
+        <v>150</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E249">
+        <v>1.2</v>
+      </c>
+      <c r="F249" t="s">
+        <v>116</v>
+      </c>
+      <c r="G249" t="b">
+        <v>0</v>
+      </c>
+      <c r="H249" t="s">
+        <v>115</v>
+      </c>
+      <c r="I249" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J249" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A250" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B250" t="s">
+        <v>54</v>
+      </c>
+      <c r="C250" t="s">
+        <v>138</v>
+      </c>
+      <c r="D250" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E250">
+        <v>5</v>
+      </c>
+      <c r="F250" t="s">
+        <v>139</v>
+      </c>
+      <c r="G250" t="b">
+        <v>0</v>
+      </c>
+      <c r="I250" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J250" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A251" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B251" t="s">
+        <v>54</v>
+      </c>
+      <c r="C251" t="s">
+        <v>138</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E251">
+        <v>260</v>
+      </c>
+      <c r="F251" t="s">
+        <v>140</v>
+      </c>
+      <c r="G251" t="b">
+        <v>0</v>
+      </c>
+      <c r="I251" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J251" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A252" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B252" t="s">
+        <v>54</v>
+      </c>
+      <c r="C252" t="s">
+        <v>56</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E252">
+        <v>6</v>
+      </c>
+      <c r="F252" t="s">
+        <v>57</v>
+      </c>
+      <c r="G252" t="b">
+        <v>0</v>
+      </c>
+      <c r="I252" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J252" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A253" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B253" t="s">
+        <v>54</v>
+      </c>
+      <c r="C253" t="s">
+        <v>56</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E253">
+        <v>10</v>
+      </c>
+      <c r="F253" t="s">
+        <v>58</v>
+      </c>
+      <c r="G253" t="b">
+        <v>0</v>
+      </c>
+      <c r="I253" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J253" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A254" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B254" t="s">
+        <v>54</v>
+      </c>
+      <c r="C254" t="s">
+        <v>59</v>
+      </c>
+      <c r="D254" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E254">
+        <v>8</v>
+      </c>
+      <c r="F254" t="s">
+        <v>60</v>
+      </c>
+      <c r="G254" t="b">
+        <v>0</v>
+      </c>
+      <c r="I254" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J254" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A255" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B255" t="s">
+        <v>54</v>
+      </c>
+      <c r="C255" t="s">
+        <v>14</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E255">
+        <v>600</v>
+      </c>
+      <c r="F255" t="s">
+        <v>61</v>
+      </c>
+      <c r="G255" t="b">
+        <v>1</v>
+      </c>
+      <c r="I255" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J255" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A256" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B256" t="s">
+        <v>54</v>
+      </c>
+      <c r="C256" t="s">
+        <v>14</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E256">
+        <v>450</v>
+      </c>
+      <c r="F256" t="s">
+        <v>38</v>
+      </c>
+      <c r="G256" t="b">
+        <v>1</v>
+      </c>
+      <c r="I256" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J256" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A257" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B257" t="s">
+        <v>54</v>
+      </c>
+      <c r="C257" t="s">
+        <v>62</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E257">
+        <v>75</v>
+      </c>
+      <c r="F257" t="s">
+        <v>63</v>
+      </c>
+      <c r="G257" t="b">
+        <v>0</v>
+      </c>
+      <c r="I257" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J257" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A258" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B258" t="s">
+        <v>54</v>
+      </c>
+      <c r="C258" t="s">
+        <v>48</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E258">
+        <v>1000</v>
+      </c>
+      <c r="F258" t="s">
+        <v>64</v>
+      </c>
+      <c r="G258" t="b">
+        <v>0</v>
+      </c>
+      <c r="I258" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J258" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A259" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B259" t="s">
+        <v>54</v>
+      </c>
+      <c r="C259" t="s">
+        <v>51</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E259">
+        <v>50</v>
+      </c>
+      <c r="F259" t="s">
+        <v>65</v>
+      </c>
+      <c r="G259" t="b">
+        <v>1</v>
+      </c>
+      <c r="I259" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J259" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A260" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B260" t="s">
+        <v>54</v>
+      </c>
+      <c r="C260" t="s">
+        <v>66</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E260" s="17">
+        <v>35</v>
+      </c>
+      <c r="F260" t="s">
+        <v>67</v>
+      </c>
+      <c r="G260" t="b">
+        <v>1</v>
+      </c>
+      <c r="H260" t="s">
+        <v>110</v>
+      </c>
+      <c r="I260" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J260" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A261" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B261" t="s">
+        <v>54</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E261">
+        <v>10</v>
+      </c>
+      <c r="F261" t="s">
+        <v>69</v>
+      </c>
+      <c r="G261" t="b">
+        <v>1</v>
+      </c>
+      <c r="I261" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J261" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A262" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B262" t="s">
+        <v>54</v>
+      </c>
+      <c r="C262" t="s">
+        <v>70</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E262">
+        <v>25</v>
+      </c>
+      <c r="F262" t="s">
+        <v>71</v>
+      </c>
+      <c r="G262" t="b">
+        <v>1</v>
+      </c>
+      <c r="I262" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J262" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A263" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B263" t="s">
+        <v>54</v>
+      </c>
+      <c r="C263" t="s">
+        <v>72</v>
+      </c>
+      <c r="D263" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263" t="s">
+        <v>73</v>
+      </c>
+      <c r="G263" t="b">
+        <v>1</v>
+      </c>
+      <c r="I263" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J263" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A264" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B264" t="s">
+        <v>54</v>
+      </c>
+      <c r="C264" t="s">
+        <v>74</v>
+      </c>
+      <c r="D264" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264" t="s">
+        <v>75</v>
+      </c>
+      <c r="G264" t="b">
+        <v>1</v>
+      </c>
+      <c r="I264" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J264" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A265" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B265" t="s">
+        <v>54</v>
+      </c>
+      <c r="C265" t="s">
+        <v>76</v>
+      </c>
+      <c r="D265" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265" t="s">
+        <v>77</v>
+      </c>
+      <c r="G265" t="b">
+        <v>1</v>
+      </c>
+      <c r="I265" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J265" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A266" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B266" t="s">
+        <v>54</v>
+      </c>
+      <c r="C266" t="s">
+        <v>78</v>
+      </c>
+      <c r="D266" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266" t="s">
+        <v>79</v>
+      </c>
+      <c r="G266" t="b">
+        <v>1</v>
+      </c>
+      <c r="I266" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J266" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A267" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B267" t="s">
+        <v>54</v>
+      </c>
+      <c r="C267" t="s">
+        <v>80</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E267">
+        <v>50</v>
+      </c>
+      <c r="F267" t="s">
+        <v>81</v>
+      </c>
+      <c r="G267" t="b">
+        <v>1</v>
+      </c>
+      <c r="I267" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J267" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A268" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B268" t="s">
+        <v>54</v>
+      </c>
+      <c r="C268" t="s">
+        <v>91</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E268" s="17">
+        <v>50</v>
+      </c>
+      <c r="F268" t="s">
+        <v>82</v>
+      </c>
+      <c r="G268" t="b">
+        <v>1</v>
+      </c>
+      <c r="H268" t="s">
+        <v>110</v>
+      </c>
+      <c r="I268" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J268" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A269" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B269" t="s">
+        <v>54</v>
+      </c>
+      <c r="C269" t="s">
+        <v>83</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E269">
+        <v>30</v>
+      </c>
+      <c r="F269" t="s">
+        <v>84</v>
+      </c>
+      <c r="G269" t="b">
+        <v>1</v>
+      </c>
+      <c r="I269" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J269" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A270" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B270" t="s">
+        <v>54</v>
+      </c>
+      <c r="C270" t="s">
+        <v>85</v>
+      </c>
+      <c r="D270" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E270">
+        <v>10</v>
+      </c>
+      <c r="F270" t="s">
+        <v>86</v>
+      </c>
+      <c r="G270" t="b">
+        <v>1</v>
+      </c>
+      <c r="I270" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J270" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A271" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B271" t="s">
+        <v>54</v>
+      </c>
+      <c r="C271" t="s">
+        <v>87</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E271">
+        <v>10</v>
+      </c>
+      <c r="F271" t="s">
+        <v>88</v>
+      </c>
+      <c r="G271" t="b">
+        <v>1</v>
+      </c>
+      <c r="I271" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J271" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A272" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B272" t="s">
+        <v>54</v>
+      </c>
+      <c r="C272" t="s">
+        <v>89</v>
+      </c>
+      <c r="D272" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272" t="s">
+        <v>49</v>
+      </c>
+      <c r="G272" t="b">
+        <v>1</v>
+      </c>
+      <c r="I272" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J272" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A273" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B273" t="s">
+        <v>54</v>
+      </c>
+      <c r="C273" t="s">
+        <v>101</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273" t="s">
+        <v>102</v>
+      </c>
+      <c r="G273" t="b">
+        <v>1</v>
+      </c>
+      <c r="H273" t="s">
+        <v>109</v>
+      </c>
+      <c r="I273" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J273" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A274" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B274" t="s">
+        <v>54</v>
+      </c>
+      <c r="C274" t="s">
+        <v>104</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E274">
+        <v>1000</v>
+      </c>
+      <c r="F274" t="s">
+        <v>105</v>
+      </c>
+      <c r="G274" t="b">
+        <v>0</v>
+      </c>
+      <c r="H274" t="s">
+        <v>117</v>
+      </c>
+      <c r="I274" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J274" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A275" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B275" t="s">
+        <v>54</v>
+      </c>
+      <c r="C275" t="s">
+        <v>106</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E275" s="8">
+        <v>10</v>
+      </c>
+      <c r="F275" t="s">
+        <v>107</v>
+      </c>
+      <c r="G275" t="b">
+        <v>1</v>
+      </c>
+      <c r="H275" t="s">
+        <v>117</v>
+      </c>
+      <c r="I275" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J275" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A276" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B276" t="s">
+        <v>54</v>
+      </c>
+      <c r="C276" t="s">
+        <v>113</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E276" s="8">
+        <v>10</v>
+      </c>
+      <c r="F276" t="s">
+        <v>108</v>
+      </c>
+      <c r="G276" t="b">
+        <v>1</v>
+      </c>
+      <c r="H276" t="s">
+        <v>117</v>
+      </c>
+      <c r="I276" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+      <c r="J276" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A277" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B277" t="s">
+        <v>103</v>
+      </c>
+      <c r="C277" t="s">
+        <v>150</v>
+      </c>
+      <c r="D277" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E277" s="21">
+        <v>8</v>
+      </c>
+      <c r="F277" t="s">
+        <v>111</v>
+      </c>
+      <c r="G277" t="b">
+        <v>0</v>
+      </c>
+      <c r="I277" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J277" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A278" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B278" t="s">
+        <v>103</v>
+      </c>
+      <c r="C278" t="s">
+        <v>150</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E278">
+        <v>3</v>
+      </c>
+      <c r="F278" t="s">
+        <v>112</v>
+      </c>
+      <c r="G278" t="b">
+        <v>0</v>
+      </c>
+      <c r="I278" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J278" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A279" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B279" t="s">
+        <v>103</v>
+      </c>
+      <c r="C279" t="s">
+        <v>138</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E279">
+        <v>5</v>
+      </c>
+      <c r="F279" t="s">
+        <v>139</v>
+      </c>
+      <c r="G279" t="b">
+        <v>0</v>
+      </c>
+      <c r="I279" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J279" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A280" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B280" t="s">
+        <v>103</v>
+      </c>
+      <c r="C280" t="s">
+        <v>138</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E280">
+        <v>260</v>
+      </c>
+      <c r="F280" t="s">
+        <v>140</v>
+      </c>
+      <c r="G280" t="b">
+        <v>0</v>
+      </c>
+      <c r="I280" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J280" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A281" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B281" t="s">
+        <v>103</v>
+      </c>
+      <c r="C281" t="s">
+        <v>104</v>
+      </c>
+      <c r="D281" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E281">
+        <v>1000</v>
+      </c>
+      <c r="F281" t="s">
+        <v>105</v>
+      </c>
+      <c r="G281" t="b">
+        <v>0</v>
+      </c>
+      <c r="I281" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J281" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A282" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B282" t="s">
+        <v>103</v>
+      </c>
+      <c r="C282" t="s">
+        <v>56</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E282">
+        <v>6</v>
+      </c>
+      <c r="F282" t="s">
+        <v>57</v>
+      </c>
+      <c r="G282" t="b">
+        <v>0</v>
+      </c>
+      <c r="I282" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J282" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A283" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B283" t="s">
+        <v>103</v>
+      </c>
+      <c r="C283" t="s">
+        <v>56</v>
+      </c>
+      <c r="D283" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E283">
+        <v>10</v>
+      </c>
+      <c r="F283" t="s">
+        <v>58</v>
+      </c>
+      <c r="G283" t="b">
+        <v>0</v>
+      </c>
+      <c r="I283" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J283" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A284" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B284" t="s">
+        <v>103</v>
+      </c>
+      <c r="C284" t="s">
+        <v>59</v>
+      </c>
+      <c r="D284" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E284">
+        <v>8</v>
+      </c>
+      <c r="F284" t="s">
+        <v>60</v>
+      </c>
+      <c r="G284" t="b">
+        <v>0</v>
+      </c>
+      <c r="I284" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J284" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A285" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B285" t="s">
+        <v>103</v>
+      </c>
+      <c r="C285" t="s">
+        <v>14</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E285">
+        <v>600</v>
+      </c>
+      <c r="F285" t="s">
+        <v>61</v>
+      </c>
+      <c r="G285" t="b">
+        <v>1</v>
+      </c>
+      <c r="I285" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J285" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A286" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B286" t="s">
+        <v>103</v>
+      </c>
+      <c r="C286" t="s">
+        <v>14</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E286">
+        <v>450</v>
+      </c>
+      <c r="F286" t="s">
+        <v>38</v>
+      </c>
+      <c r="G286" t="b">
+        <v>1</v>
+      </c>
+      <c r="I286" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J286" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A287" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B287" t="s">
+        <v>103</v>
+      </c>
+      <c r="C287" t="s">
+        <v>62</v>
+      </c>
+      <c r="D287" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E287">
+        <v>75</v>
+      </c>
+      <c r="F287" t="s">
+        <v>63</v>
+      </c>
+      <c r="G287" t="b">
+        <v>0</v>
+      </c>
+      <c r="I287" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J287" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A288" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B288" t="s">
+        <v>103</v>
+      </c>
+      <c r="C288" t="s">
+        <v>48</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E288">
+        <v>1000</v>
+      </c>
+      <c r="F288" t="s">
+        <v>64</v>
+      </c>
+      <c r="G288" t="b">
+        <v>0</v>
+      </c>
+      <c r="I288" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J288" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A289" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B289" t="s">
+        <v>103</v>
+      </c>
+      <c r="C289" t="s">
+        <v>51</v>
+      </c>
+      <c r="D289" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E289">
+        <v>50</v>
+      </c>
+      <c r="F289" t="s">
+        <v>65</v>
+      </c>
+      <c r="G289" t="b">
+        <v>1</v>
+      </c>
+      <c r="I289" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J289" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A290" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B290" t="s">
+        <v>103</v>
+      </c>
+      <c r="C290" t="s">
+        <v>66</v>
+      </c>
+      <c r="D290" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E290">
+        <v>35</v>
+      </c>
+      <c r="F290" t="s">
+        <v>67</v>
+      </c>
+      <c r="G290" t="b">
+        <v>1</v>
+      </c>
+      <c r="I290" s="19" t="str">
+        <f t="shared" ref="I290:I333" si="13">B290</f>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J290" s="19" t="str">
+        <f t="shared" ref="J290:J333" si="14">B290</f>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A291" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B291" t="s">
+        <v>103</v>
+      </c>
+      <c r="C291" t="s">
+        <v>68</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E291">
+        <v>10</v>
+      </c>
+      <c r="F291" t="s">
+        <v>69</v>
+      </c>
+      <c r="G291" t="b">
+        <v>1</v>
+      </c>
+      <c r="I291" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J291" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A292" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B292" t="s">
+        <v>103</v>
+      </c>
+      <c r="C292" t="s">
+        <v>70</v>
+      </c>
+      <c r="D292" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E292">
+        <v>25</v>
+      </c>
+      <c r="F292" t="s">
+        <v>71</v>
+      </c>
+      <c r="G292" t="b">
+        <v>1</v>
+      </c>
+      <c r="I292" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J292" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A293" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B293" t="s">
+        <v>103</v>
+      </c>
+      <c r="C293" t="s">
+        <v>72</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293" t="s">
+        <v>73</v>
+      </c>
+      <c r="G293" t="b">
+        <v>1</v>
+      </c>
+      <c r="I293" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J293" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A294" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B294" t="s">
+        <v>103</v>
+      </c>
+      <c r="C294" t="s">
+        <v>74</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294" t="s">
+        <v>75</v>
+      </c>
+      <c r="G294" t="b">
+        <v>1</v>
+      </c>
+      <c r="I294" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J294" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A295" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B295" t="s">
+        <v>103</v>
+      </c>
+      <c r="C295" t="s">
+        <v>76</v>
+      </c>
+      <c r="D295" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295" t="s">
+        <v>77</v>
+      </c>
+      <c r="G295" t="b">
+        <v>1</v>
+      </c>
+      <c r="I295" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J295" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A296" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B296" t="s">
+        <v>103</v>
+      </c>
+      <c r="C296" t="s">
+        <v>78</v>
+      </c>
+      <c r="D296" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296" t="s">
+        <v>79</v>
+      </c>
+      <c r="G296" t="b">
+        <v>1</v>
+      </c>
+      <c r="I296" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J296" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A297" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B297" t="s">
+        <v>103</v>
+      </c>
+      <c r="C297" t="s">
+        <v>80</v>
+      </c>
+      <c r="D297" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E297">
+        <v>50</v>
+      </c>
+      <c r="F297" t="s">
+        <v>81</v>
+      </c>
+      <c r="G297" t="b">
+        <v>1</v>
+      </c>
+      <c r="I297" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J297" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A298" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B298" t="s">
+        <v>103</v>
+      </c>
+      <c r="C298" t="s">
+        <v>91</v>
+      </c>
+      <c r="D298" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E298">
+        <v>50</v>
+      </c>
+      <c r="F298" t="s">
+        <v>82</v>
+      </c>
+      <c r="G298" t="b">
+        <v>1</v>
+      </c>
+      <c r="I298" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J298" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A299" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B299" t="s">
+        <v>103</v>
+      </c>
+      <c r="C299" t="s">
+        <v>83</v>
+      </c>
+      <c r="D299" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E299">
+        <v>30</v>
+      </c>
+      <c r="F299" t="s">
+        <v>84</v>
+      </c>
+      <c r="G299" t="b">
+        <v>1</v>
+      </c>
+      <c r="I299" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J299" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A300" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B300" t="s">
+        <v>103</v>
+      </c>
+      <c r="C300" t="s">
+        <v>85</v>
+      </c>
+      <c r="D300" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E300">
+        <v>10</v>
+      </c>
+      <c r="F300" t="s">
+        <v>86</v>
+      </c>
+      <c r="G300" t="b">
+        <v>1</v>
+      </c>
+      <c r="I300" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J300" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A301" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B301" t="s">
+        <v>103</v>
+      </c>
+      <c r="C301" t="s">
+        <v>87</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E301">
+        <v>10</v>
+      </c>
+      <c r="F301" t="s">
+        <v>88</v>
+      </c>
+      <c r="G301" t="b">
+        <v>1</v>
+      </c>
+      <c r="I301" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J301" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A302" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B302" t="s">
+        <v>103</v>
+      </c>
+      <c r="C302" t="s">
+        <v>89</v>
+      </c>
+      <c r="D302" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302" t="s">
+        <v>49</v>
+      </c>
+      <c r="G302" t="b">
+        <v>1</v>
+      </c>
+      <c r="I302" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J302" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A303" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B303" t="s">
+        <v>103</v>
+      </c>
+      <c r="C303" t="s">
+        <v>101</v>
+      </c>
+      <c r="D303" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303" t="s">
+        <v>102</v>
+      </c>
+      <c r="G303" t="b">
+        <v>1</v>
+      </c>
+      <c r="I303" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J303" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A304" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B304" t="s">
+        <v>103</v>
+      </c>
+      <c r="C304" t="s">
+        <v>106</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E304">
+        <v>10</v>
+      </c>
+      <c r="F304" t="s">
+        <v>107</v>
+      </c>
+      <c r="G304" t="b">
+        <v>1</v>
+      </c>
+      <c r="I304" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J304" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A305" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B305" t="s">
+        <v>103</v>
+      </c>
+      <c r="C305" t="s">
+        <v>113</v>
+      </c>
+      <c r="D305" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E305">
+        <v>10</v>
+      </c>
+      <c r="F305" t="s">
+        <v>108</v>
+      </c>
+      <c r="G305" t="b">
+        <v>1</v>
+      </c>
+      <c r="I305" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+      <c r="J305" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>HiGrad-HiElev</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A306" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B306" t="s">
+        <v>119</v>
+      </c>
+      <c r="C306" t="s">
+        <v>150</v>
+      </c>
+      <c r="D306" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E306">
+        <v>0.7</v>
+      </c>
+      <c r="F306" t="s">
+        <v>112</v>
+      </c>
+      <c r="G306" t="b">
+        <v>0</v>
+      </c>
+      <c r="H306" t="s">
+        <v>120</v>
+      </c>
+      <c r="I306" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J306" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A307" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B307" t="s">
+        <v>119</v>
+      </c>
+      <c r="C307" t="s">
+        <v>138</v>
+      </c>
+      <c r="D307" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E307">
+        <v>5</v>
+      </c>
+      <c r="F307" t="s">
+        <v>139</v>
+      </c>
+      <c r="G307" t="b">
+        <v>0</v>
+      </c>
+      <c r="H307" t="s">
+        <v>118</v>
+      </c>
+      <c r="I307" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J307" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A308" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B308" t="s">
+        <v>119</v>
+      </c>
+      <c r="C308" t="s">
+        <v>138</v>
+      </c>
+      <c r="D308" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E308">
+        <v>260</v>
+      </c>
+      <c r="F308" t="s">
+        <v>140</v>
+      </c>
+      <c r="G308" t="b">
+        <v>0</v>
+      </c>
+      <c r="H308" t="s">
+        <v>118</v>
+      </c>
+      <c r="I308" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J308" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A309" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B309" t="s">
+        <v>119</v>
+      </c>
+      <c r="C309" t="s">
+        <v>104</v>
+      </c>
+      <c r="D309" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E309">
+        <v>1000</v>
+      </c>
+      <c r="F309" t="s">
+        <v>105</v>
+      </c>
+      <c r="G309" t="b">
+        <v>0</v>
+      </c>
+      <c r="H309" t="s">
+        <v>118</v>
+      </c>
+      <c r="I309" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J309" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A310" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B310" t="s">
+        <v>119</v>
+      </c>
+      <c r="C310" t="s">
+        <v>56</v>
+      </c>
+      <c r="D310" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E310">
+        <v>6</v>
+      </c>
+      <c r="F310" t="s">
+        <v>57</v>
+      </c>
+      <c r="G310" t="b">
+        <v>0</v>
+      </c>
+      <c r="H310" t="s">
+        <v>118</v>
+      </c>
+      <c r="I310" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J310" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A311" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B311" t="s">
+        <v>119</v>
+      </c>
+      <c r="C311" t="s">
+        <v>56</v>
+      </c>
+      <c r="D311" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E311">
+        <v>10</v>
+      </c>
+      <c r="F311" t="s">
+        <v>58</v>
+      </c>
+      <c r="G311" t="b">
+        <v>0</v>
+      </c>
+      <c r="H311" t="s">
+        <v>118</v>
+      </c>
+      <c r="I311" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J311" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A312" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B312" t="s">
+        <v>119</v>
+      </c>
+      <c r="C312" t="s">
+        <v>59</v>
+      </c>
+      <c r="D312" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E312">
+        <v>8</v>
+      </c>
+      <c r="F312" t="s">
+        <v>60</v>
+      </c>
+      <c r="G312" t="b">
+        <v>0</v>
+      </c>
+      <c r="H312" t="s">
+        <v>118</v>
+      </c>
+      <c r="I312" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J312" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A313" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B313" t="s">
+        <v>119</v>
+      </c>
+      <c r="C313" t="s">
+        <v>14</v>
+      </c>
+      <c r="D313" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E313">
+        <v>600</v>
+      </c>
+      <c r="F313" t="s">
+        <v>61</v>
+      </c>
+      <c r="G313" t="b">
+        <v>1</v>
+      </c>
+      <c r="H313" t="s">
+        <v>118</v>
+      </c>
+      <c r="I313" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J313" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A314" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B314" t="s">
+        <v>119</v>
+      </c>
+      <c r="C314" t="s">
+        <v>14</v>
+      </c>
+      <c r="D314" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E314">
+        <v>450</v>
+      </c>
+      <c r="F314" t="s">
+        <v>38</v>
+      </c>
+      <c r="G314" t="b">
+        <v>1</v>
+      </c>
+      <c r="H314" t="s">
+        <v>118</v>
+      </c>
+      <c r="I314" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J314" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A315" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B315" t="s">
+        <v>119</v>
+      </c>
+      <c r="C315" t="s">
+        <v>62</v>
+      </c>
+      <c r="D315" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E315">
+        <v>75</v>
+      </c>
+      <c r="F315" t="s">
+        <v>63</v>
+      </c>
+      <c r="G315" t="b">
+        <v>0</v>
+      </c>
+      <c r="H315" t="s">
+        <v>118</v>
+      </c>
+      <c r="I315" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J315" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A316" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B316" t="s">
+        <v>119</v>
+      </c>
+      <c r="C316" t="s">
+        <v>48</v>
+      </c>
+      <c r="D316" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E316">
+        <v>1000</v>
+      </c>
+      <c r="F316" t="s">
+        <v>64</v>
+      </c>
+      <c r="G316" t="b">
+        <v>0</v>
+      </c>
+      <c r="H316" t="s">
+        <v>118</v>
+      </c>
+      <c r="I316" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J316" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A317" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B317" t="s">
+        <v>119</v>
+      </c>
+      <c r="C317" t="s">
+        <v>51</v>
+      </c>
+      <c r="D317" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E317">
+        <v>50</v>
+      </c>
+      <c r="F317" t="s">
+        <v>65</v>
+      </c>
+      <c r="G317" t="b">
+        <v>1</v>
+      </c>
+      <c r="H317" t="s">
+        <v>118</v>
+      </c>
+      <c r="I317" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J317" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A318" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B318" t="s">
+        <v>119</v>
+      </c>
+      <c r="C318" t="s">
+        <v>66</v>
+      </c>
+      <c r="D318" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E318">
+        <v>35</v>
+      </c>
+      <c r="F318" t="s">
+        <v>67</v>
+      </c>
+      <c r="G318" t="b">
+        <v>1</v>
+      </c>
+      <c r="H318" t="s">
+        <v>118</v>
+      </c>
+      <c r="I318" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J318" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A319" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B319" t="s">
+        <v>119</v>
+      </c>
+      <c r="C319" t="s">
+        <v>68</v>
+      </c>
+      <c r="D319" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E319">
+        <v>10</v>
+      </c>
+      <c r="F319" t="s">
+        <v>69</v>
+      </c>
+      <c r="G319" t="b">
+        <v>1</v>
+      </c>
+      <c r="H319" t="s">
+        <v>118</v>
+      </c>
+      <c r="I319" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J319" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A320" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B320" t="s">
+        <v>119</v>
+      </c>
+      <c r="C320" t="s">
+        <v>70</v>
+      </c>
+      <c r="D320" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E320">
+        <v>25</v>
+      </c>
+      <c r="F320" t="s">
+        <v>71</v>
+      </c>
+      <c r="G320" t="b">
+        <v>1</v>
+      </c>
+      <c r="H320" t="s">
+        <v>118</v>
+      </c>
+      <c r="I320" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J320" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A321" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B321" t="s">
+        <v>119</v>
+      </c>
+      <c r="C321" t="s">
+        <v>72</v>
+      </c>
+      <c r="D321" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+      <c r="F321" t="s">
+        <v>73</v>
+      </c>
+      <c r="G321" t="b">
+        <v>1</v>
+      </c>
+      <c r="H321" t="s">
+        <v>118</v>
+      </c>
+      <c r="I321" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J321" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A322" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B322" t="s">
+        <v>119</v>
+      </c>
+      <c r="C322" t="s">
+        <v>74</v>
+      </c>
+      <c r="D322" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
+      <c r="F322" t="s">
+        <v>75</v>
+      </c>
+      <c r="G322" t="b">
+        <v>1</v>
+      </c>
+      <c r="H322" t="s">
+        <v>118</v>
+      </c>
+      <c r="I322" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J322" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A323" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B323" t="s">
+        <v>119</v>
+      </c>
+      <c r="C323" t="s">
+        <v>76</v>
+      </c>
+      <c r="D323" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
+      <c r="F323" t="s">
+        <v>77</v>
+      </c>
+      <c r="G323" t="b">
+        <v>1</v>
+      </c>
+      <c r="H323" t="s">
+        <v>118</v>
+      </c>
+      <c r="I323" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J323" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A324" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B324" t="s">
+        <v>119</v>
+      </c>
+      <c r="C324" t="s">
+        <v>78</v>
+      </c>
+      <c r="D324" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
+      <c r="F324" t="s">
+        <v>79</v>
+      </c>
+      <c r="G324" t="b">
+        <v>1</v>
+      </c>
+      <c r="H324" t="s">
+        <v>118</v>
+      </c>
+      <c r="I324" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J324" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A325" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B325" t="s">
+        <v>119</v>
+      </c>
+      <c r="C325" t="s">
+        <v>80</v>
+      </c>
+      <c r="D325" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E325">
+        <v>50</v>
+      </c>
+      <c r="F325" t="s">
+        <v>81</v>
+      </c>
+      <c r="G325" t="b">
+        <v>1</v>
+      </c>
+      <c r="H325" t="s">
+        <v>118</v>
+      </c>
+      <c r="I325" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J325" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A326" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B326" t="s">
+        <v>119</v>
+      </c>
+      <c r="C326" t="s">
+        <v>91</v>
+      </c>
+      <c r="D326" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E326">
+        <v>50</v>
+      </c>
+      <c r="F326" t="s">
+        <v>82</v>
+      </c>
+      <c r="G326" t="b">
+        <v>1</v>
+      </c>
+      <c r="H326" t="s">
+        <v>118</v>
+      </c>
+      <c r="I326" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J326" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A327" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B327" t="s">
+        <v>119</v>
+      </c>
+      <c r="C327" t="s">
+        <v>83</v>
+      </c>
+      <c r="D327" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E327">
+        <v>30</v>
+      </c>
+      <c r="F327" t="s">
+        <v>84</v>
+      </c>
+      <c r="G327" t="b">
+        <v>1</v>
+      </c>
+      <c r="H327" t="s">
+        <v>118</v>
+      </c>
+      <c r="I327" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J327" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A328" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B328" t="s">
+        <v>119</v>
+      </c>
+      <c r="C328" t="s">
+        <v>85</v>
+      </c>
+      <c r="D328" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E328">
+        <v>10</v>
+      </c>
+      <c r="F328" t="s">
+        <v>86</v>
+      </c>
+      <c r="G328" t="b">
+        <v>1</v>
+      </c>
+      <c r="H328" t="s">
+        <v>118</v>
+      </c>
+      <c r="I328" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J328" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A329" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B329" t="s">
+        <v>119</v>
+      </c>
+      <c r="C329" t="s">
+        <v>87</v>
+      </c>
+      <c r="D329" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E329">
+        <v>10</v>
+      </c>
+      <c r="F329" t="s">
+        <v>88</v>
+      </c>
+      <c r="G329" t="b">
+        <v>1</v>
+      </c>
+      <c r="H329" t="s">
+        <v>118</v>
+      </c>
+      <c r="I329" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J329" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A330" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B330" t="s">
+        <v>119</v>
+      </c>
+      <c r="C330" t="s">
+        <v>89</v>
+      </c>
+      <c r="D330" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
+      <c r="F330" t="s">
+        <v>49</v>
+      </c>
+      <c r="G330" t="b">
+        <v>1</v>
+      </c>
+      <c r="H330" t="s">
+        <v>118</v>
+      </c>
+      <c r="I330" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J330" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A331" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B331" t="s">
+        <v>119</v>
+      </c>
+      <c r="C331" t="s">
+        <v>101</v>
+      </c>
+      <c r="D331" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+      <c r="F331" t="s">
+        <v>102</v>
+      </c>
+      <c r="G331" t="b">
+        <v>1</v>
+      </c>
+      <c r="H331" t="s">
+        <v>118</v>
+      </c>
+      <c r="I331" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J331" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A332" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B332" t="s">
+        <v>119</v>
+      </c>
+      <c r="C332" t="s">
+        <v>106</v>
+      </c>
+      <c r="D332" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E332">
+        <v>10</v>
+      </c>
+      <c r="F332" t="s">
+        <v>107</v>
+      </c>
+      <c r="G332" t="b">
+        <v>1</v>
+      </c>
+      <c r="H332" t="s">
+        <v>118</v>
+      </c>
+      <c r="I332" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J332" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A333" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B333" t="s">
+        <v>119</v>
+      </c>
+      <c r="C333" t="s">
+        <v>113</v>
+      </c>
+      <c r="D333" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E333">
+        <v>10</v>
+      </c>
+      <c r="F333" t="s">
+        <v>108</v>
+      </c>
+      <c r="G333" t="b">
+        <v>1</v>
+      </c>
+      <c r="H333" t="s">
+        <v>118</v>
+      </c>
+      <c r="I333" s="19" t="str">
+        <f t="shared" si="13"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+      <c r="J333" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>LoGrad-LoElev</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J132" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <conditionalFormatting sqref="C2:C66">
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="10" priority="14">
       <formula>$G2=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$G128=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G153">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+  <conditionalFormatting sqref="G2:G161">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H100:H127">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G154:G161">
+  <conditionalFormatting sqref="C162:C186">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>$G162=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C248:C272">
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>$G248=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G162:G333">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H174">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H220:H247 H306:H333">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H260">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614C22D4-6558-4998-802C-2764CB46DF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C59034-4403-4FE3-B451-CCD686EA421E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Flags" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$333</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="181">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -709,6 +709,9 @@
   </si>
   <si>
     <t>BCG_ORWA_v1_Bugs500ct</t>
+  </si>
+  <si>
+    <t>Move ni_total flags to top of each index_class</t>
   </si>
 </sst>
 </file>
@@ -820,7 +823,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -863,6 +866,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -901,7 +910,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
@@ -949,6 +958,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
@@ -957,7 +967,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -975,40 +985,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1078,7 +1054,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Worksheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descriptions"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="11">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="7">
       <calculatedColumnFormula>HYPERLINK(FileName&amp;A16&amp;"!A1",A16)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1376,7 +1352,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1642,6 +1618,11 @@
       </c>
       <c r="B43" t="s">
         <v>177</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -1765,6 +1746,7 @@
     <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -6859,27 +6841,27 @@
       <c r="B162" t="s">
         <v>54</v>
       </c>
-      <c r="C162" t="s">
-        <v>150</v>
+      <c r="C162" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E162">
-        <v>5</v>
+        <v>600</v>
       </c>
       <c r="F162" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" s="19" t="str">
-        <f t="shared" ref="I162:I225" si="9">B162</f>
+        <f>B162</f>
         <v>HiGrad-LoElev</v>
       </c>
       <c r="J162" s="19" t="str">
-        <f t="shared" ref="J162:J225" si="10">B162</f>
+        <f>B162</f>
         <v>HiGrad-LoElev</v>
       </c>
     </row>
@@ -6890,30 +6872,27 @@
       <c r="B163" t="s">
         <v>54</v>
       </c>
-      <c r="C163" t="s">
-        <v>150</v>
+      <c r="C163" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E163">
-        <v>1.2</v>
+        <v>450</v>
       </c>
       <c r="F163" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="G163" t="b">
-        <v>0</v>
-      </c>
-      <c r="H163" t="s">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="I163" s="19" t="str">
-        <f t="shared" si="9"/>
+        <f>B163</f>
         <v>HiGrad-LoElev</v>
       </c>
       <c r="J163" s="19" t="str">
-        <f t="shared" si="10"/>
+        <f>B163</f>
         <v>HiGrad-LoElev</v>
       </c>
     </row>
@@ -6925,26 +6904,26 @@
         <v>54</v>
       </c>
       <c r="C164" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E164">
         <v>5</v>
       </c>
       <c r="F164" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="G164" t="b">
         <v>0</v>
       </c>
       <c r="I164" s="19" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="I164:I227" si="9">B164</f>
         <v>HiGrad-LoElev</v>
       </c>
       <c r="J164" s="19" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="J164:J227" si="10">B164</f>
         <v>HiGrad-LoElev</v>
       </c>
     </row>
@@ -6956,19 +6935,22 @@
         <v>54</v>
       </c>
       <c r="C165" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E165">
-        <v>260</v>
+        <v>1.2</v>
       </c>
       <c r="F165" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="G165" t="b">
         <v>0</v>
+      </c>
+      <c r="H165" t="s">
+        <v>115</v>
       </c>
       <c r="I165" s="19" t="str">
         <f t="shared" si="9"/>
@@ -6987,16 +6969,16 @@
         <v>54</v>
       </c>
       <c r="C166" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D166" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F166" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="G166" t="b">
         <v>0</v>
@@ -7018,16 +7000,16 @@
         <v>54</v>
       </c>
       <c r="C167" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D167" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E167">
-        <v>10</v>
+        <v>260</v>
       </c>
       <c r="F167" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="G167" t="b">
         <v>0</v>
@@ -7049,16 +7031,16 @@
         <v>54</v>
       </c>
       <c r="C168" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D168" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E168">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F168" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G168" t="b">
         <v>0</v>
@@ -7080,19 +7062,19 @@
         <v>54</v>
       </c>
       <c r="C169" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D169" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E169">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="F169" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169" s="19" t="str">
         <f t="shared" si="9"/>
@@ -7111,19 +7093,19 @@
         <v>54</v>
       </c>
       <c r="C170" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D170" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E170">
-        <v>450</v>
+        <v>8</v>
       </c>
       <c r="F170" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170" s="19" t="str">
         <f t="shared" si="9"/>
@@ -7779,27 +7761,27 @@
       <c r="B191" t="s">
         <v>103</v>
       </c>
-      <c r="C191" t="s">
-        <v>150</v>
+      <c r="C191" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E191" s="21">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="E191">
+        <v>600</v>
       </c>
       <c r="F191" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="G191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I191" s="19" t="str">
-        <f t="shared" si="9"/>
+        <f>B191</f>
         <v>HiGrad-HiElev</v>
       </c>
       <c r="J191" s="19" t="str">
-        <f t="shared" si="10"/>
+        <f>B191</f>
         <v>HiGrad-HiElev</v>
       </c>
     </row>
@@ -7810,27 +7792,27 @@
       <c r="B192" t="s">
         <v>103</v>
       </c>
-      <c r="C192" t="s">
-        <v>150</v>
+      <c r="C192" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D192" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E192">
-        <v>3</v>
+        <v>450</v>
       </c>
       <c r="F192" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="G192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I192" s="19" t="str">
-        <f t="shared" si="9"/>
+        <f>B192</f>
         <v>HiGrad-HiElev</v>
       </c>
       <c r="J192" s="19" t="str">
-        <f t="shared" si="10"/>
+        <f>B192</f>
         <v>HiGrad-HiElev</v>
       </c>
     </row>
@@ -7842,16 +7824,16 @@
         <v>103</v>
       </c>
       <c r="C193" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E193">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="E193" s="21">
+        <v>8</v>
       </c>
       <c r="F193" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="G193" t="b">
         <v>0</v>
@@ -7873,16 +7855,16 @@
         <v>103</v>
       </c>
       <c r="C194" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E194">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="F194" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="G194" t="b">
         <v>0</v>
@@ -7904,16 +7886,16 @@
         <v>103</v>
       </c>
       <c r="C195" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E195">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="F195" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="G195" t="b">
         <v>0</v>
@@ -7935,16 +7917,16 @@
         <v>103</v>
       </c>
       <c r="C196" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E196">
-        <v>6</v>
+        <v>260</v>
       </c>
       <c r="F196" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="G196" t="b">
         <v>0</v>
@@ -7966,16 +7948,16 @@
         <v>103</v>
       </c>
       <c r="C197" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E197">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F197" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="G197" t="b">
         <v>0</v>
@@ -7997,16 +7979,16 @@
         <v>103</v>
       </c>
       <c r="C198" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E198">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F198" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G198" t="b">
         <v>0</v>
@@ -8028,19 +8010,19 @@
         <v>103</v>
       </c>
       <c r="C199" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D199" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E199">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="F199" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199" s="19" t="str">
         <f t="shared" si="9"/>
@@ -8059,19 +8041,19 @@
         <v>103</v>
       </c>
       <c r="C200" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D200" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E200">
-        <v>450</v>
+        <v>8</v>
       </c>
       <c r="F200" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200" s="19" t="str">
         <f t="shared" si="9"/>
@@ -8678,30 +8660,30 @@
       <c r="B220" t="s">
         <v>119</v>
       </c>
-      <c r="C220" t="s">
-        <v>150</v>
+      <c r="C220" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D220" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E220">
-        <v>0.7</v>
+        <v>600</v>
       </c>
       <c r="F220" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="G220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H220" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I220" s="19" t="str">
-        <f t="shared" si="9"/>
+        <f>B220</f>
         <v>LoGrad-LoElev</v>
       </c>
       <c r="J220" s="19" t="str">
-        <f t="shared" si="10"/>
+        <f>B220</f>
         <v>LoGrad-LoElev</v>
       </c>
     </row>
@@ -8712,30 +8694,30 @@
       <c r="B221" t="s">
         <v>119</v>
       </c>
-      <c r="C221" t="s">
-        <v>138</v>
+      <c r="C221" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D221" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E221">
-        <v>5</v>
+        <v>450</v>
       </c>
       <c r="F221" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H221" t="s">
         <v>118</v>
       </c>
       <c r="I221" s="19" t="str">
-        <f t="shared" si="9"/>
+        <f>B221</f>
         <v>LoGrad-LoElev</v>
       </c>
       <c r="J221" s="19" t="str">
-        <f t="shared" si="10"/>
+        <f>B221</f>
         <v>LoGrad-LoElev</v>
       </c>
     </row>
@@ -8747,22 +8729,22 @@
         <v>119</v>
       </c>
       <c r="C222" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D222" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E222">
-        <v>260</v>
+        <v>0.7</v>
       </c>
       <c r="F222" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="G222" t="b">
         <v>0</v>
       </c>
       <c r="H222" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I222" s="19" t="str">
         <f t="shared" si="9"/>
@@ -8781,16 +8763,16 @@
         <v>119</v>
       </c>
       <c r="C223" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="D223" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E223">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="F223" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="G223" t="b">
         <v>0</v>
@@ -8815,16 +8797,16 @@
         <v>119</v>
       </c>
       <c r="C224" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D224" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E224">
-        <v>6</v>
+        <v>260</v>
       </c>
       <c r="F224" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="G224" t="b">
         <v>0</v>
@@ -8849,16 +8831,16 @@
         <v>119</v>
       </c>
       <c r="C225" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E225">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F225" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="G225" t="b">
         <v>0</v>
@@ -8883,16 +8865,16 @@
         <v>119</v>
       </c>
       <c r="C226" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D226" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E226">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F226" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G226" t="b">
         <v>0</v>
@@ -8901,11 +8883,11 @@
         <v>118</v>
       </c>
       <c r="I226" s="19" t="str">
-        <f t="shared" ref="I226:I289" si="11">B226</f>
+        <f t="shared" si="9"/>
         <v>LoGrad-LoElev</v>
       </c>
       <c r="J226" s="19" t="str">
-        <f t="shared" ref="J226:J289" si="12">B226</f>
+        <f t="shared" si="10"/>
         <v>LoGrad-LoElev</v>
       </c>
     </row>
@@ -8917,29 +8899,29 @@
         <v>119</v>
       </c>
       <c r="C227" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D227" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E227">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="F227" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H227" t="s">
         <v>118</v>
       </c>
       <c r="I227" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>LoGrad-LoElev</v>
       </c>
       <c r="J227" s="19" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>LoGrad-LoElev</v>
       </c>
     </row>
@@ -8951,29 +8933,29 @@
         <v>119</v>
       </c>
       <c r="C228" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D228" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E228">
-        <v>450</v>
+        <v>8</v>
       </c>
       <c r="F228" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G228" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H228" t="s">
         <v>118</v>
       </c>
       <c r="I228" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="I228:I289" si="11">B228</f>
         <v>LoGrad-LoElev</v>
       </c>
       <c r="J228" s="19" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="J228:J289" si="12">B228</f>
         <v>LoGrad-LoElev</v>
       </c>
     </row>
@@ -9630,27 +9612,27 @@
       <c r="B248" t="s">
         <v>54</v>
       </c>
-      <c r="C248" t="s">
-        <v>150</v>
+      <c r="C248" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E248">
-        <v>5</v>
+        <v>600</v>
       </c>
       <c r="F248" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I248" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f>B248</f>
         <v>HiGrad-LoElev</v>
       </c>
       <c r="J248" s="19" t="str">
-        <f t="shared" si="12"/>
+        <f>B248</f>
         <v>HiGrad-LoElev</v>
       </c>
     </row>
@@ -9661,30 +9643,27 @@
       <c r="B249" t="s">
         <v>54</v>
       </c>
-      <c r="C249" t="s">
-        <v>150</v>
+      <c r="C249" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D249" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E249">
-        <v>1.2</v>
+        <v>450</v>
       </c>
       <c r="F249" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="G249" t="b">
-        <v>0</v>
-      </c>
-      <c r="H249" t="s">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="I249" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f>B249</f>
         <v>HiGrad-LoElev</v>
       </c>
       <c r="J249" s="19" t="str">
-        <f t="shared" si="12"/>
+        <f>B249</f>
         <v>HiGrad-LoElev</v>
       </c>
     </row>
@@ -9696,16 +9675,16 @@
         <v>54</v>
       </c>
       <c r="C250" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E250">
         <v>5</v>
       </c>
       <c r="F250" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="G250" t="b">
         <v>0</v>
@@ -9727,19 +9706,22 @@
         <v>54</v>
       </c>
       <c r="C251" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E251">
-        <v>260</v>
+        <v>1.2</v>
       </c>
       <c r="F251" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="G251" t="b">
         <v>0</v>
+      </c>
+      <c r="H251" t="s">
+        <v>115</v>
       </c>
       <c r="I251" s="19" t="str">
         <f t="shared" si="11"/>
@@ -9758,16 +9740,16 @@
         <v>54</v>
       </c>
       <c r="C252" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D252" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E252">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F252" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="G252" t="b">
         <v>0</v>
@@ -9789,16 +9771,16 @@
         <v>54</v>
       </c>
       <c r="C253" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D253" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E253">
-        <v>10</v>
+        <v>260</v>
       </c>
       <c r="F253" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="G253" t="b">
         <v>0</v>
@@ -9820,16 +9802,16 @@
         <v>54</v>
       </c>
       <c r="C254" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D254" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E254">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F254" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G254" t="b">
         <v>0</v>
@@ -9851,19 +9833,19 @@
         <v>54</v>
       </c>
       <c r="C255" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D255" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E255">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="F255" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G255" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I255" s="19" t="str">
         <f t="shared" si="11"/>
@@ -9882,19 +9864,19 @@
         <v>54</v>
       </c>
       <c r="C256" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D256" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E256">
-        <v>450</v>
+        <v>8</v>
       </c>
       <c r="F256" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I256" s="19" t="str">
         <f t="shared" si="11"/>
@@ -10550,27 +10532,27 @@
       <c r="B277" t="s">
         <v>103</v>
       </c>
-      <c r="C277" t="s">
-        <v>150</v>
+      <c r="C277" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E277" s="21">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="E277">
+        <v>600</v>
       </c>
       <c r="F277" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="G277" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I277" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f>B277</f>
         <v>HiGrad-HiElev</v>
       </c>
       <c r="J277" s="19" t="str">
-        <f t="shared" si="12"/>
+        <f>B277</f>
         <v>HiGrad-HiElev</v>
       </c>
     </row>
@@ -10581,27 +10563,27 @@
       <c r="B278" t="s">
         <v>103</v>
       </c>
-      <c r="C278" t="s">
-        <v>150</v>
+      <c r="C278" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D278" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E278">
-        <v>3</v>
+        <v>450</v>
       </c>
       <c r="F278" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="G278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I278" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f>B278</f>
         <v>HiGrad-HiElev</v>
       </c>
       <c r="J278" s="19" t="str">
-        <f t="shared" si="12"/>
+        <f>B278</f>
         <v>HiGrad-HiElev</v>
       </c>
     </row>
@@ -10613,16 +10595,16 @@
         <v>103</v>
       </c>
       <c r="C279" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E279">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="E279" s="21">
+        <v>8</v>
       </c>
       <c r="F279" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="G279" t="b">
         <v>0</v>
@@ -10644,16 +10626,16 @@
         <v>103</v>
       </c>
       <c r="C280" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D280" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E280">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="F280" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="G280" t="b">
         <v>0</v>
@@ -10675,16 +10657,16 @@
         <v>103</v>
       </c>
       <c r="C281" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="D281" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E281">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="F281" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="G281" t="b">
         <v>0</v>
@@ -10706,16 +10688,16 @@
         <v>103</v>
       </c>
       <c r="C282" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D282" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E282">
-        <v>6</v>
+        <v>260</v>
       </c>
       <c r="F282" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="G282" t="b">
         <v>0</v>
@@ -10737,16 +10719,16 @@
         <v>103</v>
       </c>
       <c r="C283" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D283" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E283">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F283" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="G283" t="b">
         <v>0</v>
@@ -10768,16 +10750,16 @@
         <v>103</v>
       </c>
       <c r="C284" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D284" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E284">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F284" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G284" t="b">
         <v>0</v>
@@ -10799,19 +10781,19 @@
         <v>103</v>
       </c>
       <c r="C285" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D285" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E285">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="F285" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G285" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I285" s="19" t="str">
         <f t="shared" si="11"/>
@@ -10830,19 +10812,19 @@
         <v>103</v>
       </c>
       <c r="C286" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D286" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E286">
-        <v>450</v>
+        <v>8</v>
       </c>
       <c r="F286" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I286" s="19" t="str">
         <f t="shared" si="11"/>
@@ -11449,30 +11431,30 @@
       <c r="B306" t="s">
         <v>119</v>
       </c>
-      <c r="C306" t="s">
-        <v>150</v>
+      <c r="C306" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D306" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E306">
-        <v>0.7</v>
+        <v>600</v>
       </c>
       <c r="F306" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="G306" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H306" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I306" s="19" t="str">
-        <f t="shared" si="13"/>
+        <f>B306</f>
         <v>LoGrad-LoElev</v>
       </c>
       <c r="J306" s="19" t="str">
-        <f t="shared" si="14"/>
+        <f>B306</f>
         <v>LoGrad-LoElev</v>
       </c>
     </row>
@@ -11483,30 +11465,30 @@
       <c r="B307" t="s">
         <v>119</v>
       </c>
-      <c r="C307" t="s">
-        <v>138</v>
+      <c r="C307" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="D307" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E307">
-        <v>5</v>
+        <v>450</v>
       </c>
       <c r="F307" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="G307" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H307" t="s">
         <v>118</v>
       </c>
       <c r="I307" s="19" t="str">
-        <f t="shared" si="13"/>
+        <f>B307</f>
         <v>LoGrad-LoElev</v>
       </c>
       <c r="J307" s="19" t="str">
-        <f t="shared" si="14"/>
+        <f>B307</f>
         <v>LoGrad-LoElev</v>
       </c>
     </row>
@@ -11518,22 +11500,22 @@
         <v>119</v>
       </c>
       <c r="C308" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D308" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E308">
-        <v>260</v>
+        <v>0.7</v>
       </c>
       <c r="F308" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="G308" t="b">
         <v>0</v>
       </c>
       <c r="H308" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I308" s="19" t="str">
         <f t="shared" si="13"/>
@@ -11552,16 +11534,16 @@
         <v>119</v>
       </c>
       <c r="C309" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="D309" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E309">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="F309" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="G309" t="b">
         <v>0</v>
@@ -11586,16 +11568,16 @@
         <v>119</v>
       </c>
       <c r="C310" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D310" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E310">
-        <v>6</v>
+        <v>260</v>
       </c>
       <c r="F310" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="G310" t="b">
         <v>0</v>
@@ -11620,16 +11602,16 @@
         <v>119</v>
       </c>
       <c r="C311" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D311" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E311">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F311" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="G311" t="b">
         <v>0</v>
@@ -11654,16 +11636,16 @@
         <v>119</v>
       </c>
       <c r="C312" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D312" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E312">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F312" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G312" t="b">
         <v>0</v>
@@ -11688,19 +11670,19 @@
         <v>119</v>
       </c>
       <c r="C313" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D313" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E313">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="F313" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G313" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H313" t="s">
         <v>118</v>
@@ -11722,19 +11704,19 @@
         <v>119</v>
       </c>
       <c r="C314" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D314" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E314">
-        <v>450</v>
+        <v>8</v>
       </c>
       <c r="F314" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G314" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H314" t="s">
         <v>118</v>
@@ -12395,54 +12377,34 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J132" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
-  <conditionalFormatting sqref="C2:C66">
-    <cfRule type="expression" dxfId="10" priority="14">
+  <autoFilter ref="A1:J333" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <conditionalFormatting sqref="C2:C66 C162:C186 C248:C272">
+    <cfRule type="expression" dxfId="6" priority="14">
       <formula>$G2=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="5" priority="10">
       <formula>$G128=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G161">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+  <conditionalFormatting sqref="G2:G219 G220:H228 H229:H249 G229:G305 G306:H333">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54">
-    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H100:H127">
-    <cfRule type="cellIs" dxfId="6" priority="12" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C162:C186">
-    <cfRule type="expression" dxfId="5" priority="5">
-      <formula>$G162=FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C248:C272">
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>$G248=FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G162:G333">
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H174">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H220:H247 H306:H333">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C59034-4403-4FE3-B451-CCD686EA421E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32287257-120D-42CC-B5C9-DB96B204EA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29970" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="182">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -684,9 +684,6 @@
     <t>individuals, dominant 01, Large</t>
   </si>
   <si>
-    <t>pi_SCC</t>
-  </si>
-  <si>
     <t>species of conservation concern, present</t>
   </si>
   <si>
@@ -712,6 +709,12 @@
   </si>
   <si>
     <t>Move ni_total flags to top of each index_class</t>
+  </si>
+  <si>
+    <t>pi_scc</t>
+  </si>
+  <si>
+    <t>pi_SCC to pi_scc to match BioMonTools</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1355,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1378,7 +1381,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
-        <v>45695</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1617,12 +1620,20 @@
         <v>45695</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>180</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="15">
+        <v>45820</v>
+      </c>
+      <c r="B45" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Sheet2">
+  <sheetPr codeName="Sheet2" filterMode="1">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:J333"/>
@@ -1781,7 +1792,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -1813,7 +1824,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>125</v>
       </c>
@@ -1844,7 +1855,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -1875,7 +1886,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>125</v>
       </c>
@@ -1906,7 +1917,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>125</v>
       </c>
@@ -1937,7 +1948,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -1968,7 +1979,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -1999,7 +2010,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -2030,7 +2041,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>125</v>
       </c>
@@ -2061,7 +2072,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>125</v>
       </c>
@@ -2092,7 +2103,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -2123,7 +2134,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -2154,7 +2165,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>125</v>
       </c>
@@ -2185,7 +2196,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -2216,7 +2227,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>125</v>
       </c>
@@ -2247,7 +2258,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -2278,7 +2289,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>125</v>
       </c>
@@ -2309,7 +2320,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -2340,7 +2351,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -2371,7 +2382,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -2402,7 +2413,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>126</v>
       </c>
@@ -2434,7 +2445,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>126</v>
       </c>
@@ -2466,7 +2477,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>126</v>
       </c>
@@ -2498,7 +2509,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>126</v>
       </c>
@@ -2530,7 +2541,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>126</v>
       </c>
@@ -2561,7 +2572,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>126</v>
       </c>
@@ -2592,7 +2603,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>126</v>
       </c>
@@ -2623,7 +2634,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>126</v>
       </c>
@@ -2654,7 +2665,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>126</v>
       </c>
@@ -2685,7 +2696,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>126</v>
       </c>
@@ -2716,7 +2727,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>126</v>
       </c>
@@ -2748,7 +2759,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>126</v>
       </c>
@@ -2780,7 +2791,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>126</v>
       </c>
@@ -2812,7 +2823,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>126</v>
       </c>
@@ -2844,7 +2855,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>126</v>
       </c>
@@ -2875,7 +2886,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>126</v>
       </c>
@@ -2906,7 +2917,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>126</v>
       </c>
@@ -2937,7 +2948,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>126</v>
       </c>
@@ -2968,7 +2979,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>126</v>
       </c>
@@ -2999,7 +3010,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>126</v>
       </c>
@@ -3030,7 +3041,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -3061,7 +3072,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -3095,7 +3106,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -3126,7 +3137,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -3157,7 +3168,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -3188,7 +3199,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>53</v>
       </c>
@@ -3219,7 +3230,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -3250,7 +3261,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -3281,7 +3292,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -3312,7 +3323,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -3343,7 +3354,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -3374,7 +3385,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -3405,7 +3416,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -3439,7 +3450,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -3470,7 +3481,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -3501,7 +3512,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -3532,7 +3543,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>53</v>
       </c>
@@ -3563,7 +3574,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>53</v>
       </c>
@@ -3594,7 +3605,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -3625,7 +3636,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>53</v>
       </c>
@@ -3656,7 +3667,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -3690,7 +3701,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>53</v>
       </c>
@@ -3721,7 +3732,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>53</v>
       </c>
@@ -3752,7 +3763,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>53</v>
       </c>
@@ -3783,7 +3794,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>53</v>
       </c>
@@ -3814,7 +3825,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>53</v>
       </c>
@@ -3848,7 +3859,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>53</v>
       </c>
@@ -3882,7 +3893,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>53</v>
       </c>
@@ -3916,7 +3927,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>53</v>
       </c>
@@ -3950,7 +3961,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>53</v>
       </c>
@@ -3981,7 +3992,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>53</v>
       </c>
@@ -4012,7 +4023,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>53</v>
       </c>
@@ -4043,7 +4054,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>53</v>
       </c>
@@ -4074,7 +4085,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>53</v>
       </c>
@@ -4105,7 +4116,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>53</v>
       </c>
@@ -4136,7 +4147,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>53</v>
       </c>
@@ -4167,7 +4178,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -4198,7 +4209,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>53</v>
       </c>
@@ -4229,7 +4240,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>53</v>
       </c>
@@ -4260,7 +4271,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>53</v>
       </c>
@@ -4291,7 +4302,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>53</v>
       </c>
@@ -4322,7 +4333,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>53</v>
       </c>
@@ -4353,7 +4364,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>53</v>
       </c>
@@ -4384,7 +4395,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>53</v>
       </c>
@@ -4415,7 +4426,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>53</v>
       </c>
@@ -4446,7 +4457,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>53</v>
       </c>
@@ -4477,7 +4488,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>53</v>
       </c>
@@ -4508,7 +4519,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>53</v>
       </c>
@@ -4539,7 +4550,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>53</v>
       </c>
@@ -4570,7 +4581,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>53</v>
       </c>
@@ -4601,7 +4612,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>53</v>
       </c>
@@ -4632,7 +4643,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>53</v>
       </c>
@@ -4663,7 +4674,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>53</v>
       </c>
@@ -4694,7 +4705,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>53</v>
       </c>
@@ -4725,7 +4736,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>53</v>
       </c>
@@ -4756,7 +4767,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>53</v>
       </c>
@@ -4787,7 +4798,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>53</v>
       </c>
@@ -4818,7 +4829,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>53</v>
       </c>
@@ -4849,7 +4860,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>53</v>
       </c>
@@ -4883,7 +4894,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>53</v>
       </c>
@@ -4917,7 +4928,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>53</v>
       </c>
@@ -4951,7 +4962,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>53</v>
       </c>
@@ -4985,7 +4996,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>53</v>
       </c>
@@ -5019,7 +5030,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>53</v>
       </c>
@@ -5053,7 +5064,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>53</v>
       </c>
@@ -5087,7 +5098,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>53</v>
       </c>
@@ -5121,7 +5132,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>53</v>
       </c>
@@ -5155,7 +5166,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>53</v>
       </c>
@@ -5189,7 +5200,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>53</v>
       </c>
@@ -5223,7 +5234,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>53</v>
       </c>
@@ -5257,7 +5268,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>53</v>
       </c>
@@ -5291,7 +5302,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>53</v>
       </c>
@@ -5325,7 +5336,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>53</v>
       </c>
@@ -5359,7 +5370,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>53</v>
       </c>
@@ -5393,7 +5404,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>53</v>
       </c>
@@ -5427,7 +5438,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>53</v>
       </c>
@@ -5461,7 +5472,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>53</v>
       </c>
@@ -5495,7 +5506,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>53</v>
       </c>
@@ -5529,7 +5540,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>53</v>
       </c>
@@ -5563,7 +5574,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>53</v>
       </c>
@@ -5597,7 +5608,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>53</v>
       </c>
@@ -5631,7 +5642,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>53</v>
       </c>
@@ -5665,7 +5676,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>53</v>
       </c>
@@ -5699,7 +5710,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>53</v>
       </c>
@@ -5733,7 +5744,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>53</v>
       </c>
@@ -5767,7 +5778,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>53</v>
       </c>
@@ -5801,7 +5812,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>123</v>
       </c>
@@ -5832,7 +5843,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>123</v>
       </c>
@@ -5866,7 +5877,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>123</v>
       </c>
@@ -5900,7 +5911,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>123</v>
       </c>
@@ -5934,7 +5945,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>123</v>
       </c>
@@ -5968,7 +5979,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>53</v>
       </c>
@@ -6002,7 +6013,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>53</v>
       </c>
@@ -6036,7 +6047,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>53</v>
       </c>
@@ -6070,7 +6081,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>154</v>
       </c>
@@ -6104,7 +6115,7 @@
         <v>CREMP_Keys</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>154</v>
       </c>
@@ -6138,7 +6149,7 @@
         <v>NOT_CREMP_Keys</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>162</v>
       </c>
@@ -6167,7 +6178,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>162</v>
       </c>
@@ -6196,7 +6207,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>162</v>
       </c>
@@ -6225,7 +6236,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>162</v>
       </c>
@@ -6254,7 +6265,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>162</v>
       </c>
@@ -6283,7 +6294,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>162</v>
       </c>
@@ -6312,7 +6323,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>162</v>
       </c>
@@ -6341,7 +6352,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>162</v>
       </c>
@@ -6370,7 +6381,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>162</v>
       </c>
@@ -6399,7 +6410,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>162</v>
       </c>
@@ -6428,7 +6439,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>162</v>
       </c>
@@ -6457,7 +6468,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>162</v>
       </c>
@@ -6494,7 +6505,7 @@
         <v>163</v>
       </c>
       <c r="C150" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D150" t="s">
         <v>15</v>
@@ -6503,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="F150" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G150" t="b">
         <v>1</v>
@@ -6523,7 +6534,7 @@
         <v>164</v>
       </c>
       <c r="C151" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D151" t="s">
         <v>15</v>
@@ -6532,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="F151" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G151" t="b">
         <v>1</v>
@@ -6552,7 +6563,7 @@
         <v>165</v>
       </c>
       <c r="C152" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D152" t="s">
         <v>15</v>
@@ -6561,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="F152" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G152" t="b">
         <v>1</v>
@@ -6581,7 +6592,7 @@
         <v>166</v>
       </c>
       <c r="C153" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D153" t="s">
         <v>15</v>
@@ -6590,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="F153" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G153" t="b">
         <v>1</v>
@@ -6602,7 +6613,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>162</v>
       </c>
@@ -6610,7 +6621,7 @@
         <v>163</v>
       </c>
       <c r="C154" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D154" t="s">
         <v>15</v>
@@ -6619,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="F154" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G154" t="b">
         <v>1</v>
@@ -6631,7 +6642,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -6639,7 +6650,7 @@
         <v>164</v>
       </c>
       <c r="C155" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D155" t="s">
         <v>15</v>
@@ -6648,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="F155" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G155" t="b">
         <v>1</v>
@@ -6660,7 +6671,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>162</v>
       </c>
@@ -6668,7 +6679,7 @@
         <v>165</v>
       </c>
       <c r="C156" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D156" t="s">
         <v>15</v>
@@ -6677,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="F156" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G156" t="b">
         <v>1</v>
@@ -6689,7 +6700,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>162</v>
       </c>
@@ -6697,7 +6708,7 @@
         <v>166</v>
       </c>
       <c r="C157" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D157" t="s">
         <v>15</v>
@@ -6706,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="F157" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G157" t="b">
         <v>1</v>
@@ -6718,7 +6729,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>162</v>
       </c>
@@ -6726,7 +6737,7 @@
         <v>163</v>
       </c>
       <c r="C158" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D158" t="s">
         <v>15</v>
@@ -6735,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="F158" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G158" t="b">
         <v>1</v>
@@ -6747,7 +6758,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>162</v>
       </c>
@@ -6755,7 +6766,7 @@
         <v>164</v>
       </c>
       <c r="C159" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D159" t="s">
         <v>15</v>
@@ -6764,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="F159" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G159" t="b">
         <v>1</v>
@@ -6776,7 +6787,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -6784,7 +6795,7 @@
         <v>165</v>
       </c>
       <c r="C160" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D160" t="s">
         <v>15</v>
@@ -6793,7 +6804,7 @@
         <v>0</v>
       </c>
       <c r="F160" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G160" t="b">
         <v>1</v>
@@ -6805,7 +6816,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>162</v>
       </c>
@@ -6813,7 +6824,7 @@
         <v>166</v>
       </c>
       <c r="C161" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D161" t="s">
         <v>15</v>
@@ -6822,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="F161" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G161" t="b">
         <v>1</v>
@@ -6834,9 +6845,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B162" t="s">
         <v>54</v>
@@ -6865,9 +6876,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B163" t="s">
         <v>54</v>
@@ -6896,9 +6907,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B164" t="s">
         <v>54</v>
@@ -6927,9 +6938,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B165" t="s">
         <v>54</v>
@@ -6961,9 +6972,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B166" t="s">
         <v>54</v>
@@ -6992,9 +7003,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B167" t="s">
         <v>54</v>
@@ -7023,9 +7034,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B168" t="s">
         <v>54</v>
@@ -7054,9 +7065,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B169" t="s">
         <v>54</v>
@@ -7085,9 +7096,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B170" t="s">
         <v>54</v>
@@ -7116,9 +7127,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B171" t="s">
         <v>54</v>
@@ -7147,9 +7158,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B172" t="s">
         <v>54</v>
@@ -7178,9 +7189,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B173" t="s">
         <v>54</v>
@@ -7209,9 +7220,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B174" t="s">
         <v>54</v>
@@ -7243,9 +7254,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B175" t="s">
         <v>54</v>
@@ -7274,9 +7285,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B176" t="s">
         <v>54</v>
@@ -7305,9 +7316,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B177" t="s">
         <v>54</v>
@@ -7336,9 +7347,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B178" t="s">
         <v>54</v>
@@ -7367,9 +7378,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B179" t="s">
         <v>54</v>
@@ -7398,9 +7409,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B180" t="s">
         <v>54</v>
@@ -7429,9 +7440,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B181" t="s">
         <v>54</v>
@@ -7460,9 +7471,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B182" t="s">
         <v>54</v>
@@ -7494,9 +7505,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B183" t="s">
         <v>54</v>
@@ -7525,9 +7536,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B184" t="s">
         <v>54</v>
@@ -7556,9 +7567,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B185" t="s">
         <v>54</v>
@@ -7587,9 +7598,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B186" t="s">
         <v>54</v>
@@ -7618,9 +7629,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B187" t="s">
         <v>54</v>
@@ -7652,9 +7663,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B188" t="s">
         <v>54</v>
@@ -7686,9 +7697,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B189" t="s">
         <v>54</v>
@@ -7720,9 +7731,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B190" t="s">
         <v>54</v>
@@ -7754,9 +7765,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B191" t="s">
         <v>103</v>
@@ -7785,9 +7796,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B192" t="s">
         <v>103</v>
@@ -7816,9 +7827,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B193" t="s">
         <v>103</v>
@@ -7847,9 +7858,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B194" t="s">
         <v>103</v>
@@ -7878,9 +7889,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B195" t="s">
         <v>103</v>
@@ -7909,9 +7920,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B196" t="s">
         <v>103</v>
@@ -7940,9 +7951,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B197" t="s">
         <v>103</v>
@@ -7971,9 +7982,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B198" t="s">
         <v>103</v>
@@ -8002,9 +8013,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B199" t="s">
         <v>103</v>
@@ -8033,9 +8044,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B200" t="s">
         <v>103</v>
@@ -8064,9 +8075,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B201" t="s">
         <v>103</v>
@@ -8095,9 +8106,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B202" t="s">
         <v>103</v>
@@ -8126,9 +8137,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B203" t="s">
         <v>103</v>
@@ -8157,9 +8168,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B204" t="s">
         <v>103</v>
@@ -8188,9 +8199,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B205" t="s">
         <v>103</v>
@@ -8219,9 +8230,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B206" t="s">
         <v>103</v>
@@ -8250,9 +8261,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B207" t="s">
         <v>103</v>
@@ -8281,9 +8292,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B208" t="s">
         <v>103</v>
@@ -8312,9 +8323,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B209" t="s">
         <v>103</v>
@@ -8343,9 +8354,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B210" t="s">
         <v>103</v>
@@ -8374,9 +8385,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B211" t="s">
         <v>103</v>
@@ -8405,9 +8416,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B212" t="s">
         <v>103</v>
@@ -8436,9 +8447,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B213" t="s">
         <v>103</v>
@@ -8467,9 +8478,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B214" t="s">
         <v>103</v>
@@ -8498,9 +8509,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B215" t="s">
         <v>103</v>
@@ -8529,9 +8540,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B216" t="s">
         <v>103</v>
@@ -8560,9 +8571,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B217" t="s">
         <v>103</v>
@@ -8591,9 +8602,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B218" t="s">
         <v>103</v>
@@ -8622,9 +8633,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B219" t="s">
         <v>103</v>
@@ -8653,9 +8664,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B220" t="s">
         <v>119</v>
@@ -8687,9 +8698,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B221" t="s">
         <v>119</v>
@@ -8721,9 +8732,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B222" t="s">
         <v>119</v>
@@ -8755,9 +8766,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B223" t="s">
         <v>119</v>
@@ -8789,9 +8800,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B224" t="s">
         <v>119</v>
@@ -8823,9 +8834,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B225" t="s">
         <v>119</v>
@@ -8857,9 +8868,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B226" t="s">
         <v>119</v>
@@ -8891,9 +8902,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B227" t="s">
         <v>119</v>
@@ -8925,9 +8936,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B228" t="s">
         <v>119</v>
@@ -8959,9 +8970,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B229" t="s">
         <v>119</v>
@@ -8993,9 +9004,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B230" t="s">
         <v>119</v>
@@ -9027,9 +9038,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B231" t="s">
         <v>119</v>
@@ -9061,9 +9072,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B232" t="s">
         <v>119</v>
@@ -9095,9 +9106,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B233" t="s">
         <v>119</v>
@@ -9129,9 +9140,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B234" t="s">
         <v>119</v>
@@ -9163,9 +9174,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B235" t="s">
         <v>119</v>
@@ -9197,9 +9208,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B236" t="s">
         <v>119</v>
@@ -9231,9 +9242,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B237" t="s">
         <v>119</v>
@@ -9265,9 +9276,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B238" t="s">
         <v>119</v>
@@ -9299,9 +9310,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B239" t="s">
         <v>119</v>
@@ -9333,9 +9344,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B240" t="s">
         <v>119</v>
@@ -9367,9 +9378,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B241" t="s">
         <v>119</v>
@@ -9401,9 +9412,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B242" t="s">
         <v>119</v>
@@ -9435,9 +9446,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B243" t="s">
         <v>119</v>
@@ -9469,9 +9480,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B244" t="s">
         <v>119</v>
@@ -9503,9 +9514,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B245" t="s">
         <v>119</v>
@@ -9537,9 +9548,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B246" t="s">
         <v>119</v>
@@ -9571,9 +9582,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B247" t="s">
         <v>119</v>
@@ -9605,9 +9616,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B248" t="s">
         <v>54</v>
@@ -9636,9 +9647,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B249" t="s">
         <v>54</v>
@@ -9667,9 +9678,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B250" t="s">
         <v>54</v>
@@ -9698,9 +9709,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B251" t="s">
         <v>54</v>
@@ -9732,9 +9743,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B252" t="s">
         <v>54</v>
@@ -9763,9 +9774,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B253" t="s">
         <v>54</v>
@@ -9794,9 +9805,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B254" t="s">
         <v>54</v>
@@ -9825,9 +9836,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B255" t="s">
         <v>54</v>
@@ -9856,9 +9867,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B256" t="s">
         <v>54</v>
@@ -9887,9 +9898,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B257" t="s">
         <v>54</v>
@@ -9918,9 +9929,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B258" t="s">
         <v>54</v>
@@ -9949,9 +9960,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B259" t="s">
         <v>54</v>
@@ -9980,9 +9991,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B260" t="s">
         <v>54</v>
@@ -10014,9 +10025,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B261" t="s">
         <v>54</v>
@@ -10045,9 +10056,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B262" t="s">
         <v>54</v>
@@ -10076,9 +10087,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B263" t="s">
         <v>54</v>
@@ -10107,9 +10118,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B264" t="s">
         <v>54</v>
@@ -10138,9 +10149,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B265" t="s">
         <v>54</v>
@@ -10169,9 +10180,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B266" t="s">
         <v>54</v>
@@ -10200,9 +10211,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B267" t="s">
         <v>54</v>
@@ -10231,9 +10242,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B268" t="s">
         <v>54</v>
@@ -10265,9 +10276,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B269" t="s">
         <v>54</v>
@@ -10296,9 +10307,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B270" t="s">
         <v>54</v>
@@ -10327,9 +10338,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B271" t="s">
         <v>54</v>
@@ -10358,9 +10369,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B272" t="s">
         <v>54</v>
@@ -10389,9 +10400,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B273" t="s">
         <v>54</v>
@@ -10423,9 +10434,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B274" t="s">
         <v>54</v>
@@ -10457,9 +10468,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B275" t="s">
         <v>54</v>
@@ -10491,9 +10502,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B276" t="s">
         <v>54</v>
@@ -10525,9 +10536,9 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B277" t="s">
         <v>103</v>
@@ -10556,9 +10567,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B278" t="s">
         <v>103</v>
@@ -10587,9 +10598,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B279" t="s">
         <v>103</v>
@@ -10618,9 +10629,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B280" t="s">
         <v>103</v>
@@ -10649,9 +10660,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B281" t="s">
         <v>103</v>
@@ -10680,9 +10691,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B282" t="s">
         <v>103</v>
@@ -10711,9 +10722,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B283" t="s">
         <v>103</v>
@@ -10742,9 +10753,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B284" t="s">
         <v>103</v>
@@ -10773,9 +10784,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B285" t="s">
         <v>103</v>
@@ -10804,9 +10815,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B286" t="s">
         <v>103</v>
@@ -10835,9 +10846,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B287" t="s">
         <v>103</v>
@@ -10866,9 +10877,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B288" t="s">
         <v>103</v>
@@ -10897,9 +10908,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B289" t="s">
         <v>103</v>
@@ -10928,9 +10939,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B290" t="s">
         <v>103</v>
@@ -10959,9 +10970,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B291" t="s">
         <v>103</v>
@@ -10990,9 +11001,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B292" t="s">
         <v>103</v>
@@ -11021,9 +11032,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B293" t="s">
         <v>103</v>
@@ -11052,9 +11063,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B294" t="s">
         <v>103</v>
@@ -11083,9 +11094,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B295" t="s">
         <v>103</v>
@@ -11114,9 +11125,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B296" t="s">
         <v>103</v>
@@ -11145,9 +11156,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B297" t="s">
         <v>103</v>
@@ -11176,9 +11187,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B298" t="s">
         <v>103</v>
@@ -11207,9 +11218,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B299" t="s">
         <v>103</v>
@@ -11238,9 +11249,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B300" t="s">
         <v>103</v>
@@ -11269,9 +11280,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B301" t="s">
         <v>103</v>
@@ -11300,9 +11311,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B302" t="s">
         <v>103</v>
@@ -11331,9 +11342,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B303" t="s">
         <v>103</v>
@@ -11362,9 +11373,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B304" t="s">
         <v>103</v>
@@ -11393,9 +11404,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B305" t="s">
         <v>103</v>
@@ -11424,9 +11435,9 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B306" t="s">
         <v>119</v>
@@ -11458,9 +11469,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B307" t="s">
         <v>119</v>
@@ -11492,9 +11503,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B308" t="s">
         <v>119</v>
@@ -11526,9 +11537,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B309" t="s">
         <v>119</v>
@@ -11560,9 +11571,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B310" t="s">
         <v>119</v>
@@ -11594,9 +11605,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B311" t="s">
         <v>119</v>
@@ -11628,9 +11639,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B312" t="s">
         <v>119</v>
@@ -11662,9 +11673,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B313" t="s">
         <v>119</v>
@@ -11696,9 +11707,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B314" t="s">
         <v>119</v>
@@ -11730,9 +11741,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B315" t="s">
         <v>119</v>
@@ -11764,9 +11775,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B316" t="s">
         <v>119</v>
@@ -11798,9 +11809,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B317" t="s">
         <v>119</v>
@@ -11832,9 +11843,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B318" t="s">
         <v>119</v>
@@ -11866,9 +11877,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B319" t="s">
         <v>119</v>
@@ -11900,9 +11911,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B320" t="s">
         <v>119</v>
@@ -11934,9 +11945,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B321" t="s">
         <v>119</v>
@@ -11968,9 +11979,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B322" t="s">
         <v>119</v>
@@ -12002,9 +12013,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B323" t="s">
         <v>119</v>
@@ -12036,9 +12047,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B324" t="s">
         <v>119</v>
@@ -12070,9 +12081,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B325" t="s">
         <v>119</v>
@@ -12104,9 +12115,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B326" t="s">
         <v>119</v>
@@ -12138,9 +12149,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B327" t="s">
         <v>119</v>
@@ -12172,9 +12183,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B328" t="s">
         <v>119</v>
@@ -12206,9 +12217,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B329" t="s">
         <v>119</v>
@@ -12240,9 +12251,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B330" t="s">
         <v>119</v>
@@ -12274,9 +12285,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B331" t="s">
         <v>119</v>
@@ -12308,9 +12319,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B332" t="s">
         <v>119</v>
@@ -12342,9 +12353,9 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B333" t="s">
         <v>119</v>
@@ -12377,7 +12388,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J333" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:J333" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="pi_SCC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="C2:C66 C162:C186 C248:C272">
     <cfRule type="expression" dxfId="6" priority="14">
       <formula>$G2=FALSE</formula>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32287257-120D-42CC-B5C9-DB96B204EA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C229CC0-837E-40A6-A6C1-5190746F7658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29970" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Flags" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$363</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="202">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -716,12 +716,72 @@
   <si>
     <t>pi_SCC to pi_scc to match BioMonTools</t>
   </si>
+  <si>
+    <t>Add BCG GP flags</t>
+  </si>
+  <si>
+    <t>NE_Bugs_BCG</t>
+  </si>
+  <si>
+    <t>CGP_mNRSA</t>
+  </si>
+  <si>
+    <t>individuals, very low</t>
+  </si>
+  <si>
+    <t>target 500</t>
+  </si>
+  <si>
+    <t>individuals, low</t>
+  </si>
+  <si>
+    <t>nt_total</t>
+  </si>
+  <si>
+    <t>total taxa, low</t>
+  </si>
+  <si>
+    <t>individuals dominated by 2 taxa</t>
+  </si>
+  <si>
+    <t>Coleoptera absent</t>
+  </si>
+  <si>
+    <t>Ephemeroptera absent</t>
+  </si>
+  <si>
+    <t>nt_Odon</t>
+  </si>
+  <si>
+    <t>Odonata absent</t>
+  </si>
+  <si>
+    <t>Trichoptera absent</t>
+  </si>
+  <si>
+    <t>pt_NonIns_BCG_att456</t>
+  </si>
+  <si>
+    <t>high proportion of tolerant or non-native non-insect taxa</t>
+  </si>
+  <si>
+    <t>pi_airbreath</t>
+  </si>
+  <si>
+    <t>high proportion of air breather individuals</t>
+  </si>
+  <si>
+    <t>RifRocky_mNRSA</t>
+  </si>
+  <si>
+    <t>WCBP_mNRSA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -825,6 +885,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -913,7 +979,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
@@ -962,6 +1028,21 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
@@ -970,7 +1051,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1057,7 +1148,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Worksheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descriptions"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="7">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="8">
       <calculatedColumnFormula>HYPERLINK(FileName&amp;A16&amp;"!A1",A16)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1355,7 +1446,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1634,6 +1725,12 @@
       </c>
       <c r="B45" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="22"/>
+      <c r="B46" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -1745,10 +1842,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Sheet2" filterMode="1">
+  <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J333"/>
+  <dimension ref="A1:J363"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -1792,7 +1889,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -1824,7 +1921,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>125</v>
       </c>
@@ -1855,7 +1952,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -1886,7 +1983,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>125</v>
       </c>
@@ -1917,7 +2014,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>125</v>
       </c>
@@ -1948,7 +2045,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -1979,7 +2076,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -2010,7 +2107,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -2041,7 +2138,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>125</v>
       </c>
@@ -2072,7 +2169,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>125</v>
       </c>
@@ -2103,7 +2200,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -2134,7 +2231,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -2165,7 +2262,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>125</v>
       </c>
@@ -2196,7 +2293,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -2227,7 +2324,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>125</v>
       </c>
@@ -2258,7 +2355,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -2289,7 +2386,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>125</v>
       </c>
@@ -2320,7 +2417,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -2351,7 +2448,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -2382,7 +2479,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -2413,7 +2510,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>126</v>
       </c>
@@ -2445,7 +2542,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>126</v>
       </c>
@@ -2477,7 +2574,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>126</v>
       </c>
@@ -2509,7 +2606,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>126</v>
       </c>
@@ -2541,7 +2638,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>126</v>
       </c>
@@ -2572,7 +2669,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>126</v>
       </c>
@@ -2603,7 +2700,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>126</v>
       </c>
@@ -2634,7 +2731,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>126</v>
       </c>
@@ -2665,7 +2762,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>126</v>
       </c>
@@ -2696,7 +2793,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>126</v>
       </c>
@@ -2727,7 +2824,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>126</v>
       </c>
@@ -2759,7 +2856,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>126</v>
       </c>
@@ -2791,7 +2888,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>126</v>
       </c>
@@ -2823,7 +2920,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>126</v>
       </c>
@@ -2855,7 +2952,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>126</v>
       </c>
@@ -2886,7 +2983,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>126</v>
       </c>
@@ -2917,7 +3014,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>126</v>
       </c>
@@ -2948,7 +3045,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>126</v>
       </c>
@@ -2979,7 +3076,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>126</v>
       </c>
@@ -3010,7 +3107,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>126</v>
       </c>
@@ -3041,7 +3138,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -3072,7 +3169,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -3106,7 +3203,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -3137,7 +3234,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -3168,7 +3265,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -3199,7 +3296,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>53</v>
       </c>
@@ -3230,7 +3327,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -3261,7 +3358,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -3292,7 +3389,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -3323,7 +3420,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -3354,7 +3451,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -3385,7 +3482,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -3416,7 +3513,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -3450,7 +3547,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -3481,7 +3578,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -3512,7 +3609,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -3543,7 +3640,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>53</v>
       </c>
@@ -3574,7 +3671,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>53</v>
       </c>
@@ -3605,7 +3702,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -3636,7 +3733,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>53</v>
       </c>
@@ -3667,7 +3764,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -3701,7 +3798,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>53</v>
       </c>
@@ -3732,7 +3829,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>53</v>
       </c>
@@ -3763,7 +3860,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>53</v>
       </c>
@@ -3794,7 +3891,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>53</v>
       </c>
@@ -3825,7 +3922,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>53</v>
       </c>
@@ -3859,7 +3956,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>53</v>
       </c>
@@ -3893,7 +3990,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>53</v>
       </c>
@@ -3927,7 +4024,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>53</v>
       </c>
@@ -3961,7 +4058,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>53</v>
       </c>
@@ -3992,7 +4089,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>53</v>
       </c>
@@ -4023,7 +4120,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>53</v>
       </c>
@@ -4054,7 +4151,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>53</v>
       </c>
@@ -4085,7 +4182,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>53</v>
       </c>
@@ -4116,7 +4213,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>53</v>
       </c>
@@ -4147,7 +4244,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>53</v>
       </c>
@@ -4178,7 +4275,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -4209,7 +4306,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>53</v>
       </c>
@@ -4240,7 +4337,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>53</v>
       </c>
@@ -4271,7 +4368,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>53</v>
       </c>
@@ -4302,7 +4399,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>53</v>
       </c>
@@ -4333,7 +4430,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>53</v>
       </c>
@@ -4364,7 +4461,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>53</v>
       </c>
@@ -4395,7 +4492,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>53</v>
       </c>
@@ -4426,7 +4523,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>53</v>
       </c>
@@ -4457,7 +4554,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>53</v>
       </c>
@@ -4488,7 +4585,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>53</v>
       </c>
@@ -4519,7 +4616,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>53</v>
       </c>
@@ -4550,7 +4647,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>53</v>
       </c>
@@ -4581,7 +4678,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>53</v>
       </c>
@@ -4612,7 +4709,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>53</v>
       </c>
@@ -4643,7 +4740,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>53</v>
       </c>
@@ -4674,7 +4771,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>53</v>
       </c>
@@ -4705,7 +4802,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>53</v>
       </c>
@@ -4736,7 +4833,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>53</v>
       </c>
@@ -4767,7 +4864,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>53</v>
       </c>
@@ -4798,7 +4895,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>53</v>
       </c>
@@ -4829,7 +4926,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>53</v>
       </c>
@@ -4860,7 +4957,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>53</v>
       </c>
@@ -4894,7 +4991,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>53</v>
       </c>
@@ -4928,7 +5025,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>53</v>
       </c>
@@ -4962,7 +5059,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>53</v>
       </c>
@@ -4996,7 +5093,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>53</v>
       </c>
@@ -5030,7 +5127,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>53</v>
       </c>
@@ -5064,7 +5161,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>53</v>
       </c>
@@ -5098,7 +5195,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>53</v>
       </c>
@@ -5132,7 +5229,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>53</v>
       </c>
@@ -5166,7 +5263,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>53</v>
       </c>
@@ -5200,7 +5297,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>53</v>
       </c>
@@ -5234,7 +5331,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>53</v>
       </c>
@@ -5268,7 +5365,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>53</v>
       </c>
@@ -5302,7 +5399,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>53</v>
       </c>
@@ -5336,7 +5433,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>53</v>
       </c>
@@ -5370,7 +5467,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>53</v>
       </c>
@@ -5404,7 +5501,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>53</v>
       </c>
@@ -5438,7 +5535,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>53</v>
       </c>
@@ -5472,7 +5569,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>53</v>
       </c>
@@ -5506,7 +5603,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>53</v>
       </c>
@@ -5540,7 +5637,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>53</v>
       </c>
@@ -5574,7 +5671,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>53</v>
       </c>
@@ -5608,7 +5705,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>53</v>
       </c>
@@ -5642,7 +5739,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>53</v>
       </c>
@@ -5676,7 +5773,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>53</v>
       </c>
@@ -5710,7 +5807,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>53</v>
       </c>
@@ -5744,7 +5841,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>53</v>
       </c>
@@ -5778,7 +5875,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>53</v>
       </c>
@@ -5812,7 +5909,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>123</v>
       </c>
@@ -5843,7 +5940,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>123</v>
       </c>
@@ -5877,7 +5974,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>123</v>
       </c>
@@ -5911,7 +6008,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>123</v>
       </c>
@@ -5945,7 +6042,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>123</v>
       </c>
@@ -5979,7 +6076,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>53</v>
       </c>
@@ -6013,7 +6110,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>53</v>
       </c>
@@ -6047,7 +6144,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>53</v>
       </c>
@@ -6081,7 +6178,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>154</v>
       </c>
@@ -6115,7 +6212,7 @@
         <v>CREMP_Keys</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>154</v>
       </c>
@@ -6149,7 +6246,7 @@
         <v>NOT_CREMP_Keys</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>162</v>
       </c>
@@ -6178,7 +6275,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>162</v>
       </c>
@@ -6207,7 +6304,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>162</v>
       </c>
@@ -6236,7 +6333,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>162</v>
       </c>
@@ -6265,7 +6362,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>162</v>
       </c>
@@ -6294,7 +6391,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>162</v>
       </c>
@@ -6323,7 +6420,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>162</v>
       </c>
@@ -6352,7 +6449,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>162</v>
       </c>
@@ -6381,7 +6478,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>162</v>
       </c>
@@ -6410,7 +6507,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>162</v>
       </c>
@@ -6439,7 +6536,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>162</v>
       </c>
@@ -6468,7 +6565,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>162</v>
       </c>
@@ -6613,7 +6710,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>162</v>
       </c>
@@ -6642,7 +6739,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -6671,7 +6768,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>162</v>
       </c>
@@ -6700,7 +6797,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>162</v>
       </c>
@@ -6729,7 +6826,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>162</v>
       </c>
@@ -6758,7 +6855,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>162</v>
       </c>
@@ -6787,7 +6884,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -6816,7 +6913,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>162</v>
       </c>
@@ -6845,7 +6942,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="25" t="s">
         <v>177</v>
       </c>
@@ -6876,7 +6973,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="25" t="s">
         <v>177</v>
       </c>
@@ -6907,7 +7004,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="25" t="s">
         <v>177</v>
       </c>
@@ -6938,7 +7035,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="25" t="s">
         <v>177</v>
       </c>
@@ -6972,7 +7069,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
         <v>177</v>
       </c>
@@ -7003,7 +7100,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
         <v>177</v>
       </c>
@@ -7034,7 +7131,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="25" t="s">
         <v>177</v>
       </c>
@@ -7065,7 +7162,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
         <v>177</v>
       </c>
@@ -7096,7 +7193,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
         <v>177</v>
       </c>
@@ -7127,7 +7224,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
         <v>177</v>
       </c>
@@ -7158,7 +7255,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="25" t="s">
         <v>177</v>
       </c>
@@ -7189,7 +7286,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="25" t="s">
         <v>177</v>
       </c>
@@ -7220,7 +7317,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="25" t="s">
         <v>177</v>
       </c>
@@ -7254,7 +7351,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="25" t="s">
         <v>177</v>
       </c>
@@ -7285,7 +7382,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="25" t="s">
         <v>177</v>
       </c>
@@ -7316,7 +7413,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="25" t="s">
         <v>177</v>
       </c>
@@ -7347,7 +7444,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="25" t="s">
         <v>177</v>
       </c>
@@ -7378,7 +7475,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="25" t="s">
         <v>177</v>
       </c>
@@ -7409,7 +7506,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="25" t="s">
         <v>177</v>
       </c>
@@ -7440,7 +7537,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="25" t="s">
         <v>177</v>
       </c>
@@ -7471,7 +7568,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="25" t="s">
         <v>177</v>
       </c>
@@ -7505,7 +7602,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="25" t="s">
         <v>177</v>
       </c>
@@ -7536,7 +7633,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="25" t="s">
         <v>177</v>
       </c>
@@ -7567,7 +7664,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="25" t="s">
         <v>177</v>
       </c>
@@ -7598,7 +7695,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="25" t="s">
         <v>177</v>
       </c>
@@ -7629,7 +7726,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="25" t="s">
         <v>177</v>
       </c>
@@ -7663,7 +7760,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="25" t="s">
         <v>177</v>
       </c>
@@ -7697,7 +7794,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="25" t="s">
         <v>177</v>
       </c>
@@ -7731,7 +7828,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="25" t="s">
         <v>177</v>
       </c>
@@ -7765,7 +7862,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="25" t="s">
         <v>177</v>
       </c>
@@ -7796,7 +7893,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="25" t="s">
         <v>177</v>
       </c>
@@ -7827,7 +7924,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="25" t="s">
         <v>177</v>
       </c>
@@ -7858,7 +7955,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="25" t="s">
         <v>177</v>
       </c>
@@ -7889,7 +7986,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="25" t="s">
         <v>177</v>
       </c>
@@ -7920,7 +8017,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="25" t="s">
         <v>177</v>
       </c>
@@ -7951,7 +8048,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="25" t="s">
         <v>177</v>
       </c>
@@ -7982,7 +8079,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="25" t="s">
         <v>177</v>
       </c>
@@ -8013,7 +8110,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="25" t="s">
         <v>177</v>
       </c>
@@ -8044,7 +8141,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="25" t="s">
         <v>177</v>
       </c>
@@ -8075,7 +8172,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="25" t="s">
         <v>177</v>
       </c>
@@ -8106,7 +8203,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="25" t="s">
         <v>177</v>
       </c>
@@ -8137,7 +8234,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="25" t="s">
         <v>177</v>
       </c>
@@ -8168,7 +8265,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="25" t="s">
         <v>177</v>
       </c>
@@ -8199,7 +8296,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="25" t="s">
         <v>177</v>
       </c>
@@ -8230,7 +8327,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="25" t="s">
         <v>177</v>
       </c>
@@ -8261,7 +8358,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="25" t="s">
         <v>177</v>
       </c>
@@ -8292,7 +8389,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="25" t="s">
         <v>177</v>
       </c>
@@ -8323,7 +8420,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="25" t="s">
         <v>177</v>
       </c>
@@ -8354,7 +8451,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="25" t="s">
         <v>177</v>
       </c>
@@ -8385,7 +8482,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="25" t="s">
         <v>177</v>
       </c>
@@ -8416,7 +8513,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="25" t="s">
         <v>177</v>
       </c>
@@ -8447,7 +8544,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="25" t="s">
         <v>177</v>
       </c>
@@ -8478,7 +8575,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="25" t="s">
         <v>177</v>
       </c>
@@ -8509,7 +8606,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="25" t="s">
         <v>177</v>
       </c>
@@ -8540,7 +8637,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="25" t="s">
         <v>177</v>
       </c>
@@ -8571,7 +8668,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="25" t="s">
         <v>177</v>
       </c>
@@ -8602,7 +8699,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="25" t="s">
         <v>177</v>
       </c>
@@ -8633,7 +8730,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="25" t="s">
         <v>177</v>
       </c>
@@ -8664,7 +8761,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="25" t="s">
         <v>177</v>
       </c>
@@ -8698,7 +8795,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="25" t="s">
         <v>177</v>
       </c>
@@ -8732,7 +8829,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="25" t="s">
         <v>177</v>
       </c>
@@ -8766,7 +8863,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="25" t="s">
         <v>177</v>
       </c>
@@ -8800,7 +8897,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="25" t="s">
         <v>177</v>
       </c>
@@ -8834,7 +8931,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="25" t="s">
         <v>177</v>
       </c>
@@ -8868,7 +8965,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="25" t="s">
         <v>177</v>
       </c>
@@ -8902,7 +8999,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="25" t="s">
         <v>177</v>
       </c>
@@ -8936,7 +9033,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="25" t="s">
         <v>177</v>
       </c>
@@ -8970,7 +9067,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="25" t="s">
         <v>177</v>
       </c>
@@ -9004,7 +9101,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="25" t="s">
         <v>177</v>
       </c>
@@ -9038,7 +9135,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="25" t="s">
         <v>177</v>
       </c>
@@ -9072,7 +9169,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="25" t="s">
         <v>177</v>
       </c>
@@ -9106,7 +9203,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="25" t="s">
         <v>177</v>
       </c>
@@ -9140,7 +9237,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="25" t="s">
         <v>177</v>
       </c>
@@ -9174,7 +9271,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="25" t="s">
         <v>177</v>
       </c>
@@ -9208,7 +9305,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="25" t="s">
         <v>177</v>
       </c>
@@ -9242,7 +9339,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="25" t="s">
         <v>177</v>
       </c>
@@ -9276,7 +9373,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="25" t="s">
         <v>177</v>
       </c>
@@ -9310,7 +9407,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="25" t="s">
         <v>177</v>
       </c>
@@ -9344,7 +9441,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="25" t="s">
         <v>177</v>
       </c>
@@ -9378,7 +9475,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="25" t="s">
         <v>177</v>
       </c>
@@ -9412,7 +9509,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="25" t="s">
         <v>177</v>
       </c>
@@ -9446,7 +9543,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="25" t="s">
         <v>177</v>
       </c>
@@ -9480,7 +9577,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="25" t="s">
         <v>177</v>
       </c>
@@ -9514,7 +9611,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="25" t="s">
         <v>177</v>
       </c>
@@ -9548,7 +9645,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="25" t="s">
         <v>177</v>
       </c>
@@ -9582,7 +9679,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="25" t="s">
         <v>177</v>
       </c>
@@ -9616,7 +9713,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="26" t="s">
         <v>178</v>
       </c>
@@ -9647,7 +9744,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="26" t="s">
         <v>178</v>
       </c>
@@ -9678,7 +9775,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="26" t="s">
         <v>178</v>
       </c>
@@ -9709,7 +9806,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="26" t="s">
         <v>178</v>
       </c>
@@ -9743,7 +9840,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="26" t="s">
         <v>178</v>
       </c>
@@ -9774,7 +9871,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="26" t="s">
         <v>178</v>
       </c>
@@ -9805,7 +9902,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="26" t="s">
         <v>178</v>
       </c>
@@ -9836,7 +9933,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="26" t="s">
         <v>178</v>
       </c>
@@ -9867,7 +9964,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="26" t="s">
         <v>178</v>
       </c>
@@ -9898,7 +9995,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="26" t="s">
         <v>178</v>
       </c>
@@ -9929,7 +10026,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="26" t="s">
         <v>178</v>
       </c>
@@ -9960,7 +10057,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="26" t="s">
         <v>178</v>
       </c>
@@ -9991,7 +10088,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="26" t="s">
         <v>178</v>
       </c>
@@ -10025,7 +10122,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" s="26" t="s">
         <v>178</v>
       </c>
@@ -10056,7 +10153,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" s="26" t="s">
         <v>178</v>
       </c>
@@ -10087,7 +10184,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" s="26" t="s">
         <v>178</v>
       </c>
@@ -10118,7 +10215,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="26" t="s">
         <v>178</v>
       </c>
@@ -10149,7 +10246,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" s="26" t="s">
         <v>178</v>
       </c>
@@ -10180,7 +10277,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" s="26" t="s">
         <v>178</v>
       </c>
@@ -10211,7 +10308,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="26" t="s">
         <v>178</v>
       </c>
@@ -10242,7 +10339,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" s="26" t="s">
         <v>178</v>
       </c>
@@ -10276,7 +10373,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" s="26" t="s">
         <v>178</v>
       </c>
@@ -10307,7 +10404,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" s="26" t="s">
         <v>178</v>
       </c>
@@ -10338,7 +10435,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="26" t="s">
         <v>178</v>
       </c>
@@ -10369,7 +10466,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" s="26" t="s">
         <v>178</v>
       </c>
@@ -10400,7 +10497,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="26" t="s">
         <v>178</v>
       </c>
@@ -10434,7 +10531,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="26" t="s">
         <v>178</v>
       </c>
@@ -10468,7 +10565,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="26" t="s">
         <v>178</v>
       </c>
@@ -10502,7 +10599,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="26" t="s">
         <v>178</v>
       </c>
@@ -10536,7 +10633,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="26" t="s">
         <v>178</v>
       </c>
@@ -10567,7 +10664,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="26" t="s">
         <v>178</v>
       </c>
@@ -10598,7 +10695,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="26" t="s">
         <v>178</v>
       </c>
@@ -10629,7 +10726,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="26" t="s">
         <v>178</v>
       </c>
@@ -10660,7 +10757,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="26" t="s">
         <v>178</v>
       </c>
@@ -10691,7 +10788,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="26" t="s">
         <v>178</v>
       </c>
@@ -10722,7 +10819,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="26" t="s">
         <v>178</v>
       </c>
@@ -10753,7 +10850,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" s="26" t="s">
         <v>178</v>
       </c>
@@ -10784,7 +10881,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="26" t="s">
         <v>178</v>
       </c>
@@ -10815,7 +10912,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="26" t="s">
         <v>178</v>
       </c>
@@ -10846,7 +10943,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="26" t="s">
         <v>178</v>
       </c>
@@ -10877,7 +10974,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="26" t="s">
         <v>178</v>
       </c>
@@ -10908,7 +11005,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="26" t="s">
         <v>178</v>
       </c>
@@ -10939,7 +11036,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="26" t="s">
         <v>178</v>
       </c>
@@ -10970,7 +11067,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="26" t="s">
         <v>178</v>
       </c>
@@ -11001,7 +11098,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="26" t="s">
         <v>178</v>
       </c>
@@ -11032,7 +11129,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="26" t="s">
         <v>178</v>
       </c>
@@ -11063,7 +11160,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="26" t="s">
         <v>178</v>
       </c>
@@ -11094,7 +11191,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="26" t="s">
         <v>178</v>
       </c>
@@ -11125,7 +11222,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="26" t="s">
         <v>178</v>
       </c>
@@ -11156,7 +11253,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="26" t="s">
         <v>178</v>
       </c>
@@ -11187,7 +11284,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="26" t="s">
         <v>178</v>
       </c>
@@ -11218,7 +11315,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="26" t="s">
         <v>178</v>
       </c>
@@ -11249,7 +11346,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="26" t="s">
         <v>178</v>
       </c>
@@ -11280,7 +11377,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="26" t="s">
         <v>178</v>
       </c>
@@ -11311,7 +11408,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="26" t="s">
         <v>178</v>
       </c>
@@ -11342,7 +11439,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" s="26" t="s">
         <v>178</v>
       </c>
@@ -11373,7 +11470,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="26" t="s">
         <v>178</v>
       </c>
@@ -11404,7 +11501,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="26" t="s">
         <v>178</v>
       </c>
@@ -11435,7 +11532,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="26" t="s">
         <v>178</v>
       </c>
@@ -11469,7 +11566,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="26" t="s">
         <v>178</v>
       </c>
@@ -11503,7 +11600,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="26" t="s">
         <v>178</v>
       </c>
@@ -11537,7 +11634,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="26" t="s">
         <v>178</v>
       </c>
@@ -11571,7 +11668,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="26" t="s">
         <v>178</v>
       </c>
@@ -11605,7 +11702,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="26" t="s">
         <v>178</v>
       </c>
@@ -11639,7 +11736,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="26" t="s">
         <v>178</v>
       </c>
@@ -11673,7 +11770,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="26" t="s">
         <v>178</v>
       </c>
@@ -11707,7 +11804,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="26" t="s">
         <v>178</v>
       </c>
@@ -11741,7 +11838,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="26" t="s">
         <v>178</v>
       </c>
@@ -11775,7 +11872,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="26" t="s">
         <v>178</v>
       </c>
@@ -11809,7 +11906,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="26" t="s">
         <v>178</v>
       </c>
@@ -11843,7 +11940,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="26" t="s">
         <v>178</v>
       </c>
@@ -11877,7 +11974,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="26" t="s">
         <v>178</v>
       </c>
@@ -11911,7 +12008,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="26" t="s">
         <v>178</v>
       </c>
@@ -11945,7 +12042,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" s="26" t="s">
         <v>178</v>
       </c>
@@ -11979,7 +12076,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" s="26" t="s">
         <v>178</v>
       </c>
@@ -12013,7 +12110,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="26" t="s">
         <v>178</v>
       </c>
@@ -12047,7 +12144,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="26" t="s">
         <v>178</v>
       </c>
@@ -12081,7 +12178,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="26" t="s">
         <v>178</v>
       </c>
@@ -12115,7 +12212,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="26" t="s">
         <v>178</v>
       </c>
@@ -12149,7 +12246,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="26" t="s">
         <v>178</v>
       </c>
@@ -12183,7 +12280,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" s="26" t="s">
         <v>178</v>
       </c>
@@ -12217,7 +12314,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" s="26" t="s">
         <v>178</v>
       </c>
@@ -12251,7 +12348,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="26" t="s">
         <v>178</v>
       </c>
@@ -12285,7 +12382,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" s="26" t="s">
         <v>178</v>
       </c>
@@ -12319,7 +12416,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="26" t="s">
         <v>178</v>
       </c>
@@ -12353,7 +12450,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333" s="26" t="s">
         <v>178</v>
       </c>
@@ -12387,45 +12484,932 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>183</v>
+      </c>
+      <c r="B334" t="s">
+        <v>184</v>
+      </c>
+      <c r="C334" t="s">
+        <v>14</v>
+      </c>
+      <c r="D334" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E334" s="28">
+        <v>100</v>
+      </c>
+      <c r="F334" t="s">
+        <v>185</v>
+      </c>
+      <c r="G334" t="b">
+        <v>1</v>
+      </c>
+      <c r="H334" t="s">
+        <v>186</v>
+      </c>
+      <c r="I334" t="s">
+        <v>184</v>
+      </c>
+      <c r="J334" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>183</v>
+      </c>
+      <c r="B335" t="s">
+        <v>184</v>
+      </c>
+      <c r="C335" t="s">
+        <v>14</v>
+      </c>
+      <c r="D335" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E335" s="29">
+        <v>400</v>
+      </c>
+      <c r="F335" t="s">
+        <v>187</v>
+      </c>
+      <c r="G335" t="b">
+        <v>1</v>
+      </c>
+      <c r="H335" t="s">
+        <v>186</v>
+      </c>
+      <c r="I335" t="s">
+        <v>184</v>
+      </c>
+      <c r="J335" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>183</v>
+      </c>
+      <c r="B336" t="s">
+        <v>184</v>
+      </c>
+      <c r="C336" t="s">
+        <v>188</v>
+      </c>
+      <c r="D336" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E336" s="28">
+        <v>30</v>
+      </c>
+      <c r="F336" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="G336" t="b">
+        <v>1</v>
+      </c>
+      <c r="I336" t="s">
+        <v>184</v>
+      </c>
+      <c r="J336" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>183</v>
+      </c>
+      <c r="B337" t="s">
+        <v>184</v>
+      </c>
+      <c r="C337" t="s">
+        <v>51</v>
+      </c>
+      <c r="D337" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E337" s="31">
+        <v>55</v>
+      </c>
+      <c r="F337" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="G337" t="b">
+        <v>1</v>
+      </c>
+      <c r="I337" t="s">
+        <v>184</v>
+      </c>
+      <c r="J337" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>183</v>
+      </c>
+      <c r="B338" t="s">
+        <v>184</v>
+      </c>
+      <c r="C338" t="s">
+        <v>78</v>
+      </c>
+      <c r="D338" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E338" s="28">
+        <v>0</v>
+      </c>
+      <c r="F338" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="G338" t="b">
+        <v>1</v>
+      </c>
+      <c r="I338" t="s">
+        <v>184</v>
+      </c>
+      <c r="J338" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>183</v>
+      </c>
+      <c r="B339" t="s">
+        <v>184</v>
+      </c>
+      <c r="C339" t="s">
+        <v>72</v>
+      </c>
+      <c r="D339" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E339" s="28">
+        <v>0</v>
+      </c>
+      <c r="F339" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="G339" t="b">
+        <v>1</v>
+      </c>
+      <c r="I339" t="s">
+        <v>184</v>
+      </c>
+      <c r="J339" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>183</v>
+      </c>
+      <c r="B340" t="s">
+        <v>184</v>
+      </c>
+      <c r="C340" t="s">
+        <v>193</v>
+      </c>
+      <c r="D340" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E340" s="28">
+        <v>0</v>
+      </c>
+      <c r="F340" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="G340" t="b">
+        <v>1</v>
+      </c>
+      <c r="I340" t="s">
+        <v>184</v>
+      </c>
+      <c r="J340" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>183</v>
+      </c>
+      <c r="B341" t="s">
+        <v>184</v>
+      </c>
+      <c r="C341" t="s">
+        <v>76</v>
+      </c>
+      <c r="D341" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E341" s="28">
+        <v>0</v>
+      </c>
+      <c r="F341" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G341" t="b">
+        <v>1</v>
+      </c>
+      <c r="I341" t="s">
+        <v>184</v>
+      </c>
+      <c r="J341" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>183</v>
+      </c>
+      <c r="B342" t="s">
+        <v>184</v>
+      </c>
+      <c r="C342" t="s">
+        <v>196</v>
+      </c>
+      <c r="D342" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E342" s="32">
+        <v>25</v>
+      </c>
+      <c r="F342" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="G342" t="b">
+        <v>1</v>
+      </c>
+      <c r="I342" t="s">
+        <v>184</v>
+      </c>
+      <c r="J342" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>183</v>
+      </c>
+      <c r="B343" t="s">
+        <v>184</v>
+      </c>
+      <c r="C343" t="s">
+        <v>198</v>
+      </c>
+      <c r="D343" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E343" s="32">
+        <v>20</v>
+      </c>
+      <c r="F343" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="G343" t="b">
+        <v>1</v>
+      </c>
+      <c r="I343" t="s">
+        <v>184</v>
+      </c>
+      <c r="J343" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>183</v>
+      </c>
+      <c r="B344" t="s">
+        <v>200</v>
+      </c>
+      <c r="C344" t="s">
+        <v>14</v>
+      </c>
+      <c r="D344" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E344" s="28">
+        <v>100</v>
+      </c>
+      <c r="F344" t="s">
+        <v>185</v>
+      </c>
+      <c r="G344" t="b">
+        <v>1</v>
+      </c>
+      <c r="H344" t="s">
+        <v>186</v>
+      </c>
+      <c r="I344" t="s">
+        <v>200</v>
+      </c>
+      <c r="J344" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>183</v>
+      </c>
+      <c r="B345" t="s">
+        <v>200</v>
+      </c>
+      <c r="C345" t="s">
+        <v>14</v>
+      </c>
+      <c r="D345" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E345" s="29">
+        <v>400</v>
+      </c>
+      <c r="F345" t="s">
+        <v>187</v>
+      </c>
+      <c r="G345" t="b">
+        <v>1</v>
+      </c>
+      <c r="H345" t="s">
+        <v>186</v>
+      </c>
+      <c r="I345" t="s">
+        <v>200</v>
+      </c>
+      <c r="J345" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>183</v>
+      </c>
+      <c r="B346" t="s">
+        <v>200</v>
+      </c>
+      <c r="C346" t="s">
+        <v>188</v>
+      </c>
+      <c r="D346" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E346" s="28">
+        <v>30</v>
+      </c>
+      <c r="F346" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="G346" t="b">
+        <v>1</v>
+      </c>
+      <c r="I346" t="s">
+        <v>200</v>
+      </c>
+      <c r="J346" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>183</v>
+      </c>
+      <c r="B347" t="s">
+        <v>200</v>
+      </c>
+      <c r="C347" t="s">
+        <v>51</v>
+      </c>
+      <c r="D347" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E347" s="31">
+        <v>55</v>
+      </c>
+      <c r="F347" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="G347" t="b">
+        <v>1</v>
+      </c>
+      <c r="I347" t="s">
+        <v>200</v>
+      </c>
+      <c r="J347" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>183</v>
+      </c>
+      <c r="B348" t="s">
+        <v>200</v>
+      </c>
+      <c r="C348" t="s">
+        <v>78</v>
+      </c>
+      <c r="D348" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E348" s="28">
+        <v>0</v>
+      </c>
+      <c r="F348" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="G348" t="b">
+        <v>1</v>
+      </c>
+      <c r="I348" t="s">
+        <v>200</v>
+      </c>
+      <c r="J348" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>183</v>
+      </c>
+      <c r="B349" t="s">
+        <v>200</v>
+      </c>
+      <c r="C349" t="s">
+        <v>72</v>
+      </c>
+      <c r="D349" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E349" s="28">
+        <v>0</v>
+      </c>
+      <c r="F349" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="G349" t="b">
+        <v>1</v>
+      </c>
+      <c r="I349" t="s">
+        <v>200</v>
+      </c>
+      <c r="J349" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>183</v>
+      </c>
+      <c r="B350" t="s">
+        <v>200</v>
+      </c>
+      <c r="C350" t="s">
+        <v>193</v>
+      </c>
+      <c r="D350" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E350" s="28">
+        <v>0</v>
+      </c>
+      <c r="F350" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="G350" t="b">
+        <v>1</v>
+      </c>
+      <c r="I350" t="s">
+        <v>200</v>
+      </c>
+      <c r="J350" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>183</v>
+      </c>
+      <c r="B351" t="s">
+        <v>200</v>
+      </c>
+      <c r="C351" t="s">
+        <v>76</v>
+      </c>
+      <c r="D351" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E351" s="28">
+        <v>0</v>
+      </c>
+      <c r="F351" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G351" t="b">
+        <v>1</v>
+      </c>
+      <c r="I351" t="s">
+        <v>200</v>
+      </c>
+      <c r="J351" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>183</v>
+      </c>
+      <c r="B352" t="s">
+        <v>200</v>
+      </c>
+      <c r="C352" t="s">
+        <v>196</v>
+      </c>
+      <c r="D352" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E352" s="32">
+        <v>25</v>
+      </c>
+      <c r="F352" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="G352" t="b">
+        <v>1</v>
+      </c>
+      <c r="I352" t="s">
+        <v>200</v>
+      </c>
+      <c r="J352" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>183</v>
+      </c>
+      <c r="B353" t="s">
+        <v>200</v>
+      </c>
+      <c r="C353" t="s">
+        <v>198</v>
+      </c>
+      <c r="D353" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E353" s="32">
+        <v>20</v>
+      </c>
+      <c r="F353" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="G353" t="b">
+        <v>1</v>
+      </c>
+      <c r="I353" t="s">
+        <v>200</v>
+      </c>
+      <c r="J353" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>183</v>
+      </c>
+      <c r="B354" t="s">
+        <v>201</v>
+      </c>
+      <c r="C354" t="s">
+        <v>14</v>
+      </c>
+      <c r="D354" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E354" s="28">
+        <v>100</v>
+      </c>
+      <c r="F354" t="s">
+        <v>185</v>
+      </c>
+      <c r="G354" t="b">
+        <v>1</v>
+      </c>
+      <c r="H354" t="s">
+        <v>186</v>
+      </c>
+      <c r="I354" t="s">
+        <v>201</v>
+      </c>
+      <c r="J354" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>183</v>
+      </c>
+      <c r="B355" t="s">
+        <v>201</v>
+      </c>
+      <c r="C355" t="s">
+        <v>14</v>
+      </c>
+      <c r="D355" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E355" s="29">
+        <v>400</v>
+      </c>
+      <c r="F355" t="s">
+        <v>187</v>
+      </c>
+      <c r="G355" t="b">
+        <v>1</v>
+      </c>
+      <c r="H355" t="s">
+        <v>186</v>
+      </c>
+      <c r="I355" t="s">
+        <v>201</v>
+      </c>
+      <c r="J355" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>183</v>
+      </c>
+      <c r="B356" t="s">
+        <v>201</v>
+      </c>
+      <c r="C356" t="s">
+        <v>188</v>
+      </c>
+      <c r="D356" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E356" s="28">
+        <v>30</v>
+      </c>
+      <c r="F356" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="G356" t="b">
+        <v>1</v>
+      </c>
+      <c r="I356" t="s">
+        <v>201</v>
+      </c>
+      <c r="J356" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>183</v>
+      </c>
+      <c r="B357" t="s">
+        <v>201</v>
+      </c>
+      <c r="C357" t="s">
+        <v>51</v>
+      </c>
+      <c r="D357" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E357" s="31">
+        <v>55</v>
+      </c>
+      <c r="F357" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="G357" t="b">
+        <v>1</v>
+      </c>
+      <c r="I357" t="s">
+        <v>201</v>
+      </c>
+      <c r="J357" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>183</v>
+      </c>
+      <c r="B358" t="s">
+        <v>201</v>
+      </c>
+      <c r="C358" t="s">
+        <v>78</v>
+      </c>
+      <c r="D358" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E358" s="28">
+        <v>0</v>
+      </c>
+      <c r="F358" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="G358" t="b">
+        <v>1</v>
+      </c>
+      <c r="I358" t="s">
+        <v>201</v>
+      </c>
+      <c r="J358" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>183</v>
+      </c>
+      <c r="B359" t="s">
+        <v>201</v>
+      </c>
+      <c r="C359" t="s">
+        <v>72</v>
+      </c>
+      <c r="D359" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E359" s="28">
+        <v>0</v>
+      </c>
+      <c r="F359" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="G359" t="b">
+        <v>1</v>
+      </c>
+      <c r="I359" t="s">
+        <v>201</v>
+      </c>
+      <c r="J359" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>183</v>
+      </c>
+      <c r="B360" t="s">
+        <v>201</v>
+      </c>
+      <c r="C360" t="s">
+        <v>193</v>
+      </c>
+      <c r="D360" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E360" s="28">
+        <v>0</v>
+      </c>
+      <c r="F360" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="G360" t="b">
+        <v>1</v>
+      </c>
+      <c r="I360" t="s">
+        <v>201</v>
+      </c>
+      <c r="J360" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>183</v>
+      </c>
+      <c r="B361" t="s">
+        <v>201</v>
+      </c>
+      <c r="C361" t="s">
+        <v>76</v>
+      </c>
+      <c r="D361" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E361" s="28">
+        <v>0</v>
+      </c>
+      <c r="F361" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G361" t="b">
+        <v>1</v>
+      </c>
+      <c r="I361" t="s">
+        <v>201</v>
+      </c>
+      <c r="J361" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>183</v>
+      </c>
+      <c r="B362" t="s">
+        <v>201</v>
+      </c>
+      <c r="C362" t="s">
+        <v>196</v>
+      </c>
+      <c r="D362" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E362" s="32">
+        <v>25</v>
+      </c>
+      <c r="F362" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="G362" t="b">
+        <v>1</v>
+      </c>
+      <c r="I362" t="s">
+        <v>201</v>
+      </c>
+      <c r="J362" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>183</v>
+      </c>
+      <c r="B363" t="s">
+        <v>201</v>
+      </c>
+      <c r="C363" t="s">
+        <v>198</v>
+      </c>
+      <c r="D363" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E363" s="32">
+        <v>20</v>
+      </c>
+      <c r="F363" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="G363" t="b">
+        <v>1</v>
+      </c>
+      <c r="I363" t="s">
+        <v>201</v>
+      </c>
+      <c r="J363" t="s">
+        <v>201</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J333" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="pi_SCC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J363" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <conditionalFormatting sqref="C2:C66 C162:C186 C248:C272">
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="7" priority="15">
       <formula>$G2=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="6" priority="11">
       <formula>$G128=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G219 G220:H228 H229:H249 G229:G305 G306:H333">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H100:H127">
     <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H100:H127">
-    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H174">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H260">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G334:G363">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C229CC0-837E-40A6-A6C1-5190746F7658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C9CD93-B8DF-42E4-9A93-A63BFAE82DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2122" uniqueCount="209">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -775,6 +775,27 @@
   </si>
   <si>
     <t>WCBP_mNRSA</t>
+  </si>
+  <si>
+    <t>Add flags for Boise BCG, Main_Eckert</t>
+  </si>
+  <si>
+    <t>LBR_Fish_BCG_v1</t>
+  </si>
+  <si>
+    <t>Main_Eckert</t>
+  </si>
+  <si>
+    <t>low number of total individuals</t>
+  </si>
+  <si>
+    <t>low number of total taxa</t>
+  </si>
+  <si>
+    <t>imbalance, dominance by one taxon</t>
+  </si>
+  <si>
+    <t>imbalance, dominance by two taxa</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1467,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1472,7 +1493,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
-        <v>45820</v>
+        <v>46017</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1731,6 +1752,14 @@
       <c r="A46" s="22"/>
       <c r="B46" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="15">
+        <v>46017</v>
+      </c>
+      <c r="B47" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1874,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J363"/>
+  <dimension ref="A1:J367"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -13372,45 +13401,137 @@
         <v>201</v>
       </c>
     </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>203</v>
+      </c>
+      <c r="B364" t="s">
+        <v>204</v>
+      </c>
+      <c r="C364" t="s">
+        <v>14</v>
+      </c>
+      <c r="D364" t="s">
+        <v>16</v>
+      </c>
+      <c r="E364">
+        <v>100</v>
+      </c>
+      <c r="F364" t="s">
+        <v>205</v>
+      </c>
+      <c r="G364" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>203</v>
+      </c>
+      <c r="B365" t="s">
+        <v>204</v>
+      </c>
+      <c r="C365" t="s">
+        <v>188</v>
+      </c>
+      <c r="D365" t="s">
+        <v>16</v>
+      </c>
+      <c r="E365">
+        <v>4</v>
+      </c>
+      <c r="F365" t="s">
+        <v>206</v>
+      </c>
+      <c r="G365" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>203</v>
+      </c>
+      <c r="B366" t="s">
+        <v>204</v>
+      </c>
+      <c r="C366" t="s">
+        <v>169</v>
+      </c>
+      <c r="D366" t="s">
+        <v>17</v>
+      </c>
+      <c r="E366">
+        <v>70</v>
+      </c>
+      <c r="F366" t="s">
+        <v>207</v>
+      </c>
+      <c r="G366" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>203</v>
+      </c>
+      <c r="B367" t="s">
+        <v>204</v>
+      </c>
+      <c r="C367" t="s">
+        <v>51</v>
+      </c>
+      <c r="D367" t="s">
+        <v>17</v>
+      </c>
+      <c r="E367">
+        <v>85</v>
+      </c>
+      <c r="F367" t="s">
+        <v>208</v>
+      </c>
+      <c r="G367" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J363" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <conditionalFormatting sqref="C2:C66 C162:C186 C248:C272">
-    <cfRule type="expression" dxfId="7" priority="15">
+    <cfRule type="expression" dxfId="7" priority="16">
       <formula>$G2=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="6" priority="12">
       <formula>$G128=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G219 G220:H228 H229:H249 G229:G305 G306:H333">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G334:G367">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54">
-    <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="15" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H100:H127">
-    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="14" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H174">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H260">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G334:G363">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C9CD93-B8DF-42E4-9A93-A63BFAE82DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD68B06-4627-4CCF-9A3F-379B73171C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2122" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="231">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -796,6 +796,72 @@
   </si>
   <si>
     <t>imbalance, dominance by two taxa</t>
+  </si>
+  <si>
+    <t>LBR_Bugs_BCG_v1</t>
+  </si>
+  <si>
+    <t>Main_BarberPool</t>
+  </si>
+  <si>
+    <t>low total individuals</t>
+  </si>
+  <si>
+    <t>high total individuals</t>
+  </si>
+  <si>
+    <t>pi_BCG_att6t</t>
+  </si>
+  <si>
+    <t>≥</t>
+  </si>
+  <si>
+    <t>high percentage non-native, tolerant individuals</t>
+  </si>
+  <si>
+    <t>x_Shan_2</t>
+  </si>
+  <si>
+    <t>≤</t>
+  </si>
+  <si>
+    <t>extremely unbalanced</t>
+  </si>
+  <si>
+    <t>unusually low number of mayfly taxa</t>
+  </si>
+  <si>
+    <t>missing stonefly taxa</t>
+  </si>
+  <si>
+    <t>unusually low number of caddisfly taxa</t>
+  </si>
+  <si>
+    <t>nt_ti_stenocold_cold_cool</t>
+  </si>
+  <si>
+    <t>missing coolwater taxa</t>
+  </si>
+  <si>
+    <t>nt_ti_stenowarm</t>
+  </si>
+  <si>
+    <t>high number of warm stenotherm taxa</t>
+  </si>
+  <si>
+    <t>Main_Middleton</t>
+  </si>
+  <si>
+    <t>Main_NotusParma</t>
+  </si>
+  <si>
+    <t>Main_SoChannel</t>
+  </si>
+  <si>
+    <t>Main_VetGlen</t>
+  </si>
+  <si>
+    <t>Boise BCG, bugs</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1138,81 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1169,7 +1309,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Worksheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descriptions"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="8">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="16">
       <calculatedColumnFormula>HYPERLINK(FileName&amp;A16&amp;"!A1",A16)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1467,7 +1607,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1493,7 +1633,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
-        <v>46017</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1760,6 +1900,14 @@
       </c>
       <c r="B47" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="15">
+        <v>46160</v>
+      </c>
+      <c r="B48" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +2022,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J367"/>
+  <dimension ref="A1:J420"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -13493,45 +13641,1264 @@
         <v>1</v>
       </c>
     </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>209</v>
+      </c>
+      <c r="B368" t="s">
+        <v>210</v>
+      </c>
+      <c r="C368" t="s">
+        <v>14</v>
+      </c>
+      <c r="D368" t="s">
+        <v>16</v>
+      </c>
+      <c r="E368">
+        <v>500</v>
+      </c>
+      <c r="F368" t="s">
+        <v>211</v>
+      </c>
+      <c r="G368" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>209</v>
+      </c>
+      <c r="B369" t="s">
+        <v>210</v>
+      </c>
+      <c r="C369" t="s">
+        <v>14</v>
+      </c>
+      <c r="D369" t="s">
+        <v>15</v>
+      </c>
+      <c r="E369">
+        <v>650</v>
+      </c>
+      <c r="F369" t="s">
+        <v>212</v>
+      </c>
+      <c r="G369" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>209</v>
+      </c>
+      <c r="B370" t="s">
+        <v>210</v>
+      </c>
+      <c r="C370" t="s">
+        <v>213</v>
+      </c>
+      <c r="D370" t="s">
+        <v>214</v>
+      </c>
+      <c r="E370">
+        <v>1</v>
+      </c>
+      <c r="F370" t="s">
+        <v>215</v>
+      </c>
+      <c r="G370" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>209</v>
+      </c>
+      <c r="B371" t="s">
+        <v>210</v>
+      </c>
+      <c r="C371" t="s">
+        <v>216</v>
+      </c>
+      <c r="D371" t="s">
+        <v>217</v>
+      </c>
+      <c r="E371">
+        <v>2</v>
+      </c>
+      <c r="F371" t="s">
+        <v>218</v>
+      </c>
+      <c r="G371" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>209</v>
+      </c>
+      <c r="B372" t="s">
+        <v>210</v>
+      </c>
+      <c r="C372" t="s">
+        <v>72</v>
+      </c>
+      <c r="D372" t="s">
+        <v>16</v>
+      </c>
+      <c r="E372">
+        <v>3</v>
+      </c>
+      <c r="F372" t="s">
+        <v>219</v>
+      </c>
+      <c r="G372" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>209</v>
+      </c>
+      <c r="B373" t="s">
+        <v>210</v>
+      </c>
+      <c r="C373" t="s">
+        <v>74</v>
+      </c>
+      <c r="D373" t="s">
+        <v>16</v>
+      </c>
+      <c r="E373">
+        <v>1</v>
+      </c>
+      <c r="F373" t="s">
+        <v>220</v>
+      </c>
+      <c r="G373" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>209</v>
+      </c>
+      <c r="B374" t="s">
+        <v>210</v>
+      </c>
+      <c r="C374" t="s">
+        <v>76</v>
+      </c>
+      <c r="D374" t="s">
+        <v>217</v>
+      </c>
+      <c r="E374">
+        <v>2</v>
+      </c>
+      <c r="F374" t="s">
+        <v>221</v>
+      </c>
+      <c r="G374" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>209</v>
+      </c>
+      <c r="B375" t="s">
+        <v>210</v>
+      </c>
+      <c r="C375" t="s">
+        <v>222</v>
+      </c>
+      <c r="D375" t="s">
+        <v>16</v>
+      </c>
+      <c r="E375">
+        <v>1</v>
+      </c>
+      <c r="F375" t="s">
+        <v>223</v>
+      </c>
+      <c r="G375" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>209</v>
+      </c>
+      <c r="B376" t="s">
+        <v>210</v>
+      </c>
+      <c r="C376" t="s">
+        <v>224</v>
+      </c>
+      <c r="D376" t="s">
+        <v>214</v>
+      </c>
+      <c r="E376">
+        <v>3</v>
+      </c>
+      <c r="F376" t="s">
+        <v>225</v>
+      </c>
+      <c r="G376" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>209</v>
+      </c>
+      <c r="B377" t="s">
+        <v>204</v>
+      </c>
+      <c r="C377" t="s">
+        <v>14</v>
+      </c>
+      <c r="D377" t="s">
+        <v>16</v>
+      </c>
+      <c r="E377">
+        <v>500</v>
+      </c>
+      <c r="F377" t="s">
+        <v>211</v>
+      </c>
+      <c r="G377" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>209</v>
+      </c>
+      <c r="B378" t="s">
+        <v>204</v>
+      </c>
+      <c r="C378" t="s">
+        <v>14</v>
+      </c>
+      <c r="D378" t="s">
+        <v>15</v>
+      </c>
+      <c r="E378">
+        <v>650</v>
+      </c>
+      <c r="F378" t="s">
+        <v>212</v>
+      </c>
+      <c r="G378" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>209</v>
+      </c>
+      <c r="B379" t="s">
+        <v>204</v>
+      </c>
+      <c r="C379" t="s">
+        <v>213</v>
+      </c>
+      <c r="D379" t="s">
+        <v>214</v>
+      </c>
+      <c r="E379">
+        <v>1</v>
+      </c>
+      <c r="F379" t="s">
+        <v>215</v>
+      </c>
+      <c r="G379" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>209</v>
+      </c>
+      <c r="B380" t="s">
+        <v>204</v>
+      </c>
+      <c r="C380" t="s">
+        <v>216</v>
+      </c>
+      <c r="D380" t="s">
+        <v>217</v>
+      </c>
+      <c r="E380">
+        <v>2</v>
+      </c>
+      <c r="F380" t="s">
+        <v>218</v>
+      </c>
+      <c r="G380" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>209</v>
+      </c>
+      <c r="B381" t="s">
+        <v>204</v>
+      </c>
+      <c r="C381" t="s">
+        <v>72</v>
+      </c>
+      <c r="D381" t="s">
+        <v>16</v>
+      </c>
+      <c r="E381">
+        <v>3</v>
+      </c>
+      <c r="F381" t="s">
+        <v>219</v>
+      </c>
+      <c r="G381" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>209</v>
+      </c>
+      <c r="B382" t="s">
+        <v>204</v>
+      </c>
+      <c r="C382" t="s">
+        <v>74</v>
+      </c>
+      <c r="D382" t="s">
+        <v>16</v>
+      </c>
+      <c r="E382">
+        <v>1</v>
+      </c>
+      <c r="F382" t="s">
+        <v>220</v>
+      </c>
+      <c r="G382" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>209</v>
+      </c>
+      <c r="B383" t="s">
+        <v>204</v>
+      </c>
+      <c r="C383" t="s">
+        <v>76</v>
+      </c>
+      <c r="D383" t="s">
+        <v>217</v>
+      </c>
+      <c r="E383">
+        <v>2</v>
+      </c>
+      <c r="F383" t="s">
+        <v>221</v>
+      </c>
+      <c r="G383" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>209</v>
+      </c>
+      <c r="B384" t="s">
+        <v>204</v>
+      </c>
+      <c r="C384" t="s">
+        <v>222</v>
+      </c>
+      <c r="D384" t="s">
+        <v>16</v>
+      </c>
+      <c r="E384">
+        <v>1</v>
+      </c>
+      <c r="F384" t="s">
+        <v>223</v>
+      </c>
+      <c r="G384" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>209</v>
+      </c>
+      <c r="B385" t="s">
+        <v>204</v>
+      </c>
+      <c r="C385" t="s">
+        <v>224</v>
+      </c>
+      <c r="D385" t="s">
+        <v>214</v>
+      </c>
+      <c r="E385">
+        <v>3</v>
+      </c>
+      <c r="F385" t="s">
+        <v>225</v>
+      </c>
+      <c r="G385" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>209</v>
+      </c>
+      <c r="B386" t="s">
+        <v>226</v>
+      </c>
+      <c r="C386" t="s">
+        <v>14</v>
+      </c>
+      <c r="D386" t="s">
+        <v>16</v>
+      </c>
+      <c r="E386">
+        <v>500</v>
+      </c>
+      <c r="F386" t="s">
+        <v>211</v>
+      </c>
+      <c r="G386" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>209</v>
+      </c>
+      <c r="B387" t="s">
+        <v>226</v>
+      </c>
+      <c r="C387" t="s">
+        <v>14</v>
+      </c>
+      <c r="D387" t="s">
+        <v>15</v>
+      </c>
+      <c r="E387">
+        <v>650</v>
+      </c>
+      <c r="F387" t="s">
+        <v>212</v>
+      </c>
+      <c r="G387" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>209</v>
+      </c>
+      <c r="B388" t="s">
+        <v>226</v>
+      </c>
+      <c r="C388" t="s">
+        <v>213</v>
+      </c>
+      <c r="D388" t="s">
+        <v>214</v>
+      </c>
+      <c r="E388">
+        <v>10</v>
+      </c>
+      <c r="F388" t="s">
+        <v>215</v>
+      </c>
+      <c r="G388" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>209</v>
+      </c>
+      <c r="B389" t="s">
+        <v>226</v>
+      </c>
+      <c r="C389" t="s">
+        <v>216</v>
+      </c>
+      <c r="D389" t="s">
+        <v>217</v>
+      </c>
+      <c r="E389">
+        <v>2</v>
+      </c>
+      <c r="F389" t="s">
+        <v>218</v>
+      </c>
+      <c r="G389" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>209</v>
+      </c>
+      <c r="B390" t="s">
+        <v>226</v>
+      </c>
+      <c r="C390" t="s">
+        <v>72</v>
+      </c>
+      <c r="D390" t="s">
+        <v>16</v>
+      </c>
+      <c r="E390">
+        <v>3</v>
+      </c>
+      <c r="F390" t="s">
+        <v>219</v>
+      </c>
+      <c r="G390" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>209</v>
+      </c>
+      <c r="B391" t="s">
+        <v>226</v>
+      </c>
+      <c r="C391" t="s">
+        <v>74</v>
+      </c>
+      <c r="D391" t="s">
+        <v>16</v>
+      </c>
+      <c r="E391">
+        <v>1</v>
+      </c>
+      <c r="F391" t="s">
+        <v>220</v>
+      </c>
+      <c r="G391" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>209</v>
+      </c>
+      <c r="B392" t="s">
+        <v>226</v>
+      </c>
+      <c r="C392" t="s">
+        <v>76</v>
+      </c>
+      <c r="D392" t="s">
+        <v>217</v>
+      </c>
+      <c r="E392">
+        <v>2</v>
+      </c>
+      <c r="F392" t="s">
+        <v>221</v>
+      </c>
+      <c r="G392" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>209</v>
+      </c>
+      <c r="B393" t="s">
+        <v>226</v>
+      </c>
+      <c r="C393" t="s">
+        <v>222</v>
+      </c>
+      <c r="D393" t="s">
+        <v>16</v>
+      </c>
+      <c r="E393">
+        <v>1</v>
+      </c>
+      <c r="F393" t="s">
+        <v>223</v>
+      </c>
+      <c r="G393" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>209</v>
+      </c>
+      <c r="B394" t="s">
+        <v>226</v>
+      </c>
+      <c r="C394" t="s">
+        <v>224</v>
+      </c>
+      <c r="D394" t="s">
+        <v>214</v>
+      </c>
+      <c r="E394">
+        <v>5</v>
+      </c>
+      <c r="F394" t="s">
+        <v>225</v>
+      </c>
+      <c r="G394" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>209</v>
+      </c>
+      <c r="B395" t="s">
+        <v>227</v>
+      </c>
+      <c r="C395" t="s">
+        <v>14</v>
+      </c>
+      <c r="D395" t="s">
+        <v>16</v>
+      </c>
+      <c r="E395">
+        <v>500</v>
+      </c>
+      <c r="F395" t="s">
+        <v>211</v>
+      </c>
+      <c r="G395" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>209</v>
+      </c>
+      <c r="B396" t="s">
+        <v>227</v>
+      </c>
+      <c r="C396" t="s">
+        <v>14</v>
+      </c>
+      <c r="D396" t="s">
+        <v>15</v>
+      </c>
+      <c r="E396">
+        <v>650</v>
+      </c>
+      <c r="F396" t="s">
+        <v>212</v>
+      </c>
+      <c r="G396" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>209</v>
+      </c>
+      <c r="B397" t="s">
+        <v>227</v>
+      </c>
+      <c r="C397" t="s">
+        <v>213</v>
+      </c>
+      <c r="D397" t="s">
+        <v>214</v>
+      </c>
+      <c r="E397">
+        <v>10</v>
+      </c>
+      <c r="F397" t="s">
+        <v>215</v>
+      </c>
+      <c r="G397" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>209</v>
+      </c>
+      <c r="B398" t="s">
+        <v>227</v>
+      </c>
+      <c r="C398" t="s">
+        <v>216</v>
+      </c>
+      <c r="D398" t="s">
+        <v>217</v>
+      </c>
+      <c r="E398">
+        <v>2.5</v>
+      </c>
+      <c r="F398" t="s">
+        <v>218</v>
+      </c>
+      <c r="G398" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>209</v>
+      </c>
+      <c r="B399" t="s">
+        <v>227</v>
+      </c>
+      <c r="C399" t="s">
+        <v>72</v>
+      </c>
+      <c r="D399" t="s">
+        <v>16</v>
+      </c>
+      <c r="E399">
+        <v>3</v>
+      </c>
+      <c r="F399" t="s">
+        <v>219</v>
+      </c>
+      <c r="G399" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>209</v>
+      </c>
+      <c r="B400" t="s">
+        <v>227</v>
+      </c>
+      <c r="C400" t="s">
+        <v>76</v>
+      </c>
+      <c r="D400" t="s">
+        <v>217</v>
+      </c>
+      <c r="E400">
+        <v>2</v>
+      </c>
+      <c r="F400" t="s">
+        <v>221</v>
+      </c>
+      <c r="G400" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>209</v>
+      </c>
+      <c r="B401" t="s">
+        <v>227</v>
+      </c>
+      <c r="C401" t="s">
+        <v>222</v>
+      </c>
+      <c r="D401" t="s">
+        <v>16</v>
+      </c>
+      <c r="E401">
+        <v>1</v>
+      </c>
+      <c r="F401" t="s">
+        <v>223</v>
+      </c>
+      <c r="G401" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>209</v>
+      </c>
+      <c r="B402" t="s">
+        <v>227</v>
+      </c>
+      <c r="C402" t="s">
+        <v>224</v>
+      </c>
+      <c r="D402" t="s">
+        <v>214</v>
+      </c>
+      <c r="E402">
+        <v>5</v>
+      </c>
+      <c r="F402" t="s">
+        <v>225</v>
+      </c>
+      <c r="G402" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>209</v>
+      </c>
+      <c r="B403" t="s">
+        <v>228</v>
+      </c>
+      <c r="C403" t="s">
+        <v>14</v>
+      </c>
+      <c r="D403" t="s">
+        <v>16</v>
+      </c>
+      <c r="E403">
+        <v>500</v>
+      </c>
+      <c r="F403" t="s">
+        <v>211</v>
+      </c>
+      <c r="G403" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>209</v>
+      </c>
+      <c r="B404" t="s">
+        <v>228</v>
+      </c>
+      <c r="C404" t="s">
+        <v>14</v>
+      </c>
+      <c r="D404" t="s">
+        <v>15</v>
+      </c>
+      <c r="E404">
+        <v>650</v>
+      </c>
+      <c r="F404" t="s">
+        <v>212</v>
+      </c>
+      <c r="G404" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>209</v>
+      </c>
+      <c r="B405" t="s">
+        <v>228</v>
+      </c>
+      <c r="C405" t="s">
+        <v>213</v>
+      </c>
+      <c r="D405" t="s">
+        <v>214</v>
+      </c>
+      <c r="E405">
+        <v>5</v>
+      </c>
+      <c r="F405" t="s">
+        <v>215</v>
+      </c>
+      <c r="G405" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>209</v>
+      </c>
+      <c r="B406" t="s">
+        <v>228</v>
+      </c>
+      <c r="C406" t="s">
+        <v>216</v>
+      </c>
+      <c r="D406" t="s">
+        <v>217</v>
+      </c>
+      <c r="E406">
+        <v>1.75</v>
+      </c>
+      <c r="F406" t="s">
+        <v>218</v>
+      </c>
+      <c r="G406" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>209</v>
+      </c>
+      <c r="B407" t="s">
+        <v>228</v>
+      </c>
+      <c r="C407" t="s">
+        <v>72</v>
+      </c>
+      <c r="D407" t="s">
+        <v>16</v>
+      </c>
+      <c r="E407">
+        <v>3</v>
+      </c>
+      <c r="F407" t="s">
+        <v>219</v>
+      </c>
+      <c r="G407" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>209</v>
+      </c>
+      <c r="B408" t="s">
+        <v>228</v>
+      </c>
+      <c r="C408" t="s">
+        <v>74</v>
+      </c>
+      <c r="D408" t="s">
+        <v>16</v>
+      </c>
+      <c r="E408">
+        <v>1</v>
+      </c>
+      <c r="F408" t="s">
+        <v>220</v>
+      </c>
+      <c r="G408" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>209</v>
+      </c>
+      <c r="B409" t="s">
+        <v>228</v>
+      </c>
+      <c r="C409" t="s">
+        <v>76</v>
+      </c>
+      <c r="D409" t="s">
+        <v>217</v>
+      </c>
+      <c r="E409">
+        <v>2</v>
+      </c>
+      <c r="F409" t="s">
+        <v>221</v>
+      </c>
+      <c r="G409" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>209</v>
+      </c>
+      <c r="B410" t="s">
+        <v>228</v>
+      </c>
+      <c r="C410" t="s">
+        <v>222</v>
+      </c>
+      <c r="D410" t="s">
+        <v>16</v>
+      </c>
+      <c r="E410">
+        <v>1</v>
+      </c>
+      <c r="F410" t="s">
+        <v>223</v>
+      </c>
+      <c r="G410" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>209</v>
+      </c>
+      <c r="B411" t="s">
+        <v>228</v>
+      </c>
+      <c r="C411" t="s">
+        <v>224</v>
+      </c>
+      <c r="D411" t="s">
+        <v>214</v>
+      </c>
+      <c r="E411">
+        <v>4</v>
+      </c>
+      <c r="F411" t="s">
+        <v>225</v>
+      </c>
+      <c r="G411" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>209</v>
+      </c>
+      <c r="B412" t="s">
+        <v>229</v>
+      </c>
+      <c r="C412" t="s">
+        <v>14</v>
+      </c>
+      <c r="D412" t="s">
+        <v>16</v>
+      </c>
+      <c r="E412">
+        <v>500</v>
+      </c>
+      <c r="F412" t="s">
+        <v>211</v>
+      </c>
+      <c r="G412" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>209</v>
+      </c>
+      <c r="B413" t="s">
+        <v>229</v>
+      </c>
+      <c r="C413" t="s">
+        <v>14</v>
+      </c>
+      <c r="D413" t="s">
+        <v>15</v>
+      </c>
+      <c r="E413">
+        <v>650</v>
+      </c>
+      <c r="F413" t="s">
+        <v>212</v>
+      </c>
+      <c r="G413" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>209</v>
+      </c>
+      <c r="B414" t="s">
+        <v>229</v>
+      </c>
+      <c r="C414" t="s">
+        <v>213</v>
+      </c>
+      <c r="D414" t="s">
+        <v>214</v>
+      </c>
+      <c r="E414">
+        <v>1</v>
+      </c>
+      <c r="F414" t="s">
+        <v>215</v>
+      </c>
+      <c r="G414" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>209</v>
+      </c>
+      <c r="B415" t="s">
+        <v>229</v>
+      </c>
+      <c r="C415" t="s">
+        <v>216</v>
+      </c>
+      <c r="D415" t="s">
+        <v>217</v>
+      </c>
+      <c r="E415">
+        <v>2</v>
+      </c>
+      <c r="F415" t="s">
+        <v>218</v>
+      </c>
+      <c r="G415" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>209</v>
+      </c>
+      <c r="B416" t="s">
+        <v>229</v>
+      </c>
+      <c r="C416" t="s">
+        <v>72</v>
+      </c>
+      <c r="D416" t="s">
+        <v>16</v>
+      </c>
+      <c r="E416">
+        <v>3</v>
+      </c>
+      <c r="F416" t="s">
+        <v>219</v>
+      </c>
+      <c r="G416" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>209</v>
+      </c>
+      <c r="B417" t="s">
+        <v>229</v>
+      </c>
+      <c r="C417" t="s">
+        <v>74</v>
+      </c>
+      <c r="D417" t="s">
+        <v>16</v>
+      </c>
+      <c r="E417">
+        <v>1</v>
+      </c>
+      <c r="F417" t="s">
+        <v>220</v>
+      </c>
+      <c r="G417" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>209</v>
+      </c>
+      <c r="B418" t="s">
+        <v>229</v>
+      </c>
+      <c r="C418" t="s">
+        <v>76</v>
+      </c>
+      <c r="D418" t="s">
+        <v>217</v>
+      </c>
+      <c r="E418">
+        <v>2</v>
+      </c>
+      <c r="F418" t="s">
+        <v>221</v>
+      </c>
+      <c r="G418" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>209</v>
+      </c>
+      <c r="B419" t="s">
+        <v>229</v>
+      </c>
+      <c r="C419" t="s">
+        <v>222</v>
+      </c>
+      <c r="D419" t="s">
+        <v>16</v>
+      </c>
+      <c r="E419">
+        <v>1</v>
+      </c>
+      <c r="F419" t="s">
+        <v>223</v>
+      </c>
+      <c r="G419" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>209</v>
+      </c>
+      <c r="B420" t="s">
+        <v>229</v>
+      </c>
+      <c r="C420" t="s">
+        <v>224</v>
+      </c>
+      <c r="D420" t="s">
+        <v>214</v>
+      </c>
+      <c r="E420">
+        <v>4</v>
+      </c>
+      <c r="F420" t="s">
+        <v>225</v>
+      </c>
+      <c r="G420" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J363" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <conditionalFormatting sqref="C2:C66 C162:C186 C248:C272">
-    <cfRule type="expression" dxfId="7" priority="16">
+    <cfRule type="expression" dxfId="7" priority="17">
       <formula>$G2=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="expression" dxfId="6" priority="12">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>$G128=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G219 G220:H228 H229:H249 G229:G305 G306:H333">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G334:G367">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54">
-    <cfRule type="cellIs" dxfId="3" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="16" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H100:H127">
-    <cfRule type="cellIs" dxfId="2" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H174">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H260">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD68B06-4627-4CCF-9A3F-379B73171C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8430A3-63BB-4B14-A75A-04B5D5FDA383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Flags" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$432</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2449" uniqueCount="234">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -813,18 +813,12 @@
     <t>pi_BCG_att6t</t>
   </si>
   <si>
-    <t>≥</t>
-  </si>
-  <si>
     <t>high percentage non-native, tolerant individuals</t>
   </si>
   <si>
     <t>x_Shan_2</t>
   </si>
   <si>
-    <t>≤</t>
-  </si>
-  <si>
     <t>extremely unbalanced</t>
   </si>
   <si>
@@ -862,6 +856,21 @@
   </si>
   <si>
     <t>Boise BCG, bugs</t>
+  </si>
+  <si>
+    <t>Boise BCG, bugs, add sum_density_m2</t>
+  </si>
+  <si>
+    <t>sum_density_m2</t>
+  </si>
+  <si>
+    <t>low density</t>
+  </si>
+  <si>
+    <t>high density</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
   </si>
 </sst>
 </file>
@@ -1138,81 +1147,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1309,7 +1244,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Worksheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descriptions"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="16">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="8">
       <calculatedColumnFormula>HYPERLINK(FileName&amp;A16&amp;"!A1",A16)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1607,7 +1542,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1633,7 +1568,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1907,7 +1842,15 @@
         <v>46160</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="15">
+        <v>46161</v>
+      </c>
+      <c r="B49" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -2022,7 +1965,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J420"/>
+  <dimension ref="A1:J432"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -13698,13 +13641,13 @@
         <v>213</v>
       </c>
       <c r="D370" t="s">
+        <v>17</v>
+      </c>
+      <c r="E370">
+        <v>1</v>
+      </c>
+      <c r="F370" t="s">
         <v>214</v>
-      </c>
-      <c r="E370">
-        <v>1</v>
-      </c>
-      <c r="F370" t="s">
-        <v>215</v>
       </c>
       <c r="G370" t="b">
         <v>1</v>
@@ -13718,16 +13661,16 @@
         <v>210</v>
       </c>
       <c r="C371" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D371" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E371">
         <v>2</v>
       </c>
       <c r="F371" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G371" t="b">
         <v>1</v>
@@ -13750,7 +13693,7 @@
         <v>3</v>
       </c>
       <c r="F372" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G372" t="b">
         <v>1</v>
@@ -13773,7 +13716,7 @@
         <v>1</v>
       </c>
       <c r="F373" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G373" t="b">
         <v>1</v>
@@ -13790,13 +13733,13 @@
         <v>76</v>
       </c>
       <c r="D374" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E374">
         <v>2</v>
       </c>
       <c r="F374" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G374" t="b">
         <v>1</v>
@@ -13810,7 +13753,7 @@
         <v>210</v>
       </c>
       <c r="C375" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D375" t="s">
         <v>16</v>
@@ -13819,7 +13762,7 @@
         <v>1</v>
       </c>
       <c r="F375" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G375" t="b">
         <v>1</v>
@@ -13833,16 +13776,16 @@
         <v>210</v>
       </c>
       <c r="C376" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D376" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="E376">
         <v>3</v>
       </c>
       <c r="F376" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G376" t="b">
         <v>1</v>
@@ -13905,13 +13848,13 @@
         <v>213</v>
       </c>
       <c r="D379" t="s">
+        <v>17</v>
+      </c>
+      <c r="E379">
+        <v>1</v>
+      </c>
+      <c r="F379" t="s">
         <v>214</v>
-      </c>
-      <c r="E379">
-        <v>1</v>
-      </c>
-      <c r="F379" t="s">
-        <v>215</v>
       </c>
       <c r="G379" t="b">
         <v>1</v>
@@ -13925,16 +13868,16 @@
         <v>204</v>
       </c>
       <c r="C380" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D380" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E380">
         <v>2</v>
       </c>
       <c r="F380" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G380" t="b">
         <v>1</v>
@@ -13957,7 +13900,7 @@
         <v>3</v>
       </c>
       <c r="F381" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G381" t="b">
         <v>1</v>
@@ -13980,7 +13923,7 @@
         <v>1</v>
       </c>
       <c r="F382" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G382" t="b">
         <v>1</v>
@@ -13997,13 +13940,13 @@
         <v>76</v>
       </c>
       <c r="D383" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E383">
         <v>2</v>
       </c>
       <c r="F383" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G383" t="b">
         <v>1</v>
@@ -14017,7 +13960,7 @@
         <v>204</v>
       </c>
       <c r="C384" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D384" t="s">
         <v>16</v>
@@ -14026,7 +13969,7 @@
         <v>1</v>
       </c>
       <c r="F384" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G384" t="b">
         <v>1</v>
@@ -14040,16 +13983,16 @@
         <v>204</v>
       </c>
       <c r="C385" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D385" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="E385">
         <v>3</v>
       </c>
       <c r="F385" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G385" t="b">
         <v>1</v>
@@ -14060,7 +14003,7 @@
         <v>209</v>
       </c>
       <c r="B386" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C386" t="s">
         <v>14</v>
@@ -14083,7 +14026,7 @@
         <v>209</v>
       </c>
       <c r="B387" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C387" t="s">
         <v>14</v>
@@ -14106,19 +14049,19 @@
         <v>209</v>
       </c>
       <c r="B388" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C388" t="s">
         <v>213</v>
       </c>
       <c r="D388" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="E388">
         <v>10</v>
       </c>
       <c r="F388" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G388" t="b">
         <v>1</v>
@@ -14129,19 +14072,19 @@
         <v>209</v>
       </c>
       <c r="B389" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C389" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D389" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E389">
         <v>2</v>
       </c>
       <c r="F389" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G389" t="b">
         <v>1</v>
@@ -14152,7 +14095,7 @@
         <v>209</v>
       </c>
       <c r="B390" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C390" t="s">
         <v>72</v>
@@ -14164,7 +14107,7 @@
         <v>3</v>
       </c>
       <c r="F390" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G390" t="b">
         <v>1</v>
@@ -14175,7 +14118,7 @@
         <v>209</v>
       </c>
       <c r="B391" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C391" t="s">
         <v>74</v>
@@ -14187,7 +14130,7 @@
         <v>1</v>
       </c>
       <c r="F391" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G391" t="b">
         <v>1</v>
@@ -14198,19 +14141,19 @@
         <v>209</v>
       </c>
       <c r="B392" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C392" t="s">
         <v>76</v>
       </c>
       <c r="D392" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E392">
         <v>2</v>
       </c>
       <c r="F392" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G392" t="b">
         <v>1</v>
@@ -14221,10 +14164,10 @@
         <v>209</v>
       </c>
       <c r="B393" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C393" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D393" t="s">
         <v>16</v>
@@ -14233,7 +14176,7 @@
         <v>1</v>
       </c>
       <c r="F393" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G393" t="b">
         <v>1</v>
@@ -14244,19 +14187,19 @@
         <v>209</v>
       </c>
       <c r="B394" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C394" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D394" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="E394">
         <v>5</v>
       </c>
       <c r="F394" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G394" t="b">
         <v>1</v>
@@ -14267,7 +14210,7 @@
         <v>209</v>
       </c>
       <c r="B395" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C395" t="s">
         <v>14</v>
@@ -14290,7 +14233,7 @@
         <v>209</v>
       </c>
       <c r="B396" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C396" t="s">
         <v>14</v>
@@ -14313,19 +14256,19 @@
         <v>209</v>
       </c>
       <c r="B397" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C397" t="s">
         <v>213</v>
       </c>
       <c r="D397" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="E397">
         <v>10</v>
       </c>
       <c r="F397" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G397" t="b">
         <v>1</v>
@@ -14336,19 +14279,19 @@
         <v>209</v>
       </c>
       <c r="B398" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C398" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D398" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E398">
         <v>2.5</v>
       </c>
       <c r="F398" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G398" t="b">
         <v>1</v>
@@ -14359,7 +14302,7 @@
         <v>209</v>
       </c>
       <c r="B399" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C399" t="s">
         <v>72</v>
@@ -14371,7 +14314,7 @@
         <v>3</v>
       </c>
       <c r="F399" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G399" t="b">
         <v>1</v>
@@ -14382,19 +14325,19 @@
         <v>209</v>
       </c>
       <c r="B400" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C400" t="s">
         <v>76</v>
       </c>
       <c r="D400" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E400">
         <v>2</v>
       </c>
       <c r="F400" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G400" t="b">
         <v>1</v>
@@ -14405,10 +14348,10 @@
         <v>209</v>
       </c>
       <c r="B401" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C401" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D401" t="s">
         <v>16</v>
@@ -14417,7 +14360,7 @@
         <v>1</v>
       </c>
       <c r="F401" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G401" t="b">
         <v>1</v>
@@ -14428,19 +14371,19 @@
         <v>209</v>
       </c>
       <c r="B402" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C402" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D402" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="E402">
         <v>5</v>
       </c>
       <c r="F402" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G402" t="b">
         <v>1</v>
@@ -14451,7 +14394,7 @@
         <v>209</v>
       </c>
       <c r="B403" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C403" t="s">
         <v>14</v>
@@ -14474,7 +14417,7 @@
         <v>209</v>
       </c>
       <c r="B404" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C404" t="s">
         <v>14</v>
@@ -14497,19 +14440,19 @@
         <v>209</v>
       </c>
       <c r="B405" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C405" t="s">
         <v>213</v>
       </c>
       <c r="D405" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="E405">
         <v>5</v>
       </c>
       <c r="F405" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G405" t="b">
         <v>1</v>
@@ -14520,19 +14463,19 @@
         <v>209</v>
       </c>
       <c r="B406" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C406" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D406" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E406">
         <v>1.75</v>
       </c>
       <c r="F406" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G406" t="b">
         <v>1</v>
@@ -14543,7 +14486,7 @@
         <v>209</v>
       </c>
       <c r="B407" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C407" t="s">
         <v>72</v>
@@ -14555,7 +14498,7 @@
         <v>3</v>
       </c>
       <c r="F407" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G407" t="b">
         <v>1</v>
@@ -14566,7 +14509,7 @@
         <v>209</v>
       </c>
       <c r="B408" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C408" t="s">
         <v>74</v>
@@ -14578,7 +14521,7 @@
         <v>1</v>
       </c>
       <c r="F408" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G408" t="b">
         <v>1</v>
@@ -14589,19 +14532,19 @@
         <v>209</v>
       </c>
       <c r="B409" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C409" t="s">
         <v>76</v>
       </c>
       <c r="D409" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E409">
         <v>2</v>
       </c>
       <c r="F409" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G409" t="b">
         <v>1</v>
@@ -14612,10 +14555,10 @@
         <v>209</v>
       </c>
       <c r="B410" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C410" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D410" t="s">
         <v>16</v>
@@ -14624,7 +14567,7 @@
         <v>1</v>
       </c>
       <c r="F410" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G410" t="b">
         <v>1</v>
@@ -14635,19 +14578,19 @@
         <v>209</v>
       </c>
       <c r="B411" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C411" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D411" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="E411">
         <v>4</v>
       </c>
       <c r="F411" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G411" t="b">
         <v>1</v>
@@ -14658,7 +14601,7 @@
         <v>209</v>
       </c>
       <c r="B412" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C412" t="s">
         <v>14</v>
@@ -14681,7 +14624,7 @@
         <v>209</v>
       </c>
       <c r="B413" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C413" t="s">
         <v>14</v>
@@ -14704,19 +14647,19 @@
         <v>209</v>
       </c>
       <c r="B414" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C414" t="s">
         <v>213</v>
       </c>
       <c r="D414" t="s">
+        <v>17</v>
+      </c>
+      <c r="E414">
+        <v>1</v>
+      </c>
+      <c r="F414" t="s">
         <v>214</v>
-      </c>
-      <c r="E414">
-        <v>1</v>
-      </c>
-      <c r="F414" t="s">
-        <v>215</v>
       </c>
       <c r="G414" t="b">
         <v>1</v>
@@ -14727,19 +14670,19 @@
         <v>209</v>
       </c>
       <c r="B415" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C415" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D415" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E415">
         <v>2</v>
       </c>
       <c r="F415" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G415" t="b">
         <v>1</v>
@@ -14750,7 +14693,7 @@
         <v>209</v>
       </c>
       <c r="B416" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C416" t="s">
         <v>72</v>
@@ -14762,7 +14705,7 @@
         <v>3</v>
       </c>
       <c r="F416" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G416" t="b">
         <v>1</v>
@@ -14773,7 +14716,7 @@
         <v>209</v>
       </c>
       <c r="B417" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C417" t="s">
         <v>74</v>
@@ -14785,7 +14728,7 @@
         <v>1</v>
       </c>
       <c r="F417" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G417" t="b">
         <v>1</v>
@@ -14796,19 +14739,19 @@
         <v>209</v>
       </c>
       <c r="B418" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C418" t="s">
         <v>76</v>
       </c>
       <c r="D418" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E418">
         <v>2</v>
       </c>
       <c r="F418" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G418" t="b">
         <v>1</v>
@@ -14819,10 +14762,10 @@
         <v>209</v>
       </c>
       <c r="B419" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C419" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D419" t="s">
         <v>16</v>
@@ -14831,7 +14774,7 @@
         <v>1</v>
       </c>
       <c r="F419" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G419" t="b">
         <v>1</v>
@@ -14842,26 +14785,302 @@
         <v>209</v>
       </c>
       <c r="B420" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C420" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D420" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="E420">
         <v>4</v>
       </c>
       <c r="F420" t="s">
+        <v>223</v>
+      </c>
+      <c r="G420" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>209</v>
+      </c>
+      <c r="B421" t="s">
+        <v>210</v>
+      </c>
+      <c r="C421" t="s">
+        <v>230</v>
+      </c>
+      <c r="D421" t="s">
+        <v>16</v>
+      </c>
+      <c r="E421">
+        <v>1000</v>
+      </c>
+      <c r="F421" t="s">
+        <v>231</v>
+      </c>
+      <c r="G421" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>209</v>
+      </c>
+      <c r="B422" t="s">
+        <v>204</v>
+      </c>
+      <c r="C422" t="s">
+        <v>230</v>
+      </c>
+      <c r="D422" t="s">
+        <v>16</v>
+      </c>
+      <c r="E422">
+        <v>1000</v>
+      </c>
+      <c r="F422" t="s">
+        <v>231</v>
+      </c>
+      <c r="G422" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>209</v>
+      </c>
+      <c r="B423" t="s">
+        <v>224</v>
+      </c>
+      <c r="C423" t="s">
+        <v>230</v>
+      </c>
+      <c r="D423" t="s">
+        <v>16</v>
+      </c>
+      <c r="E423">
+        <v>1000</v>
+      </c>
+      <c r="F423" t="s">
+        <v>231</v>
+      </c>
+      <c r="G423" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>209</v>
+      </c>
+      <c r="B424" t="s">
         <v>225</v>
       </c>
-      <c r="G420" t="b">
+      <c r="C424" t="s">
+        <v>230</v>
+      </c>
+      <c r="D424" t="s">
+        <v>16</v>
+      </c>
+      <c r="E424">
+        <v>1000</v>
+      </c>
+      <c r="F424" t="s">
+        <v>231</v>
+      </c>
+      <c r="G424" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>209</v>
+      </c>
+      <c r="B425" t="s">
+        <v>226</v>
+      </c>
+      <c r="C425" t="s">
+        <v>230</v>
+      </c>
+      <c r="D425" t="s">
+        <v>16</v>
+      </c>
+      <c r="E425">
+        <v>1000</v>
+      </c>
+      <c r="F425" t="s">
+        <v>231</v>
+      </c>
+      <c r="G425" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>209</v>
+      </c>
+      <c r="B426" t="s">
+        <v>227</v>
+      </c>
+      <c r="C426" t="s">
+        <v>230</v>
+      </c>
+      <c r="D426" t="s">
+        <v>16</v>
+      </c>
+      <c r="E426">
+        <v>1000</v>
+      </c>
+      <c r="F426" t="s">
+        <v>231</v>
+      </c>
+      <c r="G426" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>209</v>
+      </c>
+      <c r="B427" t="s">
+        <v>210</v>
+      </c>
+      <c r="C427" t="s">
+        <v>230</v>
+      </c>
+      <c r="D427" t="s">
+        <v>15</v>
+      </c>
+      <c r="E427">
+        <v>10000</v>
+      </c>
+      <c r="F427" t="s">
+        <v>232</v>
+      </c>
+      <c r="G427" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>209</v>
+      </c>
+      <c r="B428" t="s">
+        <v>204</v>
+      </c>
+      <c r="C428" t="s">
+        <v>230</v>
+      </c>
+      <c r="D428" t="s">
+        <v>15</v>
+      </c>
+      <c r="E428">
+        <v>10000</v>
+      </c>
+      <c r="F428" t="s">
+        <v>232</v>
+      </c>
+      <c r="G428" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>209</v>
+      </c>
+      <c r="B429" t="s">
+        <v>224</v>
+      </c>
+      <c r="C429" t="s">
+        <v>230</v>
+      </c>
+      <c r="D429" t="s">
+        <v>15</v>
+      </c>
+      <c r="E429">
+        <v>10000</v>
+      </c>
+      <c r="F429" t="s">
+        <v>232</v>
+      </c>
+      <c r="G429" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>209</v>
+      </c>
+      <c r="B430" t="s">
+        <v>225</v>
+      </c>
+      <c r="C430" t="s">
+        <v>230</v>
+      </c>
+      <c r="D430" t="s">
+        <v>15</v>
+      </c>
+      <c r="E430">
+        <v>10000</v>
+      </c>
+      <c r="F430" t="s">
+        <v>232</v>
+      </c>
+      <c r="G430" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>209</v>
+      </c>
+      <c r="B431" t="s">
+        <v>226</v>
+      </c>
+      <c r="C431" t="s">
+        <v>230</v>
+      </c>
+      <c r="D431" t="s">
+        <v>15</v>
+      </c>
+      <c r="E431">
+        <v>10000</v>
+      </c>
+      <c r="F431" t="s">
+        <v>232</v>
+      </c>
+      <c r="G431" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>209</v>
+      </c>
+      <c r="B432" t="s">
+        <v>227</v>
+      </c>
+      <c r="C432" t="s">
+        <v>230</v>
+      </c>
+      <c r="D432" t="s">
+        <v>15</v>
+      </c>
+      <c r="E432">
+        <v>10000</v>
+      </c>
+      <c r="F432" t="s">
+        <v>232</v>
+      </c>
+      <c r="G432" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J363" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:J432" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <conditionalFormatting sqref="C2:C66 C162:C186 C248:C272">
     <cfRule type="expression" dxfId="7" priority="17">
       <formula>$G2=FALSE</formula>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8430A3-63BB-4B14-A75A-04B5D5FDA383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F301F61-0BAD-49DB-81CF-497AB54A188F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Flags" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$432</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$523</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2449" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="276">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -872,12 +872,141 @@
   <si>
     <t>&lt;=</t>
   </si>
+  <si>
+    <t>Xeric_Multihab</t>
+  </si>
+  <si>
+    <t>imbalanced</t>
+  </si>
+  <si>
+    <t>nt_EPT_volt_semi</t>
+  </si>
+  <si>
+    <t>missing semivoltine EPT taxa</t>
+  </si>
+  <si>
+    <t>nt_ffg_pred_scrap_shred</t>
+  </si>
+  <si>
+    <t>missing taxa from key FFGs</t>
+  </si>
+  <si>
+    <t>lack of cold or cool taxa</t>
+  </si>
+  <si>
+    <t>high number warm stenotherm taxa</t>
+  </si>
+  <si>
+    <t>potential disturbance; high percent Simuliidae and Baetis tricaudatus complex individuals</t>
+  </si>
+  <si>
+    <t>pt_habitat_loti</t>
+  </si>
+  <si>
+    <t>high percent lotic taxa</t>
+  </si>
+  <si>
+    <t>nt_noteworthy</t>
+  </si>
+  <si>
+    <t>more than two noteworthy taxa</t>
+  </si>
+  <si>
+    <t>Xeric_Riffle</t>
+  </si>
+  <si>
+    <t>MountainCold_Multihab</t>
+  </si>
+  <si>
+    <t>unusually low number of taxa</t>
+  </si>
+  <si>
+    <t>imbalanced for this class</t>
+  </si>
+  <si>
+    <t>pi_BCG_att56t</t>
+  </si>
+  <si>
+    <t>presence of highly tolerant individuals</t>
+  </si>
+  <si>
+    <t>pi_NonInsTrombJuga_BCG_att456</t>
+  </si>
+  <si>
+    <t>unusually high proportion of non-sensitive, non-insect individuals</t>
+  </si>
+  <si>
+    <t>presence of warm stenotherm taxa</t>
+  </si>
+  <si>
+    <t>presence of four or more noteworthy taxa</t>
+  </si>
+  <si>
+    <t>unusually low percent lotic taxa for this class</t>
+  </si>
+  <si>
+    <t>MountainCold_Riffle</t>
+  </si>
+  <si>
+    <t>high highly tolerant (Att56t) individuals for this class</t>
+  </si>
+  <si>
+    <t>unusually low number of semivoltine EPT taxa</t>
+  </si>
+  <si>
+    <t>low number of cold water taxa</t>
+  </si>
+  <si>
+    <t>unusually low number of stonefly taxa</t>
+  </si>
+  <si>
+    <t>presence of more than four noteworthy taxa</t>
+  </si>
+  <si>
+    <t>NBR_Riffle</t>
+  </si>
+  <si>
+    <t>nt_largeriver</t>
+  </si>
+  <si>
+    <t>large river signal</t>
+  </si>
+  <si>
+    <t>two or more noteworthy taxa</t>
+  </si>
+  <si>
+    <t>Foothills_Multihab</t>
+  </si>
+  <si>
+    <t>Foothills_Riffle</t>
+  </si>
+  <si>
+    <t>pi_dom02_BCG_att456</t>
+  </si>
+  <si>
+    <t>high dominance by two tolerant (Attr IV,V,VI) taxa</t>
+  </si>
+  <si>
+    <t>pt_Chiro</t>
+  </si>
+  <si>
+    <t>unusually high percentage of Chironomidae taxa</t>
+  </si>
+  <si>
+    <t>unusually low number of cold or cool water taxa</t>
+  </si>
+  <si>
+    <t>dom02 version is new, dom01 version exists</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -987,8 +1116,53 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1037,6 +1211,16 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1065,7 +1249,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1074,8 +1258,11 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
@@ -1139,12 +1326,99 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="7" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="7" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="6"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="8">
+    <cellStyle name="Bad" xfId="6" builtinId="27"/>
+    <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="3" builtinId="17"/>
     <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal_SpCorr" xfId="7" xr:uid="{990E98AA-77C4-4E24-BA1A-407362A1E1AF}"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
   <dxfs count="9">
@@ -1542,7 +1816,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1568,7 +1842,8 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
-        <v>46161</v>
+        <f>MAX(A22:A574)</f>
+        <v>46182</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1851,6 +2126,14 @@
       </c>
       <c r="B49" t="s">
         <v>229</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="15">
+        <v>46182</v>
+      </c>
+      <c r="B50" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1965,13 +2248,13 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J432"/>
+  <dimension ref="A1:J523"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
     <col min="2" max="2" width="16.140625" customWidth="1"/>
     <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47" customWidth="1"/>
     <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="58.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -13514,6 +13797,14 @@
       <c r="G364" t="b">
         <v>1</v>
       </c>
+      <c r="I364" t="str">
+        <f t="shared" ref="I364:I427" si="15">B364</f>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J364" t="str">
+        <f t="shared" ref="J364:J427" si="16">A364</f>
+        <v>LBR_Fish_BCG_v1</v>
+      </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
@@ -13537,6 +13828,14 @@
       <c r="G365" t="b">
         <v>1</v>
       </c>
+      <c r="I365" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J365" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Fish_BCG_v1</v>
+      </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
@@ -13560,6 +13859,14 @@
       <c r="G366" t="b">
         <v>1</v>
       </c>
+      <c r="I366" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J366" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Fish_BCG_v1</v>
+      </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
@@ -13583,6 +13890,14 @@
       <c r="G367" t="b">
         <v>1</v>
       </c>
+      <c r="I367" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J367" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Fish_BCG_v1</v>
+      </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
@@ -13606,8 +13921,16 @@
       <c r="G368" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I368" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J368" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>209</v>
       </c>
@@ -13629,8 +13952,16 @@
       <c r="G369" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I369" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J369" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>209</v>
       </c>
@@ -13652,8 +13983,16 @@
       <c r="G370" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I370" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J370" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>209</v>
       </c>
@@ -13675,8 +14014,16 @@
       <c r="G371" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I371" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J371" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>209</v>
       </c>
@@ -13698,8 +14045,16 @@
       <c r="G372" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I372" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J372" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>209</v>
       </c>
@@ -13721,8 +14076,16 @@
       <c r="G373" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I373" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J373" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>209</v>
       </c>
@@ -13744,8 +14107,16 @@
       <c r="G374" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I374" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J374" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>209</v>
       </c>
@@ -13767,8 +14138,16 @@
       <c r="G375" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I375" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J375" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>209</v>
       </c>
@@ -13790,8 +14169,16 @@
       <c r="G376" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I376" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J376" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>209</v>
       </c>
@@ -13813,8 +14200,16 @@
       <c r="G377" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I377" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J377" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>209</v>
       </c>
@@ -13836,8 +14231,16 @@
       <c r="G378" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I378" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J378" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>209</v>
       </c>
@@ -13859,8 +14262,16 @@
       <c r="G379" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I379" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J379" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>209</v>
       </c>
@@ -13882,8 +14293,16 @@
       <c r="G380" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I380" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J380" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>209</v>
       </c>
@@ -13905,8 +14324,16 @@
       <c r="G381" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I381" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J381" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>209</v>
       </c>
@@ -13928,8 +14355,16 @@
       <c r="G382" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I382" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J382" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>209</v>
       </c>
@@ -13951,8 +14386,16 @@
       <c r="G383" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I383" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J383" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>209</v>
       </c>
@@ -13974,8 +14417,16 @@
       <c r="G384" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I384" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J384" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>209</v>
       </c>
@@ -13997,8 +14448,16 @@
       <c r="G385" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I385" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J385" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>209</v>
       </c>
@@ -14020,8 +14479,16 @@
       <c r="G386" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I386" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J386" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>209</v>
       </c>
@@ -14043,8 +14510,16 @@
       <c r="G387" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I387" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J387" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>209</v>
       </c>
@@ -14066,8 +14541,16 @@
       <c r="G388" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I388" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J388" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>209</v>
       </c>
@@ -14089,8 +14572,16 @@
       <c r="G389" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I389" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J389" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>209</v>
       </c>
@@ -14112,8 +14603,16 @@
       <c r="G390" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I390" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J390" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>209</v>
       </c>
@@ -14135,8 +14634,16 @@
       <c r="G391" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I391" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J391" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>209</v>
       </c>
@@ -14158,8 +14665,16 @@
       <c r="G392" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I392" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J392" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>209</v>
       </c>
@@ -14181,8 +14696,16 @@
       <c r="G393" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I393" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J393" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>209</v>
       </c>
@@ -14204,8 +14727,16 @@
       <c r="G394" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I394" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J394" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>209</v>
       </c>
@@ -14227,8 +14758,16 @@
       <c r="G395" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I395" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J395" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>209</v>
       </c>
@@ -14250,8 +14789,16 @@
       <c r="G396" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I396" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J396" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>209</v>
       </c>
@@ -14273,8 +14820,16 @@
       <c r="G397" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I397" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J397" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>209</v>
       </c>
@@ -14296,8 +14851,16 @@
       <c r="G398" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I398" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J398" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>209</v>
       </c>
@@ -14319,8 +14882,16 @@
       <c r="G399" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I399" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J399" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>209</v>
       </c>
@@ -14342,8 +14913,16 @@
       <c r="G400" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I400" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J400" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>209</v>
       </c>
@@ -14365,8 +14944,16 @@
       <c r="G401" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I401" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J401" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>209</v>
       </c>
@@ -14388,8 +14975,16 @@
       <c r="G402" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I402" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J402" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>209</v>
       </c>
@@ -14411,8 +15006,16 @@
       <c r="G403" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I403" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J403" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>209</v>
       </c>
@@ -14434,8 +15037,16 @@
       <c r="G404" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I404" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J404" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>209</v>
       </c>
@@ -14457,8 +15068,16 @@
       <c r="G405" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I405" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J405" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>209</v>
       </c>
@@ -14480,8 +15099,16 @@
       <c r="G406" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I406" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J406" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>209</v>
       </c>
@@ -14503,8 +15130,16 @@
       <c r="G407" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I407" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J407" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>209</v>
       </c>
@@ -14526,8 +15161,16 @@
       <c r="G408" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I408" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J408" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>209</v>
       </c>
@@ -14549,8 +15192,16 @@
       <c r="G409" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I409" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J409" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>209</v>
       </c>
@@ -14572,8 +15223,16 @@
       <c r="G410" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I410" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J410" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>209</v>
       </c>
@@ -14595,8 +15254,16 @@
       <c r="G411" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I411" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J411" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>209</v>
       </c>
@@ -14618,8 +15285,16 @@
       <c r="G412" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I412" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J412" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>209</v>
       </c>
@@ -14641,8 +15316,16 @@
       <c r="G413" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I413" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J413" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>209</v>
       </c>
@@ -14664,8 +15347,16 @@
       <c r="G414" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I414" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J414" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>209</v>
       </c>
@@ -14687,8 +15378,16 @@
       <c r="G415" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I415" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J415" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>209</v>
       </c>
@@ -14710,8 +15409,16 @@
       <c r="G416" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I416" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J416" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>209</v>
       </c>
@@ -14733,8 +15440,16 @@
       <c r="G417" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I417" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J417" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>209</v>
       </c>
@@ -14756,8 +15471,16 @@
       <c r="G418" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I418" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J418" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>209</v>
       </c>
@@ -14779,8 +15502,16 @@
       <c r="G419" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I419" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J419" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>209</v>
       </c>
@@ -14802,8 +15533,16 @@
       <c r="G420" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I420" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J420" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>209</v>
       </c>
@@ -14825,8 +15564,16 @@
       <c r="G421" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I421" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J421" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>209</v>
       </c>
@@ -14848,8 +15595,16 @@
       <c r="G422" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I422" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J422" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>209</v>
       </c>
@@ -14871,8 +15626,16 @@
       <c r="G423" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I423" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J423" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>209</v>
       </c>
@@ -14894,8 +15657,16 @@
       <c r="G424" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I424" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J424" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>209</v>
       </c>
@@ -14917,8 +15688,16 @@
       <c r="G425" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I425" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J425" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>209</v>
       </c>
@@ -14940,8 +15719,16 @@
       <c r="G426" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I426" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J426" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>209</v>
       </c>
@@ -14963,8 +15750,16 @@
       <c r="G427" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I427" t="str">
+        <f t="shared" si="15"/>
+        <v>Main_BarberPool</v>
+      </c>
+      <c r="J427" t="str">
+        <f t="shared" si="16"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>209</v>
       </c>
@@ -14986,8 +15781,16 @@
       <c r="G428" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I428" t="str">
+        <f t="shared" ref="I428:I432" si="17">B428</f>
+        <v>Main_Eckert</v>
+      </c>
+      <c r="J428" t="str">
+        <f t="shared" ref="J428:J432" si="18">A428</f>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>209</v>
       </c>
@@ -15009,8 +15812,16 @@
       <c r="G429" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I429" t="str">
+        <f t="shared" si="17"/>
+        <v>Main_Middleton</v>
+      </c>
+      <c r="J429" t="str">
+        <f t="shared" si="18"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>209</v>
       </c>
@@ -15032,8 +15843,16 @@
       <c r="G430" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I430" t="str">
+        <f t="shared" si="17"/>
+        <v>Main_NotusParma</v>
+      </c>
+      <c r="J430" t="str">
+        <f t="shared" si="18"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>209</v>
       </c>
@@ -15055,8 +15874,16 @@
       <c r="G431" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I431" t="str">
+        <f t="shared" si="17"/>
+        <v>Main_SoChannel</v>
+      </c>
+      <c r="J431" t="str">
+        <f t="shared" si="18"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>209</v>
       </c>
@@ -15078,46 +15905,2878 @@
       <c r="G432" t="b">
         <v>1</v>
       </c>
+      <c r="I432" t="str">
+        <f t="shared" si="17"/>
+        <v>Main_VetGlen</v>
+      </c>
+      <c r="J432" t="str">
+        <f t="shared" si="18"/>
+        <v>LBR_Bugs_BCG_v1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A433" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B433" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C433" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D433" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E433" s="35">
+        <v>450</v>
+      </c>
+      <c r="F433" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="G433" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I433" t="str">
+        <f>B433</f>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J433" t="str">
+        <f>A433</f>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A434" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B434" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C434" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="D434" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E434" s="35">
+        <v>3.3</v>
+      </c>
+      <c r="F434" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="G434" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I434" t="str">
+        <f t="shared" ref="I434:I497" si="19">B434</f>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J434" t="str">
+        <f t="shared" ref="J434:J497" si="20">A434</f>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A435" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B435" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C435" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="D435" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E435" s="35">
+        <v>0</v>
+      </c>
+      <c r="F435" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="G435" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I435" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J435" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A436" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B436" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C436" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="D436" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E436" s="35">
+        <v>20</v>
+      </c>
+      <c r="F436" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="G436" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I436" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J436" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A437" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B437" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C437" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D437" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E437" s="35">
+        <v>2</v>
+      </c>
+      <c r="F437" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="G437" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I437" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J437" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A438" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B438" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C438" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D438" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E438" s="35">
+        <v>5</v>
+      </c>
+      <c r="F438" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="G438" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I438" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J438" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A439" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B439" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C439" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D439" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E439" s="35">
+        <v>3</v>
+      </c>
+      <c r="F439" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="G439" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I439" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J439" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A440" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B440" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C440" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D440" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E440" s="35">
+        <v>0</v>
+      </c>
+      <c r="F440" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="G440" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I440" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J440" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A441" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B441" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C441" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D441" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E441" s="35">
+        <v>2</v>
+      </c>
+      <c r="F441" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="G441" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I441" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J441" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A442" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B442" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C442" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D442" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E442" s="35">
+        <v>25</v>
+      </c>
+      <c r="F442" t="s">
+        <v>242</v>
+      </c>
+      <c r="G442" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I442" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J442" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A443" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B443" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="C443" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="D443" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E443" s="42">
+        <v>50</v>
+      </c>
+      <c r="F443" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="G443" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I443" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J443" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A444" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B444" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C444" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="D444" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E444" s="35">
+        <v>2</v>
+      </c>
+      <c r="F444" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="G444" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I444" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J444" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A445" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B445" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C445" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D445" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E445" s="35">
+        <v>450</v>
+      </c>
+      <c r="F445" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="G445" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I445" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J445" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A446" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B446" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C446" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="D446" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E446" s="35">
+        <v>2.5</v>
+      </c>
+      <c r="F446" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="G446" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I446" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J446" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A447" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B447" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C447" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="D447" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E447" s="35">
+        <v>0</v>
+      </c>
+      <c r="F447" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="G447" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I447" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J447" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A448" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B448" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C448" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="D448" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E448" s="35">
+        <v>20</v>
+      </c>
+      <c r="F448" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="G448" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I448" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J448" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A449" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B449" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C449" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D449" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E449" s="35">
+        <v>1</v>
+      </c>
+      <c r="F449" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="G449" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I449" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J449" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A450" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B450" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C450" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D450" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E450" s="35">
+        <v>5</v>
+      </c>
+      <c r="F450" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="G450" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I450" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J450" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A451" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B451" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C451" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D451" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E451" s="35">
+        <v>4</v>
+      </c>
+      <c r="F451" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="G451" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I451" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J451" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A452" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B452" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C452" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D452" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E452" s="35">
+        <v>0</v>
+      </c>
+      <c r="F452" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="G452" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I452" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J452" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A453" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B453" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C453" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D453" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E453" s="35">
+        <v>4</v>
+      </c>
+      <c r="F453" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="G453" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I453" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J453" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A454" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B454" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C454" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D454" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E454" s="35">
+        <v>5</v>
+      </c>
+      <c r="F454" t="s">
+        <v>242</v>
+      </c>
+      <c r="G454" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I454" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J454" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A455" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B455" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C455" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="D455" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E455" s="42">
+        <v>55</v>
+      </c>
+      <c r="F455" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="G455" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I455" t="str">
+        <f t="shared" si="19"/>
+        <v>Xeric_Riffle</v>
+      </c>
+      <c r="J455" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="456" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A456" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B456" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C456" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D456" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E456" s="35">
+        <v>450</v>
+      </c>
+      <c r="F456" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="G456" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I456" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J456" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A457" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B457" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C457" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D457" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E457" s="35">
+        <v>35</v>
+      </c>
+      <c r="F457" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="G457" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I457" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J457" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="458" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A458" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B458" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C458" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="D458" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E458" s="35">
+        <v>3.5</v>
+      </c>
+      <c r="F458" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="G458" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I458" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J458" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="459" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A459" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B459" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C459" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="D459" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E459" s="35">
+        <v>0</v>
+      </c>
+      <c r="F459" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="G459" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I459" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J459" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="460" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A460" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B460" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C460" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="D460" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E460" s="35">
+        <v>30</v>
+      </c>
+      <c r="F460" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="G460" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I460" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J460" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="461" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A461" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B461" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C461" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="D461" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E461" s="35">
+        <v>0</v>
+      </c>
+      <c r="F461" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="G461" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I461" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J461" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="462" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A462" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B462" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C462" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="D462" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E462" s="35">
+        <v>25</v>
+      </c>
+      <c r="F462" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="G462" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I462" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J462" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="463" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A463" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B463" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C463" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D463" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E463" s="35">
+        <v>0</v>
+      </c>
+      <c r="F463" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="G463" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I463" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J463" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="464" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A464" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B464" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C464" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D464" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E464" s="35">
+        <v>4</v>
+      </c>
+      <c r="F464" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="G464" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I464" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J464" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="465" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A465" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B465" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C465" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D465" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E465" s="35">
+        <v>3</v>
+      </c>
+      <c r="F465" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="G465" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I465" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J465" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A466" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B466" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C466" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D466" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E466" s="35">
+        <v>4</v>
+      </c>
+      <c r="F466" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="G466" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I466" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J466" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="467" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A467" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="B467" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="C467" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D467" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E467" s="46">
+        <v>5</v>
+      </c>
+      <c r="F467" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="G467" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I467" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J467" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="468" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A468" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B468" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C468" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="D468" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E468" s="35">
+        <v>4</v>
+      </c>
+      <c r="F468" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="G468" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I468" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J468" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="469" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A469" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B469" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="C469" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="D469" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E469" s="42">
+        <v>45</v>
+      </c>
+      <c r="F469" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="G469" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I469" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Multihab</v>
+      </c>
+      <c r="J469" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A470" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B470" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C470" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D470" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E470" s="28">
+        <v>450</v>
+      </c>
+      <c r="F470" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="G470" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I470" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J470" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="471" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A471" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B471" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C471" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="D471" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E471" s="28">
+        <v>35</v>
+      </c>
+      <c r="F471" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="G471" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I471" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J471" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="472" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A472" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B472" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C472" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="D472" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E472" s="49">
+        <v>3</v>
+      </c>
+      <c r="F472" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="G472" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I472" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J472" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A473" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B473" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C473" t="s">
+        <v>251</v>
+      </c>
+      <c r="D473" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E473" s="28">
+        <v>1</v>
+      </c>
+      <c r="F473" s="48" t="s">
+        <v>259</v>
+      </c>
+      <c r="G473" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I473" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J473" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A474" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B474" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C474" t="s">
+        <v>253</v>
+      </c>
+      <c r="D474" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E474" s="28">
+        <v>15</v>
+      </c>
+      <c r="F474" s="48" t="s">
+        <v>254</v>
+      </c>
+      <c r="G474" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I474" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J474" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A475" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B475" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C475" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="D475" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E475" s="28">
+        <v>3</v>
+      </c>
+      <c r="F475" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="G475" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I475" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J475" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A476" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B476" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C476" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="D476" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E476" s="28">
+        <v>24</v>
+      </c>
+      <c r="F476" s="48" t="s">
+        <v>239</v>
+      </c>
+      <c r="G476" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I476" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J476" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A477" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B477" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C477" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="D477" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E477" s="35">
+        <v>5</v>
+      </c>
+      <c r="F477" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="G477" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I477" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J477" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A478" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B478" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C478" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="D478" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E478" s="28">
+        <v>0</v>
+      </c>
+      <c r="F478" s="48" t="s">
+        <v>255</v>
+      </c>
+      <c r="G478" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I478" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J478" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A479" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B479" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C479" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="D479" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E479" s="28">
+        <v>5</v>
+      </c>
+      <c r="F479" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="G479" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I479" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J479" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A480" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B480" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C480" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="D480" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E480" s="28">
+        <v>4</v>
+      </c>
+      <c r="F480" s="48" t="s">
+        <v>262</v>
+      </c>
+      <c r="G480" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I480" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J480" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A481" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B481" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C481" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="D481" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E481" s="28">
+        <v>5</v>
+      </c>
+      <c r="F481" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="G481" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I481" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J481" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A482" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="B482" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="C482" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D482" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E482" s="46">
+        <v>5</v>
+      </c>
+      <c r="F482" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="G482" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I482" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J482" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A483" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B483" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C483" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="D483" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E483" s="28">
+        <v>4</v>
+      </c>
+      <c r="F483" s="48" t="s">
+        <v>263</v>
+      </c>
+      <c r="G483" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I483" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J483" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A484" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B484" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="C484" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="D484" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="E484" s="53">
+        <v>60</v>
+      </c>
+      <c r="F484" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="G484" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I484" t="str">
+        <f t="shared" si="19"/>
+        <v>MountainCold_Riffle</v>
+      </c>
+      <c r="J484" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A485" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B485" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C485" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D485" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E485" s="28">
+        <v>450</v>
+      </c>
+      <c r="F485" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="G485" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I485" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J485" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A486" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B486" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C486" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="D486" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E486" s="55">
+        <v>3</v>
+      </c>
+      <c r="F486" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="G486" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I486" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J486" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A487" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B487" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C487" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="D487" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E487" s="28">
+        <v>0</v>
+      </c>
+      <c r="F487" s="48" t="s">
+        <v>237</v>
+      </c>
+      <c r="G487" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I487" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J487" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A488" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B488" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C488" s="48" t="s">
+        <v>220</v>
+      </c>
+      <c r="D488" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E488" s="28">
+        <v>1</v>
+      </c>
+      <c r="F488" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="G488" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I488" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J488" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A489" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B489" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C489" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="D489" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E489" s="28">
+        <v>5</v>
+      </c>
+      <c r="F489" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="G489" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I489" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J489" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A490" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B490" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C490" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="D490" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E490" s="28">
+        <v>4</v>
+      </c>
+      <c r="F490" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="G490" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I490" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J490" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A491" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B491" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C491" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="D491" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E491" s="28">
+        <v>0</v>
+      </c>
+      <c r="F491" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="G491" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I491" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J491" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A492" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B492" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C492" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="D492" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E492" s="28">
+        <v>4</v>
+      </c>
+      <c r="F492" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="G492" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I492" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J492" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A493" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B493" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C493" s="48" t="s">
+        <v>265</v>
+      </c>
+      <c r="D493" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E493" s="28">
+        <v>3</v>
+      </c>
+      <c r="F493" s="48" t="s">
+        <v>266</v>
+      </c>
+      <c r="G493" s="62" t="b">
+        <v>0</v>
+      </c>
+      <c r="I493" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J493" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A494" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B494" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C494" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D494" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E494" s="35">
+        <v>20</v>
+      </c>
+      <c r="F494" t="s">
+        <v>242</v>
+      </c>
+      <c r="G494" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I494" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J494" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A495" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B495" s="56" t="s">
+        <v>264</v>
+      </c>
+      <c r="C495" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="D495" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E495" s="42">
+        <v>50</v>
+      </c>
+      <c r="F495" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="G495" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I495" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J495" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A496" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B496" s="58" t="s">
+        <v>264</v>
+      </c>
+      <c r="C496" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="D496" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="E496" s="35">
+        <v>2</v>
+      </c>
+      <c r="F496" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="G496" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I496" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR_Riffle</v>
+      </c>
+      <c r="J496" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A497" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B497" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C497" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D497" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E497" s="35">
+        <v>450</v>
+      </c>
+      <c r="F497" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="G497" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I497" t="str">
+        <f t="shared" si="19"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J497" t="str">
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A498" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B498" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C498" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D498" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E498" s="35">
+        <v>35</v>
+      </c>
+      <c r="F498" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="G498" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I498" t="str">
+        <f t="shared" ref="I498:I523" si="21">B498</f>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J498" t="str">
+        <f t="shared" ref="J498:J523" si="22">A498</f>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A499" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B499" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C499" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="D499" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E499" s="35">
+        <v>45</v>
+      </c>
+      <c r="F499" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="G499" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I499" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J499" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A500" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B500" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C500" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="D500" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E500" s="35">
+        <v>3.3</v>
+      </c>
+      <c r="F500" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="G500" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I500" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J500" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A501" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B501" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C501" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="D501" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E501" s="35">
+        <v>0</v>
+      </c>
+      <c r="F501" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="G501" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I501" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J501" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A502" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B502" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C502" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="D502" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E502" s="35">
+        <v>20</v>
+      </c>
+      <c r="F502" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="G502" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I502" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J502" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A503" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B503" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C503" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D503" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E503" s="35">
+        <v>0</v>
+      </c>
+      <c r="F503" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="G503" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I503" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J503" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A504" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B504" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C504" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D504" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E504" s="35">
+        <v>4</v>
+      </c>
+      <c r="F504" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="G504" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I504" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J504" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A505" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B505" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C505" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D505" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E505" s="35">
+        <v>3</v>
+      </c>
+      <c r="F505" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="G505" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I505" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J505" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A506" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B506" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C506" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D506" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E506" s="35">
+        <v>3</v>
+      </c>
+      <c r="F506" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="G506" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I506" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J506" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="507" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A507" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B507" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C507" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="D507" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E507" s="35">
+        <v>4</v>
+      </c>
+      <c r="F507" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="G507" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I507" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J507" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A508" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B508" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="C508" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="D508" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E508" s="42">
+        <v>45</v>
+      </c>
+      <c r="F508" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="G508" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I508" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J508" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A509" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B509" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C509" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D509" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E509" s="35">
+        <v>25</v>
+      </c>
+      <c r="F509" t="s">
+        <v>242</v>
+      </c>
+      <c r="G509" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I509" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J509" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A510" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B510" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C510" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D510" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E510" s="35">
+        <v>450</v>
+      </c>
+      <c r="F510" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="G510" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I510" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J510" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A511" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B511" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C511" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D511" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E511" s="35">
+        <v>650</v>
+      </c>
+      <c r="F511" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="G511" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I511" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J511" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A512" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B512" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="C512" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="D512" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E512" s="42">
+        <v>60</v>
+      </c>
+      <c r="F512" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="G512" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I512" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J512" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A513" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B513" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="C513" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D513" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E513" s="42">
+        <v>50</v>
+      </c>
+      <c r="F513" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="G513" s="62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H513" t="s">
+        <v>275</v>
+      </c>
+      <c r="I513" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J513" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A514" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B514" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C514" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="D514" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E514" s="35">
+        <v>3</v>
+      </c>
+      <c r="F514" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="G514" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I514" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J514" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A515" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B515" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C515" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="D515" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="E515" s="35">
+        <v>35</v>
+      </c>
+      <c r="F515" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="G515" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I515" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J515" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A516" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B516" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C516" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="D516" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="E516" s="35">
+        <v>20</v>
+      </c>
+      <c r="F516" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="G516" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I516" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J516" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A517" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B517" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C517" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D517" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="E517" s="35">
+        <v>10</v>
+      </c>
+      <c r="F517" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="G517" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I517" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J517" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A518" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B518" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C518" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D518" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E518" s="35">
+        <v>0</v>
+      </c>
+      <c r="F518" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="G518" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I518" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J518" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A519" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B519" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C519" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D519" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E519" s="35">
+        <v>4</v>
+      </c>
+      <c r="F519" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="G519" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I519" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J519" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A520" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B520" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C520" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D520" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E520" s="35">
+        <v>3</v>
+      </c>
+      <c r="F520" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="G520" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I520" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J520" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="521" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A521" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B521" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C521" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D521" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E521" s="35">
+        <v>6</v>
+      </c>
+      <c r="F521" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="G521" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I521" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J521" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A522" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B522" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C522" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="D522" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E522" s="35">
+        <v>4</v>
+      </c>
+      <c r="F522" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="G522" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I522" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J522" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A523" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B523" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C523" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D523" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E523" s="35">
+        <v>40</v>
+      </c>
+      <c r="F523" t="s">
+        <v>242</v>
+      </c>
+      <c r="G523" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I523" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Riffle</v>
+      </c>
+      <c r="J523" t="str">
+        <f t="shared" si="22"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J432" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:J523" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <conditionalFormatting sqref="C2:C66 C162:C186 C248:C272">
-    <cfRule type="expression" dxfId="7" priority="17">
+    <cfRule type="expression" dxfId="7" priority="18">
       <formula>$G2=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="expression" dxfId="6" priority="13">
+    <cfRule type="expression" dxfId="6" priority="14">
       <formula>$G128=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G219 G220:H228 H229:H249 G229:G305 G306:H333">
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G334:G367">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54">
-    <cfRule type="cellIs" dxfId="3" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="17" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H100:H127">
-    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="16" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H174">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H260">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BCGcalc/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F301F61-0BAD-49DB-81CF-497AB54A188F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{9F301F61-0BAD-49DB-81CF-497AB54A188F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0DBF658-4378-4FBF-89A3-28E72759A95B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3200" uniqueCount="286">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -997,6 +997,36 @@
   </si>
   <si>
     <t>dom02 version is new, dom01 version exists</t>
+  </si>
+  <si>
+    <t>Lowlands_Riffle</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>≤</t>
+  </si>
+  <si>
+    <t>missing noteworthy taxa</t>
+  </si>
+  <si>
+    <t>Lowlands_Multihab_HiGrad</t>
+  </si>
+  <si>
+    <t>unusually low number of cold or cool water taxa for this class</t>
+  </si>
+  <si>
+    <t>Lowlands_Multihab_LoGrad</t>
+  </si>
+  <si>
+    <t>unusually high percent lotic taxa for this class</t>
+  </si>
+  <si>
+    <t>very imbalanced for this class</t>
+  </si>
+  <si>
+    <t>more than one warm stenotherm taxa</t>
   </si>
 </sst>
 </file>
@@ -1852,7 +1882,7 @@
       </c>
       <c r="B7" s="6" t="str">
         <f ca="1">LEFT(CELL("filename",B7),FIND("]",CELL("filename",B7)))</f>
-        <v>C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\[MetricFlags.xlsx]</v>
+        <v>https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BCGcalc/inst/extdata/[MetricFlags.xlsx]</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2248,7 +2278,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J523"/>
+  <dimension ref="A1:J565"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -18736,6 +18766,1224 @@
       <c r="J523" t="str">
         <f t="shared" si="22"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>178</v>
+      </c>
+      <c r="B524" t="s">
+        <v>276</v>
+      </c>
+      <c r="C524" t="s">
+        <v>14</v>
+      </c>
+      <c r="D524" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E524" s="28">
+        <v>450</v>
+      </c>
+      <c r="F524" t="s">
+        <v>211</v>
+      </c>
+      <c r="G524" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I524" t="s">
+        <v>276</v>
+      </c>
+      <c r="J524" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>178</v>
+      </c>
+      <c r="B525" t="s">
+        <v>276</v>
+      </c>
+      <c r="C525" t="s">
+        <v>14</v>
+      </c>
+      <c r="D525" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E525" s="28">
+        <v>650</v>
+      </c>
+      <c r="F525" t="s">
+        <v>212</v>
+      </c>
+      <c r="G525" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I525" t="s">
+        <v>276</v>
+      </c>
+      <c r="J525" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>178</v>
+      </c>
+      <c r="B526" t="s">
+        <v>276</v>
+      </c>
+      <c r="C526" t="s">
+        <v>243</v>
+      </c>
+      <c r="D526" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E526" s="28">
+        <v>40</v>
+      </c>
+      <c r="F526" t="s">
+        <v>257</v>
+      </c>
+      <c r="G526" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I526" t="s">
+        <v>276</v>
+      </c>
+      <c r="J526" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>178</v>
+      </c>
+      <c r="B527" t="s">
+        <v>276</v>
+      </c>
+      <c r="C527" t="s">
+        <v>270</v>
+      </c>
+      <c r="D527" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E527" s="28">
+        <v>50</v>
+      </c>
+      <c r="F527" t="s">
+        <v>271</v>
+      </c>
+      <c r="G527" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I527" t="s">
+        <v>276</v>
+      </c>
+      <c r="J527" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="528" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>178</v>
+      </c>
+      <c r="B528" t="s">
+        <v>276</v>
+      </c>
+      <c r="C528" t="s">
+        <v>236</v>
+      </c>
+      <c r="D528" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="E528" s="28">
+        <v>0</v>
+      </c>
+      <c r="F528" t="s">
+        <v>237</v>
+      </c>
+      <c r="G528" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I528" t="s">
+        <v>276</v>
+      </c>
+      <c r="J528" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="529" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>178</v>
+      </c>
+      <c r="B529" t="s">
+        <v>276</v>
+      </c>
+      <c r="C529" t="s">
+        <v>272</v>
+      </c>
+      <c r="D529" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E529" s="28">
+        <v>40</v>
+      </c>
+      <c r="F529" t="s">
+        <v>273</v>
+      </c>
+      <c r="G529" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I529" t="s">
+        <v>276</v>
+      </c>
+      <c r="J529" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="530" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>178</v>
+      </c>
+      <c r="B530" t="s">
+        <v>276</v>
+      </c>
+      <c r="C530" t="s">
+        <v>238</v>
+      </c>
+      <c r="D530" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="E530" s="28">
+        <v>20</v>
+      </c>
+      <c r="F530" t="s">
+        <v>239</v>
+      </c>
+      <c r="G530" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I530" t="s">
+        <v>276</v>
+      </c>
+      <c r="J530" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="531" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>178</v>
+      </c>
+      <c r="B531" t="s">
+        <v>276</v>
+      </c>
+      <c r="C531" t="s">
+        <v>220</v>
+      </c>
+      <c r="D531" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="E531" s="28">
+        <v>5</v>
+      </c>
+      <c r="F531" t="s">
+        <v>274</v>
+      </c>
+      <c r="G531" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I531" t="s">
+        <v>276</v>
+      </c>
+      <c r="J531" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>178</v>
+      </c>
+      <c r="B532" t="s">
+        <v>276</v>
+      </c>
+      <c r="C532" t="s">
+        <v>222</v>
+      </c>
+      <c r="D532" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E532" s="28">
+        <v>2</v>
+      </c>
+      <c r="F532" t="s">
+        <v>255</v>
+      </c>
+      <c r="G532" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I532" t="s">
+        <v>276</v>
+      </c>
+      <c r="J532" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>178</v>
+      </c>
+      <c r="B533" t="s">
+        <v>276</v>
+      </c>
+      <c r="C533" t="s">
+        <v>72</v>
+      </c>
+      <c r="D533" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E533" s="28">
+        <v>3</v>
+      </c>
+      <c r="F533" t="s">
+        <v>217</v>
+      </c>
+      <c r="G533" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I533" t="s">
+        <v>276</v>
+      </c>
+      <c r="J533" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>178</v>
+      </c>
+      <c r="B534" t="s">
+        <v>276</v>
+      </c>
+      <c r="C534" t="s">
+        <v>74</v>
+      </c>
+      <c r="D534" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E534" s="28">
+        <v>3</v>
+      </c>
+      <c r="F534" t="s">
+        <v>262</v>
+      </c>
+      <c r="G534" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I534" t="s">
+        <v>276</v>
+      </c>
+      <c r="J534" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>178</v>
+      </c>
+      <c r="B535" t="s">
+        <v>276</v>
+      </c>
+      <c r="C535" t="s">
+        <v>76</v>
+      </c>
+      <c r="D535" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E535" s="28">
+        <v>3</v>
+      </c>
+      <c r="F535" t="s">
+        <v>219</v>
+      </c>
+      <c r="G535" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I535" t="s">
+        <v>276</v>
+      </c>
+      <c r="J535" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="536" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
+        <v>178</v>
+      </c>
+      <c r="B536" t="s">
+        <v>276</v>
+      </c>
+      <c r="C536" t="s">
+        <v>245</v>
+      </c>
+      <c r="D536" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="E536" s="28">
+        <v>0</v>
+      </c>
+      <c r="F536" t="s">
+        <v>279</v>
+      </c>
+      <c r="G536" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I536" t="s">
+        <v>276</v>
+      </c>
+      <c r="J536" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="537" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>178</v>
+      </c>
+      <c r="B537" t="s">
+        <v>276</v>
+      </c>
+      <c r="C537" t="s">
+        <v>66</v>
+      </c>
+      <c r="D537" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E537" s="28">
+        <v>35</v>
+      </c>
+      <c r="F537" t="s">
+        <v>242</v>
+      </c>
+      <c r="G537" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I537" t="s">
+        <v>276</v>
+      </c>
+      <c r="J537" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="538" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>178</v>
+      </c>
+      <c r="B538" t="s">
+        <v>280</v>
+      </c>
+      <c r="C538" t="s">
+        <v>14</v>
+      </c>
+      <c r="D538" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E538" s="28">
+        <v>450</v>
+      </c>
+      <c r="F538" t="s">
+        <v>211</v>
+      </c>
+      <c r="G538" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I538" t="s">
+        <v>280</v>
+      </c>
+      <c r="J538" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="539" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>178</v>
+      </c>
+      <c r="B539" t="s">
+        <v>280</v>
+      </c>
+      <c r="C539" t="s">
+        <v>14</v>
+      </c>
+      <c r="D539" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E539" s="28">
+        <v>650</v>
+      </c>
+      <c r="F539" t="s">
+        <v>212</v>
+      </c>
+      <c r="G539" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I539" t="s">
+        <v>280</v>
+      </c>
+      <c r="J539" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="540" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>178</v>
+      </c>
+      <c r="B540" t="s">
+        <v>280</v>
+      </c>
+      <c r="C540" t="s">
+        <v>243</v>
+      </c>
+      <c r="D540" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E540" s="28">
+        <v>40</v>
+      </c>
+      <c r="F540" t="s">
+        <v>257</v>
+      </c>
+      <c r="G540" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I540" t="s">
+        <v>280</v>
+      </c>
+      <c r="J540" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="541" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>178</v>
+      </c>
+      <c r="B541" t="s">
+        <v>280</v>
+      </c>
+      <c r="C541" t="s">
+        <v>215</v>
+      </c>
+      <c r="D541" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E541" s="28">
+        <v>3.5</v>
+      </c>
+      <c r="F541" t="s">
+        <v>250</v>
+      </c>
+      <c r="G541" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I541" t="s">
+        <v>280</v>
+      </c>
+      <c r="J541" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="542" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>178</v>
+      </c>
+      <c r="B542" t="s">
+        <v>280</v>
+      </c>
+      <c r="C542" t="s">
+        <v>236</v>
+      </c>
+      <c r="D542" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="E542" s="28">
+        <v>0</v>
+      </c>
+      <c r="F542" t="s">
+        <v>237</v>
+      </c>
+      <c r="G542" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I542" t="s">
+        <v>280</v>
+      </c>
+      <c r="J542" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="543" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>178</v>
+      </c>
+      <c r="B543" t="s">
+        <v>280</v>
+      </c>
+      <c r="C543" t="s">
+        <v>272</v>
+      </c>
+      <c r="D543" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E543" s="28">
+        <v>35</v>
+      </c>
+      <c r="F543" t="s">
+        <v>273</v>
+      </c>
+      <c r="G543" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I543" t="s">
+        <v>280</v>
+      </c>
+      <c r="J543" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="544" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>178</v>
+      </c>
+      <c r="B544" t="s">
+        <v>280</v>
+      </c>
+      <c r="C544" t="s">
+        <v>238</v>
+      </c>
+      <c r="D544" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="E544" s="28">
+        <v>20</v>
+      </c>
+      <c r="F544" t="s">
+        <v>239</v>
+      </c>
+      <c r="G544" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I544" t="s">
+        <v>280</v>
+      </c>
+      <c r="J544" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>178</v>
+      </c>
+      <c r="B545" t="s">
+        <v>280</v>
+      </c>
+      <c r="C545" t="s">
+        <v>220</v>
+      </c>
+      <c r="D545" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="E545" s="28">
+        <v>10</v>
+      </c>
+      <c r="F545" t="s">
+        <v>281</v>
+      </c>
+      <c r="G545" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I545" t="s">
+        <v>280</v>
+      </c>
+      <c r="J545" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>178</v>
+      </c>
+      <c r="B546" t="s">
+        <v>280</v>
+      </c>
+      <c r="C546" t="s">
+        <v>222</v>
+      </c>
+      <c r="D546" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E546" s="28">
+        <v>0</v>
+      </c>
+      <c r="F546" t="s">
+        <v>255</v>
+      </c>
+      <c r="G546" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I546" t="s">
+        <v>280</v>
+      </c>
+      <c r="J546" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="547" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>178</v>
+      </c>
+      <c r="B547" t="s">
+        <v>280</v>
+      </c>
+      <c r="C547" t="s">
+        <v>72</v>
+      </c>
+      <c r="D547" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E547" s="28">
+        <v>3</v>
+      </c>
+      <c r="F547" t="s">
+        <v>217</v>
+      </c>
+      <c r="G547" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I547" t="s">
+        <v>280</v>
+      </c>
+      <c r="J547" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>178</v>
+      </c>
+      <c r="B548" t="s">
+        <v>280</v>
+      </c>
+      <c r="C548" t="s">
+        <v>74</v>
+      </c>
+      <c r="D548" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E548" s="28">
+        <v>3</v>
+      </c>
+      <c r="F548" t="s">
+        <v>262</v>
+      </c>
+      <c r="G548" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I548" t="s">
+        <v>280</v>
+      </c>
+      <c r="J548" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>178</v>
+      </c>
+      <c r="B549" t="s">
+        <v>280</v>
+      </c>
+      <c r="C549" t="s">
+        <v>76</v>
+      </c>
+      <c r="D549" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E549" s="28">
+        <v>3</v>
+      </c>
+      <c r="F549" t="s">
+        <v>219</v>
+      </c>
+      <c r="G549" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I549" t="s">
+        <v>280</v>
+      </c>
+      <c r="J549" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>178</v>
+      </c>
+      <c r="B550" t="s">
+        <v>280</v>
+      </c>
+      <c r="C550" t="s">
+        <v>245</v>
+      </c>
+      <c r="D550" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="E550" s="28">
+        <v>0</v>
+      </c>
+      <c r="F550" t="s">
+        <v>279</v>
+      </c>
+      <c r="G550" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I550" t="s">
+        <v>280</v>
+      </c>
+      <c r="J550" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="551" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>178</v>
+      </c>
+      <c r="B551" t="s">
+        <v>280</v>
+      </c>
+      <c r="C551" t="s">
+        <v>66</v>
+      </c>
+      <c r="D551" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E551" s="28">
+        <v>35</v>
+      </c>
+      <c r="F551" t="s">
+        <v>242</v>
+      </c>
+      <c r="G551" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I551" t="s">
+        <v>280</v>
+      </c>
+      <c r="J551" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="552" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>178</v>
+      </c>
+      <c r="B552" t="s">
+        <v>282</v>
+      </c>
+      <c r="C552" t="s">
+        <v>14</v>
+      </c>
+      <c r="D552" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E552" s="28">
+        <v>450</v>
+      </c>
+      <c r="F552" t="s">
+        <v>211</v>
+      </c>
+      <c r="G552" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I552" t="s">
+        <v>282</v>
+      </c>
+      <c r="J552" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="553" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>178</v>
+      </c>
+      <c r="B553" t="s">
+        <v>282</v>
+      </c>
+      <c r="C553" t="s">
+        <v>14</v>
+      </c>
+      <c r="D553" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E553" s="28">
+        <v>650</v>
+      </c>
+      <c r="F553" t="s">
+        <v>212</v>
+      </c>
+      <c r="G553" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I553" t="s">
+        <v>282</v>
+      </c>
+      <c r="J553" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>178</v>
+      </c>
+      <c r="B554" t="s">
+        <v>282</v>
+      </c>
+      <c r="C554" t="s">
+        <v>243</v>
+      </c>
+      <c r="D554" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E554" s="28">
+        <v>30</v>
+      </c>
+      <c r="F554" t="s">
+        <v>283</v>
+      </c>
+      <c r="G554" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I554" t="s">
+        <v>282</v>
+      </c>
+      <c r="J554" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="555" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>178</v>
+      </c>
+      <c r="B555" t="s">
+        <v>282</v>
+      </c>
+      <c r="C555" t="s">
+        <v>215</v>
+      </c>
+      <c r="D555" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E555" s="28">
+        <v>3</v>
+      </c>
+      <c r="F555" t="s">
+        <v>284</v>
+      </c>
+      <c r="G555" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I555" t="s">
+        <v>282</v>
+      </c>
+      <c r="J555" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="556" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>178</v>
+      </c>
+      <c r="B556" t="s">
+        <v>282</v>
+      </c>
+      <c r="C556" t="s">
+        <v>236</v>
+      </c>
+      <c r="D556" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="E556" s="28">
+        <v>0</v>
+      </c>
+      <c r="F556" t="s">
+        <v>237</v>
+      </c>
+      <c r="G556" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I556" t="s">
+        <v>282</v>
+      </c>
+      <c r="J556" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="557" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>178</v>
+      </c>
+      <c r="B557" t="s">
+        <v>282</v>
+      </c>
+      <c r="C557" t="s">
+        <v>272</v>
+      </c>
+      <c r="D557" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E557" s="28">
+        <v>40</v>
+      </c>
+      <c r="F557" t="s">
+        <v>273</v>
+      </c>
+      <c r="G557" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I557" t="s">
+        <v>282</v>
+      </c>
+      <c r="J557" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="558" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>178</v>
+      </c>
+      <c r="B558" t="s">
+        <v>282</v>
+      </c>
+      <c r="C558" t="s">
+        <v>238</v>
+      </c>
+      <c r="D558" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="E558" s="28">
+        <v>20</v>
+      </c>
+      <c r="F558" t="s">
+        <v>239</v>
+      </c>
+      <c r="G558" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I558" t="s">
+        <v>282</v>
+      </c>
+      <c r="J558" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="559" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>178</v>
+      </c>
+      <c r="B559" t="s">
+        <v>282</v>
+      </c>
+      <c r="C559" t="s">
+        <v>220</v>
+      </c>
+      <c r="D559" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="E559" s="28">
+        <v>5</v>
+      </c>
+      <c r="F559" t="s">
+        <v>274</v>
+      </c>
+      <c r="G559" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I559" t="s">
+        <v>282</v>
+      </c>
+      <c r="J559" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="560" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>178</v>
+      </c>
+      <c r="B560" t="s">
+        <v>282</v>
+      </c>
+      <c r="C560" t="s">
+        <v>222</v>
+      </c>
+      <c r="D560" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E560" s="28">
+        <v>1</v>
+      </c>
+      <c r="F560" t="s">
+        <v>285</v>
+      </c>
+      <c r="G560" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I560" t="s">
+        <v>282</v>
+      </c>
+      <c r="J560" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>178</v>
+      </c>
+      <c r="B561" t="s">
+        <v>282</v>
+      </c>
+      <c r="C561" t="s">
+        <v>72</v>
+      </c>
+      <c r="D561" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E561" s="28">
+        <v>3</v>
+      </c>
+      <c r="F561" t="s">
+        <v>217</v>
+      </c>
+      <c r="G561" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I561" t="s">
+        <v>282</v>
+      </c>
+      <c r="J561" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>178</v>
+      </c>
+      <c r="B562" t="s">
+        <v>282</v>
+      </c>
+      <c r="C562" t="s">
+        <v>74</v>
+      </c>
+      <c r="D562" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E562" s="28">
+        <v>2</v>
+      </c>
+      <c r="F562" t="s">
+        <v>262</v>
+      </c>
+      <c r="G562" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I562" t="s">
+        <v>282</v>
+      </c>
+      <c r="J562" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>178</v>
+      </c>
+      <c r="B563" t="s">
+        <v>282</v>
+      </c>
+      <c r="C563" t="s">
+        <v>76</v>
+      </c>
+      <c r="D563" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E563" s="28">
+        <v>3</v>
+      </c>
+      <c r="F563" t="s">
+        <v>219</v>
+      </c>
+      <c r="G563" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I563" t="s">
+        <v>282</v>
+      </c>
+      <c r="J563" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>178</v>
+      </c>
+      <c r="B564" t="s">
+        <v>282</v>
+      </c>
+      <c r="C564" t="s">
+        <v>245</v>
+      </c>
+      <c r="D564" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="E564" s="28">
+        <v>0</v>
+      </c>
+      <c r="F564" t="s">
+        <v>279</v>
+      </c>
+      <c r="G564" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I564" t="s">
+        <v>282</v>
+      </c>
+      <c r="J564" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>178</v>
+      </c>
+      <c r="B565" t="s">
+        <v>282</v>
+      </c>
+      <c r="C565" t="s">
+        <v>66</v>
+      </c>
+      <c r="D565" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E565" s="28">
+        <v>20</v>
+      </c>
+      <c r="F565" t="s">
+        <v>242</v>
+      </c>
+      <c r="G565" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I565" t="s">
+        <v>282</v>
+      </c>
+      <c r="J565" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BCGcalc/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{9F301F61-0BAD-49DB-81CF-497AB54A188F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0DBF658-4378-4FBF-89A3-28E72759A95B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACAF9432-1605-41DD-B89F-77F178F6E244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Flags" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$523</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$565</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3200" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="286">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -1002,12 +1002,6 @@
     <t>Lowlands_Riffle</t>
   </si>
   <si>
-    <t>=</t>
-  </si>
-  <si>
-    <t>≤</t>
-  </si>
-  <si>
     <t>missing noteworthy taxa</t>
   </si>
   <si>
@@ -1027,6 +1021,12 @@
   </si>
   <si>
     <t>more than one warm stenotherm taxa</t>
+  </si>
+  <si>
+    <t>Ben, updates from Jen for ORWA</t>
+  </si>
+  <si>
+    <t>Fix symbols from last update</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1292,7 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
@@ -1440,6 +1440,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="5"/>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Bad" xfId="6" builtinId="27"/>
@@ -1846,7 +1849,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1873,7 +1876,7 @@
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <f>MAX(A22:A574)</f>
-        <v>46182</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1882,7 +1885,7 @@
       </c>
       <c r="B7" s="6" t="str">
         <f ca="1">LEFT(CELL("filename",B7),FIND("]",CELL("filename",B7)))</f>
-        <v>https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BCGcalc/inst/extdata/[MetricFlags.xlsx]</v>
+        <v>C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\[MetricFlags.xlsx]</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2164,6 +2167,22 @@
       </c>
       <c r="B50" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="15">
+        <v>46196</v>
+      </c>
+      <c r="B51" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="15">
+        <v>46209</v>
+      </c>
+      <c r="B52" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -18894,8 +18913,8 @@
       <c r="C528" t="s">
         <v>236</v>
       </c>
-      <c r="D528" s="28" t="s">
-        <v>277</v>
+      <c r="D528" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="E528" s="28">
         <v>0</v>
@@ -18953,7 +18972,7 @@
         <v>238</v>
       </c>
       <c r="D530" s="28" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="E530" s="28">
         <v>20</v>
@@ -19126,14 +19145,14 @@
       <c r="C536" t="s">
         <v>245</v>
       </c>
-      <c r="D536" s="28" t="s">
+      <c r="D536" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="E536" s="28">
+        <v>0</v>
+      </c>
+      <c r="F536" t="s">
         <v>277</v>
-      </c>
-      <c r="E536" s="28">
-        <v>0</v>
-      </c>
-      <c r="F536" t="s">
-        <v>279</v>
       </c>
       <c r="G536" s="61" t="b">
         <v>1</v>
@@ -19179,7 +19198,7 @@
         <v>178</v>
       </c>
       <c r="B538" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C538" t="s">
         <v>14</v>
@@ -19197,7 +19216,7 @@
         <v>1</v>
       </c>
       <c r="I538" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J538" t="s">
         <v>178</v>
@@ -19208,7 +19227,7 @@
         <v>178</v>
       </c>
       <c r="B539" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C539" t="s">
         <v>14</v>
@@ -19226,7 +19245,7 @@
         <v>1</v>
       </c>
       <c r="I539" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J539" t="s">
         <v>178</v>
@@ -19237,7 +19256,7 @@
         <v>178</v>
       </c>
       <c r="B540" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C540" t="s">
         <v>243</v>
@@ -19255,7 +19274,7 @@
         <v>1</v>
       </c>
       <c r="I540" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J540" t="s">
         <v>178</v>
@@ -19266,7 +19285,7 @@
         <v>178</v>
       </c>
       <c r="B541" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C541" t="s">
         <v>215</v>
@@ -19284,7 +19303,7 @@
         <v>1</v>
       </c>
       <c r="I541" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J541" t="s">
         <v>178</v>
@@ -19295,13 +19314,13 @@
         <v>178</v>
       </c>
       <c r="B542" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C542" t="s">
         <v>236</v>
       </c>
-      <c r="D542" s="28" t="s">
-        <v>277</v>
+      <c r="D542" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="E542" s="28">
         <v>0</v>
@@ -19313,7 +19332,7 @@
         <v>1</v>
       </c>
       <c r="I542" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J542" t="s">
         <v>178</v>
@@ -19324,7 +19343,7 @@
         <v>178</v>
       </c>
       <c r="B543" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C543" t="s">
         <v>272</v>
@@ -19342,7 +19361,7 @@
         <v>1</v>
       </c>
       <c r="I543" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J543" t="s">
         <v>178</v>
@@ -19353,13 +19372,13 @@
         <v>178</v>
       </c>
       <c r="B544" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C544" t="s">
         <v>238</v>
       </c>
       <c r="D544" s="28" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="E544" s="28">
         <v>20</v>
@@ -19371,7 +19390,7 @@
         <v>1</v>
       </c>
       <c r="I544" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J544" t="s">
         <v>178</v>
@@ -19382,7 +19401,7 @@
         <v>178</v>
       </c>
       <c r="B545" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C545" t="s">
         <v>220</v>
@@ -19394,13 +19413,13 @@
         <v>10</v>
       </c>
       <c r="F545" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G545" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I545" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J545" t="s">
         <v>178</v>
@@ -19411,7 +19430,7 @@
         <v>178</v>
       </c>
       <c r="B546" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C546" t="s">
         <v>222</v>
@@ -19429,7 +19448,7 @@
         <v>1</v>
       </c>
       <c r="I546" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J546" t="s">
         <v>178</v>
@@ -19440,7 +19459,7 @@
         <v>178</v>
       </c>
       <c r="B547" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C547" t="s">
         <v>72</v>
@@ -19458,7 +19477,7 @@
         <v>1</v>
       </c>
       <c r="I547" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J547" t="s">
         <v>178</v>
@@ -19469,7 +19488,7 @@
         <v>178</v>
       </c>
       <c r="B548" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C548" t="s">
         <v>74</v>
@@ -19487,7 +19506,7 @@
         <v>1</v>
       </c>
       <c r="I548" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J548" t="s">
         <v>178</v>
@@ -19498,7 +19517,7 @@
         <v>178</v>
       </c>
       <c r="B549" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C549" t="s">
         <v>76</v>
@@ -19516,7 +19535,7 @@
         <v>1</v>
       </c>
       <c r="I549" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J549" t="s">
         <v>178</v>
@@ -19527,25 +19546,25 @@
         <v>178</v>
       </c>
       <c r="B550" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C550" t="s">
         <v>245</v>
       </c>
-      <c r="D550" s="28" t="s">
+      <c r="D550" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="E550" s="28">
+        <v>0</v>
+      </c>
+      <c r="F550" t="s">
         <v>277</v>
       </c>
-      <c r="E550" s="28">
-        <v>0</v>
-      </c>
-      <c r="F550" t="s">
-        <v>279</v>
-      </c>
       <c r="G550" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I550" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J550" t="s">
         <v>178</v>
@@ -19556,7 +19575,7 @@
         <v>178</v>
       </c>
       <c r="B551" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C551" t="s">
         <v>66</v>
@@ -19574,7 +19593,7 @@
         <v>1</v>
       </c>
       <c r="I551" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J551" t="s">
         <v>178</v>
@@ -19585,7 +19604,7 @@
         <v>178</v>
       </c>
       <c r="B552" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C552" t="s">
         <v>14</v>
@@ -19603,7 +19622,7 @@
         <v>1</v>
       </c>
       <c r="I552" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J552" t="s">
         <v>178</v>
@@ -19614,7 +19633,7 @@
         <v>178</v>
       </c>
       <c r="B553" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C553" t="s">
         <v>14</v>
@@ -19632,7 +19651,7 @@
         <v>1</v>
       </c>
       <c r="I553" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J553" t="s">
         <v>178</v>
@@ -19643,7 +19662,7 @@
         <v>178</v>
       </c>
       <c r="B554" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C554" t="s">
         <v>243</v>
@@ -19655,13 +19674,13 @@
         <v>30</v>
       </c>
       <c r="F554" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G554" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I554" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J554" t="s">
         <v>178</v>
@@ -19672,7 +19691,7 @@
         <v>178</v>
       </c>
       <c r="B555" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C555" t="s">
         <v>215</v>
@@ -19684,13 +19703,13 @@
         <v>3</v>
       </c>
       <c r="F555" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G555" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I555" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J555" t="s">
         <v>178</v>
@@ -19701,13 +19720,13 @@
         <v>178</v>
       </c>
       <c r="B556" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C556" t="s">
         <v>236</v>
       </c>
-      <c r="D556" s="28" t="s">
-        <v>277</v>
+      <c r="D556" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="E556" s="28">
         <v>0</v>
@@ -19719,7 +19738,7 @@
         <v>1</v>
       </c>
       <c r="I556" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J556" t="s">
         <v>178</v>
@@ -19730,7 +19749,7 @@
         <v>178</v>
       </c>
       <c r="B557" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C557" t="s">
         <v>272</v>
@@ -19748,7 +19767,7 @@
         <v>1</v>
       </c>
       <c r="I557" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J557" t="s">
         <v>178</v>
@@ -19759,13 +19778,13 @@
         <v>178</v>
       </c>
       <c r="B558" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C558" t="s">
         <v>238</v>
       </c>
       <c r="D558" s="28" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="E558" s="28">
         <v>20</v>
@@ -19777,7 +19796,7 @@
         <v>1</v>
       </c>
       <c r="I558" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J558" t="s">
         <v>178</v>
@@ -19788,7 +19807,7 @@
         <v>178</v>
       </c>
       <c r="B559" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C559" t="s">
         <v>220</v>
@@ -19806,7 +19825,7 @@
         <v>1</v>
       </c>
       <c r="I559" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J559" t="s">
         <v>178</v>
@@ -19817,7 +19836,7 @@
         <v>178</v>
       </c>
       <c r="B560" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C560" t="s">
         <v>222</v>
@@ -19829,13 +19848,13 @@
         <v>1</v>
       </c>
       <c r="F560" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G560" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I560" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J560" t="s">
         <v>178</v>
@@ -19846,7 +19865,7 @@
         <v>178</v>
       </c>
       <c r="B561" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C561" t="s">
         <v>72</v>
@@ -19864,7 +19883,7 @@
         <v>1</v>
       </c>
       <c r="I561" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J561" t="s">
         <v>178</v>
@@ -19875,7 +19894,7 @@
         <v>178</v>
       </c>
       <c r="B562" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C562" t="s">
         <v>74</v>
@@ -19893,7 +19912,7 @@
         <v>1</v>
       </c>
       <c r="I562" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J562" t="s">
         <v>178</v>
@@ -19904,7 +19923,7 @@
         <v>178</v>
       </c>
       <c r="B563" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C563" t="s">
         <v>76</v>
@@ -19922,7 +19941,7 @@
         <v>1</v>
       </c>
       <c r="I563" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J563" t="s">
         <v>178</v>
@@ -19933,25 +19952,25 @@
         <v>178</v>
       </c>
       <c r="B564" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C564" t="s">
         <v>245</v>
       </c>
-      <c r="D564" s="28" t="s">
+      <c r="D564" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="E564" s="28">
+        <v>0</v>
+      </c>
+      <c r="F564" t="s">
         <v>277</v>
       </c>
-      <c r="E564" s="28">
-        <v>0</v>
-      </c>
-      <c r="F564" t="s">
-        <v>279</v>
-      </c>
       <c r="G564" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I564" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J564" t="s">
         <v>178</v>
@@ -19962,7 +19981,7 @@
         <v>178</v>
       </c>
       <c r="B565" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C565" t="s">
         <v>66</v>
@@ -19980,14 +19999,14 @@
         <v>1</v>
       </c>
       <c r="I565" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J565" t="s">
         <v>178</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J523" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:J565" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <conditionalFormatting sqref="C2:C66 C162:C186 C248:C272">
     <cfRule type="expression" dxfId="7" priority="18">
       <formula>$G2=FALSE</formula>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACAF9432-1605-41DD-B89F-77F178F6E244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92EEF72-8B0E-442C-B9C5-FA2CC30B0829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3203" uniqueCount="287">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -930,9 +930,6 @@
     <t>presence of highly tolerant individuals</t>
   </si>
   <si>
-    <t>pi_NonInsTrombJuga_BCG_att456</t>
-  </si>
-  <si>
     <t>unusually high proportion of non-sensitive, non-insect individuals</t>
   </si>
   <si>
@@ -981,12 +978,6 @@
     <t>Foothills_Riffle</t>
   </si>
   <si>
-    <t>pi_dom02_BCG_att456</t>
-  </si>
-  <si>
-    <t>high dominance by two tolerant (Attr IV,V,VI) taxa</t>
-  </si>
-  <si>
     <t>pt_Chiro</t>
   </si>
   <si>
@@ -1027,6 +1018,18 @@
   </si>
   <si>
     <t>Fix symbols from last update</t>
+  </si>
+  <si>
+    <t>Update ORWA 456 to 456m6t</t>
+  </si>
+  <si>
+    <t>pi_NonInsTrombJuga_BCG_att456m6t</t>
+  </si>
+  <si>
+    <t>pi_dom02_BCG_att456m6t</t>
+  </si>
+  <si>
+    <t>high dominance by two tolerant (Attr 4, 5, 6m, 6t) taxa</t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1852,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1876,7 +1879,7 @@
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <f>MAX(A22:A574)</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2174,7 +2177,7 @@
         <v>46196</v>
       </c>
       <c r="B51" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2182,7 +2185,15 @@
         <v>46209</v>
       </c>
       <c r="B52" t="s">
-        <v>285</v>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="15">
+        <v>46210</v>
+      </c>
+      <c r="B53" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -2294,7 +2305,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Sheet2">
+  <sheetPr codeName="Sheet2" filterMode="1">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:J565"/>
@@ -2302,7 +2313,7 @@
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
     <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
     <col min="6" max="6" width="47" customWidth="1"/>
     <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="58.42578125" bestFit="1" customWidth="1"/>
@@ -2341,7 +2352,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -2373,7 +2384,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>125</v>
       </c>
@@ -2404,7 +2415,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -2435,7 +2446,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>125</v>
       </c>
@@ -2466,7 +2477,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>125</v>
       </c>
@@ -2497,7 +2508,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -2528,7 +2539,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -2559,7 +2570,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -2590,7 +2601,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>125</v>
       </c>
@@ -2621,7 +2632,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>125</v>
       </c>
@@ -2652,7 +2663,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -2683,7 +2694,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -2714,7 +2725,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>125</v>
       </c>
@@ -2745,7 +2756,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -2776,7 +2787,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>125</v>
       </c>
@@ -2807,7 +2818,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -2838,7 +2849,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>125</v>
       </c>
@@ -2869,7 +2880,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -2900,7 +2911,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -2931,7 +2942,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -2962,7 +2973,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>126</v>
       </c>
@@ -2994,7 +3005,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>126</v>
       </c>
@@ -3026,7 +3037,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>126</v>
       </c>
@@ -3058,7 +3069,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>126</v>
       </c>
@@ -3090,7 +3101,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>126</v>
       </c>
@@ -3121,7 +3132,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>126</v>
       </c>
@@ -3152,7 +3163,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>126</v>
       </c>
@@ -3183,7 +3194,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>126</v>
       </c>
@@ -3214,7 +3225,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>126</v>
       </c>
@@ -3245,7 +3256,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>126</v>
       </c>
@@ -3276,7 +3287,7 @@
         <v>Hi</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>126</v>
       </c>
@@ -3308,7 +3319,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>126</v>
       </c>
@@ -3340,7 +3351,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>126</v>
       </c>
@@ -3372,7 +3383,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>126</v>
       </c>
@@ -3404,7 +3415,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>126</v>
       </c>
@@ -3435,7 +3446,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>126</v>
       </c>
@@ -3466,7 +3477,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>126</v>
       </c>
@@ -3497,7 +3508,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>126</v>
       </c>
@@ -3528,7 +3539,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>126</v>
       </c>
@@ -3559,7 +3570,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>126</v>
       </c>
@@ -3590,7 +3601,7 @@
         <v>Lo</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -3621,7 +3632,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -3655,7 +3666,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -3686,7 +3697,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -3717,7 +3728,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -3748,7 +3759,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>53</v>
       </c>
@@ -3779,7 +3790,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -3810,7 +3821,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -3841,7 +3852,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -3872,7 +3883,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -3903,7 +3914,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -3934,7 +3945,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -3965,7 +3976,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -3999,7 +4010,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -4030,7 +4041,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -4061,7 +4072,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -4092,7 +4103,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>53</v>
       </c>
@@ -4123,7 +4134,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>53</v>
       </c>
@@ -4154,7 +4165,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -4185,7 +4196,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>53</v>
       </c>
@@ -4216,7 +4227,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -4250,7 +4261,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>53</v>
       </c>
@@ -4281,7 +4292,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>53</v>
       </c>
@@ -4312,7 +4323,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>53</v>
       </c>
@@ -4343,7 +4354,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>53</v>
       </c>
@@ -4374,7 +4385,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>53</v>
       </c>
@@ -4408,7 +4419,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>53</v>
       </c>
@@ -4442,7 +4453,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>53</v>
       </c>
@@ -4476,7 +4487,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>53</v>
       </c>
@@ -4510,7 +4521,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>53</v>
       </c>
@@ -4541,7 +4552,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>53</v>
       </c>
@@ -4572,7 +4583,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>53</v>
       </c>
@@ -4603,7 +4614,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>53</v>
       </c>
@@ -4634,7 +4645,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>53</v>
       </c>
@@ -4665,7 +4676,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>53</v>
       </c>
@@ -4696,7 +4707,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>53</v>
       </c>
@@ -4727,7 +4738,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -4758,7 +4769,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>53</v>
       </c>
@@ -4789,7 +4800,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>53</v>
       </c>
@@ -4820,7 +4831,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>53</v>
       </c>
@@ -4851,7 +4862,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>53</v>
       </c>
@@ -4882,7 +4893,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>53</v>
       </c>
@@ -4913,7 +4924,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>53</v>
       </c>
@@ -4944,7 +4955,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>53</v>
       </c>
@@ -4975,7 +4986,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>53</v>
       </c>
@@ -5006,7 +5017,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>53</v>
       </c>
@@ -5037,7 +5048,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>53</v>
       </c>
@@ -5068,7 +5079,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>53</v>
       </c>
@@ -5099,7 +5110,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>53</v>
       </c>
@@ -5130,7 +5141,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>53</v>
       </c>
@@ -5161,7 +5172,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>53</v>
       </c>
@@ -5192,7 +5203,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>53</v>
       </c>
@@ -5223,7 +5234,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>53</v>
       </c>
@@ -5254,7 +5265,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>53</v>
       </c>
@@ -5285,7 +5296,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>53</v>
       </c>
@@ -5316,7 +5327,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>53</v>
       </c>
@@ -5347,7 +5358,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>53</v>
       </c>
@@ -5378,7 +5389,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>53</v>
       </c>
@@ -5409,7 +5420,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>53</v>
       </c>
@@ -5443,7 +5454,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>53</v>
       </c>
@@ -5477,7 +5488,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>53</v>
       </c>
@@ -5511,7 +5522,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>53</v>
       </c>
@@ -5545,7 +5556,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>53</v>
       </c>
@@ -5579,7 +5590,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>53</v>
       </c>
@@ -5613,7 +5624,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>53</v>
       </c>
@@ -5647,7 +5658,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>53</v>
       </c>
@@ -5681,7 +5692,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>53</v>
       </c>
@@ -5715,7 +5726,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>53</v>
       </c>
@@ -5749,7 +5760,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>53</v>
       </c>
@@ -5783,7 +5794,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>53</v>
       </c>
@@ -5817,7 +5828,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>53</v>
       </c>
@@ -5851,7 +5862,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>53</v>
       </c>
@@ -5885,7 +5896,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>53</v>
       </c>
@@ -5919,7 +5930,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>53</v>
       </c>
@@ -5953,7 +5964,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>53</v>
       </c>
@@ -5987,7 +5998,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>53</v>
       </c>
@@ -6021,7 +6032,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>53</v>
       </c>
@@ -6055,7 +6066,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>53</v>
       </c>
@@ -6089,7 +6100,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>53</v>
       </c>
@@ -6123,7 +6134,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>53</v>
       </c>
@@ -6157,7 +6168,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>53</v>
       </c>
@@ -6191,7 +6202,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>53</v>
       </c>
@@ -6225,7 +6236,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>53</v>
       </c>
@@ -6259,7 +6270,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>53</v>
       </c>
@@ -6293,7 +6304,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>53</v>
       </c>
@@ -6327,7 +6338,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>53</v>
       </c>
@@ -6361,7 +6372,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>123</v>
       </c>
@@ -6392,7 +6403,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>123</v>
       </c>
@@ -6426,7 +6437,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>123</v>
       </c>
@@ -6460,7 +6471,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>123</v>
       </c>
@@ -6494,7 +6505,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>123</v>
       </c>
@@ -6528,7 +6539,7 @@
         <v>ORWA</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>53</v>
       </c>
@@ -6562,7 +6573,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>53</v>
       </c>
@@ -6596,7 +6607,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>53</v>
       </c>
@@ -6630,7 +6641,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>154</v>
       </c>
@@ -6664,7 +6675,7 @@
         <v>CREMP_Keys</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>154</v>
       </c>
@@ -6698,7 +6709,7 @@
         <v>NOT_CREMP_Keys</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>162</v>
       </c>
@@ -6727,7 +6738,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>162</v>
       </c>
@@ -6756,7 +6767,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>162</v>
       </c>
@@ -6785,7 +6796,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>162</v>
       </c>
@@ -6814,7 +6825,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>162</v>
       </c>
@@ -6843,7 +6854,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>162</v>
       </c>
@@ -6872,7 +6883,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>162</v>
       </c>
@@ -6901,7 +6912,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>162</v>
       </c>
@@ -6930,7 +6941,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>162</v>
       </c>
@@ -6959,7 +6970,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>162</v>
       </c>
@@ -6988,7 +6999,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>162</v>
       </c>
@@ -7017,7 +7028,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>162</v>
       </c>
@@ -7046,7 +7057,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>162</v>
       </c>
@@ -7075,7 +7086,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>162</v>
       </c>
@@ -7104,7 +7115,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>162</v>
       </c>
@@ -7133,7 +7144,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>162</v>
       </c>
@@ -7162,7 +7173,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>162</v>
       </c>
@@ -7191,7 +7202,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -7220,7 +7231,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>162</v>
       </c>
@@ -7249,7 +7260,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>162</v>
       </c>
@@ -7278,7 +7289,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>162</v>
       </c>
@@ -7307,7 +7318,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>162</v>
       </c>
@@ -7336,7 +7347,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -7365,7 +7376,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>162</v>
       </c>
@@ -7394,7 +7405,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="25" t="s">
         <v>177</v>
       </c>
@@ -7425,7 +7436,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="25" t="s">
         <v>177</v>
       </c>
@@ -7456,7 +7467,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="25" t="s">
         <v>177</v>
       </c>
@@ -7487,7 +7498,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="25" t="s">
         <v>177</v>
       </c>
@@ -7521,7 +7532,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
         <v>177</v>
       </c>
@@ -7552,7 +7563,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
         <v>177</v>
       </c>
@@ -7583,7 +7594,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="25" t="s">
         <v>177</v>
       </c>
@@ -7614,7 +7625,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
         <v>177</v>
       </c>
@@ -7645,7 +7656,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
         <v>177</v>
       </c>
@@ -7676,7 +7687,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
         <v>177</v>
       </c>
@@ -7707,7 +7718,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="25" t="s">
         <v>177</v>
       </c>
@@ -7738,7 +7749,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="25" t="s">
         <v>177</v>
       </c>
@@ -7769,7 +7780,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="25" t="s">
         <v>177</v>
       </c>
@@ -7803,7 +7814,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="25" t="s">
         <v>177</v>
       </c>
@@ -7834,7 +7845,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="25" t="s">
         <v>177</v>
       </c>
@@ -7865,7 +7876,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="25" t="s">
         <v>177</v>
       </c>
@@ -7896,7 +7907,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="25" t="s">
         <v>177</v>
       </c>
@@ -7927,7 +7938,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="25" t="s">
         <v>177</v>
       </c>
@@ -7958,7 +7969,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="25" t="s">
         <v>177</v>
       </c>
@@ -7989,7 +8000,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="25" t="s">
         <v>177</v>
       </c>
@@ -8020,7 +8031,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="25" t="s">
         <v>177</v>
       </c>
@@ -8054,7 +8065,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="25" t="s">
         <v>177</v>
       </c>
@@ -8085,7 +8096,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="25" t="s">
         <v>177</v>
       </c>
@@ -8116,7 +8127,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="25" t="s">
         <v>177</v>
       </c>
@@ -8147,7 +8158,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="25" t="s">
         <v>177</v>
       </c>
@@ -8178,7 +8189,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="25" t="s">
         <v>177</v>
       </c>
@@ -8212,7 +8223,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="25" t="s">
         <v>177</v>
       </c>
@@ -8246,7 +8257,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="25" t="s">
         <v>177</v>
       </c>
@@ -8280,7 +8291,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="25" t="s">
         <v>177</v>
       </c>
@@ -8314,7 +8325,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="25" t="s">
         <v>177</v>
       </c>
@@ -8345,7 +8356,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="25" t="s">
         <v>177</v>
       </c>
@@ -8376,7 +8387,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="25" t="s">
         <v>177</v>
       </c>
@@ -8407,7 +8418,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="25" t="s">
         <v>177</v>
       </c>
@@ -8438,7 +8449,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="25" t="s">
         <v>177</v>
       </c>
@@ -8469,7 +8480,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="25" t="s">
         <v>177</v>
       </c>
@@ -8500,7 +8511,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="25" t="s">
         <v>177</v>
       </c>
@@ -8531,7 +8542,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="25" t="s">
         <v>177</v>
       </c>
@@ -8562,7 +8573,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="25" t="s">
         <v>177</v>
       </c>
@@ -8593,7 +8604,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="25" t="s">
         <v>177</v>
       </c>
@@ -8624,7 +8635,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="25" t="s">
         <v>177</v>
       </c>
@@ -8655,7 +8666,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="25" t="s">
         <v>177</v>
       </c>
@@ -8686,7 +8697,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="25" t="s">
         <v>177</v>
       </c>
@@ -8717,7 +8728,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="25" t="s">
         <v>177</v>
       </c>
@@ -8748,7 +8759,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="25" t="s">
         <v>177</v>
       </c>
@@ -8779,7 +8790,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="25" t="s">
         <v>177</v>
       </c>
@@ -8810,7 +8821,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="25" t="s">
         <v>177</v>
       </c>
@@ -8841,7 +8852,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="25" t="s">
         <v>177</v>
       </c>
@@ -8872,7 +8883,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="25" t="s">
         <v>177</v>
       </c>
@@ -8903,7 +8914,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="25" t="s">
         <v>177</v>
       </c>
@@ -8934,7 +8945,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="25" t="s">
         <v>177</v>
       </c>
@@ -8965,7 +8976,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="25" t="s">
         <v>177</v>
       </c>
@@ -8996,7 +9007,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="25" t="s">
         <v>177</v>
       </c>
@@ -9027,7 +9038,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="25" t="s">
         <v>177</v>
       </c>
@@ -9058,7 +9069,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="25" t="s">
         <v>177</v>
       </c>
@@ -9089,7 +9100,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="25" t="s">
         <v>177</v>
       </c>
@@ -9120,7 +9131,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="25" t="s">
         <v>177</v>
       </c>
@@ -9151,7 +9162,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="25" t="s">
         <v>177</v>
       </c>
@@ -9182,7 +9193,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="25" t="s">
         <v>177</v>
       </c>
@@ -9213,7 +9224,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="25" t="s">
         <v>177</v>
       </c>
@@ -9247,7 +9258,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="25" t="s">
         <v>177</v>
       </c>
@@ -9281,7 +9292,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="25" t="s">
         <v>177</v>
       </c>
@@ -9315,7 +9326,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="25" t="s">
         <v>177</v>
       </c>
@@ -9349,7 +9360,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="25" t="s">
         <v>177</v>
       </c>
@@ -9383,7 +9394,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="25" t="s">
         <v>177</v>
       </c>
@@ -9417,7 +9428,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="25" t="s">
         <v>177</v>
       </c>
@@ -9451,7 +9462,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="25" t="s">
         <v>177</v>
       </c>
@@ -9485,7 +9496,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="25" t="s">
         <v>177</v>
       </c>
@@ -9519,7 +9530,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="25" t="s">
         <v>177</v>
       </c>
@@ -9553,7 +9564,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="25" t="s">
         <v>177</v>
       </c>
@@ -9587,7 +9598,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="25" t="s">
         <v>177</v>
       </c>
@@ -9621,7 +9632,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="25" t="s">
         <v>177</v>
       </c>
@@ -9655,7 +9666,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="25" t="s">
         <v>177</v>
       </c>
@@ -9689,7 +9700,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="25" t="s">
         <v>177</v>
       </c>
@@ -9723,7 +9734,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="25" t="s">
         <v>177</v>
       </c>
@@ -9757,7 +9768,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="25" t="s">
         <v>177</v>
       </c>
@@ -9791,7 +9802,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="25" t="s">
         <v>177</v>
       </c>
@@ -9825,7 +9836,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="25" t="s">
         <v>177</v>
       </c>
@@ -9859,7 +9870,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="25" t="s">
         <v>177</v>
       </c>
@@ -9893,7 +9904,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="25" t="s">
         <v>177</v>
       </c>
@@ -9927,7 +9938,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="25" t="s">
         <v>177</v>
       </c>
@@ -9961,7 +9972,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="25" t="s">
         <v>177</v>
       </c>
@@ -9995,7 +10006,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="25" t="s">
         <v>177</v>
       </c>
@@ -10029,7 +10040,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="25" t="s">
         <v>177</v>
       </c>
@@ -10063,7 +10074,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="25" t="s">
         <v>177</v>
       </c>
@@ -10097,7 +10108,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="25" t="s">
         <v>177</v>
       </c>
@@ -10131,7 +10142,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="25" t="s">
         <v>177</v>
       </c>
@@ -10165,7 +10176,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="26" t="s">
         <v>178</v>
       </c>
@@ -10196,7 +10207,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="26" t="s">
         <v>178</v>
       </c>
@@ -10227,7 +10238,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="26" t="s">
         <v>178</v>
       </c>
@@ -10258,7 +10269,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="26" t="s">
         <v>178</v>
       </c>
@@ -10292,7 +10303,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="26" t="s">
         <v>178</v>
       </c>
@@ -10323,7 +10334,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="26" t="s">
         <v>178</v>
       </c>
@@ -10354,7 +10365,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="26" t="s">
         <v>178</v>
       </c>
@@ -10385,7 +10396,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="26" t="s">
         <v>178</v>
       </c>
@@ -10416,7 +10427,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="26" t="s">
         <v>178</v>
       </c>
@@ -10447,7 +10458,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="26" t="s">
         <v>178</v>
       </c>
@@ -10478,7 +10489,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="26" t="s">
         <v>178</v>
       </c>
@@ -10509,7 +10520,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="26" t="s">
         <v>178</v>
       </c>
@@ -10540,7 +10551,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="26" t="s">
         <v>178</v>
       </c>
@@ -10574,7 +10585,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="26" t="s">
         <v>178</v>
       </c>
@@ -10605,7 +10616,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="26" t="s">
         <v>178</v>
       </c>
@@ -10636,7 +10647,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="26" t="s">
         <v>178</v>
       </c>
@@ -10667,7 +10678,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="26" t="s">
         <v>178</v>
       </c>
@@ -10698,7 +10709,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="26" t="s">
         <v>178</v>
       </c>
@@ -10729,7 +10740,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="26" t="s">
         <v>178</v>
       </c>
@@ -10760,7 +10771,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="26" t="s">
         <v>178</v>
       </c>
@@ -10791,7 +10802,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="26" t="s">
         <v>178</v>
       </c>
@@ -10825,7 +10836,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="26" t="s">
         <v>178</v>
       </c>
@@ -10856,7 +10867,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="26" t="s">
         <v>178</v>
       </c>
@@ -10887,7 +10898,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="26" t="s">
         <v>178</v>
       </c>
@@ -10918,7 +10929,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="26" t="s">
         <v>178</v>
       </c>
@@ -10949,7 +10960,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="26" t="s">
         <v>178</v>
       </c>
@@ -10983,7 +10994,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="26" t="s">
         <v>178</v>
       </c>
@@ -11017,7 +11028,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="26" t="s">
         <v>178</v>
       </c>
@@ -11051,7 +11062,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="26" t="s">
         <v>178</v>
       </c>
@@ -11085,7 +11096,7 @@
         <v>HiGrad-LoElev</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="26" t="s">
         <v>178</v>
       </c>
@@ -11116,7 +11127,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="26" t="s">
         <v>178</v>
       </c>
@@ -11147,7 +11158,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="26" t="s">
         <v>178</v>
       </c>
@@ -11178,7 +11189,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="26" t="s">
         <v>178</v>
       </c>
@@ -11209,7 +11220,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="26" t="s">
         <v>178</v>
       </c>
@@ -11240,7 +11251,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="26" t="s">
         <v>178</v>
       </c>
@@ -11271,7 +11282,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="26" t="s">
         <v>178</v>
       </c>
@@ -11302,7 +11313,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="26" t="s">
         <v>178</v>
       </c>
@@ -11333,7 +11344,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="26" t="s">
         <v>178</v>
       </c>
@@ -11364,7 +11375,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="26" t="s">
         <v>178</v>
       </c>
@@ -11395,7 +11406,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="26" t="s">
         <v>178</v>
       </c>
@@ -11426,7 +11437,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="26" t="s">
         <v>178</v>
       </c>
@@ -11457,7 +11468,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="26" t="s">
         <v>178</v>
       </c>
@@ -11488,7 +11499,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="26" t="s">
         <v>178</v>
       </c>
@@ -11519,7 +11530,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="26" t="s">
         <v>178</v>
       </c>
@@ -11550,7 +11561,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="26" t="s">
         <v>178</v>
       </c>
@@ -11581,7 +11592,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="26" t="s">
         <v>178</v>
       </c>
@@ -11612,7 +11623,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="26" t="s">
         <v>178</v>
       </c>
@@ -11643,7 +11654,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="26" t="s">
         <v>178</v>
       </c>
@@ -11674,7 +11685,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="26" t="s">
         <v>178</v>
       </c>
@@ -11705,7 +11716,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="26" t="s">
         <v>178</v>
       </c>
@@ -11736,7 +11747,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="26" t="s">
         <v>178</v>
       </c>
@@ -11767,7 +11778,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="26" t="s">
         <v>178</v>
       </c>
@@ -11798,7 +11809,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="26" t="s">
         <v>178</v>
       </c>
@@ -11829,7 +11840,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="26" t="s">
         <v>178</v>
       </c>
@@ -11860,7 +11871,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="26" t="s">
         <v>178</v>
       </c>
@@ -11891,7 +11902,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="26" t="s">
         <v>178</v>
       </c>
@@ -11922,7 +11933,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="26" t="s">
         <v>178</v>
       </c>
@@ -11953,7 +11964,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="26" t="s">
         <v>178</v>
       </c>
@@ -11984,7 +11995,7 @@
         <v>HiGrad-HiElev</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="26" t="s">
         <v>178</v>
       </c>
@@ -12018,7 +12029,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="26" t="s">
         <v>178</v>
       </c>
@@ -12052,7 +12063,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="26" t="s">
         <v>178</v>
       </c>
@@ -12086,7 +12097,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="26" t="s">
         <v>178</v>
       </c>
@@ -12120,7 +12131,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="26" t="s">
         <v>178</v>
       </c>
@@ -12154,7 +12165,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="26" t="s">
         <v>178</v>
       </c>
@@ -12188,7 +12199,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="26" t="s">
         <v>178</v>
       </c>
@@ -12222,7 +12233,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="26" t="s">
         <v>178</v>
       </c>
@@ -12256,7 +12267,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="26" t="s">
         <v>178</v>
       </c>
@@ -12290,7 +12301,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="26" t="s">
         <v>178</v>
       </c>
@@ -12324,7 +12335,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="26" t="s">
         <v>178</v>
       </c>
@@ -12358,7 +12369,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="26" t="s">
         <v>178</v>
       </c>
@@ -12392,7 +12403,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="26" t="s">
         <v>178</v>
       </c>
@@ -12426,7 +12437,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="26" t="s">
         <v>178</v>
       </c>
@@ -12460,7 +12471,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="26" t="s">
         <v>178</v>
       </c>
@@ -12494,7 +12505,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="26" t="s">
         <v>178</v>
       </c>
@@ -12528,7 +12539,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="26" t="s">
         <v>178</v>
       </c>
@@ -12562,7 +12573,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="26" t="s">
         <v>178</v>
       </c>
@@ -12596,7 +12607,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="26" t="s">
         <v>178</v>
       </c>
@@ -12630,7 +12641,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="26" t="s">
         <v>178</v>
       </c>
@@ -12664,7 +12675,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="26" t="s">
         <v>178</v>
       </c>
@@ -12698,7 +12709,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="26" t="s">
         <v>178</v>
       </c>
@@ -12732,7 +12743,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="26" t="s">
         <v>178</v>
       </c>
@@ -12766,7 +12777,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="26" t="s">
         <v>178</v>
       </c>
@@ -12800,7 +12811,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="26" t="s">
         <v>178</v>
       </c>
@@ -12834,7 +12845,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="26" t="s">
         <v>178</v>
       </c>
@@ -12868,7 +12879,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="26" t="s">
         <v>178</v>
       </c>
@@ -12902,7 +12913,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="26" t="s">
         <v>178</v>
       </c>
@@ -12936,7 +12947,7 @@
         <v>LoGrad-LoElev</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>183</v>
       </c>
@@ -12968,7 +12979,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>183</v>
       </c>
@@ -13000,7 +13011,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>183</v>
       </c>
@@ -13029,7 +13040,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>183</v>
       </c>
@@ -13058,7 +13069,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>183</v>
       </c>
@@ -13087,7 +13098,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>183</v>
       </c>
@@ -13116,7 +13127,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>183</v>
       </c>
@@ -13145,7 +13156,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>183</v>
       </c>
@@ -13174,7 +13185,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>183</v>
       </c>
@@ -13203,7 +13214,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>183</v>
       </c>
@@ -13232,7 +13243,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>183</v>
       </c>
@@ -13264,7 +13275,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>183</v>
       </c>
@@ -13296,7 +13307,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>183</v>
       </c>
@@ -13325,7 +13336,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>183</v>
       </c>
@@ -13354,7 +13365,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>183</v>
       </c>
@@ -13383,7 +13394,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>183</v>
       </c>
@@ -13412,7 +13423,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>183</v>
       </c>
@@ -13441,7 +13452,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>183</v>
       </c>
@@ -13470,7 +13481,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>183</v>
       </c>
@@ -13499,7 +13510,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>183</v>
       </c>
@@ -13528,7 +13539,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>183</v>
       </c>
@@ -13560,7 +13571,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>183</v>
       </c>
@@ -13592,7 +13603,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>183</v>
       </c>
@@ -13621,7 +13632,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>183</v>
       </c>
@@ -13650,7 +13661,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>183</v>
       </c>
@@ -13679,7 +13690,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>183</v>
       </c>
@@ -13708,7 +13719,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>183</v>
       </c>
@@ -13737,7 +13748,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>183</v>
       </c>
@@ -13766,7 +13777,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>183</v>
       </c>
@@ -13795,7 +13806,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>183</v>
       </c>
@@ -13824,7 +13835,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>203</v>
       </c>
@@ -13855,7 +13866,7 @@
         <v>LBR_Fish_BCG_v1</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>203</v>
       </c>
@@ -13886,7 +13897,7 @@
         <v>LBR_Fish_BCG_v1</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>203</v>
       </c>
@@ -13917,7 +13928,7 @@
         <v>LBR_Fish_BCG_v1</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>203</v>
       </c>
@@ -13948,7 +13959,7 @@
         <v>LBR_Fish_BCG_v1</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>209</v>
       </c>
@@ -13979,7 +13990,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>209</v>
       </c>
@@ -14010,7 +14021,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>209</v>
       </c>
@@ -14041,7 +14052,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>209</v>
       </c>
@@ -14072,7 +14083,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>209</v>
       </c>
@@ -14103,7 +14114,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>209</v>
       </c>
@@ -14134,7 +14145,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>209</v>
       </c>
@@ -14165,7 +14176,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>209</v>
       </c>
@@ -14196,7 +14207,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>209</v>
       </c>
@@ -14227,7 +14238,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>209</v>
       </c>
@@ -14258,7 +14269,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>209</v>
       </c>
@@ -14289,7 +14300,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>209</v>
       </c>
@@ -14320,7 +14331,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>209</v>
       </c>
@@ -14351,7 +14362,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>209</v>
       </c>
@@ -14382,7 +14393,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>209</v>
       </c>
@@ -14413,7 +14424,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>209</v>
       </c>
@@ -14444,7 +14455,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>209</v>
       </c>
@@ -14475,7 +14486,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>209</v>
       </c>
@@ -14506,7 +14517,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>209</v>
       </c>
@@ -14537,7 +14548,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>209</v>
       </c>
@@ -14568,7 +14579,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>209</v>
       </c>
@@ -14599,7 +14610,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>209</v>
       </c>
@@ -14630,7 +14641,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>209</v>
       </c>
@@ -14661,7 +14672,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>209</v>
       </c>
@@ -14692,7 +14703,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>209</v>
       </c>
@@ -14723,7 +14734,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>209</v>
       </c>
@@ -14754,7 +14765,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>209</v>
       </c>
@@ -14785,7 +14796,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>209</v>
       </c>
@@ -14816,7 +14827,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>209</v>
       </c>
@@ -14847,7 +14858,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>209</v>
       </c>
@@ -14878,7 +14889,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>209</v>
       </c>
@@ -14909,7 +14920,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>209</v>
       </c>
@@ -14940,7 +14951,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>209</v>
       </c>
@@ -14971,7 +14982,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>209</v>
       </c>
@@ -15002,7 +15013,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>209</v>
       </c>
@@ -15033,7 +15044,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>209</v>
       </c>
@@ -15064,7 +15075,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>209</v>
       </c>
@@ -15095,7 +15106,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>209</v>
       </c>
@@ -15126,7 +15137,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>209</v>
       </c>
@@ -15157,7 +15168,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>209</v>
       </c>
@@ -15188,7 +15199,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>209</v>
       </c>
@@ -15219,7 +15230,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>209</v>
       </c>
@@ -15250,7 +15261,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>209</v>
       </c>
@@ -15281,7 +15292,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>209</v>
       </c>
@@ -15312,7 +15323,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>209</v>
       </c>
@@ -15343,7 +15354,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>209</v>
       </c>
@@ -15374,7 +15385,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>209</v>
       </c>
@@ -15405,7 +15416,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>209</v>
       </c>
@@ -15436,7 +15447,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>209</v>
       </c>
@@ -15467,7 +15478,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>209</v>
       </c>
@@ -15498,7 +15509,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>209</v>
       </c>
@@ -15529,7 +15540,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>209</v>
       </c>
@@ -15560,7 +15571,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>209</v>
       </c>
@@ -15591,7 +15602,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>209</v>
       </c>
@@ -15622,7 +15633,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>209</v>
       </c>
@@ -15653,7 +15664,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>209</v>
       </c>
@@ -15684,7 +15695,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>209</v>
       </c>
@@ -15715,7 +15726,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>209</v>
       </c>
@@ -15746,7 +15757,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>209</v>
       </c>
@@ -15777,7 +15788,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>209</v>
       </c>
@@ -15808,7 +15819,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>209</v>
       </c>
@@ -15839,7 +15850,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>209</v>
       </c>
@@ -15870,7 +15881,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>209</v>
       </c>
@@ -15901,7 +15912,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>209</v>
       </c>
@@ -15932,7 +15943,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>209</v>
       </c>
@@ -15963,7 +15974,7 @@
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="33" t="s">
         <v>178</v>
       </c>
@@ -15994,7 +16005,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="33" t="s">
         <v>178</v>
       </c>
@@ -16025,7 +16036,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="33" t="s">
         <v>178</v>
       </c>
@@ -16056,7 +16067,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="33" t="s">
         <v>178</v>
       </c>
@@ -16087,7 +16098,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="33" t="s">
         <v>178</v>
       </c>
@@ -16118,7 +16129,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="33" t="s">
         <v>178</v>
       </c>
@@ -16149,7 +16160,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="33" t="s">
         <v>178</v>
       </c>
@@ -16180,7 +16191,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="33" t="s">
         <v>178</v>
       </c>
@@ -16211,7 +16222,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="33" t="s">
         <v>178</v>
       </c>
@@ -16242,7 +16253,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="33" t="s">
         <v>178</v>
       </c>
@@ -16273,7 +16284,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="40" t="s">
         <v>178</v>
       </c>
@@ -16304,7 +16315,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="33" t="s">
         <v>178</v>
       </c>
@@ -16335,7 +16346,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="33" t="s">
         <v>178</v>
       </c>
@@ -16366,7 +16377,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="33" t="s">
         <v>178</v>
       </c>
@@ -16397,7 +16408,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="33" t="s">
         <v>178</v>
       </c>
@@ -16428,7 +16439,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="33" t="s">
         <v>178</v>
       </c>
@@ -16459,7 +16470,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="33" t="s">
         <v>178</v>
       </c>
@@ -16490,7 +16501,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="33" t="s">
         <v>178</v>
       </c>
@@ -16521,7 +16532,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="33" t="s">
         <v>178</v>
       </c>
@@ -16552,7 +16563,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="33" t="s">
         <v>178</v>
       </c>
@@ -16583,7 +16594,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="33" t="s">
         <v>178</v>
       </c>
@@ -16614,7 +16625,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="33" t="s">
         <v>178</v>
       </c>
@@ -16645,7 +16656,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="40" t="s">
         <v>178</v>
       </c>
@@ -16676,7 +16687,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="456" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="33" t="s">
         <v>178</v>
       </c>
@@ -16707,7 +16718,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="457" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="33" t="s">
         <v>178</v>
       </c>
@@ -16738,7 +16749,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="458" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="33" t="s">
         <v>178</v>
       </c>
@@ -16769,7 +16780,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="459" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="33" t="s">
         <v>178</v>
       </c>
@@ -16808,7 +16819,7 @@
         <v>248</v>
       </c>
       <c r="C460" s="43" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="D460" s="8" t="s">
         <v>17</v>
@@ -16817,7 +16828,7 @@
         <v>30</v>
       </c>
       <c r="F460" s="34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G460" s="61" t="b">
         <v>1</v>
@@ -16831,7 +16842,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="461" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="33" t="s">
         <v>178</v>
       </c>
@@ -16862,7 +16873,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="462" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="33" t="s">
         <v>178</v>
       </c>
@@ -16893,7 +16904,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="463" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="33" t="s">
         <v>178</v>
       </c>
@@ -16910,7 +16921,7 @@
         <v>0</v>
       </c>
       <c r="F463" s="34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G463" s="61" t="b">
         <v>1</v>
@@ -16924,7 +16935,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="464" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="33" t="s">
         <v>178</v>
       </c>
@@ -16955,7 +16966,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="465" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="33" t="s">
         <v>178</v>
       </c>
@@ -16986,7 +16997,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="466" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="33" t="s">
         <v>178</v>
       </c>
@@ -17017,7 +17028,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="467" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="44" t="s">
         <v>178</v>
       </c>
@@ -17048,7 +17059,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="468" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="33" t="s">
         <v>178</v>
       </c>
@@ -17065,7 +17076,7 @@
         <v>4</v>
       </c>
       <c r="F468" s="34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G468" s="61" t="b">
         <v>1</v>
@@ -17079,7 +17090,7 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="469" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="40" t="s">
         <v>178</v>
       </c>
@@ -17096,7 +17107,7 @@
         <v>45</v>
       </c>
       <c r="F469" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G469" s="61" t="b">
         <v>1</v>
@@ -17110,12 +17121,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="470" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B470" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C470" s="48" t="s">
         <v>14</v>
@@ -17141,12 +17152,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="471" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B471" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C471" s="48" t="s">
         <v>188</v>
@@ -17172,12 +17183,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="472" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B472" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C472" s="30" t="s">
         <v>215</v>
@@ -17203,12 +17214,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="473" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B473" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C473" t="s">
         <v>251</v>
@@ -17220,7 +17231,7 @@
         <v>1</v>
       </c>
       <c r="F473" s="48" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G473" s="61" t="b">
         <v>1</v>
@@ -17239,10 +17250,10 @@
         <v>178</v>
       </c>
       <c r="B474" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C474" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="D474" s="8" t="s">
         <v>17</v>
@@ -17251,7 +17262,7 @@
         <v>15</v>
       </c>
       <c r="F474" s="48" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G474" s="61" t="b">
         <v>1</v>
@@ -17265,12 +17276,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="475" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B475" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C475" s="48" t="s">
         <v>236</v>
@@ -17282,7 +17293,7 @@
         <v>3</v>
       </c>
       <c r="F475" s="48" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G475" s="61" t="b">
         <v>1</v>
@@ -17296,12 +17307,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="476" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B476" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C476" s="50" t="s">
         <v>238</v>
@@ -17327,12 +17338,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="477" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B477" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C477" s="30" t="s">
         <v>134</v>
@@ -17344,7 +17355,7 @@
         <v>5</v>
       </c>
       <c r="F477" s="48" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G477" s="61" t="b">
         <v>1</v>
@@ -17358,12 +17369,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="478" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B478" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C478" s="48" t="s">
         <v>222</v>
@@ -17375,7 +17386,7 @@
         <v>0</v>
       </c>
       <c r="F478" s="48" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G478" s="61" t="b">
         <v>1</v>
@@ -17389,12 +17400,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="479" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B479" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C479" s="48" t="s">
         <v>72</v>
@@ -17420,12 +17431,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="480" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B480" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C480" s="48" t="s">
         <v>74</v>
@@ -17437,7 +17448,7 @@
         <v>4</v>
       </c>
       <c r="F480" s="48" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G480" s="61" t="b">
         <v>1</v>
@@ -17451,12 +17462,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="481" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B481" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C481" s="48" t="s">
         <v>76</v>
@@ -17482,12 +17493,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="482" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="44" t="s">
         <v>178</v>
       </c>
       <c r="B482" s="44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C482" s="39" t="s">
         <v>66</v>
@@ -17513,12 +17524,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="483" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B483" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C483" s="48" t="s">
         <v>245</v>
@@ -17530,7 +17541,7 @@
         <v>4</v>
       </c>
       <c r="F483" s="48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G483" s="61" t="b">
         <v>1</v>
@@ -17544,12 +17555,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="484" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="40" t="s">
         <v>178</v>
       </c>
       <c r="B484" s="40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C484" s="51" t="s">
         <v>243</v>
@@ -17561,7 +17572,7 @@
         <v>60</v>
       </c>
       <c r="F484" s="51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G484" s="61" t="b">
         <v>1</v>
@@ -17575,12 +17586,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B485" s="54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C485" s="34" t="s">
         <v>14</v>
@@ -17606,12 +17617,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B486" s="54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C486" s="36" t="s">
         <v>215</v>
@@ -17637,12 +17648,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B487" s="54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C487" s="48" t="s">
         <v>236</v>
@@ -17668,12 +17679,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B488" s="54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C488" s="48" t="s">
         <v>220</v>
@@ -17699,12 +17710,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B489" s="54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C489" s="48" t="s">
         <v>222</v>
@@ -17730,12 +17741,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B490" s="54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C490" s="48" t="s">
         <v>72</v>
@@ -17761,12 +17772,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B491" s="54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C491" s="48" t="s">
         <v>74</v>
@@ -17792,12 +17803,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B492" s="54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C492" s="48" t="s">
         <v>76</v>
@@ -17823,15 +17834,15 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B493" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="C493" s="48" t="s">
         <v>264</v>
-      </c>
-      <c r="C493" s="48" t="s">
-        <v>265</v>
       </c>
       <c r="D493" s="8" t="s">
         <v>17</v>
@@ -17840,7 +17851,7 @@
         <v>3</v>
       </c>
       <c r="F493" s="48" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G493" s="62" t="b">
         <v>0</v>
@@ -17854,12 +17865,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B494" s="54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C494" s="39" t="s">
         <v>66</v>
@@ -17885,12 +17896,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="40" t="s">
         <v>178</v>
       </c>
       <c r="B495" s="56" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C495" s="41" t="s">
         <v>243</v>
@@ -17916,12 +17927,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B496" s="58" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C496" s="34" t="s">
         <v>245</v>
@@ -17933,7 +17944,7 @@
         <v>2</v>
       </c>
       <c r="F496" s="34" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G496" s="61" t="b">
         <v>1</v>
@@ -17947,12 +17958,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B497" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C497" s="34" t="s">
         <v>14</v>
@@ -17978,12 +17989,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B498" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C498" s="34" t="s">
         <v>188</v>
@@ -18009,12 +18020,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B499" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C499" s="34" t="s">
         <v>169</v>
@@ -18040,12 +18051,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B500" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C500" s="36" t="s">
         <v>215</v>
@@ -18071,12 +18082,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B501" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C501" s="34" t="s">
         <v>236</v>
@@ -18102,12 +18113,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B502" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C502" s="60" t="s">
         <v>238</v>
@@ -18133,12 +18144,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B503" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C503" s="34" t="s">
         <v>222</v>
@@ -18150,7 +18161,7 @@
         <v>0</v>
       </c>
       <c r="F503" s="34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G503" s="61" t="b">
         <v>1</v>
@@ -18164,12 +18175,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B504" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C504" s="34" t="s">
         <v>72</v>
@@ -18195,12 +18206,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B505" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C505" s="34" t="s">
         <v>74</v>
@@ -18226,12 +18237,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B506" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C506" s="34" t="s">
         <v>76</v>
@@ -18257,12 +18268,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B507" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C507" s="34" t="s">
         <v>245</v>
@@ -18274,7 +18285,7 @@
         <v>4</v>
       </c>
       <c r="F507" s="34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G507" s="61" t="b">
         <v>1</v>
@@ -18288,12 +18299,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="41" t="s">
         <v>178</v>
       </c>
       <c r="B508" s="41" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C508" s="41" t="s">
         <v>243</v>
@@ -18305,7 +18316,7 @@
         <v>45</v>
       </c>
       <c r="F508" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G508" s="61" t="b">
         <v>1</v>
@@ -18319,12 +18330,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B509" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C509" s="39" t="s">
         <v>66</v>
@@ -18350,12 +18361,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B510" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C510" s="34" t="s">
         <v>14</v>
@@ -18381,12 +18392,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B511" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C511" s="34" t="s">
         <v>14</v>
@@ -18412,12 +18423,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="41" t="s">
         <v>178</v>
       </c>
       <c r="B512" s="41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C512" s="41" t="s">
         <v>243</v>
@@ -18429,7 +18440,7 @@
         <v>60</v>
       </c>
       <c r="F512" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G512" s="61" t="b">
         <v>1</v>
@@ -18448,10 +18459,10 @@
         <v>178</v>
       </c>
       <c r="B513" s="41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C513" s="41" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D513" s="57" t="s">
         <v>17</v>
@@ -18460,13 +18471,13 @@
         <v>50</v>
       </c>
       <c r="F513" s="41" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="G513" s="62" t="b">
         <v>0</v>
       </c>
       <c r="H513" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I513" t="str">
         <f t="shared" si="21"/>
@@ -18477,12 +18488,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B514" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C514" s="34" t="s">
         <v>236</v>
@@ -18494,7 +18505,7 @@
         <v>3</v>
       </c>
       <c r="F514" s="34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G514" s="61" t="b">
         <v>1</v>
@@ -18508,15 +18519,15 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B515" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C515" s="34" t="s">
         <v>269</v>
-      </c>
-      <c r="C515" s="34" t="s">
-        <v>272</v>
       </c>
       <c r="D515" s="59" t="s">
         <v>17</v>
@@ -18525,7 +18536,7 @@
         <v>35</v>
       </c>
       <c r="F515" s="34" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G515" s="61" t="b">
         <v>1</v>
@@ -18539,12 +18550,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B516" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C516" s="60" t="s">
         <v>238</v>
@@ -18570,12 +18581,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B517" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C517" s="34" t="s">
         <v>220</v>
@@ -18587,7 +18598,7 @@
         <v>10</v>
       </c>
       <c r="F517" s="34" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G517" s="61" t="b">
         <v>1</v>
@@ -18601,12 +18612,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B518" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C518" s="34" t="s">
         <v>222</v>
@@ -18618,7 +18629,7 @@
         <v>0</v>
       </c>
       <c r="F518" s="34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G518" s="61" t="b">
         <v>1</v>
@@ -18632,12 +18643,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B519" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C519" s="34" t="s">
         <v>72</v>
@@ -18663,12 +18674,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B520" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C520" s="34" t="s">
         <v>74</v>
@@ -18680,7 +18691,7 @@
         <v>3</v>
       </c>
       <c r="F520" s="34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G520" s="61" t="b">
         <v>1</v>
@@ -18694,12 +18705,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="521" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B521" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C521" s="34" t="s">
         <v>76</v>
@@ -18725,12 +18736,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="522" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B522" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C522" s="34" t="s">
         <v>245</v>
@@ -18742,7 +18753,7 @@
         <v>4</v>
       </c>
       <c r="F522" s="34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G522" s="61" t="b">
         <v>1</v>
@@ -18756,12 +18767,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B523" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C523" s="39" t="s">
         <v>66</v>
@@ -18787,12 +18798,12 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>178</v>
       </c>
       <c r="B524" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C524" t="s">
         <v>14</v>
@@ -18810,18 +18821,18 @@
         <v>1</v>
       </c>
       <c r="I524" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J524" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>178</v>
       </c>
       <c r="B525" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C525" t="s">
         <v>14</v>
@@ -18839,18 +18850,18 @@
         <v>1</v>
       </c>
       <c r="I525" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J525" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>178</v>
       </c>
       <c r="B526" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C526" t="s">
         <v>243</v>
@@ -18862,13 +18873,13 @@
         <v>40</v>
       </c>
       <c r="F526" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G526" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I526" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J526" t="s">
         <v>178</v>
@@ -18879,10 +18890,10 @@
         <v>178</v>
       </c>
       <c r="B527" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C527" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D527" s="28" t="s">
         <v>17</v>
@@ -18891,24 +18902,24 @@
         <v>50</v>
       </c>
       <c r="F527" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="G527" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I527" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J527" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="528" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>178</v>
       </c>
       <c r="B528" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C528" t="s">
         <v>236</v>
@@ -18926,21 +18937,21 @@
         <v>1</v>
       </c>
       <c r="I528" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J528" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="529" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>178</v>
       </c>
       <c r="B529" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C529" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D529" s="28" t="s">
         <v>17</v>
@@ -18949,24 +18960,24 @@
         <v>40</v>
       </c>
       <c r="F529" t="s">
+        <v>270</v>
+      </c>
+      <c r="G529" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I529" t="s">
         <v>273</v>
       </c>
-      <c r="G529" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I529" t="s">
-        <v>276</v>
-      </c>
       <c r="J529" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>178</v>
       </c>
       <c r="B530" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C530" t="s">
         <v>238</v>
@@ -18984,18 +18995,18 @@
         <v>1</v>
       </c>
       <c r="I530" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J530" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>178</v>
       </c>
       <c r="B531" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C531" t="s">
         <v>220</v>
@@ -19007,24 +19018,24 @@
         <v>5</v>
       </c>
       <c r="F531" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G531" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I531" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J531" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>178</v>
       </c>
       <c r="B532" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C532" t="s">
         <v>222</v>
@@ -19036,24 +19047,24 @@
         <v>2</v>
       </c>
       <c r="F532" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G532" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I532" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J532" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>178</v>
       </c>
       <c r="B533" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C533" t="s">
         <v>72</v>
@@ -19071,18 +19082,18 @@
         <v>1</v>
       </c>
       <c r="I533" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J533" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>178</v>
       </c>
       <c r="B534" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C534" t="s">
         <v>74</v>
@@ -19094,24 +19105,24 @@
         <v>3</v>
       </c>
       <c r="F534" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G534" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I534" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J534" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>178</v>
       </c>
       <c r="B535" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C535" t="s">
         <v>76</v>
@@ -19129,18 +19140,18 @@
         <v>1</v>
       </c>
       <c r="I535" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J535" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>178</v>
       </c>
       <c r="B536" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C536" t="s">
         <v>245</v>
@@ -19152,24 +19163,24 @@
         <v>0</v>
       </c>
       <c r="F536" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G536" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I536" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J536" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>178</v>
       </c>
       <c r="B537" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C537" t="s">
         <v>66</v>
@@ -19187,18 +19198,18 @@
         <v>1</v>
       </c>
       <c r="I537" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J537" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>178</v>
       </c>
       <c r="B538" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C538" t="s">
         <v>14</v>
@@ -19216,18 +19227,18 @@
         <v>1</v>
       </c>
       <c r="I538" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J538" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>178</v>
       </c>
       <c r="B539" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C539" t="s">
         <v>14</v>
@@ -19245,18 +19256,18 @@
         <v>1</v>
       </c>
       <c r="I539" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J539" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>178</v>
       </c>
       <c r="B540" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C540" t="s">
         <v>243</v>
@@ -19268,24 +19279,24 @@
         <v>40</v>
       </c>
       <c r="F540" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G540" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I540" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J540" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>178</v>
       </c>
       <c r="B541" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C541" t="s">
         <v>215</v>
@@ -19303,18 +19314,18 @@
         <v>1</v>
       </c>
       <c r="I541" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J541" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>178</v>
       </c>
       <c r="B542" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C542" t="s">
         <v>236</v>
@@ -19332,21 +19343,21 @@
         <v>1</v>
       </c>
       <c r="I542" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J542" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>178</v>
       </c>
       <c r="B543" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C543" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D543" s="28" t="s">
         <v>17</v>
@@ -19355,24 +19366,24 @@
         <v>35</v>
       </c>
       <c r="F543" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G543" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I543" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J543" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>178</v>
       </c>
       <c r="B544" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C544" t="s">
         <v>238</v>
@@ -19390,18 +19401,18 @@
         <v>1</v>
       </c>
       <c r="I544" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J544" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="545" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>178</v>
       </c>
       <c r="B545" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C545" t="s">
         <v>220</v>
@@ -19413,24 +19424,24 @@
         <v>10</v>
       </c>
       <c r="F545" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G545" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I545" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J545" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>178</v>
       </c>
       <c r="B546" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C546" t="s">
         <v>222</v>
@@ -19442,24 +19453,24 @@
         <v>0</v>
       </c>
       <c r="F546" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G546" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I546" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J546" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>178</v>
       </c>
       <c r="B547" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C547" t="s">
         <v>72</v>
@@ -19477,18 +19488,18 @@
         <v>1</v>
       </c>
       <c r="I547" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J547" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>178</v>
       </c>
       <c r="B548" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C548" t="s">
         <v>74</v>
@@ -19500,24 +19511,24 @@
         <v>3</v>
       </c>
       <c r="F548" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G548" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I548" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J548" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="549" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>178</v>
       </c>
       <c r="B549" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C549" t="s">
         <v>76</v>
@@ -19535,18 +19546,18 @@
         <v>1</v>
       </c>
       <c r="I549" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J549" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>178</v>
       </c>
       <c r="B550" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C550" t="s">
         <v>245</v>
@@ -19558,24 +19569,24 @@
         <v>0</v>
       </c>
       <c r="F550" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G550" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I550" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J550" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>178</v>
       </c>
       <c r="B551" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C551" t="s">
         <v>66</v>
@@ -19593,18 +19604,18 @@
         <v>1</v>
       </c>
       <c r="I551" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J551" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>178</v>
       </c>
       <c r="B552" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C552" t="s">
         <v>14</v>
@@ -19622,18 +19633,18 @@
         <v>1</v>
       </c>
       <c r="I552" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J552" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="553" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>178</v>
       </c>
       <c r="B553" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C553" t="s">
         <v>14</v>
@@ -19651,18 +19662,18 @@
         <v>1</v>
       </c>
       <c r="I553" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J553" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>178</v>
       </c>
       <c r="B554" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C554" t="s">
         <v>243</v>
@@ -19674,24 +19685,24 @@
         <v>30</v>
       </c>
       <c r="F554" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G554" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I554" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J554" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="555" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>178</v>
       </c>
       <c r="B555" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C555" t="s">
         <v>215</v>
@@ -19703,24 +19714,24 @@
         <v>3</v>
       </c>
       <c r="F555" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G555" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I555" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J555" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="556" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>178</v>
       </c>
       <c r="B556" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C556" t="s">
         <v>236</v>
@@ -19738,21 +19749,21 @@
         <v>1</v>
       </c>
       <c r="I556" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J556" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="557" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>178</v>
       </c>
       <c r="B557" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C557" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D557" s="28" t="s">
         <v>17</v>
@@ -19761,24 +19772,24 @@
         <v>40</v>
       </c>
       <c r="F557" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G557" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I557" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J557" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="558" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>178</v>
       </c>
       <c r="B558" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C558" t="s">
         <v>238</v>
@@ -19796,18 +19807,18 @@
         <v>1</v>
       </c>
       <c r="I558" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J558" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="559" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>178</v>
       </c>
       <c r="B559" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C559" t="s">
         <v>220</v>
@@ -19819,24 +19830,24 @@
         <v>5</v>
       </c>
       <c r="F559" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G559" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I559" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J559" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="560" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>178</v>
       </c>
       <c r="B560" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C560" t="s">
         <v>222</v>
@@ -19848,24 +19859,24 @@
         <v>1</v>
       </c>
       <c r="F560" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G560" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I560" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J560" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>178</v>
       </c>
       <c r="B561" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C561" t="s">
         <v>72</v>
@@ -19883,18 +19894,18 @@
         <v>1</v>
       </c>
       <c r="I561" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J561" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>178</v>
       </c>
       <c r="B562" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C562" t="s">
         <v>74</v>
@@ -19906,24 +19917,24 @@
         <v>2</v>
       </c>
       <c r="F562" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G562" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I562" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J562" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>178</v>
       </c>
       <c r="B563" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C563" t="s">
         <v>76</v>
@@ -19941,18 +19952,18 @@
         <v>1</v>
       </c>
       <c r="I563" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J563" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>178</v>
       </c>
       <c r="B564" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C564" t="s">
         <v>245</v>
@@ -19964,24 +19975,24 @@
         <v>0</v>
       </c>
       <c r="F564" t="s">
+        <v>274</v>
+      </c>
+      <c r="G564" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I564" t="s">
         <v>277</v>
       </c>
-      <c r="G564" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I564" t="s">
-        <v>280</v>
-      </c>
       <c r="J564" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>178</v>
       </c>
       <c r="B565" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C565" t="s">
         <v>66</v>
@@ -19999,14 +20010,27 @@
         <v>1</v>
       </c>
       <c r="I565" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J565" t="s">
         <v>178</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J565" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:J565" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="BCG_ORWA_v1_Bugs500ct"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="pi_dom02_BCG_att456"/>
+        <filter val="pi_NonInsTrombJuga_BCG_att456"/>
+        <filter val="pt_NonIns_BCG_att456"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="C2:C66 C162:C186 C248:C272">
     <cfRule type="expression" dxfId="7" priority="18">
       <formula>$G2=FALSE</formula>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92EEF72-8B0E-442C-B9C5-FA2CC30B0829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99D74C3-B0E2-4E09-9DBC-A4A1F4DC4B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Flags" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$565</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$561</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3203" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="306">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -792,12 +792,6 @@
     <t>low number of total taxa</t>
   </si>
   <si>
-    <t>imbalance, dominance by one taxon</t>
-  </si>
-  <si>
-    <t>imbalance, dominance by two taxa</t>
-  </si>
-  <si>
     <t>LBR_Bugs_BCG_v1</t>
   </si>
   <si>
@@ -1030,6 +1024,69 @@
   </si>
   <si>
     <t>high dominance by two tolerant (Attr 4, 5, 6m, 6t) taxa</t>
+  </si>
+  <si>
+    <t>Update LBR_Fish_BCG_v1</t>
+  </si>
+  <si>
+    <t>Removed Main_Eckert before adding</t>
+  </si>
+  <si>
+    <t>pi_delt</t>
+  </si>
+  <si>
+    <t>delt anomalies</t>
+  </si>
+  <si>
+    <t>high number of total individuals</t>
+  </si>
+  <si>
+    <t>nt_hybrid</t>
+  </si>
+  <si>
+    <t>hybrid taxa present</t>
+  </si>
+  <si>
+    <t>pi_Cott</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>sculpins absent</t>
+  </si>
+  <si>
+    <t>nt_BCG_att123</t>
+  </si>
+  <si>
+    <t>low number sensitive (BCG Attribute I + II + III) taxa</t>
+  </si>
+  <si>
+    <t>sensitive (BCG Attribute I + II + III) taxa absent</t>
+  </si>
+  <si>
+    <t>nt_BCG_att6t</t>
+  </si>
+  <si>
+    <t>very tolerant, non-native taxa (BCG Attribute VI t) present</t>
+  </si>
+  <si>
+    <t>higher number of very tolerant, non-native taxa (BCG Attribute VI t)</t>
+  </si>
+  <si>
+    <t>pi_ti_cold</t>
+  </si>
+  <si>
+    <t>low number of cold water individuals</t>
+  </si>
+  <si>
+    <t>cold water taxa absent</t>
+  </si>
+  <si>
+    <t>n_ac_mwf</t>
+  </si>
+  <si>
+    <t>mountain whitefish, low number of age classes</t>
   </si>
 </sst>
 </file>
@@ -1852,7 +1909,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1879,7 +1936,7 @@
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <f>MAX(A22:A574)</f>
-        <v>46210</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2153,7 +2210,7 @@
         <v>46160</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2161,7 +2218,7 @@
         <v>46161</v>
       </c>
       <c r="B49" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2177,7 +2234,7 @@
         <v>46196</v>
       </c>
       <c r="B51" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2185,7 +2242,7 @@
         <v>46209</v>
       </c>
       <c r="B52" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2193,7 +2250,20 @@
         <v>46210</v>
       </c>
       <c r="B53" t="s">
-        <v>283</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="15">
+        <v>46241</v>
+      </c>
+      <c r="B54" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -2308,7 +2378,7 @@
   <sheetPr codeName="Sheet2" filterMode="1">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J565"/>
+  <dimension ref="A1:J619"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -13837,10 +13907,10 @@
     </row>
     <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B364" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C364" t="s">
         <v>14</v>
@@ -13849,134 +13919,134 @@
         <v>16</v>
       </c>
       <c r="E364">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F364" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G364" t="b">
         <v>1</v>
       </c>
       <c r="I364" t="str">
-        <f t="shared" ref="I364:I427" si="15">B364</f>
-        <v>Main_Eckert</v>
+        <f t="shared" ref="I364:I423" si="15">B364</f>
+        <v>Main_BarberPool</v>
       </c>
       <c r="J364" t="str">
-        <f t="shared" ref="J364:J427" si="16">A364</f>
-        <v>LBR_Fish_BCG_v1</v>
+        <f t="shared" ref="J364:J423" si="16">A364</f>
+        <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
     <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B365" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C365" t="s">
-        <v>188</v>
+        <v>14</v>
       </c>
       <c r="D365" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E365">
-        <v>4</v>
+        <v>650</v>
       </c>
       <c r="F365" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G365" t="b">
         <v>1</v>
       </c>
       <c r="I365" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Eckert</v>
+        <v>Main_BarberPool</v>
       </c>
       <c r="J365" t="str">
         <f t="shared" si="16"/>
-        <v>LBR_Fish_BCG_v1</v>
+        <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
     <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B366" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C366" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="D366" t="s">
         <v>17</v>
       </c>
       <c r="E366">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="F366" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G366" t="b">
         <v>1</v>
       </c>
       <c r="I366" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Eckert</v>
+        <v>Main_BarberPool</v>
       </c>
       <c r="J366" t="str">
         <f t="shared" si="16"/>
-        <v>LBR_Fish_BCG_v1</v>
+        <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
     <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B367" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C367" t="s">
-        <v>51</v>
+        <v>213</v>
       </c>
       <c r="D367" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E367">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="F367" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G367" t="b">
         <v>1</v>
       </c>
       <c r="I367" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Eckert</v>
+        <v>Main_BarberPool</v>
       </c>
       <c r="J367" t="str">
         <f t="shared" si="16"/>
-        <v>LBR_Fish_BCG_v1</v>
+        <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
     <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B368" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C368" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="D368" t="s">
         <v>16</v>
       </c>
       <c r="E368">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="F368" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G368" t="b">
         <v>1</v>
@@ -13992,22 +14062,22 @@
     </row>
     <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B369" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C369" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D369" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E369">
-        <v>650</v>
+        <v>1</v>
       </c>
       <c r="F369" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G369" t="b">
         <v>1</v>
@@ -14023,22 +14093,22 @@
     </row>
     <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B370" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C370" t="s">
-        <v>213</v>
+        <v>76</v>
       </c>
       <c r="D370" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F370" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G370" t="b">
         <v>1</v>
@@ -14054,22 +14124,22 @@
     </row>
     <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B371" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C371" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D371" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E371">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F371" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G371" t="b">
         <v>1</v>
@@ -14085,22 +14155,22 @@
     </row>
     <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B372" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C372" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="D372" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E372">
         <v>3</v>
       </c>
       <c r="F372" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G372" t="b">
         <v>1</v>
@@ -14116,29 +14186,29 @@
     </row>
     <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
+        <v>207</v>
+      </c>
+      <c r="B373" t="s">
+        <v>204</v>
+      </c>
+      <c r="C373" t="s">
+        <v>14</v>
+      </c>
+      <c r="D373" t="s">
+        <v>16</v>
+      </c>
+      <c r="E373">
+        <v>500</v>
+      </c>
+      <c r="F373" t="s">
         <v>209</v>
-      </c>
-      <c r="B373" t="s">
-        <v>210</v>
-      </c>
-      <c r="C373" t="s">
-        <v>74</v>
-      </c>
-      <c r="D373" t="s">
-        <v>16</v>
-      </c>
-      <c r="E373">
-        <v>1</v>
-      </c>
-      <c r="F373" t="s">
-        <v>218</v>
       </c>
       <c r="G373" t="b">
         <v>1</v>
       </c>
       <c r="I373" t="str">
         <f t="shared" si="15"/>
-        <v>Main_BarberPool</v>
+        <v>Main_Eckert</v>
       </c>
       <c r="J373" t="str">
         <f t="shared" si="16"/>
@@ -14147,29 +14217,29 @@
     </row>
     <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B374" t="s">
+        <v>204</v>
+      </c>
+      <c r="C374" t="s">
+        <v>14</v>
+      </c>
+      <c r="D374" t="s">
+        <v>15</v>
+      </c>
+      <c r="E374">
+        <v>650</v>
+      </c>
+      <c r="F374" t="s">
         <v>210</v>
-      </c>
-      <c r="C374" t="s">
-        <v>76</v>
-      </c>
-      <c r="D374" t="s">
-        <v>233</v>
-      </c>
-      <c r="E374">
-        <v>2</v>
-      </c>
-      <c r="F374" t="s">
-        <v>219</v>
       </c>
       <c r="G374" t="b">
         <v>1</v>
       </c>
       <c r="I374" t="str">
         <f t="shared" si="15"/>
-        <v>Main_BarberPool</v>
+        <v>Main_Eckert</v>
       </c>
       <c r="J374" t="str">
         <f t="shared" si="16"/>
@@ -14178,29 +14248,29 @@
     </row>
     <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B375" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C375" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D375" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E375">
         <v>1</v>
       </c>
       <c r="F375" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G375" t="b">
         <v>1</v>
       </c>
       <c r="I375" t="str">
         <f t="shared" si="15"/>
-        <v>Main_BarberPool</v>
+        <v>Main_Eckert</v>
       </c>
       <c r="J375" t="str">
         <f t="shared" si="16"/>
@@ -14209,29 +14279,29 @@
     </row>
     <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B376" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C376" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D376" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E376">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F376" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G376" t="b">
         <v>1</v>
       </c>
       <c r="I376" t="str">
         <f t="shared" si="15"/>
-        <v>Main_BarberPool</v>
+        <v>Main_Eckert</v>
       </c>
       <c r="J376" t="str">
         <f t="shared" si="16"/>
@@ -14240,22 +14310,22 @@
     </row>
     <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B377" t="s">
         <v>204</v>
       </c>
       <c r="C377" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="D377" t="s">
         <v>16</v>
       </c>
       <c r="E377">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="F377" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G377" t="b">
         <v>1</v>
@@ -14271,22 +14341,22 @@
     </row>
     <row r="378" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B378" t="s">
         <v>204</v>
       </c>
       <c r="C378" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D378" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E378">
-        <v>650</v>
+        <v>1</v>
       </c>
       <c r="F378" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G378" t="b">
         <v>1</v>
@@ -14302,22 +14372,22 @@
     </row>
     <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B379" t="s">
         <v>204</v>
       </c>
       <c r="C379" t="s">
-        <v>213</v>
+        <v>76</v>
       </c>
       <c r="D379" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E379">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F379" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G379" t="b">
         <v>1</v>
@@ -14333,22 +14403,22 @@
     </row>
     <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B380" t="s">
         <v>204</v>
       </c>
       <c r="C380" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D380" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F380" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G380" t="b">
         <v>1</v>
@@ -14364,22 +14434,22 @@
     </row>
     <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B381" t="s">
         <v>204</v>
       </c>
       <c r="C381" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="D381" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E381">
         <v>3</v>
       </c>
       <c r="F381" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G381" t="b">
         <v>1</v>
@@ -14395,29 +14465,29 @@
     </row>
     <row r="382" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>207</v>
+      </c>
+      <c r="B382" t="s">
+        <v>222</v>
+      </c>
+      <c r="C382" t="s">
+        <v>14</v>
+      </c>
+      <c r="D382" t="s">
+        <v>16</v>
+      </c>
+      <c r="E382">
+        <v>500</v>
+      </c>
+      <c r="F382" t="s">
         <v>209</v>
-      </c>
-      <c r="B382" t="s">
-        <v>204</v>
-      </c>
-      <c r="C382" t="s">
-        <v>74</v>
-      </c>
-      <c r="D382" t="s">
-        <v>16</v>
-      </c>
-      <c r="E382">
-        <v>1</v>
-      </c>
-      <c r="F382" t="s">
-        <v>218</v>
       </c>
       <c r="G382" t="b">
         <v>1</v>
       </c>
       <c r="I382" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Eckert</v>
+        <v>Main_Middleton</v>
       </c>
       <c r="J382" t="str">
         <f t="shared" si="16"/>
@@ -14426,29 +14496,29 @@
     </row>
     <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B383" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C383" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D383" t="s">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="E383">
-        <v>2</v>
+        <v>650</v>
       </c>
       <c r="F383" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G383" t="b">
         <v>1</v>
       </c>
       <c r="I383" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Eckert</v>
+        <v>Main_Middleton</v>
       </c>
       <c r="J383" t="str">
         <f t="shared" si="16"/>
@@ -14457,29 +14527,29 @@
     </row>
     <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B384" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C384" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D384" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E384">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F384" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G384" t="b">
         <v>1</v>
       </c>
       <c r="I384" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Eckert</v>
+        <v>Main_Middleton</v>
       </c>
       <c r="J384" t="str">
         <f t="shared" si="16"/>
@@ -14488,29 +14558,29 @@
     </row>
     <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B385" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C385" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D385" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E385">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F385" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G385" t="b">
         <v>1</v>
       </c>
       <c r="I385" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Eckert</v>
+        <v>Main_Middleton</v>
       </c>
       <c r="J385" t="str">
         <f t="shared" si="16"/>
@@ -14519,22 +14589,22 @@
     </row>
     <row r="386" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B386" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C386" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="D386" t="s">
         <v>16</v>
       </c>
       <c r="E386">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="F386" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G386" t="b">
         <v>1</v>
@@ -14550,22 +14620,22 @@
     </row>
     <row r="387" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B387" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C387" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D387" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E387">
-        <v>650</v>
+        <v>1</v>
       </c>
       <c r="F387" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G387" t="b">
         <v>1</v>
@@ -14581,22 +14651,22 @@
     </row>
     <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B388" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C388" t="s">
-        <v>213</v>
+        <v>76</v>
       </c>
       <c r="D388" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E388">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F388" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G388" t="b">
         <v>1</v>
@@ -14612,22 +14682,22 @@
     </row>
     <row r="389" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B389" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C389" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D389" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E389">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F389" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G389" t="b">
         <v>1</v>
@@ -14643,22 +14713,22 @@
     </row>
     <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B390" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C390" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="D390" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E390">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F390" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G390" t="b">
         <v>1</v>
@@ -14674,29 +14744,29 @@
     </row>
     <row r="391" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
+        <v>207</v>
+      </c>
+      <c r="B391" t="s">
+        <v>223</v>
+      </c>
+      <c r="C391" t="s">
+        <v>14</v>
+      </c>
+      <c r="D391" t="s">
+        <v>16</v>
+      </c>
+      <c r="E391">
+        <v>500</v>
+      </c>
+      <c r="F391" t="s">
         <v>209</v>
-      </c>
-      <c r="B391" t="s">
-        <v>224</v>
-      </c>
-      <c r="C391" t="s">
-        <v>74</v>
-      </c>
-      <c r="D391" t="s">
-        <v>16</v>
-      </c>
-      <c r="E391">
-        <v>1</v>
-      </c>
-      <c r="F391" t="s">
-        <v>218</v>
       </c>
       <c r="G391" t="b">
         <v>1</v>
       </c>
       <c r="I391" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Middleton</v>
+        <v>Main_NotusParma</v>
       </c>
       <c r="J391" t="str">
         <f t="shared" si="16"/>
@@ -14705,29 +14775,29 @@
     </row>
     <row r="392" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B392" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C392" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D392" t="s">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="E392">
-        <v>2</v>
+        <v>650</v>
       </c>
       <c r="F392" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G392" t="b">
         <v>1</v>
       </c>
       <c r="I392" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Middleton</v>
+        <v>Main_NotusParma</v>
       </c>
       <c r="J392" t="str">
         <f t="shared" si="16"/>
@@ -14736,29 +14806,29 @@
     </row>
     <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B393" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C393" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D393" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E393">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F393" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G393" t="b">
         <v>1</v>
       </c>
       <c r="I393" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Middleton</v>
+        <v>Main_NotusParma</v>
       </c>
       <c r="J393" t="str">
         <f t="shared" si="16"/>
@@ -14767,29 +14837,29 @@
     </row>
     <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B394" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C394" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D394" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E394">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="F394" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G394" t="b">
         <v>1</v>
       </c>
       <c r="I394" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Middleton</v>
+        <v>Main_NotusParma</v>
       </c>
       <c r="J394" t="str">
         <f t="shared" si="16"/>
@@ -14798,22 +14868,22 @@
     </row>
     <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B395" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C395" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="D395" t="s">
         <v>16</v>
       </c>
       <c r="E395">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="F395" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G395" t="b">
         <v>1</v>
@@ -14829,22 +14899,22 @@
     </row>
     <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B396" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C396" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D396" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
       <c r="E396">
-        <v>650</v>
+        <v>2</v>
       </c>
       <c r="F396" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G396" t="b">
         <v>1</v>
@@ -14860,22 +14930,22 @@
     </row>
     <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B397" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C397" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D397" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E397">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F397" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G397" t="b">
         <v>1</v>
@@ -14891,22 +14961,22 @@
     </row>
     <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B398" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C398" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D398" t="s">
-        <v>233</v>
+        <v>17</v>
       </c>
       <c r="E398">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="F398" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G398" t="b">
         <v>1</v>
@@ -14922,29 +14992,29 @@
     </row>
     <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
+        <v>207</v>
+      </c>
+      <c r="B399" t="s">
+        <v>224</v>
+      </c>
+      <c r="C399" t="s">
+        <v>14</v>
+      </c>
+      <c r="D399" t="s">
+        <v>16</v>
+      </c>
+      <c r="E399">
+        <v>500</v>
+      </c>
+      <c r="F399" t="s">
         <v>209</v>
-      </c>
-      <c r="B399" t="s">
-        <v>225</v>
-      </c>
-      <c r="C399" t="s">
-        <v>72</v>
-      </c>
-      <c r="D399" t="s">
-        <v>16</v>
-      </c>
-      <c r="E399">
-        <v>3</v>
-      </c>
-      <c r="F399" t="s">
-        <v>217</v>
       </c>
       <c r="G399" t="b">
         <v>1</v>
       </c>
       <c r="I399" t="str">
         <f t="shared" si="15"/>
-        <v>Main_NotusParma</v>
+        <v>Main_SoChannel</v>
       </c>
       <c r="J399" t="str">
         <f t="shared" si="16"/>
@@ -14953,29 +15023,29 @@
     </row>
     <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B400" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C400" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D400" t="s">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="E400">
-        <v>2</v>
+        <v>650</v>
       </c>
       <c r="F400" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G400" t="b">
         <v>1</v>
       </c>
       <c r="I400" t="str">
         <f t="shared" si="15"/>
-        <v>Main_NotusParma</v>
+        <v>Main_SoChannel</v>
       </c>
       <c r="J400" t="str">
         <f t="shared" si="16"/>
@@ -14984,29 +15054,29 @@
     </row>
     <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B401" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C401" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D401" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E401">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F401" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G401" t="b">
         <v>1</v>
       </c>
       <c r="I401" t="str">
         <f t="shared" si="15"/>
-        <v>Main_NotusParma</v>
+        <v>Main_SoChannel</v>
       </c>
       <c r="J401" t="str">
         <f t="shared" si="16"/>
@@ -15015,29 +15085,29 @@
     </row>
     <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B402" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C402" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D402" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E402">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="F402" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G402" t="b">
         <v>1</v>
       </c>
       <c r="I402" t="str">
         <f t="shared" si="15"/>
-        <v>Main_NotusParma</v>
+        <v>Main_SoChannel</v>
       </c>
       <c r="J402" t="str">
         <f t="shared" si="16"/>
@@ -15046,22 +15116,22 @@
     </row>
     <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B403" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C403" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="D403" t="s">
         <v>16</v>
       </c>
       <c r="E403">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="F403" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G403" t="b">
         <v>1</v>
@@ -15077,22 +15147,22 @@
     </row>
     <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B404" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C404" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D404" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E404">
-        <v>650</v>
+        <v>1</v>
       </c>
       <c r="F404" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G404" t="b">
         <v>1</v>
@@ -15108,22 +15178,22 @@
     </row>
     <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B405" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C405" t="s">
-        <v>213</v>
+        <v>76</v>
       </c>
       <c r="D405" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E405">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F405" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G405" t="b">
         <v>1</v>
@@ -15139,22 +15209,22 @@
     </row>
     <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B406" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C406" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D406" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E406">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="F406" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G406" t="b">
         <v>1</v>
@@ -15170,22 +15240,22 @@
     </row>
     <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B407" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C407" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="D407" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E407">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F407" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G407" t="b">
         <v>1</v>
@@ -15201,29 +15271,29 @@
     </row>
     <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
+        <v>207</v>
+      </c>
+      <c r="B408" t="s">
+        <v>225</v>
+      </c>
+      <c r="C408" t="s">
+        <v>14</v>
+      </c>
+      <c r="D408" t="s">
+        <v>16</v>
+      </c>
+      <c r="E408">
+        <v>500</v>
+      </c>
+      <c r="F408" t="s">
         <v>209</v>
-      </c>
-      <c r="B408" t="s">
-        <v>226</v>
-      </c>
-      <c r="C408" t="s">
-        <v>74</v>
-      </c>
-      <c r="D408" t="s">
-        <v>16</v>
-      </c>
-      <c r="E408">
-        <v>1</v>
-      </c>
-      <c r="F408" t="s">
-        <v>218</v>
       </c>
       <c r="G408" t="b">
         <v>1</v>
       </c>
       <c r="I408" t="str">
         <f t="shared" si="15"/>
-        <v>Main_SoChannel</v>
+        <v>Main_VetGlen</v>
       </c>
       <c r="J408" t="str">
         <f t="shared" si="16"/>
@@ -15232,29 +15302,29 @@
     </row>
     <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B409" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C409" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D409" t="s">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="E409">
-        <v>2</v>
+        <v>650</v>
       </c>
       <c r="F409" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G409" t="b">
         <v>1</v>
       </c>
       <c r="I409" t="str">
         <f t="shared" si="15"/>
-        <v>Main_SoChannel</v>
+        <v>Main_VetGlen</v>
       </c>
       <c r="J409" t="str">
         <f t="shared" si="16"/>
@@ -15263,29 +15333,29 @@
     </row>
     <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B410" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C410" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D410" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E410">
         <v>1</v>
       </c>
       <c r="F410" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G410" t="b">
         <v>1</v>
       </c>
       <c r="I410" t="str">
         <f t="shared" si="15"/>
-        <v>Main_SoChannel</v>
+        <v>Main_VetGlen</v>
       </c>
       <c r="J410" t="str">
         <f t="shared" si="16"/>
@@ -15294,29 +15364,29 @@
     </row>
     <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B411" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C411" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D411" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E411">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F411" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G411" t="b">
         <v>1</v>
       </c>
       <c r="I411" t="str">
         <f t="shared" si="15"/>
-        <v>Main_SoChannel</v>
+        <v>Main_VetGlen</v>
       </c>
       <c r="J411" t="str">
         <f t="shared" si="16"/>
@@ -15325,22 +15395,22 @@
     </row>
     <row r="412" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B412" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C412" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="D412" t="s">
         <v>16</v>
       </c>
       <c r="E412">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="F412" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G412" t="b">
         <v>1</v>
@@ -15356,22 +15426,22 @@
     </row>
     <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B413" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C413" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D413" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E413">
-        <v>650</v>
+        <v>1</v>
       </c>
       <c r="F413" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G413" t="b">
         <v>1</v>
@@ -15387,22 +15457,22 @@
     </row>
     <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B414" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C414" t="s">
-        <v>213</v>
+        <v>76</v>
       </c>
       <c r="D414" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E414">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F414" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G414" t="b">
         <v>1</v>
@@ -15418,22 +15488,22 @@
     </row>
     <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B415" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C415" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D415" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E415">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F415" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G415" t="b">
         <v>1</v>
@@ -15449,22 +15519,22 @@
     </row>
     <row r="416" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B416" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C416" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="D416" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E416">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F416" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G416" t="b">
         <v>1</v>
@@ -15480,29 +15550,29 @@
     </row>
     <row r="417" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B417" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="C417" t="s">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="D417" t="s">
         <v>16</v>
       </c>
       <c r="E417">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F417" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="G417" t="b">
         <v>1</v>
       </c>
       <c r="I417" t="str">
         <f t="shared" si="15"/>
-        <v>Main_VetGlen</v>
+        <v>Main_BarberPool</v>
       </c>
       <c r="J417" t="str">
         <f t="shared" si="16"/>
@@ -15511,29 +15581,29 @@
     </row>
     <row r="418" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B418" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="C418" t="s">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="D418" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E418">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="F418" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="G418" t="b">
         <v>1</v>
       </c>
       <c r="I418" t="str">
         <f t="shared" si="15"/>
-        <v>Main_VetGlen</v>
+        <v>Main_Eckert</v>
       </c>
       <c r="J418" t="str">
         <f t="shared" si="16"/>
@@ -15542,29 +15612,29 @@
     </row>
     <row r="419" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B419" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C419" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D419" t="s">
         <v>16</v>
       </c>
       <c r="E419">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F419" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G419" t="b">
         <v>1</v>
       </c>
       <c r="I419" t="str">
         <f t="shared" si="15"/>
-        <v>Main_VetGlen</v>
+        <v>Main_Middleton</v>
       </c>
       <c r="J419" t="str">
         <f t="shared" si="16"/>
@@ -15573,29 +15643,29 @@
     </row>
     <row r="420" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B420" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C420" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D420" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E420">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="F420" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="G420" t="b">
         <v>1</v>
       </c>
       <c r="I420" t="str">
         <f t="shared" si="15"/>
-        <v>Main_VetGlen</v>
+        <v>Main_NotusParma</v>
       </c>
       <c r="J420" t="str">
         <f t="shared" si="16"/>
@@ -15604,13 +15674,13 @@
     </row>
     <row r="421" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B421" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C421" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D421" t="s">
         <v>16</v>
@@ -15619,14 +15689,14 @@
         <v>1000</v>
       </c>
       <c r="F421" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G421" t="b">
         <v>1</v>
       </c>
       <c r="I421" t="str">
         <f t="shared" si="15"/>
-        <v>Main_BarberPool</v>
+        <v>Main_SoChannel</v>
       </c>
       <c r="J421" t="str">
         <f t="shared" si="16"/>
@@ -15635,13 +15705,13 @@
     </row>
     <row r="422" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B422" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C422" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D422" t="s">
         <v>16</v>
@@ -15650,14 +15720,14 @@
         <v>1000</v>
       </c>
       <c r="F422" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G422" t="b">
         <v>1</v>
       </c>
       <c r="I422" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Eckert</v>
+        <v>Main_VetGlen</v>
       </c>
       <c r="J422" t="str">
         <f t="shared" si="16"/>
@@ -15666,29 +15736,29 @@
     </row>
     <row r="423" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B423" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C423" t="s">
+        <v>228</v>
+      </c>
+      <c r="D423" t="s">
+        <v>15</v>
+      </c>
+      <c r="E423">
+        <v>10000</v>
+      </c>
+      <c r="F423" t="s">
         <v>230</v>
-      </c>
-      <c r="D423" t="s">
-        <v>16</v>
-      </c>
-      <c r="E423">
-        <v>1000</v>
-      </c>
-      <c r="F423" t="s">
-        <v>231</v>
       </c>
       <c r="G423" t="b">
         <v>1</v>
       </c>
       <c r="I423" t="str">
         <f t="shared" si="15"/>
-        <v>Main_Middleton</v>
+        <v>Main_BarberPool</v>
       </c>
       <c r="J423" t="str">
         <f t="shared" si="16"/>
@@ -15697,106 +15767,106 @@
     </row>
     <row r="424" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B424" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="C424" t="s">
+        <v>228</v>
+      </c>
+      <c r="D424" t="s">
+        <v>15</v>
+      </c>
+      <c r="E424">
+        <v>10000</v>
+      </c>
+      <c r="F424" t="s">
         <v>230</v>
       </c>
-      <c r="D424" t="s">
-        <v>16</v>
-      </c>
-      <c r="E424">
-        <v>1000</v>
-      </c>
-      <c r="F424" t="s">
-        <v>231</v>
-      </c>
       <c r="G424" t="b">
         <v>1</v>
       </c>
       <c r="I424" t="str">
-        <f t="shared" si="15"/>
-        <v>Main_NotusParma</v>
+        <f t="shared" ref="I424:I428" si="17">B424</f>
+        <v>Main_Eckert</v>
       </c>
       <c r="J424" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="J424:J428" si="18">A424</f>
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
     <row r="425" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B425" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C425" t="s">
+        <v>228</v>
+      </c>
+      <c r="D425" t="s">
+        <v>15</v>
+      </c>
+      <c r="E425">
+        <v>10000</v>
+      </c>
+      <c r="F425" t="s">
         <v>230</v>
       </c>
-      <c r="D425" t="s">
-        <v>16</v>
-      </c>
-      <c r="E425">
-        <v>1000</v>
-      </c>
-      <c r="F425" t="s">
-        <v>231</v>
-      </c>
       <c r="G425" t="b">
         <v>1</v>
       </c>
       <c r="I425" t="str">
-        <f t="shared" si="15"/>
-        <v>Main_SoChannel</v>
+        <f t="shared" si="17"/>
+        <v>Main_Middleton</v>
       </c>
       <c r="J425" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
     <row r="426" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B426" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C426" t="s">
+        <v>228</v>
+      </c>
+      <c r="D426" t="s">
+        <v>15</v>
+      </c>
+      <c r="E426">
+        <v>10000</v>
+      </c>
+      <c r="F426" t="s">
         <v>230</v>
       </c>
-      <c r="D426" t="s">
-        <v>16</v>
-      </c>
-      <c r="E426">
-        <v>1000</v>
-      </c>
-      <c r="F426" t="s">
-        <v>231</v>
-      </c>
       <c r="G426" t="b">
         <v>1</v>
       </c>
       <c r="I426" t="str">
-        <f t="shared" si="15"/>
-        <v>Main_VetGlen</v>
+        <f t="shared" si="17"/>
+        <v>Main_NotusParma</v>
       </c>
       <c r="J426" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
     <row r="427" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B427" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C427" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D427" t="s">
         <v>15</v>
@@ -15805,29 +15875,29 @@
         <v>10000</v>
       </c>
       <c r="F427" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G427" t="b">
         <v>1</v>
       </c>
       <c r="I427" t="str">
-        <f t="shared" si="15"/>
-        <v>Main_BarberPool</v>
+        <f t="shared" si="17"/>
+        <v>Main_SoChannel</v>
       </c>
       <c r="J427" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
     <row r="428" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B428" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C428" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D428" t="s">
         <v>15</v>
@@ -15836,142 +15906,142 @@
         <v>10000</v>
       </c>
       <c r="F428" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G428" t="b">
         <v>1</v>
       </c>
       <c r="I428" t="str">
-        <f t="shared" ref="I428:I432" si="17">B428</f>
-        <v>Main_Eckert</v>
+        <f t="shared" si="17"/>
+        <v>Main_VetGlen</v>
       </c>
       <c r="J428" t="str">
-        <f t="shared" ref="J428:J432" si="18">A428</f>
-        <v>LBR_Bugs_BCG_v1</v>
-      </c>
-    </row>
-    <row r="429" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
-        <v>209</v>
-      </c>
-      <c r="B429" t="s">
-        <v>224</v>
-      </c>
-      <c r="C429" t="s">
-        <v>230</v>
-      </c>
-      <c r="D429" t="s">
-        <v>15</v>
-      </c>
-      <c r="E429">
-        <v>10000</v>
-      </c>
-      <c r="F429" t="s">
-        <v>232</v>
-      </c>
-      <c r="G429" t="b">
-        <v>1</v>
-      </c>
-      <c r="I429" t="str">
-        <f t="shared" si="17"/>
-        <v>Main_Middleton</v>
-      </c>
-      <c r="J429" t="str">
         <f t="shared" si="18"/>
         <v>LBR_Bugs_BCG_v1</v>
       </c>
     </row>
+    <row r="429" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A429" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B429" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="C429" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D429" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E429" s="35">
+        <v>450</v>
+      </c>
+      <c r="F429" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="G429" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I429" t="str">
+        <f>B429</f>
+        <v>Xeric_Multihab</v>
+      </c>
+      <c r="J429" t="str">
+        <f>A429</f>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
     <row r="430" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
-        <v>209</v>
-      </c>
-      <c r="B430" t="s">
-        <v>225</v>
-      </c>
-      <c r="C430" t="s">
-        <v>230</v>
-      </c>
-      <c r="D430" t="s">
-        <v>15</v>
-      </c>
-      <c r="E430">
-        <v>10000</v>
-      </c>
-      <c r="F430" t="s">
+      <c r="A430" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B430" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="G430" t="b">
+      <c r="C430" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="D430" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E430" s="35">
+        <v>3.3</v>
+      </c>
+      <c r="F430" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="G430" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I430" t="str">
-        <f t="shared" si="17"/>
-        <v>Main_NotusParma</v>
+        <f t="shared" ref="I430:I493" si="19">B430</f>
+        <v>Xeric_Multihab</v>
       </c>
       <c r="J430" t="str">
-        <f t="shared" si="18"/>
-        <v>LBR_Bugs_BCG_v1</v>
+        <f t="shared" ref="J430:J493" si="20">A430</f>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
     <row r="431" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A431" t="s">
-        <v>209</v>
-      </c>
-      <c r="B431" t="s">
-        <v>226</v>
-      </c>
-      <c r="C431" t="s">
-        <v>230</v>
-      </c>
-      <c r="D431" t="s">
-        <v>15</v>
-      </c>
-      <c r="E431">
-        <v>10000</v>
-      </c>
-      <c r="F431" t="s">
+      <c r="A431" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B431" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="G431" t="b">
+      <c r="C431" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="D431" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E431" s="35">
+        <v>0</v>
+      </c>
+      <c r="F431" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="G431" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I431" t="str">
-        <f t="shared" si="17"/>
-        <v>Main_SoChannel</v>
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
       </c>
       <c r="J431" t="str">
-        <f t="shared" si="18"/>
-        <v>LBR_Bugs_BCG_v1</v>
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
     <row r="432" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A432" t="s">
-        <v>209</v>
-      </c>
-      <c r="B432" t="s">
-        <v>227</v>
-      </c>
-      <c r="C432" t="s">
-        <v>230</v>
-      </c>
-      <c r="D432" t="s">
-        <v>15</v>
-      </c>
-      <c r="E432">
-        <v>10000</v>
-      </c>
-      <c r="F432" t="s">
+      <c r="A432" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B432" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="G432" t="b">
+      <c r="C432" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="D432" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E432" s="35">
+        <v>20</v>
+      </c>
+      <c r="F432" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="G432" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I432" t="str">
-        <f t="shared" si="17"/>
-        <v>Main_VetGlen</v>
+        <f t="shared" si="19"/>
+        <v>Xeric_Multihab</v>
       </c>
       <c r="J432" t="str">
-        <f t="shared" si="18"/>
-        <v>LBR_Bugs_BCG_v1</v>
+        <f t="shared" si="20"/>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
     <row r="433" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
@@ -15979,29 +16049,29 @@
         <v>178</v>
       </c>
       <c r="B433" s="33" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C433" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D433" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="D433" s="37" t="s">
         <v>16</v>
       </c>
       <c r="E433" s="35">
-        <v>450</v>
-      </c>
-      <c r="F433" s="36" t="s">
-        <v>211</v>
+        <v>2</v>
+      </c>
+      <c r="F433" s="34" t="s">
+        <v>238</v>
       </c>
       <c r="G433" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I433" t="str">
-        <f>B433</f>
+        <f t="shared" si="19"/>
         <v>Xeric_Multihab</v>
       </c>
       <c r="J433" t="str">
-        <f>A433</f>
+        <f t="shared" si="20"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
@@ -16010,29 +16080,29 @@
         <v>178</v>
       </c>
       <c r="B434" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="C434" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="D434" s="37" t="s">
-        <v>16</v>
+        <v>232</v>
+      </c>
+      <c r="C434" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D434" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E434" s="35">
-        <v>3.3</v>
-      </c>
-      <c r="F434" s="36" t="s">
-        <v>235</v>
+        <v>5</v>
+      </c>
+      <c r="F434" s="34" t="s">
+        <v>239</v>
       </c>
       <c r="G434" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I434" t="str">
-        <f t="shared" ref="I434:I497" si="19">B434</f>
+        <f t="shared" si="19"/>
         <v>Xeric_Multihab</v>
       </c>
       <c r="J434" t="str">
-        <f t="shared" ref="J434:J497" si="20">A434</f>
+        <f t="shared" si="20"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
@@ -16041,19 +16111,19 @@
         <v>178</v>
       </c>
       <c r="B435" s="33" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C435" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="D435" s="20" t="s">
-        <v>96</v>
+        <v>72</v>
+      </c>
+      <c r="D435" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E435" s="35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F435" s="34" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="G435" s="61" t="b">
         <v>1</v>
@@ -16072,19 +16142,19 @@
         <v>178</v>
       </c>
       <c r="B436" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="C436" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="D436" s="37" t="s">
-        <v>16</v>
+        <v>232</v>
+      </c>
+      <c r="C436" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D436" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="E436" s="35">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F436" s="34" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="G436" s="61" t="b">
         <v>1</v>
@@ -16103,19 +16173,19 @@
         <v>178</v>
       </c>
       <c r="B437" s="33" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C437" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="D437" s="37" t="s">
-        <v>16</v>
+        <v>76</v>
+      </c>
+      <c r="D437" s="8" t="s">
+        <v>231</v>
       </c>
       <c r="E437" s="35">
         <v>2</v>
       </c>
       <c r="F437" s="34" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="G437" s="61" t="b">
         <v>1</v>
@@ -16134,19 +16204,19 @@
         <v>178</v>
       </c>
       <c r="B438" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="C438" s="34" t="s">
-        <v>222</v>
+        <v>232</v>
+      </c>
+      <c r="C438" s="39" t="s">
+        <v>66</v>
       </c>
       <c r="D438" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E438" s="35">
-        <v>5</v>
-      </c>
-      <c r="F438" s="34" t="s">
-        <v>241</v>
+        <v>25</v>
+      </c>
+      <c r="F438" t="s">
+        <v>240</v>
       </c>
       <c r="G438" s="61" t="b">
         <v>1</v>
@@ -16161,23 +16231,23 @@
       </c>
     </row>
     <row r="439" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A439" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B439" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="C439" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D439" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E439" s="35">
-        <v>3</v>
-      </c>
-      <c r="F439" s="34" t="s">
-        <v>217</v>
+      <c r="A439" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B439" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="C439" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D439" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E439" s="42">
+        <v>50</v>
+      </c>
+      <c r="F439" s="41" t="s">
+        <v>242</v>
       </c>
       <c r="G439" s="61" t="b">
         <v>1</v>
@@ -16196,19 +16266,19 @@
         <v>178</v>
       </c>
       <c r="B440" s="33" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C440" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="D440" s="20" t="s">
-        <v>96</v>
+        <v>243</v>
+      </c>
+      <c r="D440" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="E440" s="35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F440" s="34" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="G440" s="61" t="b">
         <v>1</v>
@@ -16227,26 +16297,26 @@
         <v>178</v>
       </c>
       <c r="B441" s="33" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C441" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="D441" s="8" t="s">
-        <v>233</v>
+        <v>14</v>
+      </c>
+      <c r="D441" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E441" s="35">
-        <v>2</v>
-      </c>
-      <c r="F441" s="34" t="s">
-        <v>219</v>
+        <v>450</v>
+      </c>
+      <c r="F441" s="36" t="s">
+        <v>209</v>
       </c>
       <c r="G441" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I441" t="str">
         <f t="shared" si="19"/>
-        <v>Xeric_Multihab</v>
+        <v>Xeric_Riffle</v>
       </c>
       <c r="J441" t="str">
         <f t="shared" si="20"/>
@@ -16258,26 +16328,26 @@
         <v>178</v>
       </c>
       <c r="B442" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="C442" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D442" s="8" t="s">
-        <v>17</v>
+        <v>245</v>
+      </c>
+      <c r="C442" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="D442" s="37" t="s">
+        <v>16</v>
       </c>
       <c r="E442" s="35">
-        <v>25</v>
-      </c>
-      <c r="F442" t="s">
-        <v>242</v>
+        <v>2.5</v>
+      </c>
+      <c r="F442" s="36" t="s">
+        <v>233</v>
       </c>
       <c r="G442" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I442" t="str">
         <f t="shared" si="19"/>
-        <v>Xeric_Multihab</v>
+        <v>Xeric_Riffle</v>
       </c>
       <c r="J442" t="str">
         <f t="shared" si="20"/>
@@ -16285,30 +16355,30 @@
       </c>
     </row>
     <row r="443" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A443" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="B443" s="40" t="s">
+      <c r="A443" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B443" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="C443" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="C443" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="D443" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E443" s="42">
-        <v>50</v>
-      </c>
-      <c r="F443" s="41" t="s">
-        <v>244</v>
+      <c r="D443" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E443" s="35">
+        <v>0</v>
+      </c>
+      <c r="F443" s="34" t="s">
+        <v>235</v>
       </c>
       <c r="G443" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I443" t="str">
         <f t="shared" si="19"/>
-        <v>Xeric_Multihab</v>
+        <v>Xeric_Riffle</v>
       </c>
       <c r="J443" t="str">
         <f t="shared" si="20"/>
@@ -16320,26 +16390,26 @@
         <v>178</v>
       </c>
       <c r="B444" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="C444" s="34" t="s">
         <v>245</v>
       </c>
+      <c r="C444" s="38" t="s">
+        <v>236</v>
+      </c>
       <c r="D444" s="37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E444" s="35">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F444" s="34" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="G444" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I444" t="str">
         <f t="shared" si="19"/>
-        <v>Xeric_Multihab</v>
+        <v>Xeric_Riffle</v>
       </c>
       <c r="J444" t="str">
         <f t="shared" si="20"/>
@@ -16351,19 +16421,19 @@
         <v>178</v>
       </c>
       <c r="B445" s="33" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C445" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D445" s="35" t="s">
-        <v>16</v>
+        <v>218</v>
+      </c>
+      <c r="D445" s="8" t="s">
+        <v>231</v>
       </c>
       <c r="E445" s="35">
-        <v>450</v>
-      </c>
-      <c r="F445" s="36" t="s">
-        <v>211</v>
+        <v>1</v>
+      </c>
+      <c r="F445" s="34" t="s">
+        <v>238</v>
       </c>
       <c r="G445" s="61" t="b">
         <v>1</v>
@@ -16382,19 +16452,19 @@
         <v>178</v>
       </c>
       <c r="B446" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="C446" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="D446" s="37" t="s">
-        <v>16</v>
+        <v>245</v>
+      </c>
+      <c r="C446" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D446" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E446" s="35">
-        <v>2.5</v>
-      </c>
-      <c r="F446" s="36" t="s">
-        <v>235</v>
+        <v>5</v>
+      </c>
+      <c r="F446" s="34" t="s">
+        <v>239</v>
       </c>
       <c r="G446" s="61" t="b">
         <v>1</v>
@@ -16413,19 +16483,19 @@
         <v>178</v>
       </c>
       <c r="B447" s="33" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C447" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="D447" s="20" t="s">
-        <v>96</v>
+        <v>72</v>
+      </c>
+      <c r="D447" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E447" s="35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F447" s="34" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="G447" s="61" t="b">
         <v>1</v>
@@ -16444,19 +16514,19 @@
         <v>178</v>
       </c>
       <c r="B448" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="C448" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="D448" s="37" t="s">
-        <v>16</v>
+        <v>245</v>
+      </c>
+      <c r="C448" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D448" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="E448" s="35">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F448" s="34" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="G448" s="61" t="b">
         <v>1</v>
@@ -16475,19 +16545,19 @@
         <v>178</v>
       </c>
       <c r="B449" s="33" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C449" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="D449" s="8" t="s">
-        <v>233</v>
+        <v>76</v>
+      </c>
+      <c r="D449" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E449" s="35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F449" s="34" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="G449" s="61" t="b">
         <v>1</v>
@@ -16506,10 +16576,10 @@
         <v>178</v>
       </c>
       <c r="B450" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="C450" s="34" t="s">
-        <v>222</v>
+        <v>245</v>
+      </c>
+      <c r="C450" s="39" t="s">
+        <v>66</v>
       </c>
       <c r="D450" s="8" t="s">
         <v>17</v>
@@ -16517,8 +16587,8 @@
       <c r="E450" s="35">
         <v>5</v>
       </c>
-      <c r="F450" s="34" t="s">
-        <v>241</v>
+      <c r="F450" t="s">
+        <v>240</v>
       </c>
       <c r="G450" s="61" t="b">
         <v>1</v>
@@ -16533,23 +16603,23 @@
       </c>
     </row>
     <row r="451" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A451" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B451" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="C451" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D451" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E451" s="35">
-        <v>4</v>
-      </c>
-      <c r="F451" s="34" t="s">
-        <v>217</v>
+      <c r="A451" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B451" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C451" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D451" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E451" s="42">
+        <v>55</v>
+      </c>
+      <c r="F451" s="41" t="s">
+        <v>242</v>
       </c>
       <c r="G451" s="61" t="b">
         <v>1</v>
@@ -16563,124 +16633,124 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="452" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B452" s="33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C452" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="D452" s="20" t="s">
-        <v>96</v>
+        <v>14</v>
+      </c>
+      <c r="D452" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E452" s="35">
-        <v>0</v>
-      </c>
-      <c r="F452" s="34" t="s">
-        <v>218</v>
+        <v>450</v>
+      </c>
+      <c r="F452" s="36" t="s">
+        <v>209</v>
       </c>
       <c r="G452" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I452" t="str">
         <f t="shared" si="19"/>
-        <v>Xeric_Riffle</v>
+        <v>MountainCold_Multihab</v>
       </c>
       <c r="J452" t="str">
         <f t="shared" si="20"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="453" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B453" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="C453" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D453" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E453" s="35">
+        <v>35</v>
+      </c>
+      <c r="F453" s="34" t="s">
         <v>247</v>
-      </c>
-      <c r="C453" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="D453" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E453" s="35">
-        <v>4</v>
-      </c>
-      <c r="F453" s="34" t="s">
-        <v>219</v>
       </c>
       <c r="G453" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I453" t="str">
         <f t="shared" si="19"/>
-        <v>Xeric_Riffle</v>
+        <v>MountainCold_Multihab</v>
       </c>
       <c r="J453" t="str">
         <f t="shared" si="20"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="454" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B454" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="C454" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D454" s="8" t="s">
-        <v>17</v>
+        <v>246</v>
+      </c>
+      <c r="C454" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="D454" s="37" t="s">
+        <v>16</v>
       </c>
       <c r="E454" s="35">
-        <v>5</v>
-      </c>
-      <c r="F454" t="s">
-        <v>242</v>
+        <v>3.5</v>
+      </c>
+      <c r="F454" s="36" t="s">
+        <v>248</v>
       </c>
       <c r="G454" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I454" t="str">
         <f t="shared" si="19"/>
-        <v>Xeric_Riffle</v>
+        <v>MountainCold_Multihab</v>
       </c>
       <c r="J454" t="str">
         <f t="shared" si="20"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="455" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A455" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="B455" s="40" t="s">
-        <v>247</v>
-      </c>
-      <c r="C455" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="D455" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E455" s="42">
-        <v>55</v>
-      </c>
-      <c r="F455" s="41" t="s">
-        <v>244</v>
+    <row r="455" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A455" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B455" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="C455" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="D455" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E455" s="35">
+        <v>0</v>
+      </c>
+      <c r="F455" s="34" t="s">
+        <v>250</v>
       </c>
       <c r="G455" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I455" t="str">
         <f t="shared" si="19"/>
-        <v>Xeric_Riffle</v>
+        <v>MountainCold_Multihab</v>
       </c>
       <c r="J455" t="str">
         <f t="shared" si="20"/>
@@ -16692,19 +16762,19 @@
         <v>178</v>
       </c>
       <c r="B456" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C456" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D456" s="35" t="s">
-        <v>16</v>
+        <v>246</v>
+      </c>
+      <c r="C456" s="43" t="s">
+        <v>282</v>
+      </c>
+      <c r="D456" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E456" s="35">
-        <v>450</v>
-      </c>
-      <c r="F456" s="36" t="s">
-        <v>211</v>
+        <v>30</v>
+      </c>
+      <c r="F456" s="34" t="s">
+        <v>251</v>
       </c>
       <c r="G456" s="61" t="b">
         <v>1</v>
@@ -16723,19 +16793,19 @@
         <v>178</v>
       </c>
       <c r="B457" s="33" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C457" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="D457" s="35" t="s">
-        <v>16</v>
+        <v>234</v>
+      </c>
+      <c r="D457" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="E457" s="35">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F457" s="34" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="G457" s="61" t="b">
         <v>1</v>
@@ -16754,19 +16824,19 @@
         <v>178</v>
       </c>
       <c r="B458" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C458" s="36" t="s">
-        <v>215</v>
+        <v>246</v>
+      </c>
+      <c r="C458" s="38" t="s">
+        <v>236</v>
       </c>
       <c r="D458" s="37" t="s">
         <v>16</v>
       </c>
       <c r="E458" s="35">
-        <v>3.5</v>
-      </c>
-      <c r="F458" s="36" t="s">
-        <v>250</v>
+        <v>25</v>
+      </c>
+      <c r="F458" s="34" t="s">
+        <v>237</v>
       </c>
       <c r="G458" s="61" t="b">
         <v>1</v>
@@ -16785,10 +16855,10 @@
         <v>178</v>
       </c>
       <c r="B459" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C459" s="43" t="s">
-        <v>251</v>
+        <v>246</v>
+      </c>
+      <c r="C459" s="34" t="s">
+        <v>220</v>
       </c>
       <c r="D459" s="37" t="s">
         <v>15</v>
@@ -16811,24 +16881,24 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="460" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B460" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C460" s="43" t="s">
-        <v>284</v>
-      </c>
-      <c r="D460" s="8" t="s">
-        <v>17</v>
+        <v>246</v>
+      </c>
+      <c r="C460" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D460" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E460" s="35">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F460" s="34" t="s">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="G460" s="61" t="b">
         <v>1</v>
@@ -16847,19 +16917,19 @@
         <v>178</v>
       </c>
       <c r="B461" s="33" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C461" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="D461" s="20" t="s">
-        <v>96</v>
+        <v>74</v>
+      </c>
+      <c r="D461" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E461" s="35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F461" s="34" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="G461" s="61" t="b">
         <v>1</v>
@@ -16878,19 +16948,19 @@
         <v>178</v>
       </c>
       <c r="B462" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C462" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="D462" s="37" t="s">
+        <v>246</v>
+      </c>
+      <c r="C462" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D462" s="35" t="s">
         <v>16</v>
       </c>
       <c r="E462" s="35">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F462" s="34" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="G462" s="61" t="b">
         <v>1</v>
@@ -16905,23 +16975,23 @@
       </c>
     </row>
     <row r="463" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A463" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B463" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C463" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="D463" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E463" s="35">
-        <v>0</v>
-      </c>
-      <c r="F463" s="34" t="s">
-        <v>254</v>
+      <c r="A463" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="B463" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="C463" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D463" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E463" s="46">
+        <v>5</v>
+      </c>
+      <c r="F463" s="13" t="s">
+        <v>240</v>
       </c>
       <c r="G463" s="61" t="b">
         <v>1</v>
@@ -16940,19 +17010,19 @@
         <v>178</v>
       </c>
       <c r="B464" s="33" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C464" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D464" s="35" t="s">
-        <v>16</v>
+        <v>243</v>
+      </c>
+      <c r="D464" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E464" s="35">
         <v>4</v>
       </c>
       <c r="F464" s="34" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="G464" s="61" t="b">
         <v>1</v>
@@ -16967,23 +17037,23 @@
       </c>
     </row>
     <row r="465" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A465" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B465" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C465" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="D465" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E465" s="35">
-        <v>3</v>
-      </c>
-      <c r="F465" s="34" t="s">
-        <v>218</v>
+      <c r="A465" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B465" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="C465" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D465" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E465" s="42">
+        <v>45</v>
+      </c>
+      <c r="F465" s="41" t="s">
+        <v>254</v>
       </c>
       <c r="G465" s="61" t="b">
         <v>1</v>
@@ -17002,26 +17072,26 @@
         <v>178</v>
       </c>
       <c r="B466" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C466" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="D466" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E466" s="35">
-        <v>4</v>
-      </c>
-      <c r="F466" s="34" t="s">
-        <v>219</v>
+        <v>255</v>
+      </c>
+      <c r="C466" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D466" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E466" s="28">
+        <v>450</v>
+      </c>
+      <c r="F466" s="30" t="s">
+        <v>209</v>
       </c>
       <c r="G466" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I466" t="str">
         <f t="shared" si="19"/>
-        <v>MountainCold_Multihab</v>
+        <v>MountainCold_Riffle</v>
       </c>
       <c r="J466" t="str">
         <f t="shared" si="20"/>
@@ -17029,30 +17099,30 @@
       </c>
     </row>
     <row r="467" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A467" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="B467" s="44" t="s">
-        <v>248</v>
-      </c>
-      <c r="C467" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D467" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="E467" s="46">
-        <v>5</v>
-      </c>
-      <c r="F467" s="13" t="s">
-        <v>242</v>
+      <c r="A467" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B467" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="C467" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="D467" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E467" s="28">
+        <v>35</v>
+      </c>
+      <c r="F467" s="48" t="s">
+        <v>247</v>
       </c>
       <c r="G467" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I467" t="str">
         <f t="shared" si="19"/>
-        <v>MountainCold_Multihab</v>
+        <v>MountainCold_Riffle</v>
       </c>
       <c r="J467" t="str">
         <f t="shared" si="20"/>
@@ -17064,26 +17134,26 @@
         <v>178</v>
       </c>
       <c r="B468" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="C468" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="D468" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E468" s="49">
+        <v>3</v>
+      </c>
+      <c r="F468" s="30" t="s">
         <v>248</v>
-      </c>
-      <c r="C468" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="D468" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E468" s="35">
-        <v>4</v>
-      </c>
-      <c r="F468" s="34" t="s">
-        <v>255</v>
       </c>
       <c r="G468" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I468" t="str">
         <f t="shared" si="19"/>
-        <v>MountainCold_Multihab</v>
+        <v>MountainCold_Riffle</v>
       </c>
       <c r="J468" t="str">
         <f t="shared" si="20"/>
@@ -17091,22 +17161,22 @@
       </c>
     </row>
     <row r="469" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A469" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="B469" s="40" t="s">
-        <v>248</v>
-      </c>
-      <c r="C469" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="D469" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="E469" s="42">
-        <v>45</v>
-      </c>
-      <c r="F469" s="41" t="s">
+      <c r="A469" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B469" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="C469" t="s">
+        <v>249</v>
+      </c>
+      <c r="D469" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E469" s="28">
+        <v>1</v>
+      </c>
+      <c r="F469" s="48" t="s">
         <v>256</v>
       </c>
       <c r="G469" s="61" t="b">
@@ -17114,7 +17184,7 @@
       </c>
       <c r="I469" t="str">
         <f t="shared" si="19"/>
-        <v>MountainCold_Multihab</v>
+        <v>MountainCold_Riffle</v>
       </c>
       <c r="J469" t="str">
         <f t="shared" si="20"/>
@@ -17126,19 +17196,19 @@
         <v>178</v>
       </c>
       <c r="B470" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C470" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="D470" s="28" t="s">
-        <v>16</v>
+        <v>255</v>
+      </c>
+      <c r="C470" t="s">
+        <v>282</v>
+      </c>
+      <c r="D470" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E470" s="28">
-        <v>450</v>
-      </c>
-      <c r="F470" s="30" t="s">
-        <v>211</v>
+        <v>15</v>
+      </c>
+      <c r="F470" s="48" t="s">
+        <v>251</v>
       </c>
       <c r="G470" s="61" t="b">
         <v>1</v>
@@ -17157,19 +17227,19 @@
         <v>178</v>
       </c>
       <c r="B471" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="C471" s="48" t="s">
+        <v>234</v>
+      </c>
+      <c r="D471" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E471" s="28">
+        <v>3</v>
+      </c>
+      <c r="F471" s="48" t="s">
         <v>257</v>
-      </c>
-      <c r="C471" s="48" t="s">
-        <v>188</v>
-      </c>
-      <c r="D471" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E471" s="28">
-        <v>35</v>
-      </c>
-      <c r="F471" s="48" t="s">
-        <v>249</v>
       </c>
       <c r="G471" s="61" t="b">
         <v>1</v>
@@ -17188,19 +17258,19 @@
         <v>178</v>
       </c>
       <c r="B472" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C472" s="30" t="s">
-        <v>215</v>
+        <v>255</v>
+      </c>
+      <c r="C472" s="50" t="s">
+        <v>236</v>
       </c>
       <c r="D472" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E472" s="49">
-        <v>3</v>
-      </c>
-      <c r="F472" s="30" t="s">
-        <v>250</v>
+      <c r="E472" s="28">
+        <v>24</v>
+      </c>
+      <c r="F472" s="48" t="s">
+        <v>237</v>
       </c>
       <c r="G472" s="61" t="b">
         <v>1</v>
@@ -17219,16 +17289,16 @@
         <v>178</v>
       </c>
       <c r="B473" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C473" t="s">
-        <v>251</v>
-      </c>
-      <c r="D473" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="E473" s="28">
-        <v>1</v>
+        <v>255</v>
+      </c>
+      <c r="C473" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="D473" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E473" s="35">
+        <v>5</v>
       </c>
       <c r="F473" s="48" t="s">
         <v>258</v>
@@ -17245,24 +17315,24 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="474" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B474" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C474" t="s">
-        <v>284</v>
-      </c>
-      <c r="D474" s="8" t="s">
-        <v>17</v>
+        <v>255</v>
+      </c>
+      <c r="C474" s="48" t="s">
+        <v>220</v>
+      </c>
+      <c r="D474" s="32" t="s">
+        <v>15</v>
       </c>
       <c r="E474" s="28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F474" s="48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G474" s="61" t="b">
         <v>1</v>
@@ -17281,19 +17351,19 @@
         <v>178</v>
       </c>
       <c r="B475" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C475" s="48" t="s">
-        <v>236</v>
-      </c>
-      <c r="D475" s="8" t="s">
-        <v>233</v>
+        <v>72</v>
+      </c>
+      <c r="D475" s="28" t="s">
+        <v>16</v>
       </c>
       <c r="E475" s="28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F475" s="48" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="G475" s="61" t="b">
         <v>1</v>
@@ -17312,19 +17382,19 @@
         <v>178</v>
       </c>
       <c r="B476" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C476" s="50" t="s">
-        <v>238</v>
-      </c>
-      <c r="D476" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C476" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="D476" s="28" t="s">
         <v>16</v>
       </c>
       <c r="E476" s="28">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F476" s="48" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="G476" s="61" t="b">
         <v>1</v>
@@ -17343,19 +17413,19 @@
         <v>178</v>
       </c>
       <c r="B477" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C477" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="D477" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E477" s="35">
+        <v>255</v>
+      </c>
+      <c r="C477" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="D477" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E477" s="28">
         <v>5</v>
       </c>
       <c r="F477" s="48" t="s">
-        <v>260</v>
+        <v>217</v>
       </c>
       <c r="G477" s="61" t="b">
         <v>1</v>
@@ -17370,23 +17440,23 @@
       </c>
     </row>
     <row r="478" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A478" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B478" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C478" s="48" t="s">
-        <v>222</v>
-      </c>
-      <c r="D478" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E478" s="28">
-        <v>0</v>
-      </c>
-      <c r="F478" s="48" t="s">
-        <v>254</v>
+      <c r="A478" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="B478" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="C478" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D478" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E478" s="46">
+        <v>5</v>
+      </c>
+      <c r="F478" s="13" t="s">
+        <v>240</v>
       </c>
       <c r="G478" s="61" t="b">
         <v>1</v>
@@ -17405,19 +17475,19 @@
         <v>178</v>
       </c>
       <c r="B479" s="33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C479" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="D479" s="28" t="s">
-        <v>16</v>
+        <v>243</v>
+      </c>
+      <c r="D479" s="32" t="s">
+        <v>15</v>
       </c>
       <c r="E479" s="28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F479" s="48" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="G479" s="61" t="b">
         <v>1</v>
@@ -17432,23 +17502,23 @@
       </c>
     </row>
     <row r="480" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B480" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C480" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="D480" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E480" s="28">
-        <v>4</v>
-      </c>
-      <c r="F480" s="48" t="s">
-        <v>261</v>
+      <c r="A480" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B480" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="C480" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="D480" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="E480" s="53">
+        <v>60</v>
+      </c>
+      <c r="F480" s="51" t="s">
+        <v>254</v>
       </c>
       <c r="G480" s="61" t="b">
         <v>1</v>
@@ -17462,124 +17532,124 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="481" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="B481" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C481" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="D481" s="28" t="s">
+      <c r="B481" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="C481" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D481" s="35" t="s">
         <v>16</v>
       </c>
       <c r="E481" s="28">
-        <v>5</v>
-      </c>
-      <c r="F481" s="48" t="s">
-        <v>219</v>
+        <v>450</v>
+      </c>
+      <c r="F481" s="36" t="s">
+        <v>209</v>
       </c>
       <c r="G481" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I481" t="str">
         <f t="shared" si="19"/>
-        <v>MountainCold_Riffle</v>
+        <v>NBR_Riffle</v>
       </c>
       <c r="J481" t="str">
         <f t="shared" si="20"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="482" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A482" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="B482" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="C482" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D482" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="E482" s="46">
-        <v>5</v>
-      </c>
-      <c r="F482" s="13" t="s">
-        <v>242</v>
+    <row r="482" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A482" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B482" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="C482" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="D482" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E482" s="55">
+        <v>3</v>
+      </c>
+      <c r="F482" s="30" t="s">
+        <v>233</v>
       </c>
       <c r="G482" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I482" t="str">
         <f t="shared" si="19"/>
-        <v>MountainCold_Riffle</v>
+        <v>NBR_Riffle</v>
       </c>
       <c r="J482" t="str">
         <f t="shared" si="20"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="483" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="B483" s="33" t="s">
-        <v>257</v>
+      <c r="B483" s="54" t="s">
+        <v>261</v>
       </c>
       <c r="C483" s="48" t="s">
-        <v>245</v>
-      </c>
-      <c r="D483" s="32" t="s">
-        <v>15</v>
+        <v>234</v>
+      </c>
+      <c r="D483" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="E483" s="28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F483" s="48" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="G483" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I483" t="str">
         <f t="shared" si="19"/>
-        <v>MountainCold_Riffle</v>
+        <v>NBR_Riffle</v>
       </c>
       <c r="J483" t="str">
         <f t="shared" si="20"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="484" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A484" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="B484" s="40" t="s">
-        <v>257</v>
-      </c>
-      <c r="C484" s="51" t="s">
-        <v>243</v>
-      </c>
-      <c r="D484" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="E484" s="53">
-        <v>60</v>
-      </c>
-      <c r="F484" s="51" t="s">
-        <v>256</v>
+    <row r="484" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A484" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B484" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="C484" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="D484" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E484" s="28">
+        <v>1</v>
+      </c>
+      <c r="F484" s="48" t="s">
+        <v>238</v>
       </c>
       <c r="G484" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I484" t="str">
         <f t="shared" si="19"/>
-        <v>MountainCold_Riffle</v>
+        <v>NBR_Riffle</v>
       </c>
       <c r="J484" t="str">
         <f t="shared" si="20"/>
@@ -17591,19 +17661,19 @@
         <v>178</v>
       </c>
       <c r="B485" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="C485" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D485" s="35" t="s">
-        <v>16</v>
+        <v>261</v>
+      </c>
+      <c r="C485" s="48" t="s">
+        <v>220</v>
+      </c>
+      <c r="D485" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E485" s="28">
-        <v>450</v>
-      </c>
-      <c r="F485" s="36" t="s">
-        <v>211</v>
+        <v>5</v>
+      </c>
+      <c r="F485" s="48" t="s">
+        <v>239</v>
       </c>
       <c r="G485" s="61" t="b">
         <v>1</v>
@@ -17622,19 +17692,19 @@
         <v>178</v>
       </c>
       <c r="B486" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="C486" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="C486" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="D486" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E486" s="28">
+        <v>4</v>
+      </c>
+      <c r="F486" s="48" t="s">
         <v>215</v>
-      </c>
-      <c r="D486" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="E486" s="55">
-        <v>3</v>
-      </c>
-      <c r="F486" s="30" t="s">
-        <v>235</v>
       </c>
       <c r="G486" s="61" t="b">
         <v>1</v>
@@ -17653,10 +17723,10 @@
         <v>178</v>
       </c>
       <c r="B487" s="54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C487" s="48" t="s">
-        <v>236</v>
+        <v>74</v>
       </c>
       <c r="D487" s="20" t="s">
         <v>96</v>
@@ -17665,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="F487" s="48" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="G487" s="61" t="b">
         <v>1</v>
@@ -17684,19 +17754,19 @@
         <v>178</v>
       </c>
       <c r="B488" s="54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C488" s="48" t="s">
-        <v>220</v>
-      </c>
-      <c r="D488" s="8" t="s">
-        <v>233</v>
+        <v>76</v>
+      </c>
+      <c r="D488" s="28" t="s">
+        <v>16</v>
       </c>
       <c r="E488" s="28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F488" s="48" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="G488" s="61" t="b">
         <v>1</v>
@@ -17715,22 +17785,22 @@
         <v>178</v>
       </c>
       <c r="B489" s="54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C489" s="48" t="s">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="D489" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E489" s="28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F489" s="48" t="s">
-        <v>241</v>
-      </c>
-      <c r="G489" s="61" t="b">
-        <v>1</v>
+        <v>263</v>
+      </c>
+      <c r="G489" s="62" t="b">
+        <v>0</v>
       </c>
       <c r="I489" t="str">
         <f t="shared" si="19"/>
@@ -17746,19 +17816,19 @@
         <v>178</v>
       </c>
       <c r="B490" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="C490" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="D490" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E490" s="28">
-        <v>4</v>
-      </c>
-      <c r="F490" s="48" t="s">
-        <v>217</v>
+        <v>261</v>
+      </c>
+      <c r="C490" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D490" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E490" s="35">
+        <v>20</v>
+      </c>
+      <c r="F490" t="s">
+        <v>240</v>
       </c>
       <c r="G490" s="61" t="b">
         <v>1</v>
@@ -17773,23 +17843,23 @@
       </c>
     </row>
     <row r="491" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A491" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B491" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="C491" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="D491" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="E491" s="28">
-        <v>0</v>
-      </c>
-      <c r="F491" s="48" t="s">
-        <v>218</v>
+      <c r="A491" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B491" s="56" t="s">
+        <v>261</v>
+      </c>
+      <c r="C491" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D491" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E491" s="42">
+        <v>50</v>
+      </c>
+      <c r="F491" s="41" t="s">
+        <v>242</v>
       </c>
       <c r="G491" s="61" t="b">
         <v>1</v>
@@ -17807,20 +17877,20 @@
       <c r="A492" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="B492" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="C492" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="D492" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E492" s="28">
-        <v>4</v>
-      </c>
-      <c r="F492" s="48" t="s">
-        <v>219</v>
+      <c r="B492" s="58" t="s">
+        <v>261</v>
+      </c>
+      <c r="C492" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="D492" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="E492" s="35">
+        <v>2</v>
+      </c>
+      <c r="F492" s="34" t="s">
+        <v>264</v>
       </c>
       <c r="G492" s="61" t="b">
         <v>1</v>
@@ -17835,30 +17905,30 @@
       </c>
     </row>
     <row r="493" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A493" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B493" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="C493" s="48" t="s">
-        <v>264</v>
-      </c>
-      <c r="D493" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E493" s="28">
-        <v>3</v>
-      </c>
-      <c r="F493" s="48" t="s">
+      <c r="A493" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B493" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="G493" s="62" t="b">
-        <v>0</v>
+      <c r="C493" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D493" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E493" s="35">
+        <v>450</v>
+      </c>
+      <c r="F493" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="G493" s="61" t="b">
+        <v>1</v>
       </c>
       <c r="I493" t="str">
         <f t="shared" si="19"/>
-        <v>NBR_Riffle</v>
+        <v>Foothills_Multihab</v>
       </c>
       <c r="J493" t="str">
         <f t="shared" si="20"/>
@@ -17866,95 +17936,95 @@
       </c>
     </row>
     <row r="494" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A494" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B494" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="C494" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D494" s="8" t="s">
+      <c r="A494" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B494" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="C494" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D494" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E494" s="35">
+        <v>35</v>
+      </c>
+      <c r="F494" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="G494" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I494" t="str">
+        <f t="shared" ref="I494:I519" si="21">B494</f>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J494" t="str">
+        <f t="shared" ref="J494:J519" si="22">A494</f>
+        <v>BCG_ORWA_v1_Bugs500ct</v>
+      </c>
+    </row>
+    <row r="495" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A495" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B495" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="C495" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="D495" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E494" s="35">
-        <v>20</v>
-      </c>
-      <c r="F494" t="s">
-        <v>242</v>
-      </c>
-      <c r="G494" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I494" t="str">
-        <f t="shared" si="19"/>
-        <v>NBR_Riffle</v>
-      </c>
-      <c r="J494" t="str">
-        <f t="shared" si="20"/>
+      <c r="E495" s="35">
+        <v>45</v>
+      </c>
+      <c r="F495" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="G495" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I495" t="str">
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
+      </c>
+      <c r="J495" t="str">
+        <f t="shared" si="22"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="495" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A495" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="B495" s="56" t="s">
-        <v>263</v>
-      </c>
-      <c r="C495" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="D495" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="E495" s="42">
-        <v>50</v>
-      </c>
-      <c r="F495" s="41" t="s">
-        <v>244</v>
-      </c>
-      <c r="G495" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I495" t="str">
-        <f t="shared" si="19"/>
-        <v>NBR_Riffle</v>
-      </c>
-      <c r="J495" t="str">
-        <f t="shared" si="20"/>
-        <v>BCG_ORWA_v1_Bugs500ct</v>
-      </c>
-    </row>
     <row r="496" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A496" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B496" s="58" t="s">
-        <v>263</v>
-      </c>
-      <c r="C496" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="D496" s="59" t="s">
-        <v>17</v>
+      <c r="A496" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B496" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="C496" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="D496" s="37" t="s">
+        <v>16</v>
       </c>
       <c r="E496" s="35">
-        <v>2</v>
-      </c>
-      <c r="F496" s="34" t="s">
-        <v>266</v>
+        <v>3.3</v>
+      </c>
+      <c r="F496" s="36" t="s">
+        <v>248</v>
       </c>
       <c r="G496" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I496" t="str">
-        <f t="shared" si="19"/>
-        <v>NBR_Riffle</v>
+        <f t="shared" si="21"/>
+        <v>Foothills_Multihab</v>
       </c>
       <c r="J496" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
@@ -17963,29 +18033,29 @@
         <v>178</v>
       </c>
       <c r="B497" s="34" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C497" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D497" s="35" t="s">
-        <v>16</v>
+        <v>234</v>
+      </c>
+      <c r="D497" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="E497" s="35">
-        <v>450</v>
-      </c>
-      <c r="F497" s="36" t="s">
-        <v>211</v>
+        <v>0</v>
+      </c>
+      <c r="F497" s="34" t="s">
+        <v>235</v>
       </c>
       <c r="G497" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I497" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>Foothills_Multihab</v>
       </c>
       <c r="J497" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
@@ -17994,29 +18064,29 @@
         <v>178</v>
       </c>
       <c r="B498" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="C498" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="D498" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="C498" s="60" t="s">
+        <v>236</v>
+      </c>
+      <c r="D498" s="37" t="s">
         <v>16</v>
       </c>
       <c r="E498" s="35">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F498" s="34" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G498" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I498" t="str">
-        <f t="shared" ref="I498:I523" si="21">B498</f>
+        <f t="shared" si="21"/>
         <v>Foothills_Multihab</v>
       </c>
       <c r="J498" t="str">
-        <f t="shared" ref="J498:J523" si="22">A498</f>
+        <f t="shared" si="22"/>
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
@@ -18025,19 +18095,19 @@
         <v>178</v>
       </c>
       <c r="B499" s="34" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C499" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="D499" s="8" t="s">
-        <v>17</v>
+        <v>220</v>
+      </c>
+      <c r="D499" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="E499" s="35">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F499" s="34" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="G499" s="61" t="b">
         <v>1</v>
@@ -18056,19 +18126,19 @@
         <v>178</v>
       </c>
       <c r="B500" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="C500" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="C500" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D500" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E500" s="35">
+        <v>4</v>
+      </c>
+      <c r="F500" s="34" t="s">
         <v>215</v>
-      </c>
-      <c r="D500" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="E500" s="35">
-        <v>3.3</v>
-      </c>
-      <c r="F500" s="36" t="s">
-        <v>250</v>
       </c>
       <c r="G500" s="61" t="b">
         <v>1</v>
@@ -18087,19 +18157,19 @@
         <v>178</v>
       </c>
       <c r="B501" s="34" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C501" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="D501" s="20" t="s">
-        <v>96</v>
+        <v>74</v>
+      </c>
+      <c r="D501" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E501" s="35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F501" s="34" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="G501" s="61" t="b">
         <v>1</v>
@@ -18118,19 +18188,19 @@
         <v>178</v>
       </c>
       <c r="B502" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="C502" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="D502" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="C502" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D502" s="35" t="s">
         <v>16</v>
       </c>
       <c r="E502" s="35">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F502" s="34" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="G502" s="61" t="b">
         <v>1</v>
@@ -18149,19 +18219,19 @@
         <v>178</v>
       </c>
       <c r="B503" s="34" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C503" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="D503" s="37" t="s">
-        <v>15</v>
+        <v>243</v>
+      </c>
+      <c r="D503" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E503" s="35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F503" s="34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G503" s="61" t="b">
         <v>1</v>
@@ -18176,23 +18246,23 @@
       </c>
     </row>
     <row r="504" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A504" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="B504" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="C504" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D504" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E504" s="35">
-        <v>4</v>
-      </c>
-      <c r="F504" s="34" t="s">
-        <v>217</v>
+      <c r="A504" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B504" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="C504" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D504" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E504" s="42">
+        <v>45</v>
+      </c>
+      <c r="F504" s="41" t="s">
+        <v>254</v>
       </c>
       <c r="G504" s="61" t="b">
         <v>1</v>
@@ -18211,19 +18281,19 @@
         <v>178</v>
       </c>
       <c r="B505" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="C505" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="D505" s="35" t="s">
-        <v>16</v>
+        <v>265</v>
+      </c>
+      <c r="C505" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D505" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E505" s="35">
-        <v>3</v>
-      </c>
-      <c r="F505" s="34" t="s">
-        <v>218</v>
+        <v>25</v>
+      </c>
+      <c r="F505" t="s">
+        <v>240</v>
       </c>
       <c r="G505" s="61" t="b">
         <v>1</v>
@@ -18242,26 +18312,26 @@
         <v>178</v>
       </c>
       <c r="B506" s="34" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C506" s="34" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D506" s="35" t="s">
         <v>16</v>
       </c>
       <c r="E506" s="35">
-        <v>3</v>
-      </c>
-      <c r="F506" s="34" t="s">
-        <v>219</v>
+        <v>450</v>
+      </c>
+      <c r="F506" s="36" t="s">
+        <v>209</v>
       </c>
       <c r="G506" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I506" t="str">
         <f t="shared" si="21"/>
-        <v>Foothills_Multihab</v>
+        <v>Foothills_Riffle</v>
       </c>
       <c r="J506" t="str">
         <f t="shared" si="22"/>
@@ -18273,26 +18343,26 @@
         <v>178</v>
       </c>
       <c r="B507" s="34" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C507" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="D507" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="D507" s="35" t="s">
+        <v>15</v>
       </c>
       <c r="E507" s="35">
-        <v>4</v>
-      </c>
-      <c r="F507" s="34" t="s">
-        <v>255</v>
+        <v>650</v>
+      </c>
+      <c r="F507" s="36" t="s">
+        <v>210</v>
       </c>
       <c r="G507" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I507" t="str">
         <f t="shared" si="21"/>
-        <v>Foothills_Multihab</v>
+        <v>Foothills_Riffle</v>
       </c>
       <c r="J507" t="str">
         <f t="shared" si="22"/>
@@ -18304,26 +18374,26 @@
         <v>178</v>
       </c>
       <c r="B508" s="41" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C508" s="41" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D508" s="47" t="s">
         <v>16</v>
       </c>
       <c r="E508" s="42">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F508" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G508" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I508" t="str">
         <f t="shared" si="21"/>
-        <v>Foothills_Multihab</v>
+        <v>Foothills_Riffle</v>
       </c>
       <c r="J508" t="str">
         <f t="shared" si="22"/>
@@ -18331,30 +18401,33 @@
       </c>
     </row>
     <row r="509" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A509" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="B509" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="C509" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D509" s="8" t="s">
+      <c r="A509" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B509" s="41" t="s">
+        <v>266</v>
+      </c>
+      <c r="C509" s="41" t="s">
+        <v>283</v>
+      </c>
+      <c r="D509" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="E509" s="35">
-        <v>25</v>
-      </c>
-      <c r="F509" t="s">
-        <v>242</v>
-      </c>
-      <c r="G509" s="61" t="b">
-        <v>1</v>
+      <c r="E509" s="42">
+        <v>50</v>
+      </c>
+      <c r="F509" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="G509" s="62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H509" t="s">
+        <v>270</v>
       </c>
       <c r="I509" t="str">
         <f t="shared" si="21"/>
-        <v>Foothills_Multihab</v>
+        <v>Foothills_Riffle</v>
       </c>
       <c r="J509" t="str">
         <f t="shared" si="22"/>
@@ -18366,19 +18439,19 @@
         <v>178</v>
       </c>
       <c r="B510" s="34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C510" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D510" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="D510" s="37" t="s">
         <v>16</v>
       </c>
       <c r="E510" s="35">
-        <v>450</v>
-      </c>
-      <c r="F510" s="36" t="s">
-        <v>211</v>
+        <v>3</v>
+      </c>
+      <c r="F510" s="34" t="s">
+        <v>257</v>
       </c>
       <c r="G510" s="61" t="b">
         <v>1</v>
@@ -18397,19 +18470,19 @@
         <v>178</v>
       </c>
       <c r="B511" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C511" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="D511" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="E511" s="35">
+        <v>35</v>
+      </c>
+      <c r="F511" s="34" t="s">
         <v>268</v>
-      </c>
-      <c r="C511" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D511" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E511" s="35">
-        <v>650</v>
-      </c>
-      <c r="F511" s="36" t="s">
-        <v>212</v>
       </c>
       <c r="G511" s="61" t="b">
         <v>1</v>
@@ -18424,23 +18497,23 @@
       </c>
     </row>
     <row r="512" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A512" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="B512" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="C512" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="D512" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="E512" s="42">
-        <v>60</v>
-      </c>
-      <c r="F512" s="41" t="s">
-        <v>256</v>
+      <c r="A512" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B512" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C512" s="60" t="s">
+        <v>236</v>
+      </c>
+      <c r="D512" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="E512" s="35">
+        <v>20</v>
+      </c>
+      <c r="F512" s="34" t="s">
+        <v>237</v>
       </c>
       <c r="G512" s="61" t="b">
         <v>1</v>
@@ -18454,30 +18527,27 @@
         <v>BCG_ORWA_v1_Bugs500ct</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A513" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="B513" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="C513" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="D513" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="E513" s="42">
-        <v>50</v>
-      </c>
-      <c r="F513" s="41" t="s">
-        <v>286</v>
-      </c>
-      <c r="G513" s="62" t="b">
-        <v>0</v>
-      </c>
-      <c r="H513" t="s">
-        <v>272</v>
+    <row r="513" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B513" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C513" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="D513" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="E513" s="35">
+        <v>10</v>
+      </c>
+      <c r="F513" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="G513" s="61" t="b">
+        <v>1</v>
       </c>
       <c r="I513" t="str">
         <f t="shared" si="21"/>
@@ -18493,19 +18563,19 @@
         <v>178</v>
       </c>
       <c r="B514" s="34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C514" s="34" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D514" s="37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E514" s="35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F514" s="34" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="G514" s="61" t="b">
         <v>1</v>
@@ -18524,19 +18594,19 @@
         <v>178</v>
       </c>
       <c r="B515" s="34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C515" s="34" t="s">
-        <v>269</v>
-      </c>
-      <c r="D515" s="59" t="s">
-        <v>17</v>
+        <v>72</v>
+      </c>
+      <c r="D515" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E515" s="35">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F515" s="34" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
       <c r="G515" s="61" t="b">
         <v>1</v>
@@ -18555,19 +18625,19 @@
         <v>178</v>
       </c>
       <c r="B516" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="C516" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="D516" s="59" t="s">
-        <v>233</v>
+        <v>266</v>
+      </c>
+      <c r="C516" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D516" s="35" t="s">
+        <v>16</v>
       </c>
       <c r="E516" s="35">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F516" s="34" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="G516" s="61" t="b">
         <v>1</v>
@@ -18586,19 +18656,19 @@
         <v>178</v>
       </c>
       <c r="B517" s="34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C517" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="D517" s="59" t="s">
-        <v>233</v>
+        <v>76</v>
+      </c>
+      <c r="D517" s="8" t="s">
+        <v>231</v>
       </c>
       <c r="E517" s="35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F517" s="34" t="s">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c r="G517" s="61" t="b">
         <v>1</v>
@@ -18617,19 +18687,19 @@
         <v>178</v>
       </c>
       <c r="B518" s="34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C518" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="D518" s="37" t="s">
-        <v>15</v>
+        <v>243</v>
+      </c>
+      <c r="D518" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E518" s="35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F518" s="34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G518" s="61" t="b">
         <v>1</v>
@@ -18648,19 +18718,19 @@
         <v>178</v>
       </c>
       <c r="B519" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="C519" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D519" s="35" t="s">
-        <v>16</v>
+        <v>266</v>
+      </c>
+      <c r="C519" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D519" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E519" s="35">
-        <v>4</v>
-      </c>
-      <c r="F519" s="34" t="s">
-        <v>217</v>
+        <v>40</v>
+      </c>
+      <c r="F519" t="s">
+        <v>240</v>
       </c>
       <c r="G519" s="61" t="b">
         <v>1</v>
@@ -18675,127 +18745,119 @@
       </c>
     </row>
     <row r="520" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A520" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="B520" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="C520" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="D520" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E520" s="35">
-        <v>3</v>
-      </c>
-      <c r="F520" s="34" t="s">
-        <v>261</v>
+      <c r="A520" t="s">
+        <v>178</v>
+      </c>
+      <c r="B520" t="s">
+        <v>271</v>
+      </c>
+      <c r="C520" t="s">
+        <v>14</v>
+      </c>
+      <c r="D520" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E520" s="28">
+        <v>450</v>
+      </c>
+      <c r="F520" t="s">
+        <v>209</v>
       </c>
       <c r="G520" s="61" t="b">
         <v>1</v>
       </c>
-      <c r="I520" t="str">
-        <f t="shared" si="21"/>
-        <v>Foothills_Riffle</v>
-      </c>
-      <c r="J520" t="str">
-        <f t="shared" si="22"/>
-        <v>BCG_ORWA_v1_Bugs500ct</v>
+      <c r="I520" t="s">
+        <v>271</v>
+      </c>
+      <c r="J520" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="521" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A521" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="B521" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="C521" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="D521" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="E521" s="35">
-        <v>6</v>
-      </c>
-      <c r="F521" s="34" t="s">
-        <v>219</v>
+      <c r="A521" t="s">
+        <v>178</v>
+      </c>
+      <c r="B521" t="s">
+        <v>271</v>
+      </c>
+      <c r="C521" t="s">
+        <v>14</v>
+      </c>
+      <c r="D521" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E521" s="28">
+        <v>650</v>
+      </c>
+      <c r="F521" t="s">
+        <v>210</v>
       </c>
       <c r="G521" s="61" t="b">
         <v>1</v>
       </c>
-      <c r="I521" t="str">
-        <f t="shared" si="21"/>
-        <v>Foothills_Riffle</v>
-      </c>
-      <c r="J521" t="str">
-        <f t="shared" si="22"/>
-        <v>BCG_ORWA_v1_Bugs500ct</v>
+      <c r="I521" t="s">
+        <v>271</v>
+      </c>
+      <c r="J521" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="522" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A522" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="B522" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="C522" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="D522" s="8" t="s">
+      <c r="A522" t="s">
+        <v>178</v>
+      </c>
+      <c r="B522" t="s">
+        <v>271</v>
+      </c>
+      <c r="C522" t="s">
+        <v>241</v>
+      </c>
+      <c r="D522" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E522" s="28">
+        <v>40</v>
+      </c>
+      <c r="F522" t="s">
+        <v>254</v>
+      </c>
+      <c r="G522" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I522" t="s">
+        <v>271</v>
+      </c>
+      <c r="J522" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>178</v>
+      </c>
+      <c r="B523" t="s">
+        <v>271</v>
+      </c>
+      <c r="C523" t="s">
+        <v>283</v>
+      </c>
+      <c r="D523" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E522" s="35">
-        <v>4</v>
-      </c>
-      <c r="F522" s="34" t="s">
-        <v>255</v>
-      </c>
-      <c r="G522" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I522" t="str">
-        <f t="shared" si="21"/>
-        <v>Foothills_Riffle</v>
-      </c>
-      <c r="J522" t="str">
-        <f t="shared" si="22"/>
-        <v>BCG_ORWA_v1_Bugs500ct</v>
-      </c>
-    </row>
-    <row r="523" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A523" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="B523" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="C523" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D523" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E523" s="35">
-        <v>40</v>
+      <c r="E523" s="28">
+        <v>50</v>
       </c>
       <c r="F523" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="G523" s="61" t="b">
         <v>1</v>
       </c>
-      <c r="I523" t="str">
-        <f t="shared" si="21"/>
-        <v>Foothills_Riffle</v>
-      </c>
-      <c r="J523" t="str">
-        <f t="shared" si="22"/>
-        <v>BCG_ORWA_v1_Bugs500ct</v>
+      <c r="I523" t="s">
+        <v>271</v>
+      </c>
+      <c r="J523" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="524" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
@@ -18803,25 +18865,25 @@
         <v>178</v>
       </c>
       <c r="B524" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C524" t="s">
-        <v>14</v>
-      </c>
-      <c r="D524" s="28" t="s">
-        <v>16</v>
+        <v>234</v>
+      </c>
+      <c r="D524" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="E524" s="28">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="F524" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="G524" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I524" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J524" t="s">
         <v>178</v>
@@ -18832,25 +18894,25 @@
         <v>178</v>
       </c>
       <c r="B525" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C525" t="s">
-        <v>14</v>
+        <v>267</v>
       </c>
       <c r="D525" s="28" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E525" s="28">
-        <v>650</v>
+        <v>40</v>
       </c>
       <c r="F525" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="G525" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I525" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J525" t="s">
         <v>178</v>
@@ -18861,54 +18923,54 @@
         <v>178</v>
       </c>
       <c r="B526" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C526" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D526" s="28" t="s">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="E526" s="28">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F526" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="G526" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I526" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J526" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>178</v>
       </c>
       <c r="B527" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C527" t="s">
-        <v>285</v>
+        <v>218</v>
       </c>
       <c r="D527" s="28" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="E527" s="28">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F527" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="G527" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I527" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J527" t="s">
         <v>178</v>
@@ -18919,25 +18981,25 @@
         <v>178</v>
       </c>
       <c r="B528" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C528" t="s">
-        <v>236</v>
-      </c>
-      <c r="D528" s="63" t="s">
-        <v>96</v>
+        <v>220</v>
+      </c>
+      <c r="D528" s="28" t="s">
+        <v>17</v>
       </c>
       <c r="E528" s="28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F528" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="G528" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I528" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J528" t="s">
         <v>178</v>
@@ -18948,25 +19010,25 @@
         <v>178</v>
       </c>
       <c r="B529" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C529" t="s">
-        <v>269</v>
+        <v>72</v>
       </c>
       <c r="D529" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E529" s="28">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F529" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
       <c r="G529" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I529" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J529" t="s">
         <v>178</v>
@@ -18977,25 +19039,25 @@
         <v>178</v>
       </c>
       <c r="B530" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C530" t="s">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="D530" s="28" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E530" s="28">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F530" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="G530" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I530" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J530" t="s">
         <v>178</v>
@@ -19006,25 +19068,25 @@
         <v>178</v>
       </c>
       <c r="B531" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C531" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="D531" s="28" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E531" s="28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F531" t="s">
+        <v>217</v>
+      </c>
+      <c r="G531" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I531" t="s">
         <v>271</v>
-      </c>
-      <c r="G531" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I531" t="s">
-        <v>273</v>
       </c>
       <c r="J531" t="s">
         <v>178</v>
@@ -19035,25 +19097,25 @@
         <v>178</v>
       </c>
       <c r="B532" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C532" t="s">
-        <v>222</v>
-      </c>
-      <c r="D532" s="28" t="s">
-        <v>17</v>
+        <v>243</v>
+      </c>
+      <c r="D532" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="E532" s="28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F532" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="G532" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I532" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J532" t="s">
         <v>178</v>
@@ -19064,25 +19126,25 @@
         <v>178</v>
       </c>
       <c r="B533" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C533" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D533" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E533" s="28">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F533" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G533" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I533" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J533" t="s">
         <v>178</v>
@@ -19096,16 +19158,16 @@
         <v>273</v>
       </c>
       <c r="C534" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D534" s="28" t="s">
         <v>16</v>
       </c>
       <c r="E534" s="28">
-        <v>3</v>
+        <v>450</v>
       </c>
       <c r="F534" t="s">
-        <v>261</v>
+        <v>209</v>
       </c>
       <c r="G534" s="61" t="b">
         <v>1</v>
@@ -19125,16 +19187,16 @@
         <v>273</v>
       </c>
       <c r="C535" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D535" s="28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E535" s="28">
-        <v>3</v>
+        <v>650</v>
       </c>
       <c r="F535" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G535" s="61" t="b">
         <v>1</v>
@@ -19154,16 +19216,16 @@
         <v>273</v>
       </c>
       <c r="C536" t="s">
-        <v>245</v>
-      </c>
-      <c r="D536" s="63" t="s">
-        <v>96</v>
+        <v>241</v>
+      </c>
+      <c r="D536" s="28" t="s">
+        <v>16</v>
       </c>
       <c r="E536" s="28">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F536" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="G536" s="61" t="b">
         <v>1</v>
@@ -19183,16 +19245,16 @@
         <v>273</v>
       </c>
       <c r="C537" t="s">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="D537" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E537" s="28">
-        <v>35</v>
+        <v>3.5</v>
       </c>
       <c r="F537" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="G537" s="61" t="b">
         <v>1</v>
@@ -19209,25 +19271,25 @@
         <v>178</v>
       </c>
       <c r="B538" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C538" t="s">
-        <v>14</v>
-      </c>
-      <c r="D538" s="28" t="s">
-        <v>16</v>
+        <v>234</v>
+      </c>
+      <c r="D538" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="E538" s="28">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="F538" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="G538" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I538" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J538" t="s">
         <v>178</v>
@@ -19238,25 +19300,25 @@
         <v>178</v>
       </c>
       <c r="B539" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C539" t="s">
-        <v>14</v>
+        <v>267</v>
       </c>
       <c r="D539" s="28" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E539" s="28">
-        <v>650</v>
+        <v>35</v>
       </c>
       <c r="F539" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="G539" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I539" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J539" t="s">
         <v>178</v>
@@ -19267,25 +19329,25 @@
         <v>178</v>
       </c>
       <c r="B540" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C540" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D540" s="28" t="s">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="E540" s="28">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F540" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="G540" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I540" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J540" t="s">
         <v>178</v>
@@ -19296,25 +19358,25 @@
         <v>178</v>
       </c>
       <c r="B541" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C541" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D541" s="28" t="s">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="E541" s="28">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="F541" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="G541" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I541" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J541" t="s">
         <v>178</v>
@@ -19325,25 +19387,25 @@
         <v>178</v>
       </c>
       <c r="B542" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C542" t="s">
-        <v>236</v>
-      </c>
-      <c r="D542" s="63" t="s">
-        <v>96</v>
+        <v>220</v>
+      </c>
+      <c r="D542" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="E542" s="28">
         <v>0</v>
       </c>
       <c r="F542" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="G542" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I542" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J542" t="s">
         <v>178</v>
@@ -19354,25 +19416,25 @@
         <v>178</v>
       </c>
       <c r="B543" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C543" t="s">
-        <v>269</v>
+        <v>72</v>
       </c>
       <c r="D543" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E543" s="28">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F543" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
       <c r="G543" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I543" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J543" t="s">
         <v>178</v>
@@ -19383,25 +19445,25 @@
         <v>178</v>
       </c>
       <c r="B544" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C544" t="s">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="D544" s="28" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E544" s="28">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F544" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="G544" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I544" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J544" t="s">
         <v>178</v>
@@ -19412,25 +19474,25 @@
         <v>178</v>
       </c>
       <c r="B545" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C545" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="D545" s="28" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E545" s="28">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F545" t="s">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="G545" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I545" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J545" t="s">
         <v>178</v>
@@ -19441,25 +19503,25 @@
         <v>178</v>
       </c>
       <c r="B546" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C546" t="s">
-        <v>222</v>
-      </c>
-      <c r="D546" s="28" t="s">
-        <v>15</v>
+        <v>243</v>
+      </c>
+      <c r="D546" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="E546" s="28">
         <v>0</v>
       </c>
       <c r="F546" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="G546" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I546" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J546" t="s">
         <v>178</v>
@@ -19470,25 +19532,25 @@
         <v>178</v>
       </c>
       <c r="B547" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C547" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D547" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E547" s="28">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F547" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G547" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I547" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J547" t="s">
         <v>178</v>
@@ -19502,16 +19564,16 @@
         <v>275</v>
       </c>
       <c r="C548" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D548" s="28" t="s">
         <v>16</v>
       </c>
       <c r="E548" s="28">
-        <v>3</v>
+        <v>450</v>
       </c>
       <c r="F548" t="s">
-        <v>261</v>
+        <v>209</v>
       </c>
       <c r="G548" s="61" t="b">
         <v>1</v>
@@ -19531,16 +19593,16 @@
         <v>275</v>
       </c>
       <c r="C549" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D549" s="28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E549" s="28">
-        <v>3</v>
+        <v>650</v>
       </c>
       <c r="F549" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G549" s="61" t="b">
         <v>1</v>
@@ -19560,16 +19622,16 @@
         <v>275</v>
       </c>
       <c r="C550" t="s">
-        <v>245</v>
-      </c>
-      <c r="D550" s="63" t="s">
-        <v>96</v>
+        <v>241</v>
+      </c>
+      <c r="D550" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="E550" s="28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F550" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G550" s="61" t="b">
         <v>1</v>
@@ -19589,16 +19651,16 @@
         <v>275</v>
       </c>
       <c r="C551" t="s">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="D551" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E551" s="28">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F551" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="G551" s="61" t="b">
         <v>1</v>
@@ -19615,25 +19677,25 @@
         <v>178</v>
       </c>
       <c r="B552" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C552" t="s">
-        <v>14</v>
-      </c>
-      <c r="D552" s="28" t="s">
-        <v>16</v>
+        <v>234</v>
+      </c>
+      <c r="D552" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="E552" s="28">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="F552" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="G552" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I552" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J552" t="s">
         <v>178</v>
@@ -19644,25 +19706,25 @@
         <v>178</v>
       </c>
       <c r="B553" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C553" t="s">
-        <v>14</v>
+        <v>267</v>
       </c>
       <c r="D553" s="28" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E553" s="28">
-        <v>650</v>
+        <v>40</v>
       </c>
       <c r="F553" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="G553" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I553" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J553" t="s">
         <v>178</v>
@@ -19673,25 +19735,25 @@
         <v>178</v>
       </c>
       <c r="B554" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C554" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D554" s="28" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
       <c r="E554" s="28">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F554" t="s">
-        <v>278</v>
+        <v>237</v>
       </c>
       <c r="G554" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I554" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J554" t="s">
         <v>178</v>
@@ -19702,25 +19764,25 @@
         <v>178</v>
       </c>
       <c r="B555" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C555" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D555" s="28" t="s">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="E555" s="28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F555" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="G555" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I555" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J555" t="s">
         <v>178</v>
@@ -19731,25 +19793,25 @@
         <v>178</v>
       </c>
       <c r="B556" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C556" t="s">
-        <v>236</v>
-      </c>
-      <c r="D556" s="63" t="s">
-        <v>96</v>
+        <v>220</v>
+      </c>
+      <c r="D556" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="E556" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F556" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="G556" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I556" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J556" t="s">
         <v>178</v>
@@ -19760,25 +19822,25 @@
         <v>178</v>
       </c>
       <c r="B557" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C557" t="s">
-        <v>269</v>
+        <v>72</v>
       </c>
       <c r="D557" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E557" s="28">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F557" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
       <c r="G557" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I557" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J557" t="s">
         <v>178</v>
@@ -19789,25 +19851,25 @@
         <v>178</v>
       </c>
       <c r="B558" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C558" t="s">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="D558" s="28" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E558" s="28">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F558" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="G558" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I558" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J558" t="s">
         <v>178</v>
@@ -19818,25 +19880,25 @@
         <v>178</v>
       </c>
       <c r="B559" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C559" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="D559" s="28" t="s">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c r="E559" s="28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F559" t="s">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c r="G559" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I559" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J559" t="s">
         <v>178</v>
@@ -19847,25 +19909,25 @@
         <v>178</v>
       </c>
       <c r="B560" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C560" t="s">
-        <v>222</v>
-      </c>
-      <c r="D560" s="28" t="s">
-        <v>15</v>
+        <v>243</v>
+      </c>
+      <c r="D560" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="E560" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F560" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G560" s="61" t="b">
         <v>1</v>
       </c>
       <c r="I560" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J560" t="s">
         <v>178</v>
@@ -19876,158 +19938,1717 @@
         <v>178</v>
       </c>
       <c r="B561" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C561" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D561" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E561" s="28">
+        <v>20</v>
+      </c>
+      <c r="F561" t="s">
+        <v>240</v>
+      </c>
+      <c r="G561" s="61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I561" t="s">
+        <v>275</v>
+      </c>
+      <c r="J561" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>203</v>
+      </c>
+      <c r="B562" t="s">
+        <v>208</v>
+      </c>
+      <c r="C562" t="s">
+        <v>287</v>
+      </c>
+      <c r="D562" t="s">
+        <v>15</v>
+      </c>
+      <c r="E562">
+        <v>0</v>
+      </c>
+      <c r="F562" t="s">
+        <v>288</v>
+      </c>
+      <c r="G562" t="b">
+        <v>1</v>
+      </c>
+      <c r="I562" t="s">
+        <v>208</v>
+      </c>
+      <c r="J562" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>203</v>
+      </c>
+      <c r="B563" t="s">
+        <v>204</v>
+      </c>
+      <c r="C563" t="s">
+        <v>287</v>
+      </c>
+      <c r="D563" t="s">
+        <v>15</v>
+      </c>
+      <c r="E563">
+        <v>0</v>
+      </c>
+      <c r="F563" t="s">
+        <v>288</v>
+      </c>
+      <c r="G563" t="b">
+        <v>1</v>
+      </c>
+      <c r="I563" t="s">
+        <v>204</v>
+      </c>
+      <c r="J563" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>203</v>
+      </c>
+      <c r="B564" t="s">
+        <v>222</v>
+      </c>
+      <c r="C564" t="s">
+        <v>287</v>
+      </c>
+      <c r="D564" t="s">
+        <v>15</v>
+      </c>
+      <c r="E564">
+        <v>0</v>
+      </c>
+      <c r="F564" t="s">
+        <v>288</v>
+      </c>
+      <c r="G564" t="b">
+        <v>1</v>
+      </c>
+      <c r="I564" t="s">
+        <v>222</v>
+      </c>
+      <c r="J564" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>203</v>
+      </c>
+      <c r="B565" t="s">
+        <v>223</v>
+      </c>
+      <c r="C565" t="s">
+        <v>287</v>
+      </c>
+      <c r="D565" t="s">
+        <v>15</v>
+      </c>
+      <c r="E565">
+        <v>0</v>
+      </c>
+      <c r="F565" t="s">
+        <v>288</v>
+      </c>
+      <c r="G565" t="b">
+        <v>1</v>
+      </c>
+      <c r="I565" t="s">
+        <v>223</v>
+      </c>
+      <c r="J565" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>203</v>
+      </c>
+      <c r="B566" t="s">
+        <v>224</v>
+      </c>
+      <c r="C566" t="s">
+        <v>287</v>
+      </c>
+      <c r="D566" t="s">
+        <v>15</v>
+      </c>
+      <c r="E566">
+        <v>0</v>
+      </c>
+      <c r="F566" t="s">
+        <v>288</v>
+      </c>
+      <c r="G566" t="b">
+        <v>1</v>
+      </c>
+      <c r="I566" t="s">
+        <v>224</v>
+      </c>
+      <c r="J566" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>203</v>
+      </c>
+      <c r="B567" t="s">
+        <v>225</v>
+      </c>
+      <c r="C567" t="s">
+        <v>287</v>
+      </c>
+      <c r="D567" t="s">
+        <v>15</v>
+      </c>
+      <c r="E567">
+        <v>0</v>
+      </c>
+      <c r="F567" t="s">
+        <v>288</v>
+      </c>
+      <c r="G567" t="b">
+        <v>1</v>
+      </c>
+      <c r="I567" t="s">
+        <v>225</v>
+      </c>
+      <c r="J567" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>203</v>
+      </c>
+      <c r="B568" t="s">
+        <v>204</v>
+      </c>
+      <c r="C568" t="s">
+        <v>14</v>
+      </c>
+      <c r="D568" t="s">
+        <v>16</v>
+      </c>
+      <c r="E568">
+        <v>150</v>
+      </c>
+      <c r="F568" t="s">
+        <v>205</v>
+      </c>
+      <c r="G568" t="b">
+        <v>1</v>
+      </c>
+      <c r="I568" t="s">
+        <v>204</v>
+      </c>
+      <c r="J568" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>203</v>
+      </c>
+      <c r="B569" t="s">
+        <v>204</v>
+      </c>
+      <c r="C569" t="s">
+        <v>14</v>
+      </c>
+      <c r="D569" t="s">
+        <v>15</v>
+      </c>
+      <c r="E569">
+        <v>600</v>
+      </c>
+      <c r="F569" t="s">
+        <v>289</v>
+      </c>
+      <c r="G569" t="b">
+        <v>1</v>
+      </c>
+      <c r="I569" t="s">
+        <v>204</v>
+      </c>
+      <c r="J569" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>203</v>
+      </c>
+      <c r="B570" t="s">
+        <v>208</v>
+      </c>
+      <c r="C570" t="s">
+        <v>14</v>
+      </c>
+      <c r="D570" t="s">
+        <v>16</v>
+      </c>
+      <c r="E570">
+        <v>150</v>
+      </c>
+      <c r="F570" t="s">
+        <v>205</v>
+      </c>
+      <c r="G570" t="b">
+        <v>1</v>
+      </c>
+      <c r="I570" t="s">
+        <v>208</v>
+      </c>
+      <c r="J570" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>203</v>
+      </c>
+      <c r="B571" t="s">
+        <v>208</v>
+      </c>
+      <c r="C571" t="s">
+        <v>14</v>
+      </c>
+      <c r="D571" t="s">
+        <v>15</v>
+      </c>
+      <c r="E571">
+        <v>600</v>
+      </c>
+      <c r="F571" t="s">
+        <v>289</v>
+      </c>
+      <c r="G571" t="b">
+        <v>1</v>
+      </c>
+      <c r="I571" t="s">
+        <v>208</v>
+      </c>
+      <c r="J571" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>203</v>
+      </c>
+      <c r="B572" t="s">
+        <v>222</v>
+      </c>
+      <c r="C572" t="s">
+        <v>14</v>
+      </c>
+      <c r="D572" t="s">
+        <v>16</v>
+      </c>
+      <c r="E572">
+        <v>100</v>
+      </c>
+      <c r="F572" t="s">
+        <v>205</v>
+      </c>
+      <c r="G572" t="b">
+        <v>1</v>
+      </c>
+      <c r="I572" t="s">
+        <v>222</v>
+      </c>
+      <c r="J572" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="573" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>203</v>
+      </c>
+      <c r="B573" t="s">
+        <v>222</v>
+      </c>
+      <c r="C573" t="s">
+        <v>14</v>
+      </c>
+      <c r="D573" t="s">
+        <v>15</v>
+      </c>
+      <c r="E573">
+        <v>500</v>
+      </c>
+      <c r="F573" t="s">
+        <v>289</v>
+      </c>
+      <c r="G573" t="b">
+        <v>1</v>
+      </c>
+      <c r="I573" t="s">
+        <v>222</v>
+      </c>
+      <c r="J573" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="574" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>203</v>
+      </c>
+      <c r="B574" t="s">
+        <v>223</v>
+      </c>
+      <c r="C574" t="s">
+        <v>14</v>
+      </c>
+      <c r="D574" t="s">
+        <v>16</v>
+      </c>
+      <c r="E574">
+        <v>25</v>
+      </c>
+      <c r="F574" t="s">
+        <v>205</v>
+      </c>
+      <c r="G574" t="b">
+        <v>1</v>
+      </c>
+      <c r="I574" t="s">
+        <v>223</v>
+      </c>
+      <c r="J574" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="575" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
+        <v>203</v>
+      </c>
+      <c r="B575" t="s">
+        <v>223</v>
+      </c>
+      <c r="C575" t="s">
+        <v>14</v>
+      </c>
+      <c r="D575" t="s">
+        <v>15</v>
+      </c>
+      <c r="E575">
+        <v>350</v>
+      </c>
+      <c r="F575" t="s">
+        <v>289</v>
+      </c>
+      <c r="G575" t="b">
+        <v>1</v>
+      </c>
+      <c r="I575" t="s">
+        <v>223</v>
+      </c>
+      <c r="J575" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="576" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
+        <v>203</v>
+      </c>
+      <c r="B576" t="s">
+        <v>224</v>
+      </c>
+      <c r="C576" t="s">
+        <v>14</v>
+      </c>
+      <c r="D576" t="s">
+        <v>16</v>
+      </c>
+      <c r="E576">
+        <v>50</v>
+      </c>
+      <c r="F576" t="s">
+        <v>205</v>
+      </c>
+      <c r="G576" t="b">
+        <v>1</v>
+      </c>
+      <c r="I576" t="s">
+        <v>224</v>
+      </c>
+      <c r="J576" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="577" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>203</v>
+      </c>
+      <c r="B577" t="s">
+        <v>224</v>
+      </c>
+      <c r="C577" t="s">
+        <v>14</v>
+      </c>
+      <c r="D577" t="s">
+        <v>15</v>
+      </c>
+      <c r="E577">
+        <v>700</v>
+      </c>
+      <c r="F577" t="s">
+        <v>289</v>
+      </c>
+      <c r="G577" t="b">
+        <v>1</v>
+      </c>
+      <c r="I577" t="s">
+        <v>224</v>
+      </c>
+      <c r="J577" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="578" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>203</v>
+      </c>
+      <c r="B578" t="s">
+        <v>225</v>
+      </c>
+      <c r="C578" t="s">
+        <v>14</v>
+      </c>
+      <c r="D578" t="s">
+        <v>16</v>
+      </c>
+      <c r="E578">
+        <v>100</v>
+      </c>
+      <c r="F578" t="s">
+        <v>205</v>
+      </c>
+      <c r="G578" t="b">
+        <v>1</v>
+      </c>
+      <c r="I578" t="s">
+        <v>225</v>
+      </c>
+      <c r="J578" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="579" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>203</v>
+      </c>
+      <c r="B579" t="s">
+        <v>225</v>
+      </c>
+      <c r="C579" t="s">
+        <v>14</v>
+      </c>
+      <c r="D579" t="s">
+        <v>15</v>
+      </c>
+      <c r="E579">
+        <v>650</v>
+      </c>
+      <c r="F579" t="s">
+        <v>289</v>
+      </c>
+      <c r="G579" t="b">
+        <v>1</v>
+      </c>
+      <c r="I579" t="s">
+        <v>225</v>
+      </c>
+      <c r="J579" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="580" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
+        <v>203</v>
+      </c>
+      <c r="B580" t="s">
+        <v>204</v>
+      </c>
+      <c r="C580" t="s">
+        <v>188</v>
+      </c>
+      <c r="D580" t="s">
+        <v>16</v>
+      </c>
+      <c r="E580">
+        <v>7</v>
+      </c>
+      <c r="F580" t="s">
+        <v>206</v>
+      </c>
+      <c r="G580" t="b">
+        <v>1</v>
+      </c>
+      <c r="I580" t="s">
+        <v>204</v>
+      </c>
+      <c r="J580" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="581" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>203</v>
+      </c>
+      <c r="B581" t="s">
+        <v>208</v>
+      </c>
+      <c r="C581" t="s">
+        <v>188</v>
+      </c>
+      <c r="D581" t="s">
+        <v>16</v>
+      </c>
+      <c r="E581">
+        <v>7</v>
+      </c>
+      <c r="F581" t="s">
+        <v>206</v>
+      </c>
+      <c r="G581" t="b">
+        <v>1</v>
+      </c>
+      <c r="I581" t="s">
+        <v>208</v>
+      </c>
+      <c r="J581" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="582" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
+        <v>203</v>
+      </c>
+      <c r="B582" t="s">
+        <v>222</v>
+      </c>
+      <c r="C582" t="s">
+        <v>188</v>
+      </c>
+      <c r="D582" t="s">
+        <v>16</v>
+      </c>
+      <c r="E582">
+        <v>5</v>
+      </c>
+      <c r="F582" t="s">
+        <v>206</v>
+      </c>
+      <c r="G582" t="b">
+        <v>1</v>
+      </c>
+      <c r="I582" t="s">
+        <v>222</v>
+      </c>
+      <c r="J582" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="583" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>203</v>
+      </c>
+      <c r="B583" t="s">
+        <v>223</v>
+      </c>
+      <c r="C583" t="s">
+        <v>188</v>
+      </c>
+      <c r="D583" t="s">
+        <v>16</v>
+      </c>
+      <c r="E583">
+        <v>5</v>
+      </c>
+      <c r="F583" t="s">
+        <v>206</v>
+      </c>
+      <c r="G583" t="b">
+        <v>1</v>
+      </c>
+      <c r="I583" t="s">
+        <v>223</v>
+      </c>
+      <c r="J583" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="584" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
+        <v>203</v>
+      </c>
+      <c r="B584" t="s">
+        <v>224</v>
+      </c>
+      <c r="C584" t="s">
+        <v>188</v>
+      </c>
+      <c r="D584" t="s">
+        <v>16</v>
+      </c>
+      <c r="E584">
+        <v>6</v>
+      </c>
+      <c r="F584" t="s">
+        <v>206</v>
+      </c>
+      <c r="G584" t="b">
+        <v>1</v>
+      </c>
+      <c r="I584" t="s">
+        <v>224</v>
+      </c>
+      <c r="J584" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="585" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
+        <v>203</v>
+      </c>
+      <c r="B585" t="s">
+        <v>225</v>
+      </c>
+      <c r="C585" t="s">
+        <v>188</v>
+      </c>
+      <c r="D585" t="s">
+        <v>16</v>
+      </c>
+      <c r="E585">
+        <v>8</v>
+      </c>
+      <c r="F585" t="s">
+        <v>206</v>
+      </c>
+      <c r="G585" t="b">
+        <v>1</v>
+      </c>
+      <c r="I585" t="s">
+        <v>225</v>
+      </c>
+      <c r="J585" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="586" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
+        <v>203</v>
+      </c>
+      <c r="B586" t="s">
+        <v>208</v>
+      </c>
+      <c r="C586" t="s">
+        <v>290</v>
+      </c>
+      <c r="D586" t="s">
+        <v>15</v>
+      </c>
+      <c r="E586">
+        <v>0</v>
+      </c>
+      <c r="F586" t="s">
+        <v>291</v>
+      </c>
+      <c r="G586" t="b">
+        <v>1</v>
+      </c>
+      <c r="I586" t="s">
+        <v>208</v>
+      </c>
+      <c r="J586" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="587" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
+        <v>203</v>
+      </c>
+      <c r="B587" t="s">
+        <v>204</v>
+      </c>
+      <c r="C587" t="s">
+        <v>290</v>
+      </c>
+      <c r="D587" t="s">
+        <v>15</v>
+      </c>
+      <c r="E587">
+        <v>0</v>
+      </c>
+      <c r="F587" t="s">
+        <v>291</v>
+      </c>
+      <c r="G587" t="b">
+        <v>1</v>
+      </c>
+      <c r="I587" t="s">
+        <v>204</v>
+      </c>
+      <c r="J587" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="588" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A588" t="s">
+        <v>203</v>
+      </c>
+      <c r="B588" t="s">
+        <v>222</v>
+      </c>
+      <c r="C588" t="s">
+        <v>290</v>
+      </c>
+      <c r="D588" t="s">
+        <v>15</v>
+      </c>
+      <c r="E588">
+        <v>0</v>
+      </c>
+      <c r="F588" t="s">
+        <v>291</v>
+      </c>
+      <c r="G588" t="b">
+        <v>1</v>
+      </c>
+      <c r="I588" t="s">
+        <v>222</v>
+      </c>
+      <c r="J588" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="589" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A589" t="s">
+        <v>203</v>
+      </c>
+      <c r="B589" t="s">
+        <v>223</v>
+      </c>
+      <c r="C589" t="s">
+        <v>290</v>
+      </c>
+      <c r="D589" t="s">
+        <v>15</v>
+      </c>
+      <c r="E589">
+        <v>0</v>
+      </c>
+      <c r="F589" t="s">
+        <v>291</v>
+      </c>
+      <c r="G589" t="b">
+        <v>1</v>
+      </c>
+      <c r="I589" t="s">
+        <v>223</v>
+      </c>
+      <c r="J589" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="590" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
+        <v>203</v>
+      </c>
+      <c r="B590" t="s">
+        <v>224</v>
+      </c>
+      <c r="C590" t="s">
+        <v>290</v>
+      </c>
+      <c r="D590" t="s">
+        <v>15</v>
+      </c>
+      <c r="E590">
+        <v>0</v>
+      </c>
+      <c r="F590" t="s">
+        <v>291</v>
+      </c>
+      <c r="G590" t="b">
+        <v>1</v>
+      </c>
+      <c r="I590" t="s">
+        <v>224</v>
+      </c>
+      <c r="J590" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="591" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>203</v>
+      </c>
+      <c r="B591" t="s">
+        <v>225</v>
+      </c>
+      <c r="C591" t="s">
+        <v>290</v>
+      </c>
+      <c r="D591" t="s">
+        <v>15</v>
+      </c>
+      <c r="E591">
+        <v>0</v>
+      </c>
+      <c r="F591" t="s">
+        <v>291</v>
+      </c>
+      <c r="G591" t="b">
+        <v>1</v>
+      </c>
+      <c r="I591" t="s">
+        <v>225</v>
+      </c>
+      <c r="J591" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="592" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
+        <v>203</v>
+      </c>
+      <c r="B592" t="s">
+        <v>208</v>
+      </c>
+      <c r="C592" t="s">
+        <v>292</v>
+      </c>
+      <c r="D592" t="s">
+        <v>293</v>
+      </c>
+      <c r="E592">
+        <v>0</v>
+      </c>
+      <c r="F592" t="s">
+        <v>294</v>
+      </c>
+      <c r="G592" t="b">
+        <v>1</v>
+      </c>
+      <c r="I592" t="s">
+        <v>208</v>
+      </c>
+      <c r="J592" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="593" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A593" t="s">
+        <v>203</v>
+      </c>
+      <c r="B593" t="s">
+        <v>204</v>
+      </c>
+      <c r="C593" t="s">
+        <v>292</v>
+      </c>
+      <c r="D593" t="s">
+        <v>293</v>
+      </c>
+      <c r="E593">
+        <v>0</v>
+      </c>
+      <c r="F593" t="s">
+        <v>294</v>
+      </c>
+      <c r="G593" t="b">
+        <v>1</v>
+      </c>
+      <c r="I593" t="s">
+        <v>204</v>
+      </c>
+      <c r="J593" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="594" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A594" t="s">
+        <v>203</v>
+      </c>
+      <c r="B594" t="s">
+        <v>224</v>
+      </c>
+      <c r="C594" t="s">
+        <v>292</v>
+      </c>
+      <c r="D594" t="s">
+        <v>293</v>
+      </c>
+      <c r="E594">
+        <v>0</v>
+      </c>
+      <c r="F594" t="s">
+        <v>294</v>
+      </c>
+      <c r="G594" t="b">
+        <v>1</v>
+      </c>
+      <c r="I594" t="s">
+        <v>224</v>
+      </c>
+      <c r="J594" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="595" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
+        <v>203</v>
+      </c>
+      <c r="B595" t="s">
+        <v>225</v>
+      </c>
+      <c r="C595" t="s">
+        <v>292</v>
+      </c>
+      <c r="D595" t="s">
+        <v>293</v>
+      </c>
+      <c r="E595">
+        <v>0</v>
+      </c>
+      <c r="F595" t="s">
+        <v>294</v>
+      </c>
+      <c r="G595" t="b">
+        <v>1</v>
+      </c>
+      <c r="I595" t="s">
+        <v>225</v>
+      </c>
+      <c r="J595" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="596" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
+        <v>203</v>
+      </c>
+      <c r="B596" t="s">
+        <v>208</v>
+      </c>
+      <c r="C596" t="s">
+        <v>295</v>
+      </c>
+      <c r="D596" t="s">
+        <v>16</v>
+      </c>
+      <c r="E596">
         <v>3</v>
       </c>
-      <c r="F561" t="s">
-        <v>217</v>
-      </c>
-      <c r="G561" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I561" t="s">
-        <v>277</v>
-      </c>
-      <c r="J561" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="562" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A562" t="s">
-        <v>178</v>
-      </c>
-      <c r="B562" t="s">
-        <v>277</v>
-      </c>
-      <c r="C562" t="s">
-        <v>74</v>
-      </c>
-      <c r="D562" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E562" s="28">
+      <c r="F596" t="s">
+        <v>296</v>
+      </c>
+      <c r="G596" t="b">
+        <v>1</v>
+      </c>
+      <c r="I596" t="s">
+        <v>208</v>
+      </c>
+      <c r="J596" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="597" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>203</v>
+      </c>
+      <c r="B597" t="s">
+        <v>204</v>
+      </c>
+      <c r="C597" t="s">
+        <v>295</v>
+      </c>
+      <c r="D597" t="s">
+        <v>16</v>
+      </c>
+      <c r="E597">
+        <v>3</v>
+      </c>
+      <c r="F597" t="s">
+        <v>296</v>
+      </c>
+      <c r="G597" t="b">
+        <v>1</v>
+      </c>
+      <c r="I597" t="s">
+        <v>204</v>
+      </c>
+      <c r="J597" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="598" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
+        <v>203</v>
+      </c>
+      <c r="B598" t="s">
+        <v>222</v>
+      </c>
+      <c r="C598" t="s">
+        <v>295</v>
+      </c>
+      <c r="D598" t="s">
+        <v>16</v>
+      </c>
+      <c r="E598">
         <v>2</v>
       </c>
-      <c r="F562" t="s">
-        <v>261</v>
-      </c>
-      <c r="G562" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I562" t="s">
-        <v>277</v>
-      </c>
-      <c r="J562" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="563" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A563" t="s">
-        <v>178</v>
-      </c>
-      <c r="B563" t="s">
-        <v>277</v>
-      </c>
-      <c r="C563" t="s">
-        <v>76</v>
-      </c>
-      <c r="D563" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E563" s="28">
+      <c r="F598" t="s">
+        <v>296</v>
+      </c>
+      <c r="G598" t="b">
+        <v>1</v>
+      </c>
+      <c r="I598" t="s">
+        <v>222</v>
+      </c>
+      <c r="J598" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="599" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>203</v>
+      </c>
+      <c r="B599" t="s">
+        <v>223</v>
+      </c>
+      <c r="C599" t="s">
+        <v>295</v>
+      </c>
+      <c r="D599" t="s">
+        <v>293</v>
+      </c>
+      <c r="E599">
+        <v>0</v>
+      </c>
+      <c r="F599" t="s">
+        <v>297</v>
+      </c>
+      <c r="G599" t="b">
+        <v>1</v>
+      </c>
+      <c r="I599" t="s">
+        <v>223</v>
+      </c>
+      <c r="J599" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="600" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
+        <v>203</v>
+      </c>
+      <c r="B600" t="s">
+        <v>224</v>
+      </c>
+      <c r="C600" t="s">
+        <v>295</v>
+      </c>
+      <c r="D600" t="s">
+        <v>16</v>
+      </c>
+      <c r="E600">
+        <v>2</v>
+      </c>
+      <c r="F600" t="s">
+        <v>296</v>
+      </c>
+      <c r="G600" t="b">
+        <v>1</v>
+      </c>
+      <c r="I600" t="s">
+        <v>224</v>
+      </c>
+      <c r="J600" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="601" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>203</v>
+      </c>
+      <c r="B601" t="s">
+        <v>225</v>
+      </c>
+      <c r="C601" t="s">
+        <v>295</v>
+      </c>
+      <c r="D601" t="s">
+        <v>16</v>
+      </c>
+      <c r="E601">
         <v>3</v>
       </c>
-      <c r="F563" t="s">
-        <v>219</v>
-      </c>
-      <c r="G563" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I563" t="s">
-        <v>277</v>
-      </c>
-      <c r="J563" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="564" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A564" t="s">
-        <v>178</v>
-      </c>
-      <c r="B564" t="s">
-        <v>277</v>
-      </c>
-      <c r="C564" t="s">
-        <v>245</v>
-      </c>
-      <c r="D564" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="E564" s="28">
-        <v>0</v>
-      </c>
-      <c r="F564" t="s">
-        <v>274</v>
-      </c>
-      <c r="G564" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I564" t="s">
-        <v>277</v>
-      </c>
-      <c r="J564" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="565" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A565" t="s">
-        <v>178</v>
-      </c>
-      <c r="B565" t="s">
-        <v>277</v>
-      </c>
-      <c r="C565" t="s">
-        <v>66</v>
-      </c>
-      <c r="D565" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E565" s="28">
-        <v>20</v>
-      </c>
-      <c r="F565" t="s">
-        <v>242</v>
-      </c>
-      <c r="G565" s="61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I565" t="s">
-        <v>277</v>
-      </c>
-      <c r="J565" t="s">
-        <v>178</v>
+      <c r="F601" t="s">
+        <v>296</v>
+      </c>
+      <c r="G601" t="b">
+        <v>1</v>
+      </c>
+      <c r="I601" t="s">
+        <v>225</v>
+      </c>
+      <c r="J601" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="602" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>203</v>
+      </c>
+      <c r="B602" t="s">
+        <v>208</v>
+      </c>
+      <c r="C602" t="s">
+        <v>298</v>
+      </c>
+      <c r="D602" t="s">
+        <v>15</v>
+      </c>
+      <c r="E602">
+        <v>0</v>
+      </c>
+      <c r="F602" t="s">
+        <v>299</v>
+      </c>
+      <c r="G602" t="b">
+        <v>1</v>
+      </c>
+      <c r="I602" t="s">
+        <v>208</v>
+      </c>
+      <c r="J602" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="603" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
+        <v>203</v>
+      </c>
+      <c r="B603" t="s">
+        <v>204</v>
+      </c>
+      <c r="C603" t="s">
+        <v>298</v>
+      </c>
+      <c r="D603" t="s">
+        <v>15</v>
+      </c>
+      <c r="E603">
+        <v>0</v>
+      </c>
+      <c r="F603" t="s">
+        <v>299</v>
+      </c>
+      <c r="G603" t="b">
+        <v>1</v>
+      </c>
+      <c r="I603" t="s">
+        <v>204</v>
+      </c>
+      <c r="J603" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="604" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>203</v>
+      </c>
+      <c r="B604" t="s">
+        <v>222</v>
+      </c>
+      <c r="C604" t="s">
+        <v>298</v>
+      </c>
+      <c r="D604" t="s">
+        <v>15</v>
+      </c>
+      <c r="E604">
+        <v>2</v>
+      </c>
+      <c r="F604" t="s">
+        <v>300</v>
+      </c>
+      <c r="G604" t="b">
+        <v>1</v>
+      </c>
+      <c r="I604" t="s">
+        <v>222</v>
+      </c>
+      <c r="J604" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="605" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
+        <v>203</v>
+      </c>
+      <c r="B605" t="s">
+        <v>223</v>
+      </c>
+      <c r="C605" t="s">
+        <v>298</v>
+      </c>
+      <c r="D605" t="s">
+        <v>15</v>
+      </c>
+      <c r="E605">
+        <v>3</v>
+      </c>
+      <c r="F605" t="s">
+        <v>300</v>
+      </c>
+      <c r="G605" t="b">
+        <v>1</v>
+      </c>
+      <c r="I605" t="s">
+        <v>223</v>
+      </c>
+      <c r="J605" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="606" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>203</v>
+      </c>
+      <c r="B606" t="s">
+        <v>224</v>
+      </c>
+      <c r="C606" t="s">
+        <v>298</v>
+      </c>
+      <c r="D606" t="s">
+        <v>15</v>
+      </c>
+      <c r="E606">
+        <v>0</v>
+      </c>
+      <c r="F606" t="s">
+        <v>299</v>
+      </c>
+      <c r="G606" t="b">
+        <v>1</v>
+      </c>
+      <c r="I606" t="s">
+        <v>224</v>
+      </c>
+      <c r="J606" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="607" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
+        <v>203</v>
+      </c>
+      <c r="B607" t="s">
+        <v>225</v>
+      </c>
+      <c r="C607" t="s">
+        <v>298</v>
+      </c>
+      <c r="D607" t="s">
+        <v>15</v>
+      </c>
+      <c r="E607">
+        <v>0</v>
+      </c>
+      <c r="F607" t="s">
+        <v>299</v>
+      </c>
+      <c r="G607" t="b">
+        <v>1</v>
+      </c>
+      <c r="I607" t="s">
+        <v>225</v>
+      </c>
+      <c r="J607" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="608" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
+        <v>203</v>
+      </c>
+      <c r="B608" t="s">
+        <v>208</v>
+      </c>
+      <c r="C608" t="s">
+        <v>301</v>
+      </c>
+      <c r="D608" t="s">
+        <v>16</v>
+      </c>
+      <c r="E608">
+        <v>70</v>
+      </c>
+      <c r="F608" t="s">
+        <v>302</v>
+      </c>
+      <c r="G608" t="b">
+        <v>1</v>
+      </c>
+      <c r="I608" t="s">
+        <v>208</v>
+      </c>
+      <c r="J608" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="609" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
+        <v>203</v>
+      </c>
+      <c r="B609" t="s">
+        <v>204</v>
+      </c>
+      <c r="C609" t="s">
+        <v>301</v>
+      </c>
+      <c r="D609" t="s">
+        <v>16</v>
+      </c>
+      <c r="E609">
+        <v>70</v>
+      </c>
+      <c r="F609" t="s">
+        <v>302</v>
+      </c>
+      <c r="G609" t="b">
+        <v>1</v>
+      </c>
+      <c r="I609" t="s">
+        <v>204</v>
+      </c>
+      <c r="J609" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="610" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
+        <v>203</v>
+      </c>
+      <c r="B610" t="s">
+        <v>222</v>
+      </c>
+      <c r="C610" t="s">
+        <v>301</v>
+      </c>
+      <c r="D610" t="s">
+        <v>16</v>
+      </c>
+      <c r="E610">
+        <v>10</v>
+      </c>
+      <c r="F610" t="s">
+        <v>302</v>
+      </c>
+      <c r="G610" t="b">
+        <v>1</v>
+      </c>
+      <c r="I610" t="s">
+        <v>222</v>
+      </c>
+      <c r="J610" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="611" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>203</v>
+      </c>
+      <c r="B611" t="s">
+        <v>223</v>
+      </c>
+      <c r="C611" t="s">
+        <v>301</v>
+      </c>
+      <c r="D611" t="s">
+        <v>293</v>
+      </c>
+      <c r="E611">
+        <v>0</v>
+      </c>
+      <c r="F611" t="s">
+        <v>303</v>
+      </c>
+      <c r="G611" t="b">
+        <v>1</v>
+      </c>
+      <c r="I611" t="s">
+        <v>223</v>
+      </c>
+      <c r="J611" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="612" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>203</v>
+      </c>
+      <c r="B612" t="s">
+        <v>224</v>
+      </c>
+      <c r="C612" t="s">
+        <v>301</v>
+      </c>
+      <c r="D612" t="s">
+        <v>16</v>
+      </c>
+      <c r="E612">
+        <v>40</v>
+      </c>
+      <c r="F612" t="s">
+        <v>302</v>
+      </c>
+      <c r="G612" t="b">
+        <v>1</v>
+      </c>
+      <c r="I612" t="s">
+        <v>224</v>
+      </c>
+      <c r="J612" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="613" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
+        <v>203</v>
+      </c>
+      <c r="B613" t="s">
+        <v>225</v>
+      </c>
+      <c r="C613" t="s">
+        <v>301</v>
+      </c>
+      <c r="D613" t="s">
+        <v>16</v>
+      </c>
+      <c r="E613">
+        <v>40</v>
+      </c>
+      <c r="F613" t="s">
+        <v>302</v>
+      </c>
+      <c r="G613" t="b">
+        <v>1</v>
+      </c>
+      <c r="I613" t="s">
+        <v>225</v>
+      </c>
+      <c r="J613" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="614" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A614" t="s">
+        <v>203</v>
+      </c>
+      <c r="B614" t="s">
+        <v>208</v>
+      </c>
+      <c r="C614" t="s">
+        <v>304</v>
+      </c>
+      <c r="D614" t="s">
+        <v>16</v>
+      </c>
+      <c r="E614">
+        <v>4</v>
+      </c>
+      <c r="F614" t="s">
+        <v>305</v>
+      </c>
+      <c r="G614" t="b">
+        <v>1</v>
+      </c>
+      <c r="I614" t="s">
+        <v>208</v>
+      </c>
+      <c r="J614" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="615" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A615" t="s">
+        <v>203</v>
+      </c>
+      <c r="B615" t="s">
+        <v>204</v>
+      </c>
+      <c r="C615" t="s">
+        <v>304</v>
+      </c>
+      <c r="D615" t="s">
+        <v>16</v>
+      </c>
+      <c r="E615">
+        <v>4</v>
+      </c>
+      <c r="F615" t="s">
+        <v>305</v>
+      </c>
+      <c r="G615" t="b">
+        <v>1</v>
+      </c>
+      <c r="I615" t="s">
+        <v>204</v>
+      </c>
+      <c r="J615" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="616" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A616" t="s">
+        <v>203</v>
+      </c>
+      <c r="B616" t="s">
+        <v>222</v>
+      </c>
+      <c r="C616" t="s">
+        <v>304</v>
+      </c>
+      <c r="D616" t="s">
+        <v>16</v>
+      </c>
+      <c r="E616">
+        <v>5</v>
+      </c>
+      <c r="F616" t="s">
+        <v>305</v>
+      </c>
+      <c r="G616" t="b">
+        <v>1</v>
+      </c>
+      <c r="I616" t="s">
+        <v>222</v>
+      </c>
+      <c r="J616" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="617" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A617" t="s">
+        <v>203</v>
+      </c>
+      <c r="B617" t="s">
+        <v>223</v>
+      </c>
+      <c r="C617" t="s">
+        <v>304</v>
+      </c>
+      <c r="D617" t="s">
+        <v>16</v>
+      </c>
+      <c r="E617">
+        <v>2</v>
+      </c>
+      <c r="F617" t="s">
+        <v>305</v>
+      </c>
+      <c r="G617" t="b">
+        <v>1</v>
+      </c>
+      <c r="I617" t="s">
+        <v>223</v>
+      </c>
+      <c r="J617" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="618" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A618" t="s">
+        <v>203</v>
+      </c>
+      <c r="B618" t="s">
+        <v>224</v>
+      </c>
+      <c r="C618" t="s">
+        <v>304</v>
+      </c>
+      <c r="D618" t="s">
+        <v>16</v>
+      </c>
+      <c r="E618">
+        <v>5</v>
+      </c>
+      <c r="F618" t="s">
+        <v>305</v>
+      </c>
+      <c r="G618" t="b">
+        <v>1</v>
+      </c>
+      <c r="I618" t="s">
+        <v>224</v>
+      </c>
+      <c r="J618" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="619" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A619" t="s">
+        <v>203</v>
+      </c>
+      <c r="B619" t="s">
+        <v>225</v>
+      </c>
+      <c r="C619" t="s">
+        <v>304</v>
+      </c>
+      <c r="D619" t="s">
+        <v>16</v>
+      </c>
+      <c r="E619">
+        <v>5</v>
+      </c>
+      <c r="F619" t="s">
+        <v>305</v>
+      </c>
+      <c r="G619" t="b">
+        <v>1</v>
+      </c>
+      <c r="I619" t="s">
+        <v>225</v>
+      </c>
+      <c r="J619" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J565" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <autoFilter ref="A1:J561" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="BCG_ORWA_v1_Bugs500ct"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="pi_dom02_BCG_att456"/>
-        <filter val="pi_NonInsTrombJuga_BCG_att456"/>
-        <filter val="pt_NonIns_BCG_att456"/>
+        <filter val="LBR_Fish_BCG_v1"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -20046,7 +21667,7 @@
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G334:G367">
+  <conditionalFormatting sqref="G334:G363">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>FALSE</formula>
     </cfRule>

--- a/inst/extdata/MetricFlags.xlsx
+++ b/inst/extdata/MetricFlags.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BCGcalc\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99D74C3-B0E2-4E09-9DBC-A4A1F4DC4B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236DDBFF-FBA8-4DD1-B72A-BC42F69B242A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Flags" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$561</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flags!$A$1:$J$619</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="305">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -1048,9 +1048,6 @@
   </si>
   <si>
     <t>pi_Cott</t>
-  </si>
-  <si>
-    <t>=</t>
   </si>
   <si>
     <t>sculpins absent</t>
@@ -1352,7 +1349,7 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
@@ -1503,6 +1500,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Bad" xfId="6" builtinId="27"/>
@@ -19962,7 +19960,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>203</v>
       </c>
@@ -19991,7 +19989,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>203</v>
       </c>
@@ -20020,7 +20018,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>203</v>
       </c>
@@ -20049,7 +20047,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>203</v>
       </c>
@@ -20078,7 +20076,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>203</v>
       </c>
@@ -20107,7 +20105,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>203</v>
       </c>
@@ -20136,7 +20134,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>203</v>
       </c>
@@ -20165,7 +20163,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>203</v>
       </c>
@@ -20194,7 +20192,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>203</v>
       </c>
@@ -20223,7 +20221,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>203</v>
       </c>
@@ -20252,7 +20250,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>203</v>
       </c>
@@ -20281,7 +20279,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="573" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>203</v>
       </c>
@@ -20310,7 +20308,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="574" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>203</v>
       </c>
@@ -20339,7 +20337,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="575" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>203</v>
       </c>
@@ -20368,7 +20366,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="576" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>203</v>
       </c>
@@ -20397,7 +20395,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="577" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>203</v>
       </c>
@@ -20426,7 +20424,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="578" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>203</v>
       </c>
@@ -20455,7 +20453,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="579" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>203</v>
       </c>
@@ -20484,7 +20482,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="580" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>203</v>
       </c>
@@ -20513,7 +20511,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="581" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>203</v>
       </c>
@@ -20542,7 +20540,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="582" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>203</v>
       </c>
@@ -20571,7 +20569,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="583" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>203</v>
       </c>
@@ -20600,7 +20598,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="584" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>203</v>
       </c>
@@ -20629,7 +20627,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="585" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>203</v>
       </c>
@@ -20658,7 +20656,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="586" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>203</v>
       </c>
@@ -20687,7 +20685,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="587" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>203</v>
       </c>
@@ -20716,7 +20714,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="588" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>203</v>
       </c>
@@ -20745,7 +20743,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="589" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>203</v>
       </c>
@@ -20774,7 +20772,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="590" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>203</v>
       </c>
@@ -20803,7 +20801,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="591" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>203</v>
       </c>
@@ -20842,14 +20840,14 @@
       <c r="C592" t="s">
         <v>292</v>
       </c>
-      <c r="D592" t="s">
+      <c r="D592" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="E592">
+        <v>0</v>
+      </c>
+      <c r="F592" t="s">
         <v>293</v>
-      </c>
-      <c r="E592">
-        <v>0</v>
-      </c>
-      <c r="F592" t="s">
-        <v>294</v>
       </c>
       <c r="G592" t="b">
         <v>1</v>
@@ -20871,14 +20869,14 @@
       <c r="C593" t="s">
         <v>292</v>
       </c>
-      <c r="D593" t="s">
+      <c r="D593" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="E593">
+        <v>0</v>
+      </c>
+      <c r="F593" t="s">
         <v>293</v>
-      </c>
-      <c r="E593">
-        <v>0</v>
-      </c>
-      <c r="F593" t="s">
-        <v>294</v>
       </c>
       <c r="G593" t="b">
         <v>1</v>
@@ -20900,14 +20898,14 @@
       <c r="C594" t="s">
         <v>292</v>
       </c>
-      <c r="D594" t="s">
+      <c r="D594" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="E594">
+        <v>0</v>
+      </c>
+      <c r="F594" t="s">
         <v>293</v>
-      </c>
-      <c r="E594">
-        <v>0</v>
-      </c>
-      <c r="F594" t="s">
-        <v>294</v>
       </c>
       <c r="G594" t="b">
         <v>1</v>
@@ -20929,14 +20927,14 @@
       <c r="C595" t="s">
         <v>292</v>
       </c>
-      <c r="D595" t="s">
+      <c r="D595" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="E595">
+        <v>0</v>
+      </c>
+      <c r="F595" t="s">
         <v>293</v>
-      </c>
-      <c r="E595">
-        <v>0</v>
-      </c>
-      <c r="F595" t="s">
-        <v>294</v>
       </c>
       <c r="G595" t="b">
         <v>1</v>
@@ -20948,7 +20946,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="596" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>203</v>
       </c>
@@ -20956,7 +20954,7 @@
         <v>208</v>
       </c>
       <c r="C596" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D596" t="s">
         <v>16</v>
@@ -20965,7 +20963,7 @@
         <v>3</v>
       </c>
       <c r="F596" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G596" t="b">
         <v>1</v>
@@ -20977,7 +20975,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="597" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>203</v>
       </c>
@@ -20985,7 +20983,7 @@
         <v>204</v>
       </c>
       <c r="C597" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D597" t="s">
         <v>16</v>
@@ -20994,7 +20992,7 @@
         <v>3</v>
       </c>
       <c r="F597" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G597" t="b">
         <v>1</v>
@@ -21006,7 +21004,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="598" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>203</v>
       </c>
@@ -21014,7 +21012,7 @@
         <v>222</v>
       </c>
       <c r="C598" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D598" t="s">
         <v>16</v>
@@ -21023,7 +21021,7 @@
         <v>2</v>
       </c>
       <c r="F598" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G598" t="b">
         <v>1</v>
@@ -21043,16 +21041,16 @@
         <v>223</v>
       </c>
       <c r="C599" t="s">
-        <v>295</v>
-      </c>
-      <c r="D599" t="s">
-        <v>293</v>
+        <v>294</v>
+      </c>
+      <c r="D599" s="64" t="s">
+        <v>96</v>
       </c>
       <c r="E599">
         <v>0</v>
       </c>
       <c r="F599" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G599" t="b">
         <v>1</v>
@@ -21064,7 +21062,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="600" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>203</v>
       </c>
@@ -21072,7 +21070,7 @@
         <v>224</v>
       </c>
       <c r="C600" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D600" t="s">
         <v>16</v>
@@ -21081,7 +21079,7 @@
         <v>2</v>
       </c>
       <c r="F600" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G600" t="b">
         <v>1</v>
@@ -21093,7 +21091,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="601" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>203</v>
       </c>
@@ -21101,7 +21099,7 @@
         <v>225</v>
       </c>
       <c r="C601" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D601" t="s">
         <v>16</v>
@@ -21110,7 +21108,7 @@
         <v>3</v>
       </c>
       <c r="F601" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G601" t="b">
         <v>1</v>
@@ -21122,7 +21120,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="602" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>203</v>
       </c>
@@ -21130,7 +21128,7 @@
         <v>208</v>
       </c>
       <c r="C602" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D602" t="s">
         <v>15</v>
@@ -21139,7 +21137,7 @@
         <v>0</v>
       </c>
       <c r="F602" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G602" t="b">
         <v>1</v>
@@ -21151,7 +21149,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="603" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>203</v>
       </c>
@@ -21159,7 +21157,7 @@
         <v>204</v>
       </c>
       <c r="C603" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D603" t="s">
         <v>15</v>
@@ -21168,7 +21166,7 @@
         <v>0</v>
       </c>
       <c r="F603" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G603" t="b">
         <v>1</v>
@@ -21180,7 +21178,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="604" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>203</v>
       </c>
@@ -21188,7 +21186,7 @@
         <v>222</v>
       </c>
       <c r="C604" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D604" t="s">
         <v>15</v>
@@ -21197,7 +21195,7 @@
         <v>2</v>
       </c>
       <c r="F604" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G604" t="b">
         <v>1</v>
@@ -21209,7 +21207,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="605" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>203</v>
       </c>
@@ -21217,7 +21215,7 @@
         <v>223</v>
       </c>
       <c r="C605" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D605" t="s">
         <v>15</v>
@@ -21226,7 +21224,7 @@
         <v>3</v>
       </c>
       <c r="F605" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G605" t="b">
         <v>1</v>
@@ -21238,7 +21236,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="606" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>203</v>
       </c>
@@ -21246,7 +21244,7 @@
         <v>224</v>
       </c>
       <c r="C606" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D606" t="s">
         <v>15</v>
@@ -21255,7 +21253,7 @@
         <v>0</v>
       </c>
       <c r="F606" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G606" t="b">
         <v>1</v>
@@ -21267,7 +21265,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="607" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>203</v>
       </c>
@@ -21275,7 +21273,7 @@
         <v>225</v>
       </c>
       <c r="C607" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D607" t="s">
         <v>15</v>
@@ -21284,7 +21282,7 @@
         <v>0</v>
       </c>
       <c r="F607" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G607" t="b">
         <v>1</v>
@@ -21296,7 +21294,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="608" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>203</v>
       </c>
@@ -21304,7 +21302,7 @@
         <v>208</v>
       </c>
       <c r="C608" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D608" t="s">
         <v>16</v>
@@ -21313,7 +21311,7 @@
         <v>70</v>
       </c>
       <c r="F608" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G608" t="b">
         <v>1</v>
@@ -21325,7 +21323,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="609" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>203</v>
       </c>
@@ -21333,7 +21331,7 @@
         <v>204</v>
       </c>
       <c r="C609" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D609" t="s">
         <v>16</v>
@@ -21342,7 +21340,7 @@
         <v>70</v>
       </c>
       <c r="F609" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G609" t="b">
         <v>1</v>
@@ -21354,7 +21352,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="610" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>203</v>
       </c>
@@ -21362,7 +21360,7 @@
         <v>222</v>
       </c>
       <c r="C610" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D610" t="s">
         <v>16</v>
@@ -21371,7 +21369,7 @@
         <v>10</v>
       </c>
       <c r="F610" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G610" t="b">
         <v>1</v>
@@ -21391,16 +21389,16 @@
         <v>223</v>
       </c>
       <c r="C611" t="s">
-        <v>301</v>
-      </c>
-      <c r="D611" t="s">
-        <v>293</v>
+        <v>300</v>
+      </c>
+      <c r="D611" s="64" t="s">
+        <v>96</v>
       </c>
       <c r="E611">
         <v>0</v>
       </c>
       <c r="F611" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G611" t="b">
         <v>1</v>
@@ -21412,7 +21410,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="612" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>203</v>
       </c>
@@ -21420,7 +21418,7 @@
         <v>224</v>
       </c>
       <c r="C612" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D612" t="s">
         <v>16</v>
@@ -21429,7 +21427,7 @@
         <v>40</v>
       </c>
       <c r="F612" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G612" t="b">
         <v>1</v>
@@ -21441,7 +21439,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="613" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>203</v>
       </c>
@@ -21449,7 +21447,7 @@
         <v>225</v>
       </c>
       <c r="C613" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D613" t="s">
         <v>16</v>
@@ -21458,7 +21456,7 @@
         <v>40</v>
       </c>
       <c r="F613" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G613" t="b">
         <v>1</v>
@@ -21470,7 +21468,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="614" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>203</v>
       </c>
@@ -21478,7 +21476,7 @@
         <v>208</v>
       </c>
       <c r="C614" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D614" t="s">
         <v>16</v>
@@ -21487,7 +21485,7 @@
         <v>4</v>
       </c>
       <c r="F614" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G614" t="b">
         <v>1</v>
@@ -21499,7 +21497,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="615" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>203</v>
       </c>
@@ -21507,7 +21505,7 @@
         <v>204</v>
       </c>
       <c r="C615" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D615" t="s">
         <v>16</v>
@@ -21516,7 +21514,7 @@
         <v>4</v>
       </c>
       <c r="F615" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G615" t="b">
         <v>1</v>
@@ -21528,7 +21526,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="616" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>203</v>
       </c>
@@ -21536,7 +21534,7 @@
         <v>222</v>
       </c>
       <c r="C616" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D616" t="s">
         <v>16</v>
@@ -21545,7 +21543,7 @@
         <v>5</v>
       </c>
       <c r="F616" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G616" t="b">
         <v>1</v>
@@ -21557,7 +21555,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="617" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>203</v>
       </c>
@@ -21565,7 +21563,7 @@
         <v>223</v>
       </c>
       <c r="C617" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D617" t="s">
         <v>16</v>
@@ -21574,7 +21572,7 @@
         <v>2</v>
       </c>
       <c r="F617" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G617" t="b">
         <v>1</v>
@@ -21586,7 +21584,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="618" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>203</v>
       </c>
@@ -21594,7 +21592,7 @@
         <v>224</v>
       </c>
       <c r="C618" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D618" t="s">
         <v>16</v>
@@ -21603,7 +21601,7 @@
         <v>5</v>
       </c>
       <c r="F618" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G618" t="b">
         <v>1</v>
@@ -21615,7 +21613,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="619" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>203</v>
       </c>
@@ -21623,7 +21621,7 @@
         <v>225</v>
       </c>
       <c r="C619" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D619" t="s">
         <v>16</v>
@@ -21632,7 +21630,7 @@
         <v>5</v>
       </c>
       <c r="F619" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G619" t="b">
         <v>1</v>
@@ -21645,10 +21643,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J561" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <autoFilter ref="A1:J619" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="LBR_Fish_BCG_v1"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="="/>
       </filters>
     </filterColumn>
   </autoFilter>
